--- a/Översikt HÖRBY.xlsx
+++ b/Översikt HÖRBY.xlsx
@@ -601,7 +601,7 @@
         <v>44964</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
         <v>44967</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         <v>44727</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -949,7 +949,7 @@
         <v>45786</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1061,7 +1061,7 @@
         <v>46160</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
         <v>45238</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 31351-2022</t>
+          <t>A 16520-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1285,14 +1285,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>44774</v>
+        <v>46112</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1305,19 +1305,19 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>13.2</v>
+        <v>2.3</v>
       </c>
       <c r="J8" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -1332,18 +1332,240 @@
         <v>3</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
       </c>
       <c r="T8" t="n">
+        <v>6</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>Slåttergubbe
+Sydlig sotticka
+Älg
+Fiskgjuse
+Större brunfladdermus</t>
+        </is>
+      </c>
+      <c r="W8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 16520-2026 artfynd.xlsx", "A 16520-2026")</f>
+        <v/>
+      </c>
+      <c r="X8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 16520-2026 karta.png", "A 16520-2026")</f>
+        <v/>
+      </c>
+      <c r="Y8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 16520-2026 georefererad karta.tif", "A 16520-2026")</f>
+        <v/>
+      </c>
+      <c r="AA8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 16520-2026 FSC-klagomål.docx", "A 16520-2026")</f>
+        <v/>
+      </c>
+      <c r="AB8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 16520-2026 FSC-klagomål mail.docx", "A 16520-2026")</f>
+        <v/>
+      </c>
+      <c r="AC8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 16520-2026 tillsynsbegäran.docx", "A 16520-2026")</f>
+        <v/>
+      </c>
+      <c r="AD8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 16520-2026 tillsynsbegäran mail.docx", "A 16520-2026")</f>
+        <v/>
+      </c>
+      <c r="AE8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/fåglar/A 16520-2026 prioriterade fågelarter.docx", "A 16520-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 39855-2022</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>44819</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>HÖRBY</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J9" t="n">
+        <v>4</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1</v>
+      </c>
+      <c r="S9" t="n">
         <v>5</v>
       </c>
-      <c r="U8" t="n">
+      <c r="T9" t="n">
+        <v>5</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Skogsknipprot
+Blåsippa
+Fläcknycklar
+Grönvit nattviol</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 39855-2022 artfynd.xlsx", "A 39855-2022")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 39855-2022 karta.png", "A 39855-2022")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 39855-2022 georefererad karta.tif", "A 39855-2022")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 39855-2022 FSC-klagomål.docx", "A 39855-2022")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 39855-2022 FSC-klagomål mail.docx", "A 39855-2022")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 39855-2022 tillsynsbegäran.docx", "A 39855-2022")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 39855-2022 tillsynsbegäran mail.docx", "A 39855-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 31351-2022</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>44774</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>HÖRBY</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="J10" t="n">
+        <v>5</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
         <v>3</v>
       </c>
-      <c r="V8" s="2" t="inlineStr">
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>3</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="n">
+        <v>5</v>
+      </c>
+      <c r="U10" t="n">
+        <v>3</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Duvhök
 Grönsångare
@@ -1352,111 +1574,111 @@
 Kungsfågel</t>
         </is>
       </c>
-      <c r="W8">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 31351-2022 artfynd.xlsx", "A 31351-2022")</f>
         <v/>
       </c>
-      <c r="X8">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 31351-2022 karta.png", "A 31351-2022")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 31351-2022 georefererad karta.tif", "A 31351-2022")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 31351-2022 FSC-klagomål.docx", "A 31351-2022")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 31351-2022 FSC-klagomål mail.docx", "A 31351-2022")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 31351-2022 tillsynsbegäran.docx", "A 31351-2022")</f>
         <v/>
       </c>
-      <c r="AD8">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 31351-2022 tillsynsbegäran mail.docx", "A 31351-2022")</f>
         <v/>
       </c>
-      <c r="AE8">
+      <c r="AE10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/fåglar/A 31351-2022 prioriterade fågelarter.docx", "A 31351-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
         <is>
           <t>A 20194-2024</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D9" s="1" t="n">
+      <c r="D11" s="1" t="n">
         <v>45434</v>
       </c>
-      <c r="E9" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>HÖRBY</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
+      <c r="E11" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>HÖRBY</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
         <v>4.4</v>
       </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
         <v>2</v>
       </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
         <v>2</v>
       </c>
-      <c r="O9" t="n">
+      <c r="O11" t="n">
         <v>1</v>
       </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
         <v>3</v>
       </c>
-      <c r="R9" t="n">
+      <c r="R11" t="n">
         <v>3</v>
       </c>
-      <c r="S9" t="n">
+      <c r="S11" t="n">
         <v>5</v>
       </c>
-      <c r="T9" t="n">
+      <c r="T11" t="n">
         <v>5</v>
       </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Naverlönn
 Ask
@@ -1465,261 +1687,39 @@
 Stor häxört</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 20194-2024 artfynd.xlsx", "A 20194-2024")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 20194-2024 karta.png", "A 20194-2024")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 20194-2024 georefererad karta.tif", "A 20194-2024")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 20194-2024 FSC-klagomål.docx", "A 20194-2024")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 20194-2024 FSC-klagomål mail.docx", "A 20194-2024")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 20194-2024 tillsynsbegäran.docx", "A 20194-2024")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 20194-2024 tillsynsbegäran mail.docx", "A 20194-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 16520-2026</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>46112</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>HÖRBY</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="J10" t="n">
-        <v>2</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>2</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>3</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1</v>
-      </c>
-      <c r="S10" t="n">
-        <v>5</v>
-      </c>
-      <c r="T10" t="n">
-        <v>6</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Slåttergubbe
-Sydlig sotticka
-Älg
-Fiskgjuse
-Större brunfladdermus</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 16520-2026 artfynd.xlsx", "A 16520-2026")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 16520-2026 karta.png", "A 16520-2026")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 16520-2026 georefererad karta.tif", "A 16520-2026")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 16520-2026 FSC-klagomål.docx", "A 16520-2026")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 16520-2026 FSC-klagomål mail.docx", "A 16520-2026")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 16520-2026 tillsynsbegäran.docx", "A 16520-2026")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 16520-2026 tillsynsbegäran mail.docx", "A 16520-2026")</f>
-        <v/>
-      </c>
-      <c r="AE10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/fåglar/A 16520-2026 prioriterade fågelarter.docx", "A 16520-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 39855-2022</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>44819</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>HÖRBY</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J11" t="n">
-        <v>4</v>
-      </c>
-      <c r="K11" t="n">
-        <v>1</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>1</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1</v>
-      </c>
-      <c r="S11" t="n">
-        <v>5</v>
-      </c>
-      <c r="T11" t="n">
-        <v>5</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Skogsknipprot
-Blåsippa
-Fläcknycklar
-Grönvit nattviol</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 39855-2022 artfynd.xlsx", "A 39855-2022")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 39855-2022 karta.png", "A 39855-2022")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 39855-2022 georefererad karta.tif", "A 39855-2022")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 39855-2022 FSC-klagomål.docx", "A 39855-2022")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 39855-2022 FSC-klagomål mail.docx", "A 39855-2022")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 39855-2022 tillsynsbegäran.docx", "A 39855-2022")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 39855-2022 tillsynsbegäran mail.docx", "A 39855-2022")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 21774-2026</t>
+          <t>A 5619-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1733,10 +1733,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46150</v>
+        <v>45334</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1749,45 +1749,153 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>1.2</v>
+        <v>4.6</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>2</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
         <v>3</v>
       </c>
-      <c r="M12" t="n">
-        <v>1</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>4</v>
-      </c>
       <c r="R12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S12" t="n">
         <v>4</v>
       </c>
       <c r="T12" t="n">
+        <v>7</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Skogsalm
+Gullpudra
+Trubbfjädermossa</t>
+        </is>
+      </c>
+      <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 5619-2024 artfynd.xlsx", "A 5619-2024")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 5619-2024 karta.png", "A 5619-2024")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 5619-2024 georefererad karta.tif", "A 5619-2024")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 5619-2024 FSC-klagomål.docx", "A 5619-2024")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 5619-2024 FSC-klagomål mail.docx", "A 5619-2024")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 5619-2024 tillsynsbegäran.docx", "A 5619-2024")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 5619-2024 tillsynsbegäran mail.docx", "A 5619-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A 21774-2026</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>46150</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>HÖRBY</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>3</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>4</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1</v>
+      </c>
+      <c r="S13" t="n">
+        <v>4</v>
+      </c>
+      <c r="T13" t="n">
         <v>6</v>
       </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>Violettkantad guldvinge
 Granspira
@@ -1795,107 +1903,107 @@
 Svinrot</t>
         </is>
       </c>
-      <c r="W12">
+      <c r="W13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 21774-2026 artfynd.xlsx", "A 21774-2026")</f>
         <v/>
       </c>
-      <c r="X12">
+      <c r="X13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 21774-2026 karta.png", "A 21774-2026")</f>
         <v/>
       </c>
-      <c r="Y12">
+      <c r="Y13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 21774-2026 georefererad karta.tif", "A 21774-2026")</f>
         <v/>
       </c>
-      <c r="AA12">
+      <c r="AA13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 21774-2026 FSC-klagomål.docx", "A 21774-2026")</f>
         <v/>
       </c>
-      <c r="AB12">
+      <c r="AB13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 21774-2026 FSC-klagomål mail.docx", "A 21774-2026")</f>
         <v/>
       </c>
-      <c r="AC12">
+      <c r="AC13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 21774-2026 tillsynsbegäran.docx", "A 21774-2026")</f>
         <v/>
       </c>
-      <c r="AD12">
+      <c r="AD13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 21774-2026 tillsynsbegäran mail.docx", "A 21774-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
         <is>
           <t>A 38084-2024</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D13" s="1" t="n">
+      <c r="D14" s="1" t="n">
         <v>45545</v>
       </c>
-      <c r="E13" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>HÖRBY</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
+      <c r="E14" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>HÖRBY</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
         <v>0.5</v>
       </c>
-      <c r="J13" t="n">
+      <c r="J14" t="n">
         <v>1</v>
       </c>
-      <c r="K13" t="n">
+      <c r="K14" t="n">
         <v>2</v>
       </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
         <v>4</v>
       </c>
-      <c r="T13" t="n">
+      <c r="T14" t="n">
         <v>4</v>
       </c>
-      <c r="U13" t="n">
+      <c r="U14" t="n">
         <v>4</v>
       </c>
-      <c r="V13" s="2" t="inlineStr">
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>Myskmadra
 Skogsbräsma
@@ -1903,147 +2011,39 @@
 Grönsiska</t>
         </is>
       </c>
-      <c r="W13">
+      <c r="W14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 38084-2024 artfynd.xlsx", "A 38084-2024")</f>
         <v/>
       </c>
-      <c r="X13">
+      <c r="X14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 38084-2024 karta.png", "A 38084-2024")</f>
         <v/>
       </c>
-      <c r="Y13">
+      <c r="Y14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 38084-2024 georefererad karta.tif", "A 38084-2024")</f>
         <v/>
       </c>
-      <c r="AA13">
+      <c r="AA14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 38084-2024 FSC-klagomål.docx", "A 38084-2024")</f>
         <v/>
       </c>
-      <c r="AB13">
+      <c r="AB14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 38084-2024 FSC-klagomål mail.docx", "A 38084-2024")</f>
         <v/>
       </c>
-      <c r="AC13">
+      <c r="AC14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 38084-2024 tillsynsbegäran.docx", "A 38084-2024")</f>
         <v/>
       </c>
-      <c r="AD13">
+      <c r="AD14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 38084-2024 tillsynsbegäran mail.docx", "A 38084-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>A 5619-2024</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>45334</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>HÖRBY</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>1</v>
-      </c>
-      <c r="L14" t="n">
-        <v>1</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>2</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>3</v>
-      </c>
-      <c r="R14" t="n">
-        <v>2</v>
-      </c>
-      <c r="S14" t="n">
-        <v>4</v>
-      </c>
-      <c r="T14" t="n">
-        <v>7</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Skogsalm
-Gullpudra
-Trubbfjädermossa</t>
-        </is>
-      </c>
-      <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 5619-2024 artfynd.xlsx", "A 5619-2024")</f>
-        <v/>
-      </c>
-      <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 5619-2024 karta.png", "A 5619-2024")</f>
-        <v/>
-      </c>
-      <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 5619-2024 georefererad karta.tif", "A 5619-2024")</f>
-        <v/>
-      </c>
-      <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 5619-2024 FSC-klagomål.docx", "A 5619-2024")</f>
-        <v/>
-      </c>
-      <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 5619-2024 FSC-klagomål mail.docx", "A 5619-2024")</f>
-        <v/>
-      </c>
-      <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 5619-2024 tillsynsbegäran.docx", "A 5619-2024")</f>
-        <v/>
-      </c>
-      <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 5619-2024 tillsynsbegäran mail.docx", "A 5619-2024")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 20193-2024</t>
+          <t>A 2823-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2053,14 +2053,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45434</v>
+        <v>45677</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2073,13 +2073,13 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>11.2</v>
+        <v>21.1</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>1</v>
@@ -2106,151 +2106,151 @@
         <v>3</v>
       </c>
       <c r="T15" t="n">
+        <v>4</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>Borsttåg
+Grönvit nattviol
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 2823-2025 artfynd.xlsx", "A 2823-2025")</f>
+        <v/>
+      </c>
+      <c r="X15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 2823-2025 karta.png", "A 2823-2025")</f>
+        <v/>
+      </c>
+      <c r="Y15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 2823-2025 georefererad karta.tif", "A 2823-2025")</f>
+        <v/>
+      </c>
+      <c r="AA15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 2823-2025 FSC-klagomål.docx", "A 2823-2025")</f>
+        <v/>
+      </c>
+      <c r="AB15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 2823-2025 FSC-klagomål mail.docx", "A 2823-2025")</f>
+        <v/>
+      </c>
+      <c r="AC15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 2823-2025 tillsynsbegäran.docx", "A 2823-2025")</f>
+        <v/>
+      </c>
+      <c r="AD15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 2823-2025 tillsynsbegäran mail.docx", "A 2823-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 20193-2024</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>45434</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>HÖRBY</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
         <v>3</v>
       </c>
-      <c r="U15" t="n">
+      <c r="T16" t="n">
+        <v>3</v>
+      </c>
+      <c r="U16" t="n">
         <v>1</v>
       </c>
-      <c r="V15" s="2" t="inlineStr">
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>Vårärt
 Strutbräken
 Vätteros</t>
         </is>
       </c>
-      <c r="W15">
+      <c r="W16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 20193-2024 artfynd.xlsx", "A 20193-2024")</f>
         <v/>
       </c>
-      <c r="X15">
+      <c r="X16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 20193-2024 karta.png", "A 20193-2024")</f>
         <v/>
       </c>
-      <c r="Y15">
+      <c r="Y16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 20193-2024 georefererad karta.tif", "A 20193-2024")</f>
         <v/>
       </c>
-      <c r="AA15">
+      <c r="AA16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 20193-2024 FSC-klagomål.docx", "A 20193-2024")</f>
         <v/>
       </c>
-      <c r="AB15">
+      <c r="AB16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 20193-2024 FSC-klagomål mail.docx", "A 20193-2024")</f>
         <v/>
       </c>
-      <c r="AC15">
+      <c r="AC16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 20193-2024 tillsynsbegäran.docx", "A 20193-2024")</f>
         <v/>
       </c>
-      <c r="AD15">
+      <c r="AD16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 20193-2024 tillsynsbegäran mail.docx", "A 20193-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>A 2823-2025</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>45677</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>HÖRBY</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>21.1</v>
-      </c>
-      <c r="J16" t="n">
-        <v>2</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>1</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>1</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>3</v>
-      </c>
-      <c r="T16" t="n">
-        <v>4</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>Borsttåg
-Grönvit nattviol
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 2823-2025 artfynd.xlsx", "A 2823-2025")</f>
-        <v/>
-      </c>
-      <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 2823-2025 karta.png", "A 2823-2025")</f>
-        <v/>
-      </c>
-      <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 2823-2025 georefererad karta.tif", "A 2823-2025")</f>
-        <v/>
-      </c>
-      <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 2823-2025 FSC-klagomål.docx", "A 2823-2025")</f>
-        <v/>
-      </c>
-      <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 2823-2025 FSC-klagomål mail.docx", "A 2823-2025")</f>
-        <v/>
-      </c>
-      <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 2823-2025 tillsynsbegäran.docx", "A 2823-2025")</f>
-        <v/>
-      </c>
-      <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 2823-2025 tillsynsbegäran mail.docx", "A 2823-2025")</f>
         <v/>
       </c>
     </row>
@@ -2274,7 +2274,7 @@
         <v>45815</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2381,7 +2381,7 @@
         <v>45799</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2488,7 +2488,7 @@
         <v>44725</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 44135-2024</t>
+          <t>A 824-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2592,10 +2592,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45572</v>
+        <v>46030</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2607,11 +2607,16 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I20" t="n">
-        <v>0.6</v>
+        <v>3.1</v>
       </c>
       <c r="J20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -2620,7 +2625,7 @@
         <v>1</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -2632,269 +2637,264 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
+        <v>2</v>
+      </c>
+      <c r="R20" t="n">
         <v>1</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>2</v>
       </c>
       <c r="T20" t="n">
+        <v>3</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>Hedblomster
+Skogslysing</t>
+        </is>
+      </c>
+      <c r="W20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 824-2026 artfynd.xlsx", "A 824-2026")</f>
+        <v/>
+      </c>
+      <c r="X20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 824-2026 karta.png", "A 824-2026")</f>
+        <v/>
+      </c>
+      <c r="Y20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 824-2026 georefererad karta.tif", "A 824-2026")</f>
+        <v/>
+      </c>
+      <c r="AA20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 824-2026 FSC-klagomål.docx", "A 824-2026")</f>
+        <v/>
+      </c>
+      <c r="AB20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 824-2026 FSC-klagomål mail.docx", "A 824-2026")</f>
+        <v/>
+      </c>
+      <c r="AC20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 824-2026 tillsynsbegäran.docx", "A 824-2026")</f>
+        <v/>
+      </c>
+      <c r="AD20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 824-2026 tillsynsbegäran mail.docx", "A 824-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>A 42724-2023</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="n">
+        <v>45176</v>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>HÖRBY</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>1</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1</v>
+      </c>
+      <c r="S21" t="n">
         <v>2</v>
       </c>
-      <c r="U20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
+      <c r="T21" t="n">
+        <v>4</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Grönvit nattviol</t>
+        </is>
+      </c>
+      <c r="W21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 42724-2023 artfynd.xlsx", "A 42724-2023")</f>
+        <v/>
+      </c>
+      <c r="X21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 42724-2023 karta.png", "A 42724-2023")</f>
+        <v/>
+      </c>
+      <c r="Y21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 42724-2023 georefererad karta.tif", "A 42724-2023")</f>
+        <v/>
+      </c>
+      <c r="AA21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 42724-2023 FSC-klagomål.docx", "A 42724-2023")</f>
+        <v/>
+      </c>
+      <c r="AB21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 42724-2023 FSC-klagomål mail.docx", "A 42724-2023")</f>
+        <v/>
+      </c>
+      <c r="AC21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 42724-2023 tillsynsbegäran.docx", "A 42724-2023")</f>
+        <v/>
+      </c>
+      <c r="AD21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 42724-2023 tillsynsbegäran mail.docx", "A 42724-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>A 44135-2024</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="n">
+        <v>45572</v>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>HÖRBY</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J22" t="n">
+        <v>2</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>Ladusvala
 Vanlig padda</t>
         </is>
       </c>
-      <c r="W20">
+      <c r="W22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 44135-2024 artfynd.xlsx", "A 44135-2024")</f>
         <v/>
       </c>
-      <c r="X20">
+      <c r="X22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 44135-2024 karta.png", "A 44135-2024")</f>
         <v/>
       </c>
-      <c r="Y20">
+      <c r="Y22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 44135-2024 georefererad karta.tif", "A 44135-2024")</f>
         <v/>
       </c>
-      <c r="AA20">
+      <c r="AA22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 44135-2024 FSC-klagomål.docx", "A 44135-2024")</f>
         <v/>
       </c>
-      <c r="AB20">
+      <c r="AB22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 44135-2024 FSC-klagomål mail.docx", "A 44135-2024")</f>
         <v/>
       </c>
-      <c r="AC20">
+      <c r="AC22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 44135-2024 tillsynsbegäran.docx", "A 44135-2024")</f>
         <v/>
       </c>
-      <c r="AD20">
+      <c r="AD22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 44135-2024 tillsynsbegäran mail.docx", "A 44135-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>A 824-2026</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D21" s="1" t="n">
-        <v>46030</v>
-      </c>
-      <c r="E21" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>HÖRBY</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="J21" t="n">
-        <v>1</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>1</v>
-      </c>
-      <c r="M21" t="n">
-        <v>1</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>2</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1</v>
-      </c>
-      <c r="S21" t="n">
-        <v>2</v>
-      </c>
-      <c r="T21" t="n">
-        <v>3</v>
-      </c>
-      <c r="U21" t="n">
-        <v>0</v>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>Hedblomster
-Skogslysing</t>
-        </is>
-      </c>
-      <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 824-2026 artfynd.xlsx", "A 824-2026")</f>
-        <v/>
-      </c>
-      <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 824-2026 karta.png", "A 824-2026")</f>
-        <v/>
-      </c>
-      <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 824-2026 georefererad karta.tif", "A 824-2026")</f>
-        <v/>
-      </c>
-      <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 824-2026 FSC-klagomål.docx", "A 824-2026")</f>
-        <v/>
-      </c>
-      <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 824-2026 FSC-klagomål mail.docx", "A 824-2026")</f>
-        <v/>
-      </c>
-      <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 824-2026 tillsynsbegäran.docx", "A 824-2026")</f>
-        <v/>
-      </c>
-      <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 824-2026 tillsynsbegäran mail.docx", "A 824-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>A 42724-2023</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D22" s="1" t="n">
-        <v>45176</v>
-      </c>
-      <c r="E22" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>HÖRBY</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="J22" t="n">
-        <v>1</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>1</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>1</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1</v>
-      </c>
-      <c r="S22" t="n">
-        <v>2</v>
-      </c>
-      <c r="T22" t="n">
-        <v>4</v>
-      </c>
-      <c r="U22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Grönvit nattviol</t>
-        </is>
-      </c>
-      <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 42724-2023 artfynd.xlsx", "A 42724-2023")</f>
-        <v/>
-      </c>
-      <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 42724-2023 karta.png", "A 42724-2023")</f>
-        <v/>
-      </c>
-      <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 42724-2023 georefererad karta.tif", "A 42724-2023")</f>
-        <v/>
-      </c>
-      <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 42724-2023 FSC-klagomål.docx", "A 42724-2023")</f>
-        <v/>
-      </c>
-      <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 42724-2023 FSC-klagomål mail.docx", "A 42724-2023")</f>
-        <v/>
-      </c>
-      <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 42724-2023 tillsynsbegäran.docx", "A 42724-2023")</f>
-        <v/>
-      </c>
-      <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 42724-2023 tillsynsbegäran mail.docx", "A 42724-2023")</f>
         <v/>
       </c>
     </row>
@@ -2918,7 +2918,7 @@
         <v>45317</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3007,7 +3007,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 47612-2023</t>
+          <t>A 31115-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45203</v>
+        <v>45502</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3037,7 +3037,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2.4</v>
+        <v>0.8</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -3046,13 +3046,13 @@
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3064,7 +3064,7 @@
         <v>1</v>
       </c>
       <c r="R24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3077,42 +3077,42 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 47612-2023 artfynd.xlsx", "A 47612-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 31115-2024 artfynd.xlsx", "A 31115-2024")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 47612-2023 karta.png", "A 47612-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 31115-2024 karta.png", "A 31115-2024")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 47612-2023 georefererad karta.tif", "A 47612-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 31115-2024 georefererad karta.tif", "A 31115-2024")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 47612-2023 FSC-klagomål.docx", "A 47612-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 31115-2024 FSC-klagomål.docx", "A 31115-2024")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 47612-2023 FSC-klagomål mail.docx", "A 47612-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 31115-2024 FSC-klagomål mail.docx", "A 31115-2024")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 47612-2023 tillsynsbegäran.docx", "A 47612-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 31115-2024 tillsynsbegäran.docx", "A 31115-2024")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 47612-2023 tillsynsbegäran mail.docx", "A 47612-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 31115-2024 tillsynsbegäran mail.docx", "A 31115-2024")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 36362-2025</t>
+          <t>A 25479-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3122,14 +3122,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45868</v>
+        <v>45802</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3142,7 +3142,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>3.7</v>
+        <v>0.7</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -3178,46 +3178,46 @@
         <v>1</v>
       </c>
       <c r="U25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Lundvårlök</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 36362-2025 artfynd.xlsx", "A 36362-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 25479-2025 artfynd.xlsx", "A 25479-2025")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 36362-2025 karta.png", "A 36362-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 25479-2025 karta.png", "A 25479-2025")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 36362-2025 georefererad karta.tif", "A 36362-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 25479-2025 georefererad karta.tif", "A 25479-2025")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 36362-2025 FSC-klagomål.docx", "A 36362-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 25479-2025 FSC-klagomål.docx", "A 25479-2025")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 36362-2025 FSC-klagomål mail.docx", "A 36362-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 25479-2025 FSC-klagomål mail.docx", "A 25479-2025")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 36362-2025 tillsynsbegäran.docx", "A 36362-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 25479-2025 tillsynsbegäran.docx", "A 25479-2025")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 36362-2025 tillsynsbegäran mail.docx", "A 36362-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 25479-2025 tillsynsbegäran mail.docx", "A 25479-2025")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 113-2023</t>
+          <t>A 36362-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3231,10 +3231,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44928</v>
+        <v>45868</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3247,19 +3247,19 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>5.1</v>
+        <v>3.7</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
         <v>0</v>
@@ -3271,10 +3271,10 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>
@@ -3283,46 +3283,46 @@
         <v>1</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Slåttergubbe</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 113-2023 artfynd.xlsx", "A 113-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 36362-2025 artfynd.xlsx", "A 36362-2025")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 113-2023 karta.png", "A 113-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 36362-2025 karta.png", "A 36362-2025")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 113-2023 georefererad karta.tif", "A 113-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 36362-2025 georefererad karta.tif", "A 36362-2025")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 113-2023 FSC-klagomål.docx", "A 113-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 36362-2025 FSC-klagomål.docx", "A 36362-2025")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 113-2023 FSC-klagomål mail.docx", "A 113-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 36362-2025 FSC-klagomål mail.docx", "A 36362-2025")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 113-2023 tillsynsbegäran.docx", "A 113-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 36362-2025 tillsynsbegäran.docx", "A 36362-2025")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 113-2023 tillsynsbegäran mail.docx", "A 113-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 36362-2025 tillsynsbegäran mail.docx", "A 36362-2025")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 25833-2024</t>
+          <t>A 24823-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3336,10 +3336,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45463</v>
+        <v>46174</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3351,8 +3351,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I27" t="n">
-        <v>1.4</v>
+        <v>5.1</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3364,7 +3369,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
         <v>0</v>
@@ -3376,58 +3381,58 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
       </c>
       <c r="T27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Slåttergubbe</t>
+          <t>Tandrot</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 25833-2024 artfynd.xlsx", "A 25833-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 24823-2026 artfynd.xlsx", "A 24823-2026")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 25833-2024 karta.png", "A 25833-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 24823-2026 karta.png", "A 24823-2026")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 25833-2024 georefererad karta.tif", "A 25833-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 24823-2026 georefererad karta.tif", "A 24823-2026")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 25833-2024 FSC-klagomål.docx", "A 25833-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 24823-2026 FSC-klagomål.docx", "A 24823-2026")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 25833-2024 FSC-klagomål mail.docx", "A 25833-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 24823-2026 FSC-klagomål mail.docx", "A 24823-2026")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 25833-2024 tillsynsbegäran.docx", "A 25833-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 24823-2026 tillsynsbegäran.docx", "A 24823-2026")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 25833-2024 tillsynsbegäran mail.docx", "A 25833-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 24823-2026 tillsynsbegäran mail.docx", "A 24823-2026")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 40376-2023</t>
+          <t>A 16519-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3441,10 +3446,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45169</v>
+        <v>46112</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3457,22 +3462,22 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2.7</v>
+        <v>0.8</v>
       </c>
       <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
         <v>1</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" t="n">
-        <v>1</v>
-      </c>
-      <c r="M28" t="n">
-        <v>0</v>
-      </c>
-      <c r="N28" t="n">
-        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3484,7 +3489,7 @@
         <v>1</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
@@ -3497,46 +3502,42 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 40376-2023 artfynd.xlsx", "A 40376-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 16519-2026 artfynd.xlsx", "A 16519-2026")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 40376-2023 karta.png", "A 40376-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 16519-2026 karta.png", "A 16519-2026")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 40376-2023 georefererad karta.tif", "A 40376-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 16519-2026 georefererad karta.tif", "A 16519-2026")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 40376-2023 FSC-klagomål.docx", "A 40376-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 16519-2026 FSC-klagomål.docx", "A 16519-2026")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 40376-2023 FSC-klagomål mail.docx", "A 40376-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 16519-2026 FSC-klagomål mail.docx", "A 16519-2026")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 40376-2023 tillsynsbegäran.docx", "A 40376-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 16519-2026 tillsynsbegäran.docx", "A 16519-2026")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 40376-2023 tillsynsbegäran mail.docx", "A 40376-2023")</f>
-        <v/>
-      </c>
-      <c r="AE28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/fåglar/A 40376-2023 prioriterade fågelarter.docx", "A 40376-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 16519-2026 tillsynsbegäran mail.docx", "A 16519-2026")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 31115-2024</t>
+          <t>A 47612-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3550,10 +3551,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45502</v>
+        <v>45203</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3566,7 +3567,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.8</v>
+        <v>2.4</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3575,13 +3576,13 @@
         <v>0</v>
       </c>
       <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
         <v>1</v>
-      </c>
-      <c r="M29" t="n">
-        <v>0</v>
-      </c>
-      <c r="N29" t="n">
-        <v>0</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3593,7 +3594,7 @@
         <v>1</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
@@ -3606,42 +3607,42 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Gullpudra</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 31115-2024 artfynd.xlsx", "A 31115-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 47612-2023 artfynd.xlsx", "A 47612-2023")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 31115-2024 karta.png", "A 31115-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 47612-2023 karta.png", "A 47612-2023")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 31115-2024 georefererad karta.tif", "A 31115-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 47612-2023 georefererad karta.tif", "A 47612-2023")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 31115-2024 FSC-klagomål.docx", "A 31115-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 47612-2023 FSC-klagomål.docx", "A 47612-2023")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 31115-2024 FSC-klagomål mail.docx", "A 31115-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 47612-2023 FSC-klagomål mail.docx", "A 47612-2023")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 31115-2024 tillsynsbegäran.docx", "A 31115-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 47612-2023 tillsynsbegäran.docx", "A 47612-2023")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 31115-2024 tillsynsbegäran mail.docx", "A 31115-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 47612-2023 tillsynsbegäran mail.docx", "A 47612-2023")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 24823-2026</t>
+          <t>A 40376-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3655,10 +3656,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46174</v>
+        <v>45169</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3670,22 +3671,17 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I30" t="n">
-        <v>5.1</v>
+        <v>2.7</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
@@ -3700,7 +3696,7 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -3712,46 +3708,50 @@
         <v>1</v>
       </c>
       <c r="U30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>Tandrot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 24823-2026 artfynd.xlsx", "A 24823-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 40376-2023 artfynd.xlsx", "A 40376-2023")</f>
         <v/>
       </c>
       <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 24823-2026 karta.png", "A 24823-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 40376-2023 karta.png", "A 40376-2023")</f>
         <v/>
       </c>
       <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 24823-2026 georefererad karta.tif", "A 24823-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 40376-2023 georefererad karta.tif", "A 40376-2023")</f>
         <v/>
       </c>
       <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 24823-2026 FSC-klagomål.docx", "A 24823-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 40376-2023 FSC-klagomål.docx", "A 40376-2023")</f>
         <v/>
       </c>
       <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 24823-2026 FSC-klagomål mail.docx", "A 24823-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 40376-2023 FSC-klagomål mail.docx", "A 40376-2023")</f>
         <v/>
       </c>
       <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 24823-2026 tillsynsbegäran.docx", "A 24823-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 40376-2023 tillsynsbegäran.docx", "A 40376-2023")</f>
         <v/>
       </c>
       <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 24823-2026 tillsynsbegäran mail.docx", "A 24823-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 40376-2023 tillsynsbegäran mail.docx", "A 40376-2023")</f>
+        <v/>
+      </c>
+      <c r="AE30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/fåglar/A 40376-2023 prioriterade fågelarter.docx", "A 40376-2023")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 16519-2026</t>
+          <t>A 31284-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3765,10 +3765,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46112</v>
+        <v>46218</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3781,10 +3781,10 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.8</v>
+        <v>6.8</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
@@ -3796,7 +3796,7 @@
         <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -3805,10 +3805,10 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
         <v>1</v>
@@ -3821,42 +3821,42 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="W31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 16519-2026 artfynd.xlsx", "A 16519-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 31284-2026 artfynd.xlsx", "A 31284-2026")</f>
         <v/>
       </c>
       <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 16519-2026 karta.png", "A 16519-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 31284-2026 karta.png", "A 31284-2026")</f>
         <v/>
       </c>
       <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 16519-2026 georefererad karta.tif", "A 16519-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 31284-2026 georefererad karta.tif", "A 31284-2026")</f>
         <v/>
       </c>
       <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 16519-2026 FSC-klagomål.docx", "A 16519-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 31284-2026 FSC-klagomål.docx", "A 31284-2026")</f>
         <v/>
       </c>
       <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 16519-2026 FSC-klagomål mail.docx", "A 16519-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 31284-2026 FSC-klagomål mail.docx", "A 31284-2026")</f>
         <v/>
       </c>
       <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 16519-2026 tillsynsbegäran.docx", "A 16519-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 31284-2026 tillsynsbegäran.docx", "A 31284-2026")</f>
         <v/>
       </c>
       <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 16519-2026 tillsynsbegäran mail.docx", "A 16519-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 31284-2026 tillsynsbegäran mail.docx", "A 31284-2026")</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 31284-2026</t>
+          <t>A 113-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3870,10 +3870,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46218</v>
+        <v>44928</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3886,20 +3886,20 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>6.8</v>
+        <v>5.1</v>
       </c>
       <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
         <v>1</v>
       </c>
-      <c r="K32" t="n">
-        <v>0</v>
-      </c>
-      <c r="L32" t="n">
-        <v>0</v>
-      </c>
-      <c r="M32" t="n">
-        <v>0</v>
-      </c>
       <c r="N32" t="n">
         <v>0</v>
       </c>
@@ -3910,10 +3910,10 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S32" t="n">
         <v>1</v>
@@ -3926,42 +3926,42 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Slåttergubbe</t>
         </is>
       </c>
       <c r="W32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 31284-2026 artfynd.xlsx", "A 31284-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 113-2023 artfynd.xlsx", "A 113-2023")</f>
         <v/>
       </c>
       <c r="X32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 31284-2026 karta.png", "A 31284-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 113-2023 karta.png", "A 113-2023")</f>
         <v/>
       </c>
       <c r="Y32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 31284-2026 georefererad karta.tif", "A 31284-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 113-2023 georefererad karta.tif", "A 113-2023")</f>
         <v/>
       </c>
       <c r="AA32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 31284-2026 FSC-klagomål.docx", "A 31284-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 113-2023 FSC-klagomål.docx", "A 113-2023")</f>
         <v/>
       </c>
       <c r="AB32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 31284-2026 FSC-klagomål mail.docx", "A 31284-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 113-2023 FSC-klagomål mail.docx", "A 113-2023")</f>
         <v/>
       </c>
       <c r="AC32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 31284-2026 tillsynsbegäran.docx", "A 31284-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 113-2023 tillsynsbegäran.docx", "A 113-2023")</f>
         <v/>
       </c>
       <c r="AD32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 31284-2026 tillsynsbegäran mail.docx", "A 31284-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 113-2023 tillsynsbegäran mail.docx", "A 113-2023")</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 29129-2026</t>
+          <t>A 30165-2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>46202</v>
+        <v>46206</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3990,13 +3990,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I33" t="n">
-        <v>10.5</v>
+        <v>1.4</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -4005,13 +4000,13 @@
         <v>0</v>
       </c>
       <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
         <v>1</v>
-      </c>
-      <c r="M33" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" t="n">
-        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4023,7 +4018,7 @@
         <v>1</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S33" t="n">
         <v>1</v>
@@ -4036,42 +4031,42 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>Ekticka</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="W33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 29129-2026 artfynd.xlsx", "A 29129-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 30165-2026 artfynd.xlsx", "A 30165-2026")</f>
         <v/>
       </c>
       <c r="X33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 29129-2026 karta.png", "A 29129-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 30165-2026 karta.png", "A 30165-2026")</f>
         <v/>
       </c>
       <c r="Y33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 29129-2026 georefererad karta.tif", "A 29129-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 30165-2026 georefererad karta.tif", "A 30165-2026")</f>
         <v/>
       </c>
       <c r="AA33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 29129-2026 FSC-klagomål.docx", "A 29129-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 30165-2026 FSC-klagomål.docx", "A 30165-2026")</f>
         <v/>
       </c>
       <c r="AB33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 29129-2026 FSC-klagomål mail.docx", "A 29129-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 30165-2026 FSC-klagomål mail.docx", "A 30165-2026")</f>
         <v/>
       </c>
       <c r="AC33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 29129-2026 tillsynsbegäran.docx", "A 29129-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 30165-2026 tillsynsbegäran.docx", "A 30165-2026")</f>
         <v/>
       </c>
       <c r="AD33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 29129-2026 tillsynsbegäran mail.docx", "A 29129-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 30165-2026 tillsynsbegäran mail.docx", "A 30165-2026")</f>
         <v/>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 30165-2026</t>
+          <t>A 29129-2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4085,10 +4080,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>46206</v>
+        <v>46202</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4100,8 +4095,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I34" t="n">
-        <v>1.4</v>
+        <v>10.5</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -4110,13 +4110,13 @@
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M34" t="n">
         <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4128,7 +4128,7 @@
         <v>1</v>
       </c>
       <c r="R34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
         <v>1</v>
@@ -4141,42 +4141,42 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Ekticka</t>
         </is>
       </c>
       <c r="W34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 30165-2026 artfynd.xlsx", "A 30165-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 29129-2026 artfynd.xlsx", "A 29129-2026")</f>
         <v/>
       </c>
       <c r="X34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 30165-2026 karta.png", "A 30165-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 29129-2026 karta.png", "A 29129-2026")</f>
         <v/>
       </c>
       <c r="Y34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 30165-2026 georefererad karta.tif", "A 30165-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 29129-2026 georefererad karta.tif", "A 29129-2026")</f>
         <v/>
       </c>
       <c r="AA34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 30165-2026 FSC-klagomål.docx", "A 30165-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 29129-2026 FSC-klagomål.docx", "A 29129-2026")</f>
         <v/>
       </c>
       <c r="AB34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 30165-2026 FSC-klagomål mail.docx", "A 30165-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 29129-2026 FSC-klagomål mail.docx", "A 29129-2026")</f>
         <v/>
       </c>
       <c r="AC34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 30165-2026 tillsynsbegäran.docx", "A 30165-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 29129-2026 tillsynsbegäran.docx", "A 29129-2026")</f>
         <v/>
       </c>
       <c r="AD34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 30165-2026 tillsynsbegäran mail.docx", "A 30165-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 29129-2026 tillsynsbegäran mail.docx", "A 29129-2026")</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 21713-2025</t>
+          <t>A 25833-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4190,10 +4190,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45783</v>
+        <v>45463</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4206,20 +4206,20 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
         <v>1</v>
       </c>
-      <c r="K35" t="n">
-        <v>0</v>
-      </c>
-      <c r="L35" t="n">
-        <v>0</v>
-      </c>
-      <c r="M35" t="n">
-        <v>0</v>
-      </c>
       <c r="N35" t="n">
         <v>0</v>
       </c>
@@ -4230,58 +4230,58 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S35" t="n">
         <v>1</v>
       </c>
       <c r="T35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U35" t="n">
         <v>0</v>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Slåttergubbe</t>
         </is>
       </c>
       <c r="W35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 21713-2025 artfynd.xlsx", "A 21713-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 25833-2024 artfynd.xlsx", "A 25833-2024")</f>
         <v/>
       </c>
       <c r="X35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 21713-2025 karta.png", "A 21713-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 25833-2024 karta.png", "A 25833-2024")</f>
         <v/>
       </c>
       <c r="Y35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 21713-2025 georefererad karta.tif", "A 21713-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 25833-2024 georefererad karta.tif", "A 25833-2024")</f>
         <v/>
       </c>
       <c r="AA35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 21713-2025 FSC-klagomål.docx", "A 21713-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 25833-2024 FSC-klagomål.docx", "A 25833-2024")</f>
         <v/>
       </c>
       <c r="AB35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 21713-2025 FSC-klagomål mail.docx", "A 21713-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 25833-2024 FSC-klagomål mail.docx", "A 25833-2024")</f>
         <v/>
       </c>
       <c r="AC35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 21713-2025 tillsynsbegäran.docx", "A 21713-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 25833-2024 tillsynsbegäran.docx", "A 25833-2024")</f>
         <v/>
       </c>
       <c r="AD35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 21713-2025 tillsynsbegäran mail.docx", "A 21713-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 25833-2024 tillsynsbegäran mail.docx", "A 25833-2024")</f>
         <v/>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 25479-2025</t>
+          <t>A 21713-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4291,14 +4291,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45802</v>
+        <v>45783</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4311,13 +4311,13 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
@@ -4351,35 +4351,35 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>Lundvårlök</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="W36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 25479-2025 artfynd.xlsx", "A 25479-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 21713-2025 artfynd.xlsx", "A 21713-2025")</f>
         <v/>
       </c>
       <c r="X36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 25479-2025 karta.png", "A 25479-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 21713-2025 karta.png", "A 21713-2025")</f>
         <v/>
       </c>
       <c r="Y36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 25479-2025 georefererad karta.tif", "A 25479-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 21713-2025 georefererad karta.tif", "A 21713-2025")</f>
         <v/>
       </c>
       <c r="AA36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 25479-2025 FSC-klagomål.docx", "A 25479-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 21713-2025 FSC-klagomål.docx", "A 21713-2025")</f>
         <v/>
       </c>
       <c r="AB36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 25479-2025 FSC-klagomål mail.docx", "A 25479-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 21713-2025 FSC-klagomål mail.docx", "A 21713-2025")</f>
         <v/>
       </c>
       <c r="AC36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 25479-2025 tillsynsbegäran.docx", "A 25479-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 21713-2025 tillsynsbegäran.docx", "A 21713-2025")</f>
         <v/>
       </c>
       <c r="AD36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 25479-2025 tillsynsbegäran mail.docx", "A 25479-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 21713-2025 tillsynsbegäran mail.docx", "A 21713-2025")</f>
         <v/>
       </c>
     </row>
@@ -4403,7 +4403,7 @@
         <v>45089</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4508,7 +4508,7 @@
         <v>44999</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4613,7 +4613,7 @@
         <v>44509</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4686,7 +4686,7 @@
         <v>44663</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4759,7 +4759,7 @@
         <v>44509</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4832,7 +4832,7 @@
         <v>44697</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4905,7 +4905,7 @@
         <v>44510</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4978,7 +4978,7 @@
         <v>44834</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5051,7 +5051,7 @@
         <v>44771</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5124,7 +5124,7 @@
         <v>44466</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5197,7 +5197,7 @@
         <v>44789</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5270,7 +5270,7 @@
         <v>44733</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5326,7 +5326,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 43380-2022</t>
+          <t>A 24670-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5336,14 +5336,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44834</v>
+        <v>45460</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5356,7 +5356,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.7</v>
+        <v>0.2</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5399,7 +5399,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 47609-2023</t>
+          <t>A 2979-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5413,10 +5413,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45203</v>
+        <v>45315</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5428,8 +5428,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I50" t="n">
-        <v>2.4</v>
+        <v>4.7</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5472,7 +5477,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 9974-2024</t>
+          <t>A 18609-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5486,10 +5491,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45363</v>
+        <v>45763</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5545,7 +5550,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 15970-2024</t>
+          <t>A 3471-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5559,10 +5564,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45405</v>
+        <v>45680</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5575,7 +5580,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.8</v>
+        <v>3.7</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5618,7 +5623,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 5163-2024</t>
+          <t>A 33359-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5632,10 +5637,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45330</v>
+        <v>45128</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5647,13 +5652,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I53" t="n">
-        <v>7.1</v>
+        <v>0.9</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5696,7 +5696,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 37724-2022</t>
+          <t>A 37757-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5710,10 +5710,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44810</v>
+        <v>45541</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5726,7 +5726,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5769,7 +5769,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 37728-2022</t>
+          <t>A 31596-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5783,10 +5783,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44810</v>
+        <v>45117</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5799,7 +5799,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5842,7 +5842,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 56818-2022</t>
+          <t>A 44613-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5856,10 +5856,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44894</v>
+        <v>45189</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5871,8 +5871,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I56" t="n">
-        <v>1.8</v>
+        <v>3.8</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5915,7 +5920,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 33359-2023</t>
+          <t>A 2816-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5925,14 +5930,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45128</v>
+        <v>45677</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5945,7 +5950,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5988,7 +5993,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 54894-2023</t>
+          <t>A 28785-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5998,14 +6003,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45236</v>
+        <v>45104</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6018,7 +6023,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.6</v>
+        <v>2.1</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -6061,7 +6066,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 28746-2024</t>
+          <t>A 16101-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6075,10 +6080,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45478</v>
+        <v>45750</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6091,7 +6096,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.9</v>
+        <v>0.5</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6134,7 +6139,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 37082-2023</t>
+          <t>A 58360-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6144,14 +6149,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45155</v>
+        <v>45250</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6164,7 +6169,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6207,7 +6212,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 2752-2023</t>
+          <t>A 4756-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6221,10 +6226,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44944</v>
+        <v>45688</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6236,13 +6241,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I61" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6285,7 +6285,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 48397-2022</t>
+          <t>A 62277-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6299,10 +6299,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44858</v>
+        <v>46006</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6315,7 +6315,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.7</v>
+        <v>2.4</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6358,7 +6358,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 13225-2024</t>
+          <t>A 16665-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6372,10 +6372,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45386</v>
+        <v>45754</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6388,7 +6388,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.7</v>
+        <v>2.4</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6431,7 +6431,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 13226-2024</t>
+          <t>A 43711-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6441,14 +6441,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45386</v>
+        <v>45569</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6461,7 +6461,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.7</v>
+        <v>3.4</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6504,7 +6504,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 28785-2023</t>
+          <t>A 23484-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6514,14 +6514,14 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45104</v>
+        <v>45792</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6534,7 +6534,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>2.1</v>
+        <v>3.5</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6577,7 +6577,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 15998-2024</t>
+          <t>A 48397-2022</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6591,10 +6591,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45405</v>
+        <v>44858</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6607,7 +6607,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.4</v>
+        <v>1.7</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6650,7 +6650,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 16001-2024</t>
+          <t>A 6886-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6664,10 +6664,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45405</v>
+        <v>45342</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6679,8 +6679,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I67" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6723,7 +6728,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 36689-2024</t>
+          <t>A 554-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6733,14 +6738,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45537</v>
+        <v>46029</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6752,13 +6757,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I68" t="n">
-        <v>9.5</v>
+        <v>0.8</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6801,7 +6801,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 43828-2024</t>
+          <t>A 826-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6815,10 +6815,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45572</v>
+        <v>46030</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6830,8 +6830,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I69" t="n">
-        <v>0.9</v>
+        <v>0.3</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6874,7 +6879,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 38080-2024</t>
+          <t>A 829-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6888,10 +6893,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45545</v>
+        <v>46030</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6903,8 +6908,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I70" t="n">
-        <v>0.7</v>
+        <v>6.9</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6947,7 +6957,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 8260-2026</t>
+          <t>A 821-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6961,10 +6971,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46064</v>
+        <v>46030</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6976,8 +6986,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I71" t="n">
-        <v>3.3</v>
+        <v>4.3</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -7020,7 +7035,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 29244-2025</t>
+          <t>A 33358-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7034,10 +7049,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45824</v>
+        <v>45128</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7050,7 +7065,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7093,7 +7108,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 8259-2026</t>
+          <t>A 28550-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7107,10 +7122,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46064</v>
+        <v>45818</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7123,7 +7138,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>3.1</v>
+        <v>5</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7166,7 +7181,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 29354-2025</t>
+          <t>A 1989-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7180,10 +7195,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45824</v>
+        <v>46035</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7196,7 +7211,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0.8</v>
+        <v>2.5</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7239,7 +7254,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 2981-2024</t>
+          <t>A 9612-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7253,10 +7268,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45315</v>
+        <v>45715</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7268,13 +7283,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I75" t="n">
-        <v>6.4</v>
+        <v>1.2</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7317,7 +7327,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 18609-2025</t>
+          <t>A 47641-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7331,10 +7341,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45763</v>
+        <v>45203</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7347,7 +7357,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0.6</v>
+        <v>4.8</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7390,7 +7400,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 56750-2023</t>
+          <t>A 3013-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7404,10 +7414,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45238</v>
+        <v>46038</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7420,7 +7430,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7463,7 +7473,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 32459-2025</t>
+          <t>A 29244-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7477,10 +7487,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45838</v>
+        <v>45824</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7493,7 +7503,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7536,7 +7546,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 42715-2023</t>
+          <t>A 29354-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7550,10 +7560,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45176</v>
+        <v>45824</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7566,7 +7576,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7609,7 +7619,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 13633-2024</t>
+          <t>A 3346-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7623,10 +7633,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45390</v>
+        <v>45317</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7639,7 +7649,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7682,7 +7692,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 32958-2025</t>
+          <t>A 39298-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7696,10 +7706,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45839</v>
+        <v>45166</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7712,7 +7722,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7755,7 +7765,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 37756-2024</t>
+          <t>A 39507-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7769,10 +7779,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45541</v>
+        <v>45551</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7784,8 +7794,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I82" t="n">
-        <v>3.2</v>
+        <v>0.3</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7828,7 +7843,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 58641-2023</t>
+          <t>A 5374-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7838,14 +7853,14 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45251</v>
+        <v>46050</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7858,7 +7873,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7901,7 +7916,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 18603-2025</t>
+          <t>A 788-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7915,10 +7930,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45763</v>
+        <v>45300</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7931,7 +7946,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7974,7 +7989,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 3346-2024</t>
+          <t>A 34154-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7988,10 +8003,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45317</v>
+        <v>45845</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8004,7 +8019,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>0.5</v>
+        <v>5</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -8047,7 +8062,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 36355-2025</t>
+          <t>A 32958-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -8061,10 +8076,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45868</v>
+        <v>45839</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8077,7 +8092,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>3.6</v>
+        <v>5</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8120,7 +8135,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 34154-2025</t>
+          <t>A 32459-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8134,10 +8149,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45845</v>
+        <v>45838</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8150,7 +8165,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>5</v>
+        <v>1.2</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8193,7 +8208,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 788-2024</t>
+          <t>A 2981-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8207,10 +8222,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45300</v>
+        <v>45315</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8222,8 +8237,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I88" t="n">
-        <v>0.6</v>
+        <v>6.4</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8266,7 +8286,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 25552-2025</t>
+          <t>A 9974-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8280,10 +8300,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45803</v>
+        <v>45363</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8296,7 +8316,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>2</v>
+        <v>0.6</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8339,7 +8359,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 10731-2026</t>
+          <t>A 37756-2024</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8353,10 +8373,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46078</v>
+        <v>45541</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8368,13 +8388,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I90" t="n">
-        <v>4.8</v>
+        <v>3.2</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8417,7 +8432,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 38147-2025</t>
+          <t>A 11943-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8431,10 +8446,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45882</v>
+        <v>45728</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8447,7 +8462,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8490,7 +8505,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 50715-2024</t>
+          <t>A 8310-2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8504,10 +8519,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45602</v>
+        <v>46064</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8520,7 +8535,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>0.4</v>
+        <v>1.4</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8563,7 +8578,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 2816-2025</t>
+          <t>A 8260-2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8573,14 +8588,14 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45677</v>
+        <v>46064</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8593,7 +8608,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>2</v>
+        <v>3.3</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8636,7 +8651,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 16101-2025</t>
+          <t>A 42715-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8650,10 +8665,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45750</v>
+        <v>45176</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8709,7 +8724,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 34147-2025</t>
+          <t>A 8259-2026</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8723,10 +8738,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45845</v>
+        <v>46064</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8739,7 +8754,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>18.7</v>
+        <v>3.1</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8782,7 +8797,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 34422-2024</t>
+          <t>A 28918-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8792,14 +8807,14 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45525</v>
+        <v>45104</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8812,7 +8827,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8855,7 +8870,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 11943-2025</t>
+          <t>A 36355-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8869,10 +8884,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45728</v>
+        <v>45868</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8885,7 +8900,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1.2</v>
+        <v>3.6</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8928,7 +8943,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 44613-2023</t>
+          <t>A 43932-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8942,10 +8957,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45189</v>
+        <v>45187</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8957,13 +8972,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I98" t="n">
-        <v>3.8</v>
+        <v>3</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -9006,7 +9016,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 14307-2026</t>
+          <t>A 43935-2023</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -9020,10 +9030,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>46099</v>
+        <v>45187</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9036,7 +9046,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1</v>
+        <v>2.9</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -9079,7 +9089,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 51757-2025</t>
+          <t>A 10731-2026</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -9089,14 +9099,14 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45951</v>
+        <v>46078</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9110,11 +9120,11 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1.3</v>
+        <v>4.8</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -9157,7 +9167,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 43937-2023</t>
+          <t>A 34147-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9171,10 +9181,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45187</v>
+        <v>45845</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9187,7 +9197,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>2.6</v>
+        <v>18.7</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9230,7 +9240,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 43939-2023</t>
+          <t>A 25552-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9244,10 +9254,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45187</v>
+        <v>45803</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9260,7 +9270,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>0.6</v>
+        <v>2</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9303,7 +9313,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 67426-2021</t>
+          <t>A 2747-2023</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9317,10 +9327,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>44523</v>
+        <v>44944</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9332,8 +9342,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I103" t="n">
-        <v>0.6</v>
+        <v>4.6</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9376,7 +9391,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 3520-2026</t>
+          <t>A 38147-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9390,10 +9405,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>46042</v>
+        <v>45882</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9406,7 +9421,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9449,7 +9464,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 52929-2025</t>
+          <t>A 51757-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9459,14 +9474,14 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45957</v>
+        <v>45951</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9484,7 +9499,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>8.300000000000001</v>
+        <v>1.3</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9527,7 +9542,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 3470-2026</t>
+          <t>A 48427-2022</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9541,10 +9556,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>46042</v>
+        <v>44858</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9556,8 +9571,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I106" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9600,7 +9620,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 52930-2025</t>
+          <t>A 8084-2022</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9614,10 +9634,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45957</v>
+        <v>44608</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9629,13 +9649,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I107" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9678,7 +9693,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 3534-2025</t>
+          <t>A 43828-2024</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9692,10 +9707,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45680</v>
+        <v>45572</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9707,13 +9722,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I108" t="n">
-        <v>4.8</v>
+        <v>0.9</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9756,7 +9766,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 9850-2026</t>
+          <t>A 13225-2024</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9770,10 +9780,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>46072</v>
+        <v>45386</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9786,7 +9796,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>2.2</v>
+        <v>0.7</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9829,7 +9839,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 7831-2025</t>
+          <t>A 13226-2024</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9843,10 +9853,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45706</v>
+        <v>45386</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9859,7 +9869,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9902,7 +9912,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 3513-2026</t>
+          <t>A 47552-2023</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9916,10 +9926,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>46042</v>
+        <v>45203</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9932,7 +9942,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9975,7 +9985,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 54765-2025</t>
+          <t>A 14307-2026</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9989,10 +9999,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45966</v>
+        <v>46099</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10005,7 +10015,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>2.6</v>
+        <v>1</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -10048,7 +10058,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 40994-2025</t>
+          <t>A 52930-2025</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -10062,10 +10072,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45898</v>
+        <v>45957</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10077,8 +10087,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I113" t="n">
-        <v>5.6</v>
+        <v>1.6</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -10121,7 +10136,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 55304-2025</t>
+          <t>A 52929-2025</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -10131,14 +10146,14 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45970</v>
+        <v>45957</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10150,8 +10165,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I114" t="n">
-        <v>0.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -10194,7 +10214,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 55306-2025</t>
+          <t>A 3470-2026</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10204,14 +10224,14 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45970</v>
+        <v>46042</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10224,7 +10244,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>0.3</v>
+        <v>1.5</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10267,7 +10287,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 18735-2023</t>
+          <t>A 3513-2026</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10281,10 +10301,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45043</v>
+        <v>46042</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10297,7 +10317,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10340,7 +10360,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 57269-2025</t>
+          <t>A 3520-2026</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10354,10 +10374,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45979</v>
+        <v>46042</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10369,13 +10389,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H117" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I117" t="n">
-        <v>5.5</v>
+        <v>0.8</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10418,7 +10433,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 28493-2023</t>
+          <t>A 9850-2026</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10432,10 +10447,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45103</v>
+        <v>46072</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10448,7 +10463,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>0.8</v>
+        <v>2.2</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10491,7 +10506,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 59308-2025</t>
+          <t>A 2752-2023</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10505,10 +10520,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45989</v>
+        <v>44944</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10520,8 +10535,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I119" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10564,7 +10584,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 7402-2026</t>
+          <t>A 54765-2025</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10578,10 +10598,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>46059</v>
+        <v>45966</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10594,7 +10614,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>4.7</v>
+        <v>2.6</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10637,7 +10657,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 36840-2024</t>
+          <t>A 37082-2023</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10647,14 +10667,14 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45538</v>
+        <v>45155</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10666,13 +10686,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I121" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10715,7 +10730,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 60913-2023</t>
+          <t>A 7402-2026</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10729,10 +10744,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45261</v>
+        <v>46059</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10745,7 +10760,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>0.7</v>
+        <v>4.7</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10788,7 +10803,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 8084-2022</t>
+          <t>A 55304-2025</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10798,14 +10813,14 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>44608</v>
+        <v>45970</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10818,7 +10833,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>1.5</v>
+        <v>0.4</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10861,7 +10876,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 62277-2025</t>
+          <t>A 55306-2025</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10871,14 +10886,14 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>46006</v>
+        <v>45970</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10891,7 +10906,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>2.4</v>
+        <v>0.3</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10934,7 +10949,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 28625-2023</t>
+          <t>A 54431-2023</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10948,10 +10963,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45103</v>
+        <v>45226</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10964,7 +10979,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>4.8</v>
+        <v>3.2</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -11007,7 +11022,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 5079-2026</t>
+          <t>A 40994-2025</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -11021,10 +11036,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>46049</v>
+        <v>45898</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11037,7 +11052,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>1.3</v>
+        <v>5.6</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -11080,7 +11095,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 826-2026</t>
+          <t>A 28625-2023</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -11094,10 +11109,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>46030</v>
+        <v>45103</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11109,13 +11124,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I127" t="n">
-        <v>0.3</v>
+        <v>4.8</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -11158,7 +11168,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 829-2026</t>
+          <t>A 57269-2025</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -11172,10 +11182,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>46030</v>
+        <v>45979</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11193,7 +11203,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>6.9</v>
+        <v>5.5</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -11236,7 +11246,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 821-2026</t>
+          <t>A 38080-2024</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11250,10 +11260,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>46030</v>
+        <v>45545</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11265,13 +11275,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I129" t="n">
-        <v>4.3</v>
+        <v>0.7</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11314,7 +11319,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 554-2026</t>
+          <t>A 59308-2025</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11328,10 +11333,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>46029</v>
+        <v>45989</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11344,7 +11349,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11387,7 +11392,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 65073-2023</t>
+          <t>A 13633-2024</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11401,10 +11406,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45287</v>
+        <v>45390</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11417,7 +11422,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11460,7 +11465,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 1989-2026</t>
+          <t>A 44816-2023</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11474,10 +11479,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>46035</v>
+        <v>45190</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11490,7 +11495,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11533,7 +11538,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 3013-2026</t>
+          <t>A 28493-2023</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11547,10 +11552,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>46038</v>
+        <v>45103</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11563,7 +11568,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11606,7 +11611,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 13804-2024</t>
+          <t>A 65073-2023</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11620,10 +11625,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45391</v>
+        <v>45287</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11636,7 +11641,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>0.5</v>
+        <v>1.7</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11679,7 +11684,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 5374-2026</t>
+          <t>A 43879-2023</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11693,10 +11698,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>46050</v>
+        <v>45187</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11708,8 +11713,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I135" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11752,7 +11762,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 6886-2024</t>
+          <t>A 5079-2026</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11766,10 +11776,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45342</v>
+        <v>46049</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11781,13 +11791,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H136" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I136" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11830,7 +11835,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 1106-2023</t>
+          <t>A 47609-2023</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11844,10 +11849,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>44935</v>
+        <v>45203</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11860,7 +11865,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>1.2</v>
+        <v>2.4</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11903,7 +11908,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 8310-2026</t>
+          <t>A 43882-2023</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11917,10 +11922,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>46064</v>
+        <v>45187</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11932,8 +11937,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I138" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11976,7 +11986,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 17073-2023</t>
+          <t>A 67426-2021</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11990,10 +12000,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45034</v>
+        <v>44523</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12006,7 +12016,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -12049,7 +12059,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 2979-2024</t>
+          <t>A 3239-2023</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -12063,10 +12073,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45315</v>
+        <v>44946</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12078,13 +12088,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H140" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I140" t="n">
-        <v>4.7</v>
+        <v>0.4</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -12127,7 +12132,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 31596-2023</t>
+          <t>A 60963-2023</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -12141,10 +12146,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45117</v>
+        <v>45261</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12157,7 +12162,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -12200,7 +12205,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 54184-2024</t>
+          <t>A 43685-2022</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -12210,14 +12215,14 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45616</v>
+        <v>44837</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12230,7 +12235,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -12273,7 +12278,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 43932-2023</t>
+          <t>A 55265-2023</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12287,10 +12292,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45187</v>
+        <v>45237</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12303,7 +12308,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>3</v>
+        <v>1.2</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -12346,7 +12351,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 43935-2023</t>
+          <t>A 5163-2024</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12360,10 +12365,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45187</v>
+        <v>45330</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12375,8 +12380,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I144" t="n">
-        <v>2.9</v>
+        <v>7.1</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -12419,7 +12429,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 20403-2024</t>
+          <t>A 18603-2025</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12433,10 +12443,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45435</v>
+        <v>45763</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12449,7 +12459,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12492,7 +12502,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 3040-2024</t>
+          <t>A 4597-2026</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12506,10 +12516,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45316</v>
+        <v>46048</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12522,7 +12532,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>4</v>
+        <v>1.3</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12565,7 +12575,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 44816-2023</t>
+          <t>A 4590-2026</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12579,10 +12589,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45190</v>
+        <v>46048</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12595,7 +12605,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12638,7 +12648,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 47552-2023</t>
+          <t>A 6350-2026</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12652,10 +12662,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45203</v>
+        <v>46051</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12668,7 +12678,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>1.3</v>
+        <v>2.4</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12711,7 +12721,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 4597-2026</t>
+          <t>A 18369-2025</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12725,10 +12735,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>46048</v>
+        <v>45762</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12741,7 +12751,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>1.3</v>
+        <v>2.2</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12784,7 +12794,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 54431-2023</t>
+          <t>A 3177-2026</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12794,14 +12804,14 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45226</v>
+        <v>46041</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12814,7 +12824,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>3.2</v>
+        <v>0.5</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12857,7 +12867,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 19777-2023</t>
+          <t>A 59284-2025</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12871,10 +12881,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45051</v>
+        <v>45988</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12887,7 +12897,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>4.3</v>
+        <v>1.5</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12930,7 +12940,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 43879-2023</t>
+          <t>A 10500-2026</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12944,10 +12954,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45187</v>
+        <v>46076</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12957,11 +12967,6 @@
       <c r="G152" t="inlineStr">
         <is>
           <t>HÖRBY</t>
-        </is>
-      </c>
-      <c r="H152" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I152" t="n">
@@ -13008,7 +13013,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 3471-2025</t>
+          <t>A 10524-2026</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -13022,10 +13027,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45680</v>
+        <v>46076</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13038,7 +13043,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>3.7</v>
+        <v>1.6</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -13081,7 +13086,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 49726-2023</t>
+          <t>A 16518-2026</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -13095,10 +13100,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45208</v>
+        <v>46112</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13111,7 +13116,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -13154,7 +13159,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 28501-2023</t>
+          <t>A 29138-2026</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -13164,14 +13169,14 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45103</v>
+        <v>46202</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13183,8 +13188,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I155" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -13227,7 +13237,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 33873-2024</t>
+          <t>A 3534-2025</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -13241,10 +13251,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45521</v>
+        <v>45680</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13256,8 +13266,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I156" t="n">
-        <v>3.5</v>
+        <v>4.8</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -13300,7 +13315,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 4590-2026</t>
+          <t>A 29124-2026</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -13314,10 +13329,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>46048</v>
+        <v>46202</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13330,7 +13345,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>1.1</v>
+        <v>2.9</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -13373,7 +13388,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 6350-2026</t>
+          <t>A 29135-2026</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -13383,14 +13398,14 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>46051</v>
+        <v>46202</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13402,8 +13417,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I158" t="n">
-        <v>2.4</v>
+        <v>4.7</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -13446,7 +13466,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 18369-2025</t>
+          <t>A 29137-2026</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13456,14 +13476,14 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45762</v>
+        <v>46202</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13475,8 +13495,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I159" t="n">
-        <v>2.2</v>
+        <v>7.8</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -13519,7 +13544,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 58360-2023</t>
+          <t>A 20595-2024</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -13533,10 +13558,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45250</v>
+        <v>45436</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13548,8 +13573,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I160" t="n">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13592,7 +13622,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 39298-2023</t>
+          <t>A 43937-2023</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13606,10 +13636,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45166</v>
+        <v>45187</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13622,7 +13652,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>4.6</v>
+        <v>2.6</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13665,7 +13695,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 29219-2023</t>
+          <t>A 43939-2023</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13679,10 +13709,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45105</v>
+        <v>45187</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13695,7 +13725,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13738,7 +13768,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 3542-2025</t>
+          <t>A 28501-2023</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13752,10 +13782,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>45680</v>
+        <v>45103</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13767,13 +13797,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H163" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I163" t="n">
-        <v>1.4</v>
+        <v>3.6</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13816,7 +13841,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 47637-2023</t>
+          <t>A 28527-2023</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13830,10 +13855,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45203</v>
+        <v>45103</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13846,7 +13871,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>2</v>
+        <v>0.7</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13889,7 +13914,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 3177-2026</t>
+          <t>A 54894-2023</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13899,14 +13924,14 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>46041</v>
+        <v>45236</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13919,7 +13944,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13962,7 +13987,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 24670-2024</t>
+          <t>A 23606-2026</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13976,10 +14001,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45460</v>
+        <v>46162</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13992,7 +14017,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>0.2</v>
+        <v>9.4</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -14035,7 +14060,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 59284-2025</t>
+          <t>A 34737-2026</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -14049,10 +14074,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45988</v>
+        <v>46258</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14065,7 +14090,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -14108,7 +14133,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 6081-2023</t>
+          <t>A 34740-2026</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -14122,10 +14147,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>44959</v>
+        <v>46258</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14138,7 +14163,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>0.4</v>
+        <v>2.1</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -14181,7 +14206,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 31114-2024</t>
+          <t>A 30934-2026</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -14195,10 +14220,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>45502</v>
+        <v>46213</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14211,7 +14236,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -14254,7 +14279,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 11941-2025</t>
+          <t>A 37276-2024</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -14268,10 +14293,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45728</v>
+        <v>45540</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14284,7 +14309,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -14327,7 +14352,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 10524-2026</t>
+          <t>A 55307-2025</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -14341,10 +14366,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>46076</v>
+        <v>45970</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14357,7 +14382,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>1.6</v>
+        <v>2.5</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -14400,7 +14425,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 10500-2026</t>
+          <t>A 31286-2026</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -14414,10 +14439,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>46076</v>
+        <v>46218</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14473,7 +14498,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 38684-2022</t>
+          <t>A 36689-2024</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -14483,14 +14508,14 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>44814</v>
+        <v>45537</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14502,8 +14527,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I173" t="n">
-        <v>2.5</v>
+        <v>9.5</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -14546,7 +14576,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 37757-2024</t>
+          <t>A 57017-2025</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14560,10 +14590,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45541</v>
+        <v>45978</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14576,7 +14606,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>0.7</v>
+        <v>5.5</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14619,7 +14649,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 25183-2023</t>
+          <t>A 31522-2022</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14633,10 +14663,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45079</v>
+        <v>44775</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14649,7 +14679,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14692,7 +14722,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 16518-2026</t>
+          <t>A 54184-2024</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14706,10 +14736,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>46112</v>
+        <v>45616</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14722,7 +14752,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14765,7 +14795,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 44073-2024</t>
+          <t>A 60913-2023</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14779,10 +14809,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45572</v>
+        <v>45261</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14795,7 +14825,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14838,7 +14868,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 37276-2024</t>
+          <t>A 20047-2026</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14852,10 +14882,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45540</v>
+        <v>46136</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14868,7 +14898,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14911,7 +14941,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 20595-2024</t>
+          <t>A 44073-2024</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14925,10 +14955,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>45436</v>
+        <v>45572</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14940,13 +14970,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H179" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I179" t="n">
-        <v>3.5</v>
+        <v>1</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14989,7 +15014,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 29138-2026</t>
+          <t>A 11941-2025</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14999,14 +15024,14 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>46202</v>
+        <v>45728</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15018,13 +15043,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H180" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I180" t="n">
-        <v>4.2</v>
+        <v>0.6</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -15067,7 +15087,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 119-2023</t>
+          <t>A 37300-2026</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -15081,10 +15101,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>44928</v>
+        <v>46274</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15097,7 +15117,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>0.8</v>
+        <v>0.2</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -15140,7 +15160,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 29135-2026</t>
+          <t>A 43380-2022</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -15150,14 +15170,14 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>46202</v>
+        <v>44834</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15169,13 +15189,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H182" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I182" t="n">
-        <v>4.7</v>
+        <v>1.7</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -15218,7 +15233,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 29137-2026</t>
+          <t>A 20403-2024</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -15228,14 +15243,14 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>46202</v>
+        <v>45435</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15247,13 +15262,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H183" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I183" t="n">
-        <v>7.8</v>
+        <v>0.9</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -15296,7 +15306,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 29124-2026</t>
+          <t>A 1106-2023</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -15310,10 +15320,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>46202</v>
+        <v>44935</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15326,7 +15336,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>2.9</v>
+        <v>1.2</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -15369,7 +15379,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 43685-2022</t>
+          <t>A 49726-2023</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -15379,14 +15389,14 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>44837</v>
+        <v>45208</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15442,7 +15452,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 24724-2024</t>
+          <t>A 36840-2024</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -15452,14 +15462,14 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>45460</v>
+        <v>45538</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15471,8 +15481,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I186" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -15515,7 +15530,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 6558-2025</t>
+          <t>A 24724-2024</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -15529,10 +15544,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>45699</v>
+        <v>45460</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15544,13 +15559,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H187" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I187" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -15593,7 +15603,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 2747-2023</t>
+          <t>A 58641-2023</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15603,14 +15613,14 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>44944</v>
+        <v>45251</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15622,13 +15632,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H188" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I188" t="n">
-        <v>4.6</v>
+        <v>1.2</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15671,7 +15676,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 31522-2022</t>
+          <t>A 3040-2024</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15685,10 +15690,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>44775</v>
+        <v>45316</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15701,7 +15706,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>1.8</v>
+        <v>4</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15744,7 +15749,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 55265-2023</t>
+          <t>A 15970-2024</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15758,10 +15763,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>45237</v>
+        <v>45405</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15774,7 +15779,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15817,7 +15822,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 28918-2023</t>
+          <t>A 18735-2023</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15831,10 +15836,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>45104</v>
+        <v>45043</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15847,7 +15852,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15890,7 +15895,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 3239-2023</t>
+          <t>A 6081-2023</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15904,10 +15909,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>44946</v>
+        <v>44959</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15963,7 +15968,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 13228-2024</t>
+          <t>A 29219-2023</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15977,10 +15982,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>45386</v>
+        <v>45105</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16036,7 +16041,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 30934-2026</t>
+          <t>A 56818-2022</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -16050,10 +16055,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>46213</v>
+        <v>44894</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16066,7 +16071,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -16109,7 +16114,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 48427-2022</t>
+          <t>A 34422-2024</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -16119,14 +16124,14 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>44858</v>
+        <v>45525</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16138,13 +16143,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H195" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I195" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -16187,7 +16187,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 34737-2026</t>
+          <t>A 7831-2025</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -16201,10 +16201,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>46258</v>
+        <v>45706</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16217,7 +16217,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -16260,7 +16260,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 34740-2026</t>
+          <t>A 56750-2023</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -16274,10 +16274,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>46258</v>
+        <v>45238</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16290,7 +16290,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>2.1</v>
+        <v>0.8</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -16333,7 +16333,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 4756-2025</t>
+          <t>A 17073-2023</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -16347,10 +16347,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>45688</v>
+        <v>45034</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16363,7 +16363,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -16406,7 +16406,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 33358-2023</t>
+          <t>A 19420-2022</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -16420,10 +16420,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>45128</v>
+        <v>44693</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16436,7 +16436,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -16479,7 +16479,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 23606-2026</t>
+          <t>A 119-2023</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -16489,14 +16489,14 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>46162</v>
+        <v>44928</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16509,7 +16509,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>9.4</v>
+        <v>0.8</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -16552,7 +16552,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 39507-2024</t>
+          <t>A 50715-2024</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -16566,10 +16566,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>45551</v>
+        <v>45602</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16581,13 +16581,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H201" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I201" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -16630,7 +16625,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 31286-2026</t>
+          <t>A 37724-2022</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -16644,10 +16639,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>46218</v>
+        <v>44810</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16660,7 +16655,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16703,7 +16698,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 41940-2022</t>
+          <t>A 37728-2022</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16717,10 +16712,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>44833</v>
+        <v>44810</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16733,7 +16728,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -16776,7 +16771,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 43882-2023</t>
+          <t>A 47637-2023</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -16790,10 +16785,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>45187</v>
+        <v>45203</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16805,13 +16800,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H204" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I204" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16854,7 +16844,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 55307-2025</t>
+          <t>A 33873-2024</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16868,10 +16858,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>45970</v>
+        <v>45521</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16884,7 +16874,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16927,7 +16917,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 28527-2023</t>
+          <t>A 3542-2025</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16941,10 +16931,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>45103</v>
+        <v>45680</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16956,8 +16946,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I206" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -17000,7 +16995,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 19420-2022</t>
+          <t>A 13228-2024</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -17014,10 +17009,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>44693</v>
+        <v>45386</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17073,7 +17068,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 57017-2025</t>
+          <t>A 15998-2024</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -17087,10 +17082,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>45978</v>
+        <v>45405</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17103,7 +17098,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>5.5</v>
+        <v>0.4</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -17146,7 +17141,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 37300-2026</t>
+          <t>A 16001-2024</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -17160,10 +17155,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>46274</v>
+        <v>45405</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17219,7 +17214,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 47641-2023</t>
+          <t>A 31114-2024</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -17233,10 +17228,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>45203</v>
+        <v>45502</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17249,7 +17244,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>4.8</v>
+        <v>0.6</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -17292,7 +17287,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 20047-2026</t>
+          <t>A 13804-2024</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -17306,10 +17301,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>46136</v>
+        <v>45391</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17322,7 +17317,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -17365,7 +17360,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 60963-2023</t>
+          <t>A 19777-2023</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -17379,10 +17374,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>45261</v>
+        <v>45051</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17395,7 +17390,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>1.2</v>
+        <v>4.3</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -17438,7 +17433,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 52310-2023</t>
+          <t>A 28746-2024</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -17452,10 +17447,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>45224</v>
+        <v>45478</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17468,7 +17463,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>3.5</v>
+        <v>1.9</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -17511,7 +17506,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 2170-2025</t>
+          <t>A 6558-2025</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -17521,14 +17516,14 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>45673</v>
+        <v>45699</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17540,8 +17535,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I214" t="n">
-        <v>3.6</v>
+        <v>0.9</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -17584,7 +17584,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 16665-2025</t>
+          <t>A 25183-2023</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -17598,10 +17598,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>45754</v>
+        <v>45079</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17614,7 +17614,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -17657,7 +17657,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 43711-2024</t>
+          <t>A 41940-2022</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -17667,14 +17667,14 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>45569</v>
+        <v>44833</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17687,7 +17687,7 @@
         </is>
       </c>
       <c r="I216" t="n">
-        <v>3.4</v>
+        <v>0.7</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -17730,7 +17730,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 23484-2025</t>
+          <t>A 38684-2022</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -17744,10 +17744,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>45792</v>
+        <v>44814</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17760,7 +17760,7 @@
         </is>
       </c>
       <c r="I217" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -17803,7 +17803,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 28550-2025</t>
+          <t>A 52310-2023</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -17817,10 +17817,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>45818</v>
+        <v>45224</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17833,7 +17833,7 @@
         </is>
       </c>
       <c r="I218" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -17876,7 +17876,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 9612-2025</t>
+          <t>A 2170-2025</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -17890,10 +17890,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>45715</v>
+        <v>45673</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17906,7 +17906,7 @@
         </is>
       </c>
       <c r="I219" t="n">
-        <v>1.2</v>
+        <v>3.6</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -17966,7 +17966,7 @@
         <v>45230</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18039,7 +18039,7 @@
         <v>44796</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18112,7 +18112,7 @@
         <v>45722</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18185,7 +18185,7 @@
         <v>46042</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18241,7 +18241,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>S 220-2026</t>
+          <t>S 1874-2026</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -18255,10 +18255,10 @@
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>46051</v>
+        <v>46202</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18270,8 +18270,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I224" t="n">
-        <v>1.7</v>
+        <v>7.8</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -18314,7 +18319,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>S 1874-2026</t>
+          <t>S 1875-2026</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -18331,7 +18336,7 @@
         <v>46202</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18349,7 +18354,7 @@
         </is>
       </c>
       <c r="I225" t="n">
-        <v>7.8</v>
+        <v>4.2</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -18392,7 +18397,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>S 1875-2026</t>
+          <t>S 1873-2026</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -18409,7 +18414,7 @@
         <v>46202</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18427,7 +18432,7 @@
         </is>
       </c>
       <c r="I226" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -18470,7 +18475,7 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>S 1873-2026</t>
+          <t>S 220-2026</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -18484,10 +18489,10 @@
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>46202</v>
+        <v>46051</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18499,13 +18504,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H227" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I227" t="n">
-        <v>4.7</v>
+        <v>1.7</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>

--- a/Översikt HÖRBY.xlsx
+++ b/Översikt HÖRBY.xlsx
@@ -601,7 +601,7 @@
         <v>44964</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
         <v>44967</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         <v>44727</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -949,7 +949,7 @@
         <v>45786</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1061,7 +1061,7 @@
         <v>46160</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
         <v>45238</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
         <v>44819</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 31351-2022</t>
+          <t>A 16520-2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1394,14 +1394,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>44774</v>
+        <v>46112</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1414,19 +1414,19 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>13.2</v>
+        <v>2.3</v>
       </c>
       <c r="J9" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -1441,18 +1441,131 @@
         <v>3</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
       </c>
       <c r="T9" t="n">
+        <v>6</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Slåttergubbe
+Sydlig sotticka
+Älg
+Fiskgjuse
+Större brunfladdermus</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 16520-2026 artfynd.xlsx", "A 16520-2026")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 16520-2026 karta.png", "A 16520-2026")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 16520-2026 georefererad karta.tif", "A 16520-2026")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 16520-2026 FSC-klagomål.docx", "A 16520-2026")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 16520-2026 FSC-klagomål mail.docx", "A 16520-2026")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 16520-2026 tillsynsbegäran.docx", "A 16520-2026")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 16520-2026 tillsynsbegäran mail.docx", "A 16520-2026")</f>
+        <v/>
+      </c>
+      <c r="AE9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/fåglar/A 16520-2026 prioriterade fågelarter.docx", "A 16520-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 31351-2022</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>44774</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>HÖRBY</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="J10" t="n">
         <v>5</v>
       </c>
-      <c r="U9" t="n">
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
         <v>3</v>
       </c>
-      <c r="V9" s="2" t="inlineStr">
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>3</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="n">
+        <v>5</v>
+      </c>
+      <c r="U10" t="n">
+        <v>3</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Duvhök
 Grönsångare
@@ -1461,149 +1574,36 @@
 Kungsfågel</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 31351-2022 artfynd.xlsx", "A 31351-2022")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 31351-2022 karta.png", "A 31351-2022")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 31351-2022 georefererad karta.tif", "A 31351-2022")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 31351-2022 FSC-klagomål.docx", "A 31351-2022")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 31351-2022 FSC-klagomål mail.docx", "A 31351-2022")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 31351-2022 tillsynsbegäran.docx", "A 31351-2022")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 31351-2022 tillsynsbegäran mail.docx", "A 31351-2022")</f>
         <v/>
       </c>
-      <c r="AE9">
+      <c r="AE10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/fåglar/A 31351-2022 prioriterade fågelarter.docx", "A 31351-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 16520-2026</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>46112</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>HÖRBY</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="J10" t="n">
-        <v>2</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>2</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>3</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1</v>
-      </c>
-      <c r="S10" t="n">
-        <v>5</v>
-      </c>
-      <c r="T10" t="n">
-        <v>6</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Slåttergubbe
-Sydlig sotticka
-Älg
-Fiskgjuse
-Större brunfladdermus</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 16520-2026 artfynd.xlsx", "A 16520-2026")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 16520-2026 karta.png", "A 16520-2026")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 16520-2026 georefererad karta.tif", "A 16520-2026")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 16520-2026 FSC-klagomål.docx", "A 16520-2026")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 16520-2026 FSC-klagomål mail.docx", "A 16520-2026")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 16520-2026 tillsynsbegäran.docx", "A 16520-2026")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 16520-2026 tillsynsbegäran mail.docx", "A 16520-2026")</f>
-        <v/>
-      </c>
-      <c r="AE10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/fåglar/A 16520-2026 prioriterade fågelarter.docx", "A 16520-2026")</f>
         <v/>
       </c>
     </row>
@@ -1627,7 +1627,7 @@
         <v>45434</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1736,7 +1736,7 @@
         <v>46150</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         <v>45545</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1952,7 +1952,7 @@
         <v>45334</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2043,7 +2043,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 20193-2024</t>
+          <t>A 2823-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2053,14 +2053,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45434</v>
+        <v>45677</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2073,13 +2073,13 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>11.2</v>
+        <v>21.1</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>1</v>
@@ -2106,479 +2106,479 @@
         <v>3</v>
       </c>
       <c r="T15" t="n">
+        <v>4</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>Borsttåg
+Grönvit nattviol
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 2823-2025 artfynd.xlsx", "A 2823-2025")</f>
+        <v/>
+      </c>
+      <c r="X15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 2823-2025 karta.png", "A 2823-2025")</f>
+        <v/>
+      </c>
+      <c r="Y15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 2823-2025 georefererad karta.tif", "A 2823-2025")</f>
+        <v/>
+      </c>
+      <c r="AA15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 2823-2025 FSC-klagomål.docx", "A 2823-2025")</f>
+        <v/>
+      </c>
+      <c r="AB15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 2823-2025 FSC-klagomål mail.docx", "A 2823-2025")</f>
+        <v/>
+      </c>
+      <c r="AC15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 2823-2025 tillsynsbegäran.docx", "A 2823-2025")</f>
+        <v/>
+      </c>
+      <c r="AD15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 2823-2025 tillsynsbegäran mail.docx", "A 2823-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 20193-2024</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>45434</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>HÖRBY</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
         <v>3</v>
       </c>
-      <c r="U15" t="n">
+      <c r="T16" t="n">
+        <v>3</v>
+      </c>
+      <c r="U16" t="n">
         <v>1</v>
       </c>
-      <c r="V15" s="2" t="inlineStr">
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>Vårärt
 Strutbräken
 Vätteros</t>
         </is>
       </c>
-      <c r="W15">
+      <c r="W16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 20193-2024 artfynd.xlsx", "A 20193-2024")</f>
         <v/>
       </c>
-      <c r="X15">
+      <c r="X16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 20193-2024 karta.png", "A 20193-2024")</f>
         <v/>
       </c>
-      <c r="Y15">
+      <c r="Y16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 20193-2024 georefererad karta.tif", "A 20193-2024")</f>
         <v/>
       </c>
-      <c r="AA15">
+      <c r="AA16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 20193-2024 FSC-klagomål.docx", "A 20193-2024")</f>
         <v/>
       </c>
-      <c r="AB15">
+      <c r="AB16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 20193-2024 FSC-klagomål mail.docx", "A 20193-2024")</f>
         <v/>
       </c>
-      <c r="AC15">
+      <c r="AC16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 20193-2024 tillsynsbegäran.docx", "A 20193-2024")</f>
         <v/>
       </c>
-      <c r="AD15">
+      <c r="AD16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 20193-2024 tillsynsbegäran mail.docx", "A 20193-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 27738-2025</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>45815</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>HÖRBY</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L17" t="n">
+        <v>2</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>Bokvårtlav
+Sydlig sotticka
+Västlig hakmossa</t>
+        </is>
+      </c>
+      <c r="W17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 27738-2025 artfynd.xlsx", "A 27738-2025")</f>
+        <v/>
+      </c>
+      <c r="X17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 27738-2025 karta.png", "A 27738-2025")</f>
+        <v/>
+      </c>
+      <c r="Y17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 27738-2025 georefererad karta.tif", "A 27738-2025")</f>
+        <v/>
+      </c>
+      <c r="AA17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 27738-2025 FSC-klagomål.docx", "A 27738-2025")</f>
+        <v/>
+      </c>
+      <c r="AB17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 27738-2025 FSC-klagomål mail.docx", "A 27738-2025")</f>
+        <v/>
+      </c>
+      <c r="AC17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 27738-2025 tillsynsbegäran.docx", "A 27738-2025")</f>
+        <v/>
+      </c>
+      <c r="AD17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 27738-2025 tillsynsbegäran mail.docx", "A 27738-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>A 24801-2025</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>45799</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>HÖRBY</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1</v>
+      </c>
+      <c r="N18" t="n">
+        <v>1</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2</v>
+      </c>
+      <c r="R18" t="n">
+        <v>2</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3</v>
+      </c>
+      <c r="T18" t="n">
+        <v>5</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Småvänderot
+Platt fjädermossa</t>
+        </is>
+      </c>
+      <c r="W18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 24801-2025 artfynd.xlsx", "A 24801-2025")</f>
+        <v/>
+      </c>
+      <c r="X18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 24801-2025 karta.png", "A 24801-2025")</f>
+        <v/>
+      </c>
+      <c r="Y18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 24801-2025 georefererad karta.tif", "A 24801-2025")</f>
+        <v/>
+      </c>
+      <c r="AA18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 24801-2025 FSC-klagomål.docx", "A 24801-2025")</f>
+        <v/>
+      </c>
+      <c r="AB18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 24801-2025 FSC-klagomål mail.docx", "A 24801-2025")</f>
+        <v/>
+      </c>
+      <c r="AC18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 24801-2025 tillsynsbegäran.docx", "A 24801-2025")</f>
+        <v/>
+      </c>
+      <c r="AD18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 24801-2025 tillsynsbegäran mail.docx", "A 24801-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
         <is>
           <t>A 24158-2022</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D16" s="1" t="n">
+      <c r="D19" s="1" t="n">
         <v>44725</v>
       </c>
-      <c r="E16" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>HÖRBY</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
+      <c r="E19" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>HÖRBY</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
         <v>3.1</v>
       </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
         <v>2</v>
       </c>
-      <c r="M16" t="n">
+      <c r="M19" t="n">
         <v>1</v>
       </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
         <v>3</v>
       </c>
-      <c r="R16" t="n">
+      <c r="R19" t="n">
         <v>1</v>
       </c>
-      <c r="S16" t="n">
+      <c r="S19" t="n">
         <v>3</v>
       </c>
-      <c r="T16" t="n">
+      <c r="T19" t="n">
         <v>5</v>
       </c>
-      <c r="U16" t="n">
+      <c r="U19" t="n">
         <v>3</v>
       </c>
-      <c r="V16" s="2" t="inlineStr">
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>Slåttergubbe
 Borsttåg
 Sotnätfjäril</t>
         </is>
       </c>
-      <c r="W16">
+      <c r="W19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 24158-2022 artfynd.xlsx", "A 24158-2022")</f>
         <v/>
       </c>
-      <c r="X16">
+      <c r="X19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 24158-2022 karta.png", "A 24158-2022")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Y19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 24158-2022 georefererad karta.tif", "A 24158-2022")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AA19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 24158-2022 FSC-klagomål.docx", "A 24158-2022")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AB19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 24158-2022 FSC-klagomål mail.docx", "A 24158-2022")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AC19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 24158-2022 tillsynsbegäran.docx", "A 24158-2022")</f>
         <v/>
       </c>
-      <c r="AD16">
+      <c r="AD19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 24158-2022 tillsynsbegäran mail.docx", "A 24158-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 27738-2025</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>45815</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>HÖRBY</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>1</v>
-      </c>
-      <c r="L17" t="n">
-        <v>2</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>2</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>3</v>
-      </c>
-      <c r="T17" t="n">
-        <v>3</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Bokvårtlav
-Sydlig sotticka
-Västlig hakmossa</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 27738-2025 artfynd.xlsx", "A 27738-2025")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 27738-2025 karta.png", "A 27738-2025")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 27738-2025 georefererad karta.tif", "A 27738-2025")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 27738-2025 FSC-klagomål.docx", "A 27738-2025")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 27738-2025 FSC-klagomål mail.docx", "A 27738-2025")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 27738-2025 tillsynsbegäran.docx", "A 27738-2025")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 27738-2025 tillsynsbegäran mail.docx", "A 27738-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>A 24801-2025</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>45799</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>HÖRBY</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>1</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>1</v>
-      </c>
-      <c r="N18" t="n">
-        <v>1</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>2</v>
-      </c>
-      <c r="R18" t="n">
-        <v>2</v>
-      </c>
-      <c r="S18" t="n">
-        <v>3</v>
-      </c>
-      <c r="T18" t="n">
-        <v>5</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Småvänderot
-Platt fjädermossa</t>
-        </is>
-      </c>
-      <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 24801-2025 artfynd.xlsx", "A 24801-2025")</f>
-        <v/>
-      </c>
-      <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 24801-2025 karta.png", "A 24801-2025")</f>
-        <v/>
-      </c>
-      <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 24801-2025 georefererad karta.tif", "A 24801-2025")</f>
-        <v/>
-      </c>
-      <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 24801-2025 FSC-klagomål.docx", "A 24801-2025")</f>
-        <v/>
-      </c>
-      <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 24801-2025 FSC-klagomål mail.docx", "A 24801-2025")</f>
-        <v/>
-      </c>
-      <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 24801-2025 tillsynsbegäran.docx", "A 24801-2025")</f>
-        <v/>
-      </c>
-      <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 24801-2025 tillsynsbegäran mail.docx", "A 24801-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>A 2823-2025</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="n">
-        <v>45677</v>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>HÖRBY</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>21.1</v>
-      </c>
-      <c r="J19" t="n">
-        <v>2</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>1</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>1</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>3</v>
-      </c>
-      <c r="T19" t="n">
-        <v>4</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>Borsttåg
-Grönvit nattviol
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 2823-2025 artfynd.xlsx", "A 2823-2025")</f>
-        <v/>
-      </c>
-      <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 2823-2025 karta.png", "A 2823-2025")</f>
-        <v/>
-      </c>
-      <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 2823-2025 georefererad karta.tif", "A 2823-2025")</f>
-        <v/>
-      </c>
-      <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 2823-2025 FSC-klagomål.docx", "A 2823-2025")</f>
-        <v/>
-      </c>
-      <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 2823-2025 FSC-klagomål mail.docx", "A 2823-2025")</f>
-        <v/>
-      </c>
-      <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 2823-2025 tillsynsbegäran.docx", "A 2823-2025")</f>
-        <v/>
-      </c>
-      <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 2823-2025 tillsynsbegäran mail.docx", "A 2823-2025")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 44135-2024</t>
+          <t>A 824-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2592,10 +2592,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45572</v>
+        <v>46030</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2607,11 +2607,16 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I20" t="n">
-        <v>0.6</v>
+        <v>3.1</v>
       </c>
       <c r="J20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -2620,7 +2625,7 @@
         <v>1</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -2632,163 +2637,158 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
+        <v>2</v>
+      </c>
+      <c r="R20" t="n">
         <v>1</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>2</v>
       </c>
       <c r="T20" t="n">
+        <v>3</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>Hedblomster
+Skogslysing</t>
+        </is>
+      </c>
+      <c r="W20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 824-2026 artfynd.xlsx", "A 824-2026")</f>
+        <v/>
+      </c>
+      <c r="X20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 824-2026 karta.png", "A 824-2026")</f>
+        <v/>
+      </c>
+      <c r="Y20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 824-2026 georefererad karta.tif", "A 824-2026")</f>
+        <v/>
+      </c>
+      <c r="AA20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 824-2026 FSC-klagomål.docx", "A 824-2026")</f>
+        <v/>
+      </c>
+      <c r="AB20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 824-2026 FSC-klagomål mail.docx", "A 824-2026")</f>
+        <v/>
+      </c>
+      <c r="AC20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 824-2026 tillsynsbegäran.docx", "A 824-2026")</f>
+        <v/>
+      </c>
+      <c r="AD20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 824-2026 tillsynsbegäran mail.docx", "A 824-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>A 44135-2024</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="n">
+        <v>45572</v>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>HÖRBY</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J21" t="n">
         <v>2</v>
       </c>
-      <c r="U20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
         <is>
           <t>Ladusvala
 Vanlig padda</t>
         </is>
       </c>
-      <c r="W20">
+      <c r="W21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 44135-2024 artfynd.xlsx", "A 44135-2024")</f>
         <v/>
       </c>
-      <c r="X20">
+      <c r="X21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 44135-2024 karta.png", "A 44135-2024")</f>
         <v/>
       </c>
-      <c r="Y20">
+      <c r="Y21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 44135-2024 georefererad karta.tif", "A 44135-2024")</f>
         <v/>
       </c>
-      <c r="AA20">
+      <c r="AA21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 44135-2024 FSC-klagomål.docx", "A 44135-2024")</f>
         <v/>
       </c>
-      <c r="AB20">
+      <c r="AB21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 44135-2024 FSC-klagomål mail.docx", "A 44135-2024")</f>
         <v/>
       </c>
-      <c r="AC20">
+      <c r="AC21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 44135-2024 tillsynsbegäran.docx", "A 44135-2024")</f>
         <v/>
       </c>
-      <c r="AD20">
+      <c r="AD21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 44135-2024 tillsynsbegäran mail.docx", "A 44135-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>A 824-2026</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D21" s="1" t="n">
-        <v>46030</v>
-      </c>
-      <c r="E21" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>HÖRBY</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="J21" t="n">
-        <v>1</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>1</v>
-      </c>
-      <c r="M21" t="n">
-        <v>1</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>2</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1</v>
-      </c>
-      <c r="S21" t="n">
-        <v>2</v>
-      </c>
-      <c r="T21" t="n">
-        <v>3</v>
-      </c>
-      <c r="U21" t="n">
-        <v>0</v>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>Hedblomster
-Skogslysing</t>
-        </is>
-      </c>
-      <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 824-2026 artfynd.xlsx", "A 824-2026")</f>
-        <v/>
-      </c>
-      <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 824-2026 karta.png", "A 824-2026")</f>
-        <v/>
-      </c>
-      <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 824-2026 georefererad karta.tif", "A 824-2026")</f>
-        <v/>
-      </c>
-      <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 824-2026 FSC-klagomål.docx", "A 824-2026")</f>
-        <v/>
-      </c>
-      <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 824-2026 FSC-klagomål mail.docx", "A 824-2026")</f>
-        <v/>
-      </c>
-      <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 824-2026 tillsynsbegäran.docx", "A 824-2026")</f>
-        <v/>
-      </c>
-      <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 824-2026 tillsynsbegäran mail.docx", "A 824-2026")</f>
         <v/>
       </c>
     </row>
@@ -2812,7 +2812,7 @@
         <v>45176</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2918,7 +2918,7 @@
         <v>45317</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3007,7 +3007,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 47612-2023</t>
+          <t>A 31115-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45203</v>
+        <v>45502</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3037,7 +3037,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2.4</v>
+        <v>0.8</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -3046,13 +3046,13 @@
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3064,7 +3064,7 @@
         <v>1</v>
       </c>
       <c r="R24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3077,42 +3077,42 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 47612-2023 artfynd.xlsx", "A 47612-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 31115-2024 artfynd.xlsx", "A 31115-2024")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 47612-2023 karta.png", "A 47612-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 31115-2024 karta.png", "A 31115-2024")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 47612-2023 georefererad karta.tif", "A 47612-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 31115-2024 georefererad karta.tif", "A 31115-2024")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 47612-2023 FSC-klagomål.docx", "A 47612-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 31115-2024 FSC-klagomål.docx", "A 31115-2024")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 47612-2023 FSC-klagomål mail.docx", "A 47612-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 31115-2024 FSC-klagomål mail.docx", "A 31115-2024")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 47612-2023 tillsynsbegäran.docx", "A 47612-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 31115-2024 tillsynsbegäran.docx", "A 31115-2024")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 47612-2023 tillsynsbegäran mail.docx", "A 47612-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 31115-2024 tillsynsbegäran mail.docx", "A 31115-2024")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 24823-2026</t>
+          <t>A 25479-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3122,14 +3122,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46174</v>
+        <v>45802</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3141,19 +3141,14 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I25" t="n">
-        <v>5.1</v>
+        <v>0.7</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
@@ -3183,46 +3178,46 @@
         <v>1</v>
       </c>
       <c r="U25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Tandrot</t>
+          <t>Lundvårlök</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 24823-2026 artfynd.xlsx", "A 24823-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 25479-2025 artfynd.xlsx", "A 25479-2025")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 24823-2026 karta.png", "A 24823-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 25479-2025 karta.png", "A 25479-2025")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 24823-2026 georefererad karta.tif", "A 24823-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 25479-2025 georefererad karta.tif", "A 25479-2025")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 24823-2026 FSC-klagomål.docx", "A 24823-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 25479-2025 FSC-klagomål.docx", "A 25479-2025")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 24823-2026 FSC-klagomål mail.docx", "A 24823-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 25479-2025 FSC-klagomål mail.docx", "A 25479-2025")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 24823-2026 tillsynsbegäran.docx", "A 24823-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 25479-2025 tillsynsbegäran.docx", "A 25479-2025")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 24823-2026 tillsynsbegäran mail.docx", "A 24823-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 25479-2025 tillsynsbegäran mail.docx", "A 25479-2025")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 113-2023</t>
+          <t>A 36362-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3236,10 +3231,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44928</v>
+        <v>45868</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3252,19 +3247,19 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>5.1</v>
+        <v>3.7</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
         <v>0</v>
@@ -3276,10 +3271,10 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>
@@ -3288,46 +3283,46 @@
         <v>1</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Slåttergubbe</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 113-2023 artfynd.xlsx", "A 113-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 36362-2025 artfynd.xlsx", "A 36362-2025")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 113-2023 karta.png", "A 113-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 36362-2025 karta.png", "A 36362-2025")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 113-2023 georefererad karta.tif", "A 113-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 36362-2025 georefererad karta.tif", "A 36362-2025")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 113-2023 FSC-klagomål.docx", "A 113-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 36362-2025 FSC-klagomål.docx", "A 36362-2025")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 113-2023 FSC-klagomål mail.docx", "A 113-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 36362-2025 FSC-klagomål mail.docx", "A 36362-2025")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 113-2023 tillsynsbegäran.docx", "A 113-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 36362-2025 tillsynsbegäran.docx", "A 36362-2025")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 113-2023 tillsynsbegäran mail.docx", "A 113-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 36362-2025 tillsynsbegäran mail.docx", "A 36362-2025")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 16519-2026</t>
+          <t>A 47612-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3341,10 +3336,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46112</v>
+        <v>45203</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3357,7 +3352,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.8</v>
+        <v>2.4</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3401,38 +3396,38 @@
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 16519-2026 artfynd.xlsx", "A 16519-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 47612-2023 artfynd.xlsx", "A 47612-2023")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 16519-2026 karta.png", "A 16519-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 47612-2023 karta.png", "A 47612-2023")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 16519-2026 georefererad karta.tif", "A 16519-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 47612-2023 georefererad karta.tif", "A 47612-2023")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 16519-2026 FSC-klagomål.docx", "A 16519-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 47612-2023 FSC-klagomål.docx", "A 47612-2023")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 16519-2026 FSC-klagomål mail.docx", "A 16519-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 47612-2023 FSC-klagomål mail.docx", "A 47612-2023")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 16519-2026 tillsynsbegäran.docx", "A 16519-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 47612-2023 tillsynsbegäran.docx", "A 47612-2023")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 16519-2026 tillsynsbegäran mail.docx", "A 16519-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 47612-2023 tillsynsbegäran mail.docx", "A 47612-2023")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 25833-2024</t>
+          <t>A 40376-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3446,10 +3441,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45463</v>
+        <v>45169</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3462,19 +3457,19 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.4</v>
+        <v>2.7</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
         <v>0</v>
@@ -3489,55 +3484,59 @@
         <v>1</v>
       </c>
       <c r="R28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
       </c>
       <c r="T28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U28" t="n">
         <v>0</v>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Slåttergubbe</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 25833-2024 artfynd.xlsx", "A 25833-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 40376-2023 artfynd.xlsx", "A 40376-2023")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 25833-2024 karta.png", "A 25833-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 40376-2023 karta.png", "A 40376-2023")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 25833-2024 georefererad karta.tif", "A 25833-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 40376-2023 georefererad karta.tif", "A 40376-2023")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 25833-2024 FSC-klagomål.docx", "A 25833-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 40376-2023 FSC-klagomål.docx", "A 40376-2023")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 25833-2024 FSC-klagomål mail.docx", "A 25833-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 40376-2023 FSC-klagomål mail.docx", "A 40376-2023")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 25833-2024 tillsynsbegäran.docx", "A 25833-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 40376-2023 tillsynsbegäran.docx", "A 40376-2023")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 25833-2024 tillsynsbegäran mail.docx", "A 25833-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 40376-2023 tillsynsbegäran mail.docx", "A 40376-2023")</f>
+        <v/>
+      </c>
+      <c r="AE28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/fåglar/A 40376-2023 prioriterade fågelarter.docx", "A 40376-2023")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 40376-2023</t>
+          <t>A 113-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3551,10 +3550,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45169</v>
+        <v>44928</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3567,19 +3566,19 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2.7</v>
+        <v>5.1</v>
       </c>
       <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
         <v>1</v>
-      </c>
-      <c r="K29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" t="n">
-        <v>1</v>
-      </c>
-      <c r="M29" t="n">
-        <v>0</v>
       </c>
       <c r="N29" t="n">
         <v>0</v>
@@ -3594,7 +3593,7 @@
         <v>1</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
@@ -3607,46 +3606,42 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Slåttergubbe</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 40376-2023 artfynd.xlsx", "A 40376-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 113-2023 artfynd.xlsx", "A 113-2023")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 40376-2023 karta.png", "A 40376-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 113-2023 karta.png", "A 113-2023")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 40376-2023 georefererad karta.tif", "A 40376-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 113-2023 georefererad karta.tif", "A 113-2023")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 40376-2023 FSC-klagomål.docx", "A 40376-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 113-2023 FSC-klagomål.docx", "A 113-2023")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 40376-2023 FSC-klagomål mail.docx", "A 40376-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 113-2023 FSC-klagomål mail.docx", "A 113-2023")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 40376-2023 tillsynsbegäran.docx", "A 40376-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 113-2023 tillsynsbegäran.docx", "A 113-2023")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 40376-2023 tillsynsbegäran mail.docx", "A 40376-2023")</f>
-        <v/>
-      </c>
-      <c r="AE29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/fåglar/A 40376-2023 prioriterade fågelarter.docx", "A 40376-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 113-2023 tillsynsbegäran mail.docx", "A 113-2023")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 31115-2024</t>
+          <t>A 25833-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3660,10 +3655,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45502</v>
+        <v>45463</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3676,7 +3671,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3685,10 +3680,10 @@
         <v>0</v>
       </c>
       <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
         <v>1</v>
-      </c>
-      <c r="M30" t="n">
-        <v>0</v>
       </c>
       <c r="N30" t="n">
         <v>0</v>
@@ -3703,55 +3698,55 @@
         <v>1</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S30" t="n">
         <v>1</v>
       </c>
       <c r="T30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U30" t="n">
         <v>0</v>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>Gullpudra</t>
+          <t>Slåttergubbe</t>
         </is>
       </c>
       <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 31115-2024 artfynd.xlsx", "A 31115-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 25833-2024 artfynd.xlsx", "A 25833-2024")</f>
         <v/>
       </c>
       <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 31115-2024 karta.png", "A 31115-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 25833-2024 karta.png", "A 25833-2024")</f>
         <v/>
       </c>
       <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 31115-2024 georefererad karta.tif", "A 31115-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 25833-2024 georefererad karta.tif", "A 25833-2024")</f>
         <v/>
       </c>
       <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 31115-2024 FSC-klagomål.docx", "A 31115-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 25833-2024 FSC-klagomål.docx", "A 25833-2024")</f>
         <v/>
       </c>
       <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 31115-2024 FSC-klagomål mail.docx", "A 31115-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 25833-2024 FSC-klagomål mail.docx", "A 25833-2024")</f>
         <v/>
       </c>
       <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 31115-2024 tillsynsbegäran.docx", "A 31115-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 25833-2024 tillsynsbegäran.docx", "A 25833-2024")</f>
         <v/>
       </c>
       <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 31115-2024 tillsynsbegäran mail.docx", "A 31115-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 25833-2024 tillsynsbegäran mail.docx", "A 25833-2024")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 31284-2026</t>
+          <t>A 24823-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3765,10 +3760,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46218</v>
+        <v>46174</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3780,11 +3775,16 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I31" t="n">
-        <v>6.8</v>
+        <v>5.1</v>
       </c>
       <c r="J31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
@@ -3817,46 +3817,46 @@
         <v>1</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Tandrot</t>
         </is>
       </c>
       <c r="W31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 31284-2026 artfynd.xlsx", "A 31284-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 24823-2026 artfynd.xlsx", "A 24823-2026")</f>
         <v/>
       </c>
       <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 31284-2026 karta.png", "A 31284-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 24823-2026 karta.png", "A 24823-2026")</f>
         <v/>
       </c>
       <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 31284-2026 georefererad karta.tif", "A 31284-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 24823-2026 georefererad karta.tif", "A 24823-2026")</f>
         <v/>
       </c>
       <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 31284-2026 FSC-klagomål.docx", "A 31284-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 24823-2026 FSC-klagomål.docx", "A 24823-2026")</f>
         <v/>
       </c>
       <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 31284-2026 FSC-klagomål mail.docx", "A 31284-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 24823-2026 FSC-klagomål mail.docx", "A 24823-2026")</f>
         <v/>
       </c>
       <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 31284-2026 tillsynsbegäran.docx", "A 31284-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 24823-2026 tillsynsbegäran.docx", "A 24823-2026")</f>
         <v/>
       </c>
       <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 31284-2026 tillsynsbegäran mail.docx", "A 31284-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 24823-2026 tillsynsbegäran mail.docx", "A 24823-2026")</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 30165-2026</t>
+          <t>A 16519-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3870,10 +3870,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46206</v>
+        <v>46112</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3886,7 +3886,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3930,38 +3930,38 @@
         </is>
       </c>
       <c r="W32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 30165-2026 artfynd.xlsx", "A 30165-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 16519-2026 artfynd.xlsx", "A 16519-2026")</f>
         <v/>
       </c>
       <c r="X32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 30165-2026 karta.png", "A 30165-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 16519-2026 karta.png", "A 16519-2026")</f>
         <v/>
       </c>
       <c r="Y32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 30165-2026 georefererad karta.tif", "A 30165-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 16519-2026 georefererad karta.tif", "A 16519-2026")</f>
         <v/>
       </c>
       <c r="AA32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 30165-2026 FSC-klagomål.docx", "A 30165-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 16519-2026 FSC-klagomål.docx", "A 16519-2026")</f>
         <v/>
       </c>
       <c r="AB32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 30165-2026 FSC-klagomål mail.docx", "A 30165-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 16519-2026 FSC-klagomål mail.docx", "A 16519-2026")</f>
         <v/>
       </c>
       <c r="AC32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 30165-2026 tillsynsbegäran.docx", "A 30165-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 16519-2026 tillsynsbegäran.docx", "A 16519-2026")</f>
         <v/>
       </c>
       <c r="AD32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 30165-2026 tillsynsbegäran mail.docx", "A 30165-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 16519-2026 tillsynsbegäran mail.docx", "A 16519-2026")</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 21713-2025</t>
+          <t>A 31284-2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45783</v>
+        <v>46218</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3991,7 +3991,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.8</v>
+        <v>6.8</v>
       </c>
       <c r="J33" t="n">
         <v>1</v>
@@ -4031,42 +4031,42 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="W33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 21713-2025 artfynd.xlsx", "A 21713-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 31284-2026 artfynd.xlsx", "A 31284-2026")</f>
         <v/>
       </c>
       <c r="X33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 21713-2025 karta.png", "A 21713-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 31284-2026 karta.png", "A 31284-2026")</f>
         <v/>
       </c>
       <c r="Y33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 21713-2025 georefererad karta.tif", "A 21713-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 31284-2026 georefererad karta.tif", "A 31284-2026")</f>
         <v/>
       </c>
       <c r="AA33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 21713-2025 FSC-klagomål.docx", "A 21713-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 31284-2026 FSC-klagomål.docx", "A 31284-2026")</f>
         <v/>
       </c>
       <c r="AB33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 21713-2025 FSC-klagomål mail.docx", "A 21713-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 31284-2026 FSC-klagomål mail.docx", "A 31284-2026")</f>
         <v/>
       </c>
       <c r="AC33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 21713-2025 tillsynsbegäran.docx", "A 21713-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 31284-2026 tillsynsbegäran.docx", "A 31284-2026")</f>
         <v/>
       </c>
       <c r="AD33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 21713-2025 tillsynsbegäran mail.docx", "A 21713-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 31284-2026 tillsynsbegäran mail.docx", "A 31284-2026")</f>
         <v/>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 29129-2026</t>
+          <t>A 30165-2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4080,10 +4080,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>46202</v>
+        <v>46206</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4095,13 +4095,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I34" t="n">
-        <v>10.5</v>
+        <v>1.4</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -4110,13 +4105,13 @@
         <v>0</v>
       </c>
       <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="n">
         <v>1</v>
-      </c>
-      <c r="M34" t="n">
-        <v>0</v>
-      </c>
-      <c r="N34" t="n">
-        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4128,7 +4123,7 @@
         <v>1</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S34" t="n">
         <v>1</v>
@@ -4141,42 +4136,42 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>Ekticka</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="W34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 29129-2026 artfynd.xlsx", "A 29129-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 30165-2026 artfynd.xlsx", "A 30165-2026")</f>
         <v/>
       </c>
       <c r="X34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 29129-2026 karta.png", "A 29129-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 30165-2026 karta.png", "A 30165-2026")</f>
         <v/>
       </c>
       <c r="Y34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 29129-2026 georefererad karta.tif", "A 29129-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 30165-2026 georefererad karta.tif", "A 30165-2026")</f>
         <v/>
       </c>
       <c r="AA34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 29129-2026 FSC-klagomål.docx", "A 29129-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 30165-2026 FSC-klagomål.docx", "A 30165-2026")</f>
         <v/>
       </c>
       <c r="AB34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 29129-2026 FSC-klagomål mail.docx", "A 29129-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 30165-2026 FSC-klagomål mail.docx", "A 30165-2026")</f>
         <v/>
       </c>
       <c r="AC34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 29129-2026 tillsynsbegäran.docx", "A 29129-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 30165-2026 tillsynsbegäran.docx", "A 30165-2026")</f>
         <v/>
       </c>
       <c r="AD34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 29129-2026 tillsynsbegäran mail.docx", "A 29129-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 30165-2026 tillsynsbegäran mail.docx", "A 30165-2026")</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 25479-2025</t>
+          <t>A 29129-2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4186,14 +4181,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45802</v>
+        <v>46202</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4205,18 +4200,23 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I35" t="n">
-        <v>0.7</v>
+        <v>10.5</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="n">
         <v>1</v>
       </c>
-      <c r="L35" t="n">
-        <v>0</v>
-      </c>
       <c r="M35" t="n">
         <v>0</v>
       </c>
@@ -4230,7 +4230,7 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -4246,42 +4246,42 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>Lundvårlök</t>
+          <t>Ekticka</t>
         </is>
       </c>
       <c r="W35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 25479-2025 artfynd.xlsx", "A 25479-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 29129-2026 artfynd.xlsx", "A 29129-2026")</f>
         <v/>
       </c>
       <c r="X35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 25479-2025 karta.png", "A 25479-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 29129-2026 karta.png", "A 29129-2026")</f>
         <v/>
       </c>
       <c r="Y35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 25479-2025 georefererad karta.tif", "A 25479-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 29129-2026 georefererad karta.tif", "A 29129-2026")</f>
         <v/>
       </c>
       <c r="AA35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 25479-2025 FSC-klagomål.docx", "A 25479-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 29129-2026 FSC-klagomål.docx", "A 29129-2026")</f>
         <v/>
       </c>
       <c r="AB35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 25479-2025 FSC-klagomål mail.docx", "A 25479-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 29129-2026 FSC-klagomål mail.docx", "A 29129-2026")</f>
         <v/>
       </c>
       <c r="AC35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 25479-2025 tillsynsbegäran.docx", "A 25479-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 29129-2026 tillsynsbegäran.docx", "A 29129-2026")</f>
         <v/>
       </c>
       <c r="AD35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 25479-2025 tillsynsbegäran mail.docx", "A 25479-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 29129-2026 tillsynsbegäran mail.docx", "A 29129-2026")</f>
         <v/>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 36362-2025</t>
+          <t>A 21713-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4295,10 +4295,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45868</v>
+        <v>45783</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4311,13 +4311,13 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>3.7</v>
+        <v>0.8</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
@@ -4347,39 +4347,39 @@
         <v>1</v>
       </c>
       <c r="U36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="W36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 36362-2025 artfynd.xlsx", "A 36362-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 21713-2025 artfynd.xlsx", "A 21713-2025")</f>
         <v/>
       </c>
       <c r="X36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 36362-2025 karta.png", "A 36362-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 21713-2025 karta.png", "A 21713-2025")</f>
         <v/>
       </c>
       <c r="Y36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 36362-2025 georefererad karta.tif", "A 36362-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 21713-2025 georefererad karta.tif", "A 21713-2025")</f>
         <v/>
       </c>
       <c r="AA36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 36362-2025 FSC-klagomål.docx", "A 36362-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 21713-2025 FSC-klagomål.docx", "A 21713-2025")</f>
         <v/>
       </c>
       <c r="AB36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 36362-2025 FSC-klagomål mail.docx", "A 36362-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 21713-2025 FSC-klagomål mail.docx", "A 21713-2025")</f>
         <v/>
       </c>
       <c r="AC36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 36362-2025 tillsynsbegäran.docx", "A 36362-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 21713-2025 tillsynsbegäran.docx", "A 21713-2025")</f>
         <v/>
       </c>
       <c r="AD36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 36362-2025 tillsynsbegäran mail.docx", "A 36362-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 21713-2025 tillsynsbegäran mail.docx", "A 21713-2025")</f>
         <v/>
       </c>
     </row>
@@ -4403,7 +4403,7 @@
         <v>45089</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4508,7 +4508,7 @@
         <v>44999</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4613,7 +4613,7 @@
         <v>44509</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4686,7 +4686,7 @@
         <v>44663</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4759,7 +4759,7 @@
         <v>44509</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4832,7 +4832,7 @@
         <v>44697</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4905,7 +4905,7 @@
         <v>44510</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4978,7 +4978,7 @@
         <v>44834</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5051,7 +5051,7 @@
         <v>44771</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5124,7 +5124,7 @@
         <v>44466</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5197,7 +5197,7 @@
         <v>44789</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5253,7 +5253,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 58360-2023</t>
+          <t>A 25850-2022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5267,10 +5267,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45250</v>
+        <v>44733</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5283,7 +5283,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>2.5</v>
+        <v>0.8</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5326,7 +5326,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 39298-2023</t>
+          <t>A 2979-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5340,10 +5340,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45166</v>
+        <v>45315</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5355,8 +5355,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I49" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5399,7 +5404,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 29219-2023</t>
+          <t>A 24670-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5409,14 +5414,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45105</v>
+        <v>45460</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5429,7 +5434,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5472,7 +5477,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 9974-2024</t>
+          <t>A 18609-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5486,10 +5491,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45363</v>
+        <v>45763</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5545,7 +5550,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 3542-2025</t>
+          <t>A 3471-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5562,7 +5567,7 @@
         <v>45680</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5574,13 +5579,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I52" t="n">
-        <v>1.4</v>
+        <v>3.7</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5623,7 +5623,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 15970-2024</t>
+          <t>A 33359-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5637,10 +5637,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45405</v>
+        <v>45128</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5653,7 +5653,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.8</v>
+        <v>0.9</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5696,7 +5696,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 25850-2022</t>
+          <t>A 37757-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5710,10 +5710,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44733</v>
+        <v>45541</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5726,7 +5726,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5769,7 +5769,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 5163-2024</t>
+          <t>A 31596-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5783,10 +5783,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45330</v>
+        <v>45117</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5798,13 +5798,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I55" t="n">
-        <v>7.1</v>
+        <v>0.5</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5847,7 +5842,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 25552-2025</t>
+          <t>A 2816-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5857,14 +5852,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45803</v>
+        <v>45677</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5920,7 +5915,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 47637-2023</t>
+          <t>A 44613-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5934,10 +5929,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45203</v>
+        <v>45189</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5949,8 +5944,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I57" t="n">
-        <v>2</v>
+        <v>3.8</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5993,7 +5993,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 37724-2022</t>
+          <t>A 58360-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6007,10 +6007,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44810</v>
+        <v>45250</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6023,7 +6023,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.2</v>
+        <v>2.5</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -6066,7 +6066,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 37728-2022</t>
+          <t>A 28785-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6076,14 +6076,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44810</v>
+        <v>45104</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6096,7 +6096,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6139,7 +6139,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 43380-2022</t>
+          <t>A 16101-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6153,10 +6153,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44834</v>
+        <v>45750</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6169,7 +6169,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.7</v>
+        <v>0.5</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6212,7 +6212,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 47609-2023</t>
+          <t>A 4756-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6226,10 +6226,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45203</v>
+        <v>45688</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6242,7 +6242,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>2.4</v>
+        <v>0.9</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6285,7 +6285,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 38147-2025</t>
+          <t>A 48397-2022</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6299,10 +6299,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45882</v>
+        <v>44858</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6315,7 +6315,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6358,7 +6358,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 56818-2022</t>
+          <t>A 6886-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6372,10 +6372,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44894</v>
+        <v>45342</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6387,8 +6387,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I63" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6431,7 +6436,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 33359-2023</t>
+          <t>A 33358-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6448,7 +6453,7 @@
         <v>45128</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6461,7 +6466,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6504,7 +6509,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 54894-2023</t>
+          <t>A 16665-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6518,10 +6523,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45236</v>
+        <v>45754</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6534,7 +6539,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.6</v>
+        <v>2.4</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6577,7 +6582,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 24670-2024</t>
+          <t>A 43711-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6591,10 +6596,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45460</v>
+        <v>45569</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6607,7 +6612,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.2</v>
+        <v>3.4</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6650,7 +6655,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 6081-2023</t>
+          <t>A 23484-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6664,10 +6669,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44959</v>
+        <v>45792</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6680,7 +6685,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.4</v>
+        <v>3.5</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6723,7 +6728,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 10731-2026</t>
+          <t>A 554-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6737,10 +6742,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46078</v>
+        <v>46029</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6752,13 +6757,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I68" t="n">
-        <v>4.8</v>
+        <v>0.8</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6801,7 +6801,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 36689-2024</t>
+          <t>A 47641-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6811,14 +6811,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45537</v>
+        <v>45203</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6830,13 +6830,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I69" t="n">
-        <v>9.5</v>
+        <v>4.8</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6879,7 +6874,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 38080-2024</t>
+          <t>A 826-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6893,10 +6888,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45545</v>
+        <v>46030</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6908,8 +6903,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I70" t="n">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6952,7 +6952,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 28746-2024</t>
+          <t>A 829-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6966,10 +6966,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45478</v>
+        <v>46030</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6981,8 +6981,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I71" t="n">
-        <v>1.9</v>
+        <v>6.9</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -7025,7 +7030,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 31114-2024</t>
+          <t>A 821-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7039,10 +7044,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45502</v>
+        <v>46030</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7054,8 +7059,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I72" t="n">
-        <v>0.6</v>
+        <v>4.3</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7098,7 +7108,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 37082-2023</t>
+          <t>A 3346-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7108,14 +7118,14 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45155</v>
+        <v>45317</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7171,7 +7181,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 11941-2025</t>
+          <t>A 39298-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7185,10 +7195,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45728</v>
+        <v>45166</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7201,7 +7211,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0.6</v>
+        <v>4.6</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7244,7 +7254,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 2752-2023</t>
+          <t>A 39507-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7258,10 +7268,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44944</v>
+        <v>45551</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7279,7 +7289,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7322,7 +7332,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 14307-2026</t>
+          <t>A 788-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7336,10 +7346,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46099</v>
+        <v>45300</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7352,7 +7362,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7395,7 +7405,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 28785-2023</t>
+          <t>A 28550-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7405,14 +7415,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45104</v>
+        <v>45818</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7425,7 +7435,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>2.1</v>
+        <v>5</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7468,7 +7478,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 3520-2026</t>
+          <t>A 9612-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7482,10 +7492,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46042</v>
+        <v>45715</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7498,7 +7508,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7541,7 +7551,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 13225-2024</t>
+          <t>A 9974-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7555,10 +7565,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45386</v>
+        <v>45363</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7571,7 +7581,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7614,7 +7624,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 13226-2024</t>
+          <t>A 29244-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7628,10 +7638,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45386</v>
+        <v>45824</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7687,7 +7697,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 3470-2026</t>
+          <t>A 29354-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7701,10 +7711,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46042</v>
+        <v>45824</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7717,7 +7727,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7760,7 +7770,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 48397-2022</t>
+          <t>A 11943-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7774,10 +7784,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>44858</v>
+        <v>45728</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7790,7 +7800,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7833,7 +7843,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 15998-2024</t>
+          <t>A 1989-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7847,10 +7857,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45405</v>
+        <v>46035</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7863,7 +7873,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>0.4</v>
+        <v>2.5</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7906,7 +7916,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 16001-2024</t>
+          <t>A 42715-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7920,10 +7930,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45405</v>
+        <v>45176</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7936,7 +7946,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7979,7 +7989,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 34154-2025</t>
+          <t>A 28918-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7993,10 +8003,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45845</v>
+        <v>45104</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8009,7 +8019,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -8052,7 +8062,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 9850-2026</t>
+          <t>A 32958-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -8066,10 +8076,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46072</v>
+        <v>45839</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8082,7 +8092,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>2.2</v>
+        <v>5</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8125,7 +8135,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 3513-2026</t>
+          <t>A 32459-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8139,10 +8149,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46042</v>
+        <v>45838</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8155,7 +8165,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8198,7 +8208,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 43828-2024</t>
+          <t>A 2981-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8212,10 +8222,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45572</v>
+        <v>45315</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8227,8 +8237,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I88" t="n">
-        <v>0.9</v>
+        <v>6.4</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8271,7 +8286,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 38684-2022</t>
+          <t>A 34154-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8285,10 +8300,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>44814</v>
+        <v>45845</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8301,7 +8316,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8344,7 +8359,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 37757-2024</t>
+          <t>A 43932-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8358,10 +8373,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45541</v>
+        <v>45187</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8374,7 +8389,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>0.7</v>
+        <v>3</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8417,7 +8432,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 7402-2026</t>
+          <t>A 43935-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8431,10 +8446,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46059</v>
+        <v>45187</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8447,7 +8462,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>4.7</v>
+        <v>2.9</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8490,7 +8505,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 25183-2023</t>
+          <t>A 37756-2024</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8504,10 +8519,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45079</v>
+        <v>45541</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8520,7 +8535,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1.5</v>
+        <v>3.2</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8563,7 +8578,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 18609-2025</t>
+          <t>A 2747-2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8577,10 +8592,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45763</v>
+        <v>44944</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8592,8 +8607,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I93" t="n">
-        <v>0.6</v>
+        <v>4.6</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8636,7 +8656,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 34147-2025</t>
+          <t>A 48427-2022</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8650,10 +8670,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45845</v>
+        <v>44858</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8665,8 +8685,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I94" t="n">
-        <v>18.7</v>
+        <v>0.5</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8709,7 +8734,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 56750-2023</t>
+          <t>A 3013-2026</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8723,10 +8748,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45238</v>
+        <v>46038</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8739,7 +8764,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8782,7 +8807,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 42715-2023</t>
+          <t>A 8084-2022</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8796,10 +8821,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45176</v>
+        <v>44608</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8812,7 +8837,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8855,7 +8880,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 13633-2024</t>
+          <t>A 43828-2024</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8869,10 +8894,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45390</v>
+        <v>45572</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8885,7 +8910,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8928,7 +8953,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 51757-2025</t>
+          <t>A 36355-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8938,14 +8963,14 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45951</v>
+        <v>45868</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8957,13 +8982,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I98" t="n">
-        <v>1.3</v>
+        <v>3.6</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -9006,7 +9026,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 5079-2026</t>
+          <t>A 13225-2024</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -9020,10 +9040,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>46049</v>
+        <v>45386</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9036,7 +9056,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -9079,7 +9099,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 52929-2025</t>
+          <t>A 13226-2024</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -9093,10 +9113,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45957</v>
+        <v>45386</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9108,13 +9128,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I100" t="n">
-        <v>8.300000000000001</v>
+        <v>0.7</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -9157,7 +9172,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 58641-2023</t>
+          <t>A 47552-2023</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9167,14 +9182,14 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45251</v>
+        <v>45203</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9187,7 +9202,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9230,7 +9245,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 52930-2025</t>
+          <t>A 25552-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9244,10 +9259,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45957</v>
+        <v>45803</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9259,13 +9274,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I102" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9308,7 +9318,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 18603-2025</t>
+          <t>A 34147-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9322,10 +9332,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45763</v>
+        <v>45845</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9338,7 +9348,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>0.5</v>
+        <v>18.7</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9381,7 +9391,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 3346-2024</t>
+          <t>A 38147-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9395,10 +9405,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45317</v>
+        <v>45882</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9411,7 +9421,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9454,7 +9464,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 65073-2023</t>
+          <t>A 51757-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9464,14 +9474,14 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45287</v>
+        <v>45951</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9483,8 +9493,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I105" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9527,7 +9542,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 788-2024</t>
+          <t>A 5374-2026</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9541,10 +9556,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45300</v>
+        <v>46050</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9557,7 +9572,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9600,7 +9615,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 54765-2025</t>
+          <t>A 52930-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9614,10 +9629,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45966</v>
+        <v>45957</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9629,8 +9644,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I107" t="n">
-        <v>2.6</v>
+        <v>1.6</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9673,7 +9693,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 44073-2024</t>
+          <t>A 52929-2025</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9687,10 +9707,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45572</v>
+        <v>45957</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9702,8 +9722,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I108" t="n">
-        <v>1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9746,7 +9771,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 40994-2025</t>
+          <t>A 2752-2023</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9760,10 +9785,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45898</v>
+        <v>44944</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9775,8 +9800,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I109" t="n">
-        <v>5.6</v>
+        <v>0.6</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9819,7 +9849,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 55304-2025</t>
+          <t>A 37082-2023</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9833,10 +9863,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45970</v>
+        <v>45155</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9849,7 +9879,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9892,7 +9922,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 55306-2025</t>
+          <t>A 54431-2023</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9902,14 +9932,14 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45970</v>
+        <v>45226</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9922,7 +9952,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>0.3</v>
+        <v>3.2</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9965,7 +9995,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 37276-2024</t>
+          <t>A 54765-2025</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9979,10 +10009,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45540</v>
+        <v>45966</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9995,7 +10025,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>1.6</v>
+        <v>2.6</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -10038,7 +10068,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 20595-2024</t>
+          <t>A 8310-2026</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -10052,10 +10082,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45436</v>
+        <v>46064</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10067,13 +10097,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I113" t="n">
-        <v>3.5</v>
+        <v>1.4</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -10116,7 +10141,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 57269-2025</t>
+          <t>A 8260-2026</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -10130,10 +10155,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45979</v>
+        <v>46064</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10145,13 +10170,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H114" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I114" t="n">
-        <v>5.5</v>
+        <v>3.3</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -10194,7 +10214,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 119-2023</t>
+          <t>A 55304-2025</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10204,14 +10224,14 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>44928</v>
+        <v>45970</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10224,7 +10244,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10267,7 +10287,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 50715-2024</t>
+          <t>A 55306-2025</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10277,14 +10297,14 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45602</v>
+        <v>45970</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10297,7 +10317,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10340,7 +10360,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 2816-2025</t>
+          <t>A 28625-2023</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10350,14 +10370,14 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45677</v>
+        <v>45103</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10370,7 +10390,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>2</v>
+        <v>4.8</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10413,7 +10433,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 16101-2025</t>
+          <t>A 8259-2026</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10427,10 +10447,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45750</v>
+        <v>46064</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10443,7 +10463,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>0.5</v>
+        <v>3.1</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10486,7 +10506,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 59308-2025</t>
+          <t>A 40994-2025</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10500,10 +10520,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45989</v>
+        <v>45898</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10516,7 +10536,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>1.2</v>
+        <v>5.6</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10559,7 +10579,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 34422-2024</t>
+          <t>A 57269-2025</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10569,14 +10589,14 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45525</v>
+        <v>45979</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10588,8 +10608,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I120" t="n">
-        <v>1.5</v>
+        <v>5.5</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10632,7 +10657,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 11943-2025</t>
+          <t>A 38080-2024</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10646,10 +10671,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45728</v>
+        <v>45545</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10662,7 +10687,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10705,7 +10730,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 44613-2023</t>
+          <t>A 13633-2024</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10719,10 +10744,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45189</v>
+        <v>45390</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10734,13 +10759,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I122" t="n">
-        <v>3.8</v>
+        <v>1.1</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10783,7 +10803,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 43685-2022</t>
+          <t>A 44816-2023</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10793,14 +10813,14 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>44837</v>
+        <v>45190</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10813,7 +10833,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10856,7 +10876,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 43937-2023</t>
+          <t>A 28493-2023</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10870,10 +10890,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45187</v>
+        <v>45103</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10886,7 +10906,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>2.6</v>
+        <v>0.8</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10929,7 +10949,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 43939-2023</t>
+          <t>A 59308-2025</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10943,10 +10963,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45187</v>
+        <v>45989</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10959,7 +10979,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -11002,7 +11022,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 67426-2021</t>
+          <t>A 10731-2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -11016,10 +11036,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>44523</v>
+        <v>46078</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11031,8 +11051,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I126" t="n">
-        <v>0.6</v>
+        <v>4.8</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -11075,7 +11100,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 3534-2025</t>
+          <t>A 43879-2023</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -11089,10 +11114,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45680</v>
+        <v>45187</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11106,11 +11131,11 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I127" t="n">
-        <v>4.8</v>
+        <v>1.1</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -11153,7 +11178,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 62277-2025</t>
+          <t>A 47609-2023</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -11167,10 +11192,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>46006</v>
+        <v>45203</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11226,7 +11251,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 7831-2025</t>
+          <t>A 62277-2025</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11240,10 +11265,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45706</v>
+        <v>46006</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11256,7 +11281,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>0.6</v>
+        <v>2.4</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11299,7 +11324,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 24724-2024</t>
+          <t>A 43882-2023</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11309,14 +11334,14 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45460</v>
+        <v>45187</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11328,8 +11353,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I130" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11372,7 +11402,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 18735-2023</t>
+          <t>A 67426-2021</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11386,10 +11416,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45043</v>
+        <v>44523</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11402,7 +11432,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11445,7 +11475,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 4597-2026</t>
+          <t>A 3239-2023</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11459,10 +11489,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>46048</v>
+        <v>44946</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11475,7 +11505,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>1.3</v>
+        <v>0.4</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11518,7 +11548,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 826-2026</t>
+          <t>A 60963-2023</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11532,10 +11562,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>46030</v>
+        <v>45261</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11547,13 +11577,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H133" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I133" t="n">
-        <v>0.3</v>
+        <v>1.2</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11596,7 +11621,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 829-2026</t>
+          <t>A 14307-2026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11610,10 +11635,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>46030</v>
+        <v>46099</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11625,13 +11650,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I134" t="n">
-        <v>6.9</v>
+        <v>1</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11674,7 +11694,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 821-2026</t>
+          <t>A 43685-2022</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11684,14 +11704,14 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>46030</v>
+        <v>44837</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11703,13 +11723,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H135" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I135" t="n">
-        <v>4.3</v>
+        <v>1.3</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11752,7 +11767,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 554-2026</t>
+          <t>A 3470-2026</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11766,10 +11781,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>46029</v>
+        <v>46042</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11782,7 +11797,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11825,7 +11840,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 1989-2026</t>
+          <t>A 55265-2023</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11839,10 +11854,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>46035</v>
+        <v>45237</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11855,7 +11870,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>2.5</v>
+        <v>1.2</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11898,7 +11913,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 28493-2023</t>
+          <t>A 3513-2026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11912,10 +11927,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45103</v>
+        <v>46042</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11928,7 +11943,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11971,7 +11986,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 3013-2026</t>
+          <t>A 3520-2026</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11985,10 +12000,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>46038</v>
+        <v>46042</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12001,7 +12016,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -12044,7 +12059,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 36840-2024</t>
+          <t>A 9850-2026</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -12058,10 +12073,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45538</v>
+        <v>46072</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12073,13 +12088,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H140" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I140" t="n">
-        <v>0.9</v>
+        <v>2.2</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -12122,7 +12132,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 6558-2025</t>
+          <t>A 5163-2024</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -12132,14 +12142,14 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45699</v>
+        <v>45330</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12153,11 +12163,11 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I141" t="n">
-        <v>0.9</v>
+        <v>7.1</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -12200,7 +12210,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 60913-2023</t>
+          <t>A 18603-2025</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -12214,10 +12224,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45261</v>
+        <v>45763</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12230,7 +12240,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -12273,7 +12283,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 4590-2026</t>
+          <t>A 7402-2026</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12287,10 +12297,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>46048</v>
+        <v>46059</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12303,7 +12313,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>1.1</v>
+        <v>4.7</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -12346,7 +12356,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 6350-2026</t>
+          <t>A 3534-2025</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12360,10 +12370,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>46051</v>
+        <v>45680</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12375,8 +12385,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I144" t="n">
-        <v>2.4</v>
+        <v>4.8</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -12419,7 +12434,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 18369-2025</t>
+          <t>A 20595-2024</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12433,10 +12448,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45762</v>
+        <v>45436</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12448,8 +12463,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I145" t="n">
-        <v>2.2</v>
+        <v>3.5</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12492,7 +12512,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 5374-2026</t>
+          <t>A 43937-2023</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12506,10 +12526,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>46050</v>
+        <v>45187</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12522,7 +12542,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>0.5</v>
+        <v>2.6</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12565,7 +12585,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 8084-2022</t>
+          <t>A 43939-2023</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12579,10 +12599,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>44608</v>
+        <v>45187</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12595,7 +12615,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12638,7 +12658,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 2747-2023</t>
+          <t>A 28501-2023</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12652,10 +12672,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>44944</v>
+        <v>45103</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12667,13 +12687,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H148" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I148" t="n">
-        <v>4.6</v>
+        <v>3.6</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12716,7 +12731,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 31522-2022</t>
+          <t>A 28527-2023</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12730,10 +12745,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>44775</v>
+        <v>45103</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12746,7 +12761,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>1.8</v>
+        <v>0.7</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12789,7 +12804,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 28625-2023</t>
+          <t>A 54894-2023</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12803,10 +12818,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45103</v>
+        <v>45236</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12819,7 +12834,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>4.8</v>
+        <v>0.6</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12862,7 +12877,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 3177-2026</t>
+          <t>A 37276-2024</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12872,14 +12887,14 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>46041</v>
+        <v>45540</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12892,7 +12907,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12935,7 +12950,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 8310-2026</t>
+          <t>A 65073-2023</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12949,10 +12964,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>46064</v>
+        <v>45287</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12965,7 +12980,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -13008,7 +13023,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 8260-2026</t>
+          <t>A 36689-2024</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -13018,14 +13033,14 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>46064</v>
+        <v>45537</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13037,8 +13052,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I153" t="n">
-        <v>3.3</v>
+        <v>9.5</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -13081,7 +13101,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 8259-2026</t>
+          <t>A 5079-2026</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -13095,10 +13115,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>46064</v>
+        <v>46049</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13111,7 +13131,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>3.1</v>
+        <v>1.3</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -13154,7 +13174,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 13804-2024</t>
+          <t>A 31522-2022</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -13168,10 +13188,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45391</v>
+        <v>44775</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13184,7 +13204,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -13227,7 +13247,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 59284-2025</t>
+          <t>A 54184-2024</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -13241,10 +13261,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45988</v>
+        <v>45616</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13257,7 +13277,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -13300,7 +13320,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 55265-2023</t>
+          <t>A 60913-2023</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -13314,10 +13334,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45237</v>
+        <v>45261</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13330,7 +13350,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -13373,7 +13393,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 28918-2023</t>
+          <t>A 44073-2024</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -13387,10 +13407,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45104</v>
+        <v>45572</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13403,7 +13423,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -13446,7 +13466,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 3239-2023</t>
+          <t>A 11941-2025</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13460,10 +13480,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>44946</v>
+        <v>45728</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13476,7 +13496,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -13519,7 +13539,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 13228-2024</t>
+          <t>A 43380-2022</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -13533,10 +13553,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45386</v>
+        <v>44834</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13549,7 +13569,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>0.7</v>
+        <v>1.7</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13592,7 +13612,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 10524-2026</t>
+          <t>A 20403-2024</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13606,10 +13626,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>46076</v>
+        <v>45435</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13622,7 +13642,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13665,7 +13685,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 48427-2022</t>
+          <t>A 1106-2023</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13679,10 +13699,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>44858</v>
+        <v>44935</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13694,13 +13714,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H162" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I162" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13743,7 +13758,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 10500-2026</t>
+          <t>A 49726-2023</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13757,10 +13772,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>46076</v>
+        <v>45208</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13773,7 +13788,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13816,7 +13831,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 6886-2024</t>
+          <t>A 36840-2024</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13830,10 +13845,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45342</v>
+        <v>45538</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13851,7 +13866,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13894,7 +13909,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 4756-2025</t>
+          <t>A 24724-2024</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13904,14 +13919,14 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45688</v>
+        <v>45460</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13924,7 +13939,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13967,7 +13982,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 16518-2026</t>
+          <t>A 4597-2026</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13981,10 +13996,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>46112</v>
+        <v>46048</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13997,7 +14012,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -14040,7 +14055,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 1106-2023</t>
+          <t>A 58641-2023</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -14050,14 +14065,14 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>44935</v>
+        <v>45251</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14113,7 +14128,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 33358-2023</t>
+          <t>A 3040-2024</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -14127,10 +14142,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>45128</v>
+        <v>45316</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14143,7 +14158,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>0.4</v>
+        <v>4</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -14186,7 +14201,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 39507-2024</t>
+          <t>A 15970-2024</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -14200,10 +14215,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>45551</v>
+        <v>45405</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14215,13 +14230,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H169" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I169" t="n">
-        <v>0.3</v>
+        <v>1.8</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -14264,7 +14274,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 17073-2023</t>
+          <t>A 18735-2023</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -14278,10 +14288,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45034</v>
+        <v>45043</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14294,7 +14304,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -14337,7 +14347,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 2979-2024</t>
+          <t>A 6081-2023</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -14351,10 +14361,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45315</v>
+        <v>44959</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14366,13 +14376,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H171" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I171" t="n">
-        <v>4.7</v>
+        <v>0.4</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -14415,7 +14420,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 29138-2026</t>
+          <t>A 29219-2023</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -14425,14 +14430,14 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>46202</v>
+        <v>45105</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14444,13 +14449,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H172" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I172" t="n">
-        <v>4.2</v>
+        <v>0.7</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -14493,7 +14493,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 31596-2023</t>
+          <t>A 56818-2022</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -14507,10 +14507,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45117</v>
+        <v>44894</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14523,7 +14523,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -14566,7 +14566,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 29135-2026</t>
+          <t>A 4590-2026</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14576,14 +14576,14 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>46202</v>
+        <v>46048</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14595,13 +14595,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H174" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I174" t="n">
-        <v>4.7</v>
+        <v>1.1</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14644,7 +14639,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 29137-2026</t>
+          <t>A 6350-2026</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14654,14 +14649,14 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>46202</v>
+        <v>46051</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14673,13 +14668,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H175" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I175" t="n">
-        <v>7.8</v>
+        <v>2.4</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14722,7 +14712,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 41940-2022</t>
+          <t>A 18369-2025</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14736,10 +14726,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>44833</v>
+        <v>45762</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14752,7 +14742,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>0.7</v>
+        <v>2.2</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14795,7 +14785,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 29124-2026</t>
+          <t>A 3177-2026</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14805,14 +14795,14 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>46202</v>
+        <v>46041</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14825,7 +14815,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>2.9</v>
+        <v>0.5</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14868,7 +14858,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 43882-2023</t>
+          <t>A 34422-2024</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14878,14 +14868,14 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45187</v>
+        <v>45525</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14897,13 +14887,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H178" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I178" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14946,7 +14931,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 54184-2024</t>
+          <t>A 7831-2025</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14960,10 +14945,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>45616</v>
+        <v>45706</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14976,7 +14961,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -15019,7 +15004,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 28527-2023</t>
+          <t>A 56750-2023</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -15033,10 +15018,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>45103</v>
+        <v>45238</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15049,7 +15034,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -15092,7 +15077,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 43932-2023</t>
+          <t>A 59284-2025</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -15106,10 +15091,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>45187</v>
+        <v>45988</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15122,7 +15107,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -15165,7 +15150,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 43935-2023</t>
+          <t>A 10500-2026</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -15179,10 +15164,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>45187</v>
+        <v>46076</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15195,7 +15180,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>2.9</v>
+        <v>1.1</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -15238,7 +15223,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 20403-2024</t>
+          <t>A 10524-2026</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -15252,10 +15237,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>45435</v>
+        <v>46076</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15268,7 +15253,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -15311,7 +15296,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 3040-2024</t>
+          <t>A 17073-2023</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -15325,10 +15310,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>45316</v>
+        <v>45034</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15341,7 +15326,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>4</v>
+        <v>1.2</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -15384,7 +15369,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 44816-2023</t>
+          <t>A 16518-2026</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -15398,10 +15383,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>45190</v>
+        <v>46112</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15414,7 +15399,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -15457,7 +15442,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 47552-2023</t>
+          <t>A 19420-2022</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -15471,10 +15456,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>45203</v>
+        <v>44693</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15487,7 +15472,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -15530,7 +15515,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 19420-2022</t>
+          <t>A 29138-2026</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -15540,14 +15525,14 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>44693</v>
+        <v>46202</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15559,8 +15544,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I187" t="n">
-        <v>0.7</v>
+        <v>4.2</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -15603,7 +15593,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 54431-2023</t>
+          <t>A 29124-2026</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15617,10 +15607,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>45226</v>
+        <v>46202</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15633,7 +15623,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15676,7 +15666,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 30934-2026</t>
+          <t>A 29135-2026</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15686,14 +15676,14 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>46213</v>
+        <v>46202</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15705,8 +15695,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I189" t="n">
-        <v>1.1</v>
+        <v>4.7</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15749,7 +15744,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 34737-2026</t>
+          <t>A 29137-2026</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15759,14 +15754,14 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>46258</v>
+        <v>46202</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15778,8 +15773,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I190" t="n">
-        <v>0.7</v>
+        <v>7.8</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15822,7 +15822,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 34740-2026</t>
+          <t>A 119-2023</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15836,10 +15836,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>46258</v>
+        <v>44928</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15852,7 +15852,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>2.1</v>
+        <v>0.8</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15895,7 +15895,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 19777-2023</t>
+          <t>A 50715-2024</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15909,10 +15909,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>45051</v>
+        <v>45602</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15925,7 +15925,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>4.3</v>
+        <v>0.4</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15968,7 +15968,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 43879-2023</t>
+          <t>A 37724-2022</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15982,10 +15982,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>45187</v>
+        <v>44810</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15997,13 +15997,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H193" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I193" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -16046,7 +16041,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 3471-2025</t>
+          <t>A 37728-2022</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -16060,10 +16055,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>45680</v>
+        <v>44810</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16076,7 +16071,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>3.7</v>
+        <v>1</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -16119,7 +16114,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 49726-2023</t>
+          <t>A 47637-2023</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -16133,10 +16128,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>45208</v>
+        <v>45203</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16149,7 +16144,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -16192,7 +16187,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 28501-2023</t>
+          <t>A 33873-2024</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -16206,10 +16201,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>45103</v>
+        <v>45521</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16222,7 +16217,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -16265,7 +16260,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 33873-2024</t>
+          <t>A 3542-2025</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -16279,10 +16274,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>45521</v>
+        <v>45680</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16294,8 +16289,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I197" t="n">
-        <v>3.5</v>
+        <v>1.4</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -16338,7 +16338,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 23606-2026</t>
+          <t>A 13228-2024</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -16348,14 +16348,14 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>46162</v>
+        <v>45386</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16368,7 +16368,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>9.4</v>
+        <v>0.7</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -16411,7 +16411,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 31286-2026</t>
+          <t>A 15998-2024</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -16425,10 +16425,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>46218</v>
+        <v>45405</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16441,7 +16441,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>1.1</v>
+        <v>0.4</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -16484,7 +16484,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 55307-2025</t>
+          <t>A 16001-2024</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -16498,10 +16498,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>45970</v>
+        <v>45405</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16514,7 +16514,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>2.5</v>
+        <v>0.2</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -16557,7 +16557,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 57017-2025</t>
+          <t>A 31114-2024</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -16571,10 +16571,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>45978</v>
+        <v>45502</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16587,7 +16587,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>5.5</v>
+        <v>0.6</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -16630,7 +16630,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 47641-2023</t>
+          <t>A 13804-2024</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -16644,10 +16644,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>45203</v>
+        <v>45391</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16660,7 +16660,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>4.8</v>
+        <v>0.5</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16703,7 +16703,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 60963-2023</t>
+          <t>A 23606-2026</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16713,14 +16713,14 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>45261</v>
+        <v>46162</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16733,7 +16733,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>1.2</v>
+        <v>9.4</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -16776,7 +16776,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 20047-2026</t>
+          <t>A 34737-2026</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -16790,10 +16790,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>46136</v>
+        <v>46258</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16806,7 +16806,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16849,7 +16849,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 38073-2026</t>
+          <t>A 34740-2026</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16863,10 +16863,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>46280</v>
+        <v>46258</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16879,7 +16879,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16922,7 +16922,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 37300-2026</t>
+          <t>A 19777-2023</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16936,10 +16936,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>46274</v>
+        <v>45051</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16952,7 +16952,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>0.2</v>
+        <v>4.3</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16995,7 +16995,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 52310-2023</t>
+          <t>A 28746-2024</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -17009,10 +17009,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>45224</v>
+        <v>45478</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17025,7 +17025,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>3.5</v>
+        <v>1.9</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -17068,7 +17068,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 2170-2025</t>
+          <t>A 30934-2026</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -17082,10 +17082,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>45673</v>
+        <v>46213</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17098,7 +17098,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>3.6</v>
+        <v>1.1</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -17141,7 +17141,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 16665-2025</t>
+          <t>A 55307-2025</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -17155,10 +17155,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>45754</v>
+        <v>45970</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17171,7 +17171,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -17214,7 +17214,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 43711-2024</t>
+          <t>A 31286-2026</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -17224,14 +17224,14 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>45569</v>
+        <v>46218</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17244,7 +17244,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>3.4</v>
+        <v>1.1</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -17287,7 +17287,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 23484-2025</t>
+          <t>A 6558-2025</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -17297,14 +17297,14 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>45792</v>
+        <v>45699</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17316,8 +17316,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I211" t="n">
-        <v>3.5</v>
+        <v>0.9</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -17360,7 +17365,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 28550-2025</t>
+          <t>A 25183-2023</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -17374,10 +17379,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>45818</v>
+        <v>45079</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17390,7 +17395,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>5</v>
+        <v>1.5</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -17433,7 +17438,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 9612-2025</t>
+          <t>A 57017-2025</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -17447,10 +17452,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>45715</v>
+        <v>45978</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17463,7 +17468,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>1.2</v>
+        <v>5.5</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -17506,7 +17511,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 29244-2025</t>
+          <t>A 41940-2022</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -17520,10 +17525,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>45824</v>
+        <v>44833</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17579,7 +17584,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 29354-2025</t>
+          <t>A 20047-2026</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -17593,10 +17598,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>45824</v>
+        <v>46136</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17609,7 +17614,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -17652,7 +17657,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 2981-2024</t>
+          <t>A 38684-2022</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -17666,10 +17671,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>45315</v>
+        <v>44814</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17681,13 +17686,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H216" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I216" t="n">
-        <v>6.4</v>
+        <v>2.5</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -17730,7 +17730,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 32459-2025</t>
+          <t>A 38073-2026</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -17744,10 +17744,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>45838</v>
+        <v>46280</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17760,7 +17760,7 @@
         </is>
       </c>
       <c r="I217" t="n">
-        <v>1.2</v>
+        <v>2.3</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -17803,7 +17803,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 32958-2025</t>
+          <t>A 52310-2023</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -17817,10 +17817,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>45839</v>
+        <v>45224</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17833,7 +17833,7 @@
         </is>
       </c>
       <c r="I218" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -17876,7 +17876,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 37756-2024</t>
+          <t>A 2170-2025</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -17890,10 +17890,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>45541</v>
+        <v>45673</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17906,7 +17906,7 @@
         </is>
       </c>
       <c r="I219" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -17949,7 +17949,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 36355-2025</t>
+          <t>A 37300-2026</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -17963,10 +17963,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>45868</v>
+        <v>46274</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17979,7 +17979,7 @@
         </is>
       </c>
       <c r="I220" t="n">
-        <v>3.6</v>
+        <v>0.2</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -18039,7 +18039,7 @@
         <v>45230</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18112,7 +18112,7 @@
         <v>44796</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18185,7 +18185,7 @@
         <v>45722</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18258,7 +18258,7 @@
         <v>46042</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18314,7 +18314,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>S 220-2026</t>
+          <t>S 1874-2026</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -18328,10 +18328,10 @@
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>46051</v>
+        <v>46202</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18343,8 +18343,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I225" t="n">
-        <v>1.7</v>
+        <v>7.8</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -18387,7 +18392,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>S 1874-2026</t>
+          <t>S 1875-2026</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -18404,7 +18409,7 @@
         <v>46202</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18422,7 +18427,7 @@
         </is>
       </c>
       <c r="I226" t="n">
-        <v>7.8</v>
+        <v>4.2</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -18465,7 +18470,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>S 1875-2026</t>
+          <t>S 1873-2026</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -18482,7 +18487,7 @@
         <v>46202</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18500,7 +18505,7 @@
         </is>
       </c>
       <c r="I227" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -18543,7 +18548,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>S 1873-2026</t>
+          <t>S 220-2026</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -18557,10 +18562,10 @@
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>46202</v>
+        <v>46051</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18572,13 +18577,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H228" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I228" t="n">
-        <v>4.7</v>
+        <v>1.7</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>

--- a/Översikt HÖRBY.xlsx
+++ b/Översikt HÖRBY.xlsx
@@ -601,7 +601,7 @@
         <v>44964</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
         <v>44967</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         <v>44727</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -949,7 +949,7 @@
         <v>45786</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1061,7 +1061,7 @@
         <v>46160</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
         <v>45238</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 39855-2022</t>
+          <t>A 31351-2022</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1289,10 +1289,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>44819</v>
+        <v>44774</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1305,22 +1305,22 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>4.2</v>
+        <v>13.2</v>
       </c>
       <c r="J8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1329,10 +1329,10 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1341,9 +1341,344 @@
         <v>5</v>
       </c>
       <c r="U8" t="n">
+        <v>3</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>Duvhök
+Grönsångare
+Sädesärla
+Fjällvråk
+Kungsfågel</t>
+        </is>
+      </c>
+      <c r="W8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 31351-2022 artfynd.xlsx", "A 31351-2022")</f>
+        <v/>
+      </c>
+      <c r="X8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 31351-2022 karta.png", "A 31351-2022")</f>
+        <v/>
+      </c>
+      <c r="Y8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 31351-2022 georefererad karta.tif", "A 31351-2022")</f>
+        <v/>
+      </c>
+      <c r="AA8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 31351-2022 FSC-klagomål.docx", "A 31351-2022")</f>
+        <v/>
+      </c>
+      <c r="AB8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 31351-2022 FSC-klagomål mail.docx", "A 31351-2022")</f>
+        <v/>
+      </c>
+      <c r="AC8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 31351-2022 tillsynsbegäran.docx", "A 31351-2022")</f>
+        <v/>
+      </c>
+      <c r="AD8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 31351-2022 tillsynsbegäran mail.docx", "A 31351-2022")</f>
+        <v/>
+      </c>
+      <c r="AE8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/fåglar/A 31351-2022 prioriterade fågelarter.docx", "A 31351-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 16520-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>46112</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>HÖRBY</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>2</v>
+      </c>
+      <c r="M9" t="n">
         <v>1</v>
       </c>
-      <c r="V8" s="2" t="inlineStr">
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>3</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="n">
+        <v>6</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Slåttergubbe
+Sydlig sotticka
+Älg
+Fiskgjuse
+Större brunfladdermus</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 16520-2026 artfynd.xlsx", "A 16520-2026")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 16520-2026 karta.png", "A 16520-2026")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 16520-2026 georefererad karta.tif", "A 16520-2026")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 16520-2026 FSC-klagomål.docx", "A 16520-2026")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 16520-2026 FSC-klagomål mail.docx", "A 16520-2026")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 16520-2026 tillsynsbegäran.docx", "A 16520-2026")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 16520-2026 tillsynsbegäran mail.docx", "A 16520-2026")</f>
+        <v/>
+      </c>
+      <c r="AE9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/fåglar/A 16520-2026 prioriterade fågelarter.docx", "A 16520-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 20194-2024</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>45434</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>HÖRBY</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>3</v>
+      </c>
+      <c r="R10" t="n">
+        <v>3</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="n">
+        <v>5</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Naverlönn
+Ask
+Skogsalm
+Scharlakansskål
+Stor häxört</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 20194-2024 artfynd.xlsx", "A 20194-2024")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 20194-2024 karta.png", "A 20194-2024")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 20194-2024 georefererad karta.tif", "A 20194-2024")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 20194-2024 FSC-klagomål.docx", "A 20194-2024")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 20194-2024 FSC-klagomål mail.docx", "A 20194-2024")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 20194-2024 tillsynsbegäran.docx", "A 20194-2024")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 20194-2024 tillsynsbegäran mail.docx", "A 20194-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 39855-2022</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>44819</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>HÖRBY</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J11" t="n">
+        <v>4</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>1</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="n">
+        <v>5</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Ask
 Skogsknipprot
@@ -1352,367 +1687,32 @@
 Grönvit nattviol</t>
         </is>
       </c>
-      <c r="W8">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 39855-2022 artfynd.xlsx", "A 39855-2022")</f>
         <v/>
       </c>
-      <c r="X8">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 39855-2022 karta.png", "A 39855-2022")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 39855-2022 georefererad karta.tif", "A 39855-2022")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 39855-2022 FSC-klagomål.docx", "A 39855-2022")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 39855-2022 FSC-klagomål mail.docx", "A 39855-2022")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 39855-2022 tillsynsbegäran.docx", "A 39855-2022")</f>
         <v/>
       </c>
-      <c r="AD8">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 39855-2022 tillsynsbegäran mail.docx", "A 39855-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A 16520-2026</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>46112</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>HÖRBY</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="J9" t="n">
-        <v>2</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>2</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>3</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1</v>
-      </c>
-      <c r="S9" t="n">
-        <v>5</v>
-      </c>
-      <c r="T9" t="n">
-        <v>6</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>Slåttergubbe
-Sydlig sotticka
-Älg
-Fiskgjuse
-Större brunfladdermus</t>
-        </is>
-      </c>
-      <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 16520-2026 artfynd.xlsx", "A 16520-2026")</f>
-        <v/>
-      </c>
-      <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 16520-2026 karta.png", "A 16520-2026")</f>
-        <v/>
-      </c>
-      <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 16520-2026 georefererad karta.tif", "A 16520-2026")</f>
-        <v/>
-      </c>
-      <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 16520-2026 FSC-klagomål.docx", "A 16520-2026")</f>
-        <v/>
-      </c>
-      <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 16520-2026 FSC-klagomål mail.docx", "A 16520-2026")</f>
-        <v/>
-      </c>
-      <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 16520-2026 tillsynsbegäran.docx", "A 16520-2026")</f>
-        <v/>
-      </c>
-      <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 16520-2026 tillsynsbegäran mail.docx", "A 16520-2026")</f>
-        <v/>
-      </c>
-      <c r="AE9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/fåglar/A 16520-2026 prioriterade fågelarter.docx", "A 16520-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 31351-2022</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>44774</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>HÖRBY</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="J10" t="n">
-        <v>5</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>3</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>3</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>5</v>
-      </c>
-      <c r="T10" t="n">
-        <v>5</v>
-      </c>
-      <c r="U10" t="n">
-        <v>3</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Duvhök
-Grönsångare
-Sädesärla
-Fjällvråk
-Kungsfågel</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 31351-2022 artfynd.xlsx", "A 31351-2022")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 31351-2022 karta.png", "A 31351-2022")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 31351-2022 georefererad karta.tif", "A 31351-2022")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 31351-2022 FSC-klagomål.docx", "A 31351-2022")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 31351-2022 FSC-klagomål mail.docx", "A 31351-2022")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 31351-2022 tillsynsbegäran.docx", "A 31351-2022")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 31351-2022 tillsynsbegäran mail.docx", "A 31351-2022")</f>
-        <v/>
-      </c>
-      <c r="AE10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/fåglar/A 31351-2022 prioriterade fågelarter.docx", "A 31351-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 20194-2024</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>45434</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>HÖRBY</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>2</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>2</v>
-      </c>
-      <c r="O11" t="n">
-        <v>1</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>3</v>
-      </c>
-      <c r="R11" t="n">
-        <v>3</v>
-      </c>
-      <c r="S11" t="n">
-        <v>5</v>
-      </c>
-      <c r="T11" t="n">
-        <v>5</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Naverlönn
-Ask
-Skogsalm
-Scharlakansskål
-Stor häxört</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 20194-2024 artfynd.xlsx", "A 20194-2024")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 20194-2024 karta.png", "A 20194-2024")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 20194-2024 georefererad karta.tif", "A 20194-2024")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 20194-2024 FSC-klagomål.docx", "A 20194-2024")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 20194-2024 FSC-klagomål mail.docx", "A 20194-2024")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 20194-2024 tillsynsbegäran.docx", "A 20194-2024")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 20194-2024 tillsynsbegäran mail.docx", "A 20194-2024")</f>
         <v/>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
         <v>46150</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         <v>45545</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1952,7 +1952,7 @@
         <v>45334</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2043,7 +2043,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 2823-2025</t>
+          <t>A 20193-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2053,14 +2053,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45677</v>
+        <v>45434</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2073,13 +2073,13 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>21.1</v>
+        <v>11.2</v>
       </c>
       <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
         <v>2</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>1</v>
@@ -2106,151 +2106,151 @@
         <v>3</v>
       </c>
       <c r="T15" t="n">
+        <v>3</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>Vårärt
+Strutbräken
+Vätteros</t>
+        </is>
+      </c>
+      <c r="W15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 20193-2024 artfynd.xlsx", "A 20193-2024")</f>
+        <v/>
+      </c>
+      <c r="X15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 20193-2024 karta.png", "A 20193-2024")</f>
+        <v/>
+      </c>
+      <c r="Y15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 20193-2024 georefererad karta.tif", "A 20193-2024")</f>
+        <v/>
+      </c>
+      <c r="AA15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 20193-2024 FSC-klagomål.docx", "A 20193-2024")</f>
+        <v/>
+      </c>
+      <c r="AB15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 20193-2024 FSC-klagomål mail.docx", "A 20193-2024")</f>
+        <v/>
+      </c>
+      <c r="AC15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 20193-2024 tillsynsbegäran.docx", "A 20193-2024")</f>
+        <v/>
+      </c>
+      <c r="AD15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 20193-2024 tillsynsbegäran mail.docx", "A 20193-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 2823-2025</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>45677</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>HÖRBY</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="J16" t="n">
+        <v>2</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3</v>
+      </c>
+      <c r="T16" t="n">
         <v>4</v>
       </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>Borsttåg
 Grönvit nattviol
 Revlummer</t>
         </is>
       </c>
-      <c r="W15">
+      <c r="W16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 2823-2025 artfynd.xlsx", "A 2823-2025")</f>
         <v/>
       </c>
-      <c r="X15">
+      <c r="X16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 2823-2025 karta.png", "A 2823-2025")</f>
         <v/>
       </c>
-      <c r="Y15">
+      <c r="Y16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 2823-2025 georefererad karta.tif", "A 2823-2025")</f>
         <v/>
       </c>
-      <c r="AA15">
+      <c r="AA16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 2823-2025 FSC-klagomål.docx", "A 2823-2025")</f>
         <v/>
       </c>
-      <c r="AB15">
+      <c r="AB16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 2823-2025 FSC-klagomål mail.docx", "A 2823-2025")</f>
         <v/>
       </c>
-      <c r="AC15">
+      <c r="AC16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 2823-2025 tillsynsbegäran.docx", "A 2823-2025")</f>
         <v/>
       </c>
-      <c r="AD15">
+      <c r="AD16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 2823-2025 tillsynsbegäran mail.docx", "A 2823-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>A 20193-2024</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>45434</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>HÖRBY</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>2</v>
-      </c>
-      <c r="L16" t="n">
-        <v>1</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>1</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>3</v>
-      </c>
-      <c r="T16" t="n">
-        <v>3</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>Vårärt
-Strutbräken
-Vätteros</t>
-        </is>
-      </c>
-      <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 20193-2024 artfynd.xlsx", "A 20193-2024")</f>
-        <v/>
-      </c>
-      <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 20193-2024 karta.png", "A 20193-2024")</f>
-        <v/>
-      </c>
-      <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 20193-2024 georefererad karta.tif", "A 20193-2024")</f>
-        <v/>
-      </c>
-      <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 20193-2024 FSC-klagomål.docx", "A 20193-2024")</f>
-        <v/>
-      </c>
-      <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 20193-2024 FSC-klagomål mail.docx", "A 20193-2024")</f>
-        <v/>
-      </c>
-      <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 20193-2024 tillsynsbegäran.docx", "A 20193-2024")</f>
-        <v/>
-      </c>
-      <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 20193-2024 tillsynsbegäran mail.docx", "A 20193-2024")</f>
         <v/>
       </c>
     </row>
@@ -2274,7 +2274,7 @@
         <v>45815</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2381,7 +2381,7 @@
         <v>45799</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2488,7 +2488,7 @@
         <v>44725</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 824-2026</t>
+          <t>A 44135-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2592,10 +2592,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46030</v>
+        <v>45572</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2607,16 +2607,11 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I20" t="n">
-        <v>3.1</v>
+        <v>0.6</v>
       </c>
       <c r="J20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -2625,276 +2620,281 @@
         <v>1</v>
       </c>
       <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
         <v>1</v>
       </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>2</v>
-      </c>
       <c r="R20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>2</v>
       </c>
       <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>Ladusvala
+Vanlig padda</t>
+        </is>
+      </c>
+      <c r="W20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 44135-2024 artfynd.xlsx", "A 44135-2024")</f>
+        <v/>
+      </c>
+      <c r="X20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 44135-2024 karta.png", "A 44135-2024")</f>
+        <v/>
+      </c>
+      <c r="Y20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 44135-2024 georefererad karta.tif", "A 44135-2024")</f>
+        <v/>
+      </c>
+      <c r="AA20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 44135-2024 FSC-klagomål.docx", "A 44135-2024")</f>
+        <v/>
+      </c>
+      <c r="AB20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 44135-2024 FSC-klagomål mail.docx", "A 44135-2024")</f>
+        <v/>
+      </c>
+      <c r="AC20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 44135-2024 tillsynsbegäran.docx", "A 44135-2024")</f>
+        <v/>
+      </c>
+      <c r="AD20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 44135-2024 tillsynsbegäran mail.docx", "A 44135-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>A 42724-2023</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="n">
+        <v>45176</v>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>HÖRBY</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>1</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2</v>
+      </c>
+      <c r="T21" t="n">
+        <v>4</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Grönvit nattviol</t>
+        </is>
+      </c>
+      <c r="W21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 42724-2023 artfynd.xlsx", "A 42724-2023")</f>
+        <v/>
+      </c>
+      <c r="X21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 42724-2023 karta.png", "A 42724-2023")</f>
+        <v/>
+      </c>
+      <c r="Y21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 42724-2023 georefererad karta.tif", "A 42724-2023")</f>
+        <v/>
+      </c>
+      <c r="AA21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 42724-2023 FSC-klagomål.docx", "A 42724-2023")</f>
+        <v/>
+      </c>
+      <c r="AB21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 42724-2023 FSC-klagomål mail.docx", "A 42724-2023")</f>
+        <v/>
+      </c>
+      <c r="AC21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 42724-2023 tillsynsbegäran.docx", "A 42724-2023")</f>
+        <v/>
+      </c>
+      <c r="AD21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 42724-2023 tillsynsbegäran mail.docx", "A 42724-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>A 824-2026</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="n">
+        <v>46030</v>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>HÖRBY</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>2</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2</v>
+      </c>
+      <c r="T22" t="n">
         <v>3</v>
       </c>
-      <c r="U20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>Hedblomster
 Skogslysing</t>
         </is>
       </c>
-      <c r="W20">
+      <c r="W22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 824-2026 artfynd.xlsx", "A 824-2026")</f>
         <v/>
       </c>
-      <c r="X20">
+      <c r="X22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 824-2026 karta.png", "A 824-2026")</f>
         <v/>
       </c>
-      <c r="Y20">
+      <c r="Y22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 824-2026 georefererad karta.tif", "A 824-2026")</f>
         <v/>
       </c>
-      <c r="AA20">
+      <c r="AA22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 824-2026 FSC-klagomål.docx", "A 824-2026")</f>
         <v/>
       </c>
-      <c r="AB20">
+      <c r="AB22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 824-2026 FSC-klagomål mail.docx", "A 824-2026")</f>
         <v/>
       </c>
-      <c r="AC20">
+      <c r="AC22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 824-2026 tillsynsbegäran.docx", "A 824-2026")</f>
         <v/>
       </c>
-      <c r="AD20">
+      <c r="AD22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 824-2026 tillsynsbegäran mail.docx", "A 824-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>A 44135-2024</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D21" s="1" t="n">
-        <v>45572</v>
-      </c>
-      <c r="E21" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>HÖRBY</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="J21" t="n">
-        <v>2</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>1</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>1</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="n">
-        <v>2</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2</v>
-      </c>
-      <c r="U21" t="n">
-        <v>0</v>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>Ladusvala
-Vanlig padda</t>
-        </is>
-      </c>
-      <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 44135-2024 artfynd.xlsx", "A 44135-2024")</f>
-        <v/>
-      </c>
-      <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 44135-2024 karta.png", "A 44135-2024")</f>
-        <v/>
-      </c>
-      <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 44135-2024 georefererad karta.tif", "A 44135-2024")</f>
-        <v/>
-      </c>
-      <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 44135-2024 FSC-klagomål.docx", "A 44135-2024")</f>
-        <v/>
-      </c>
-      <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 44135-2024 FSC-klagomål mail.docx", "A 44135-2024")</f>
-        <v/>
-      </c>
-      <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 44135-2024 tillsynsbegäran.docx", "A 44135-2024")</f>
-        <v/>
-      </c>
-      <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 44135-2024 tillsynsbegäran mail.docx", "A 44135-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>A 42724-2023</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D22" s="1" t="n">
-        <v>45176</v>
-      </c>
-      <c r="E22" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>HÖRBY</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="J22" t="n">
-        <v>1</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>1</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>1</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1</v>
-      </c>
-      <c r="S22" t="n">
-        <v>2</v>
-      </c>
-      <c r="T22" t="n">
-        <v>4</v>
-      </c>
-      <c r="U22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Grönvit nattviol</t>
-        </is>
-      </c>
-      <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 42724-2023 artfynd.xlsx", "A 42724-2023")</f>
-        <v/>
-      </c>
-      <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 42724-2023 karta.png", "A 42724-2023")</f>
-        <v/>
-      </c>
-      <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 42724-2023 georefererad karta.tif", "A 42724-2023")</f>
-        <v/>
-      </c>
-      <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 42724-2023 FSC-klagomål.docx", "A 42724-2023")</f>
-        <v/>
-      </c>
-      <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 42724-2023 FSC-klagomål mail.docx", "A 42724-2023")</f>
-        <v/>
-      </c>
-      <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 42724-2023 tillsynsbegäran.docx", "A 42724-2023")</f>
-        <v/>
-      </c>
-      <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 42724-2023 tillsynsbegäran mail.docx", "A 42724-2023")</f>
         <v/>
       </c>
     </row>
@@ -2918,7 +2918,7 @@
         <v>45317</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3007,7 +3007,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 31115-2024</t>
+          <t>A 47612-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45502</v>
+        <v>45203</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3037,7 +3037,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.8</v>
+        <v>2.4</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -3046,13 +3046,13 @@
         <v>0</v>
       </c>
       <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
         <v>1</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3064,7 +3064,7 @@
         <v>1</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3077,42 +3077,42 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Gullpudra</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 31115-2024 artfynd.xlsx", "A 31115-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 47612-2023 artfynd.xlsx", "A 47612-2023")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 31115-2024 karta.png", "A 31115-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 47612-2023 karta.png", "A 47612-2023")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 31115-2024 georefererad karta.tif", "A 31115-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 47612-2023 georefererad karta.tif", "A 47612-2023")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 31115-2024 FSC-klagomål.docx", "A 31115-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 47612-2023 FSC-klagomål.docx", "A 47612-2023")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 31115-2024 FSC-klagomål mail.docx", "A 31115-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 47612-2023 FSC-klagomål mail.docx", "A 47612-2023")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 31115-2024 tillsynsbegäran.docx", "A 31115-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 47612-2023 tillsynsbegäran.docx", "A 47612-2023")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 31115-2024 tillsynsbegäran mail.docx", "A 31115-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 47612-2023 tillsynsbegäran mail.docx", "A 47612-2023")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 25479-2025</t>
+          <t>A 36362-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3122,14 +3122,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45802</v>
+        <v>45868</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3142,7 +3142,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.7</v>
+        <v>3.7</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -3178,46 +3178,46 @@
         <v>1</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Lundvårlök</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 25479-2025 artfynd.xlsx", "A 25479-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 36362-2025 artfynd.xlsx", "A 36362-2025")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 25479-2025 karta.png", "A 25479-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 36362-2025 karta.png", "A 36362-2025")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 25479-2025 georefererad karta.tif", "A 25479-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 36362-2025 georefererad karta.tif", "A 36362-2025")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 25479-2025 FSC-klagomål.docx", "A 25479-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 36362-2025 FSC-klagomål.docx", "A 36362-2025")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 25479-2025 FSC-klagomål mail.docx", "A 25479-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 36362-2025 FSC-klagomål mail.docx", "A 36362-2025")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 25479-2025 tillsynsbegäran.docx", "A 25479-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 36362-2025 tillsynsbegäran.docx", "A 36362-2025")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 25479-2025 tillsynsbegäran mail.docx", "A 25479-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 36362-2025 tillsynsbegäran mail.docx", "A 36362-2025")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 36362-2025</t>
+          <t>A 113-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3231,10 +3231,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45868</v>
+        <v>44928</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3247,20 +3247,20 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>3.7</v>
+        <v>5.1</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
         <v>1</v>
       </c>
-      <c r="L26" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" t="n">
-        <v>0</v>
-      </c>
       <c r="N26" t="n">
         <v>0</v>
       </c>
@@ -3271,10 +3271,10 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>
@@ -3283,46 +3283,46 @@
         <v>1</v>
       </c>
       <c r="U26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Slåttergubbe</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 36362-2025 artfynd.xlsx", "A 36362-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 113-2023 artfynd.xlsx", "A 113-2023")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 36362-2025 karta.png", "A 36362-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 113-2023 karta.png", "A 113-2023")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 36362-2025 georefererad karta.tif", "A 36362-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 113-2023 georefererad karta.tif", "A 113-2023")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 36362-2025 FSC-klagomål.docx", "A 36362-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 113-2023 FSC-klagomål.docx", "A 113-2023")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 36362-2025 FSC-klagomål mail.docx", "A 36362-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 113-2023 FSC-klagomål mail.docx", "A 113-2023")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 36362-2025 tillsynsbegäran.docx", "A 36362-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 113-2023 tillsynsbegäran.docx", "A 113-2023")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 36362-2025 tillsynsbegäran mail.docx", "A 36362-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 113-2023 tillsynsbegäran mail.docx", "A 113-2023")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 47612-2023</t>
+          <t>A 25833-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3336,10 +3336,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45203</v>
+        <v>45463</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3352,7 +3352,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2.4</v>
+        <v>1.4</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3364,10 +3364,10 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3385,49 +3385,49 @@
         <v>1</v>
       </c>
       <c r="T27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U27" t="n">
         <v>0</v>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Slåttergubbe</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 47612-2023 artfynd.xlsx", "A 47612-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 25833-2024 artfynd.xlsx", "A 25833-2024")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 47612-2023 karta.png", "A 47612-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 25833-2024 karta.png", "A 25833-2024")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 47612-2023 georefererad karta.tif", "A 47612-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 25833-2024 georefererad karta.tif", "A 25833-2024")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 47612-2023 FSC-klagomål.docx", "A 47612-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 25833-2024 FSC-klagomål.docx", "A 25833-2024")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 47612-2023 FSC-klagomål mail.docx", "A 47612-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 25833-2024 FSC-klagomål mail.docx", "A 25833-2024")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 47612-2023 tillsynsbegäran.docx", "A 47612-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 25833-2024 tillsynsbegäran.docx", "A 25833-2024")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 47612-2023 tillsynsbegäran mail.docx", "A 47612-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 25833-2024 tillsynsbegäran mail.docx", "A 25833-2024")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 40376-2023</t>
+          <t>A 24823-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3441,10 +3441,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45169</v>
+        <v>46174</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3456,17 +3456,22 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I28" t="n">
-        <v>2.7</v>
+        <v>5.1</v>
       </c>
       <c r="J28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
         <v>0</v>
@@ -3481,7 +3486,7 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
@@ -3493,50 +3498,46 @@
         <v>1</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tandrot</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 40376-2023 artfynd.xlsx", "A 40376-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 24823-2026 artfynd.xlsx", "A 24823-2026")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 40376-2023 karta.png", "A 40376-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 24823-2026 karta.png", "A 24823-2026")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 40376-2023 georefererad karta.tif", "A 40376-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 24823-2026 georefererad karta.tif", "A 24823-2026")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 40376-2023 FSC-klagomål.docx", "A 40376-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 24823-2026 FSC-klagomål.docx", "A 24823-2026")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 40376-2023 FSC-klagomål mail.docx", "A 40376-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 24823-2026 FSC-klagomål mail.docx", "A 24823-2026")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 40376-2023 tillsynsbegäran.docx", "A 40376-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 24823-2026 tillsynsbegäran.docx", "A 24823-2026")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 40376-2023 tillsynsbegäran mail.docx", "A 40376-2023")</f>
-        <v/>
-      </c>
-      <c r="AE28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/fåglar/A 40376-2023 prioriterade fågelarter.docx", "A 40376-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 24823-2026 tillsynsbegäran mail.docx", "A 24823-2026")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 113-2023</t>
+          <t>A 16519-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3550,10 +3551,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44928</v>
+        <v>46112</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3566,7 +3567,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>5.1</v>
+        <v>0.8</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3578,10 +3579,10 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
         <v>1</v>
-      </c>
-      <c r="N29" t="n">
-        <v>0</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3606,42 +3607,42 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Slåttergubbe</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 113-2023 artfynd.xlsx", "A 113-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 16519-2026 artfynd.xlsx", "A 16519-2026")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 113-2023 karta.png", "A 113-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 16519-2026 karta.png", "A 16519-2026")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 113-2023 georefererad karta.tif", "A 113-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 16519-2026 georefererad karta.tif", "A 16519-2026")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 113-2023 FSC-klagomål.docx", "A 113-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 16519-2026 FSC-klagomål.docx", "A 16519-2026")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 113-2023 FSC-klagomål mail.docx", "A 113-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 16519-2026 FSC-klagomål mail.docx", "A 16519-2026")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 113-2023 tillsynsbegäran.docx", "A 113-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 16519-2026 tillsynsbegäran.docx", "A 16519-2026")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 113-2023 tillsynsbegäran mail.docx", "A 113-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 16519-2026 tillsynsbegäran mail.docx", "A 16519-2026")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 25833-2024</t>
+          <t>A 40376-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3655,10 +3656,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45463</v>
+        <v>45169</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3671,19 +3672,19 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.4</v>
+        <v>2.7</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
         <v>0</v>
@@ -3698,55 +3699,59 @@
         <v>1</v>
       </c>
       <c r="R30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
         <v>1</v>
       </c>
       <c r="T30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U30" t="n">
         <v>0</v>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>Slåttergubbe</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 25833-2024 artfynd.xlsx", "A 25833-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 40376-2023 artfynd.xlsx", "A 40376-2023")</f>
         <v/>
       </c>
       <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 25833-2024 karta.png", "A 25833-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 40376-2023 karta.png", "A 40376-2023")</f>
         <v/>
       </c>
       <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 25833-2024 georefererad karta.tif", "A 25833-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 40376-2023 georefererad karta.tif", "A 40376-2023")</f>
         <v/>
       </c>
       <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 25833-2024 FSC-klagomål.docx", "A 25833-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 40376-2023 FSC-klagomål.docx", "A 40376-2023")</f>
         <v/>
       </c>
       <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 25833-2024 FSC-klagomål mail.docx", "A 25833-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 40376-2023 FSC-klagomål mail.docx", "A 40376-2023")</f>
         <v/>
       </c>
       <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 25833-2024 tillsynsbegäran.docx", "A 25833-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 40376-2023 tillsynsbegäran.docx", "A 40376-2023")</f>
         <v/>
       </c>
       <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 25833-2024 tillsynsbegäran mail.docx", "A 25833-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 40376-2023 tillsynsbegäran mail.docx", "A 40376-2023")</f>
+        <v/>
+      </c>
+      <c r="AE30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/fåglar/A 40376-2023 prioriterade fågelarter.docx", "A 40376-2023")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 24823-2026</t>
+          <t>A 31115-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3760,10 +3765,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46174</v>
+        <v>45502</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3775,13 +3780,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I31" t="n">
-        <v>5.1</v>
+        <v>0.8</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3790,7 +3790,7 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
@@ -3805,7 +3805,7 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R31" t="n">
         <v>0</v>
@@ -3817,46 +3817,46 @@
         <v>1</v>
       </c>
       <c r="U31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>Tandrot</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="W31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 24823-2026 artfynd.xlsx", "A 24823-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 31115-2024 artfynd.xlsx", "A 31115-2024")</f>
         <v/>
       </c>
       <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 24823-2026 karta.png", "A 24823-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 31115-2024 karta.png", "A 31115-2024")</f>
         <v/>
       </c>
       <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 24823-2026 georefererad karta.tif", "A 24823-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 31115-2024 georefererad karta.tif", "A 31115-2024")</f>
         <v/>
       </c>
       <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 24823-2026 FSC-klagomål.docx", "A 24823-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 31115-2024 FSC-klagomål.docx", "A 31115-2024")</f>
         <v/>
       </c>
       <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 24823-2026 FSC-klagomål mail.docx", "A 24823-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 31115-2024 FSC-klagomål mail.docx", "A 31115-2024")</f>
         <v/>
       </c>
       <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 24823-2026 tillsynsbegäran.docx", "A 24823-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 31115-2024 tillsynsbegäran.docx", "A 31115-2024")</f>
         <v/>
       </c>
       <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 24823-2026 tillsynsbegäran mail.docx", "A 24823-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 31115-2024 tillsynsbegäran mail.docx", "A 31115-2024")</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 16519-2026</t>
+          <t>A 31284-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3870,10 +3870,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46112</v>
+        <v>46218</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3886,10 +3886,10 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.8</v>
+        <v>6.8</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
@@ -3901,7 +3901,7 @@
         <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -3910,10 +3910,10 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
         <v>1</v>
@@ -3926,42 +3926,42 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="W32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 16519-2026 artfynd.xlsx", "A 16519-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 31284-2026 artfynd.xlsx", "A 31284-2026")</f>
         <v/>
       </c>
       <c r="X32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 16519-2026 karta.png", "A 16519-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 31284-2026 karta.png", "A 31284-2026")</f>
         <v/>
       </c>
       <c r="Y32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 16519-2026 georefererad karta.tif", "A 16519-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 31284-2026 georefererad karta.tif", "A 31284-2026")</f>
         <v/>
       </c>
       <c r="AA32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 16519-2026 FSC-klagomål.docx", "A 16519-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 31284-2026 FSC-klagomål.docx", "A 31284-2026")</f>
         <v/>
       </c>
       <c r="AB32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 16519-2026 FSC-klagomål mail.docx", "A 16519-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 31284-2026 FSC-klagomål mail.docx", "A 31284-2026")</f>
         <v/>
       </c>
       <c r="AC32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 16519-2026 tillsynsbegäran.docx", "A 16519-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 31284-2026 tillsynsbegäran.docx", "A 31284-2026")</f>
         <v/>
       </c>
       <c r="AD32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 16519-2026 tillsynsbegäran mail.docx", "A 16519-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 31284-2026 tillsynsbegäran mail.docx", "A 31284-2026")</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 31284-2026</t>
+          <t>A 30165-2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>46218</v>
+        <v>46206</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3991,23 +3991,23 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>6.8</v>
+        <v>1.4</v>
       </c>
       <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
         <v>1</v>
       </c>
-      <c r="K33" t="n">
-        <v>0</v>
-      </c>
-      <c r="L33" t="n">
-        <v>0</v>
-      </c>
-      <c r="M33" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" t="n">
-        <v>0</v>
-      </c>
       <c r="O33" t="n">
         <v>0</v>
       </c>
@@ -4015,10 +4015,10 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S33" t="n">
         <v>1</v>
@@ -4031,42 +4031,42 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="W33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 31284-2026 artfynd.xlsx", "A 31284-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 30165-2026 artfynd.xlsx", "A 30165-2026")</f>
         <v/>
       </c>
       <c r="X33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 31284-2026 karta.png", "A 31284-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 30165-2026 karta.png", "A 30165-2026")</f>
         <v/>
       </c>
       <c r="Y33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 31284-2026 georefererad karta.tif", "A 31284-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 30165-2026 georefererad karta.tif", "A 30165-2026")</f>
         <v/>
       </c>
       <c r="AA33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 31284-2026 FSC-klagomål.docx", "A 31284-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 30165-2026 FSC-klagomål.docx", "A 30165-2026")</f>
         <v/>
       </c>
       <c r="AB33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 31284-2026 FSC-klagomål mail.docx", "A 31284-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 30165-2026 FSC-klagomål mail.docx", "A 30165-2026")</f>
         <v/>
       </c>
       <c r="AC33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 31284-2026 tillsynsbegäran.docx", "A 31284-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 30165-2026 tillsynsbegäran.docx", "A 30165-2026")</f>
         <v/>
       </c>
       <c r="AD33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 31284-2026 tillsynsbegäran mail.docx", "A 31284-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 30165-2026 tillsynsbegäran mail.docx", "A 30165-2026")</f>
         <v/>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 30165-2026</t>
+          <t>A 29129-2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4080,10 +4080,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>46206</v>
+        <v>46202</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4095,8 +4095,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I34" t="n">
-        <v>1.4</v>
+        <v>10.5</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -4105,13 +4110,13 @@
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M34" t="n">
         <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4123,7 +4128,7 @@
         <v>1</v>
       </c>
       <c r="R34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
         <v>1</v>
@@ -4136,42 +4141,42 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Ekticka</t>
         </is>
       </c>
       <c r="W34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 30165-2026 artfynd.xlsx", "A 30165-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 29129-2026 artfynd.xlsx", "A 29129-2026")</f>
         <v/>
       </c>
       <c r="X34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 30165-2026 karta.png", "A 30165-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 29129-2026 karta.png", "A 29129-2026")</f>
         <v/>
       </c>
       <c r="Y34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 30165-2026 georefererad karta.tif", "A 30165-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 29129-2026 georefererad karta.tif", "A 29129-2026")</f>
         <v/>
       </c>
       <c r="AA34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 30165-2026 FSC-klagomål.docx", "A 30165-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 29129-2026 FSC-klagomål.docx", "A 29129-2026")</f>
         <v/>
       </c>
       <c r="AB34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 30165-2026 FSC-klagomål mail.docx", "A 30165-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 29129-2026 FSC-klagomål mail.docx", "A 29129-2026")</f>
         <v/>
       </c>
       <c r="AC34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 30165-2026 tillsynsbegäran.docx", "A 30165-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 29129-2026 tillsynsbegäran.docx", "A 29129-2026")</f>
         <v/>
       </c>
       <c r="AD34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 30165-2026 tillsynsbegäran mail.docx", "A 30165-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 29129-2026 tillsynsbegäran mail.docx", "A 29129-2026")</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 29129-2026</t>
+          <t>A 21713-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4185,10 +4190,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>46202</v>
+        <v>45783</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4200,22 +4205,17 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I35" t="n">
-        <v>10.5</v>
+        <v>0.8</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
         <v>0</v>
@@ -4230,7 +4230,7 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -4246,42 +4246,42 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>Ekticka</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="W35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 29129-2026 artfynd.xlsx", "A 29129-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 21713-2025 artfynd.xlsx", "A 21713-2025")</f>
         <v/>
       </c>
       <c r="X35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 29129-2026 karta.png", "A 29129-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 21713-2025 karta.png", "A 21713-2025")</f>
         <v/>
       </c>
       <c r="Y35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 29129-2026 georefererad karta.tif", "A 29129-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 21713-2025 georefererad karta.tif", "A 21713-2025")</f>
         <v/>
       </c>
       <c r="AA35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 29129-2026 FSC-klagomål.docx", "A 29129-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 21713-2025 FSC-klagomål.docx", "A 21713-2025")</f>
         <v/>
       </c>
       <c r="AB35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 29129-2026 FSC-klagomål mail.docx", "A 29129-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 21713-2025 FSC-klagomål mail.docx", "A 21713-2025")</f>
         <v/>
       </c>
       <c r="AC35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 29129-2026 tillsynsbegäran.docx", "A 29129-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 21713-2025 tillsynsbegäran.docx", "A 21713-2025")</f>
         <v/>
       </c>
       <c r="AD35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 29129-2026 tillsynsbegäran mail.docx", "A 29129-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 21713-2025 tillsynsbegäran mail.docx", "A 21713-2025")</f>
         <v/>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 21713-2025</t>
+          <t>A 25479-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4291,14 +4291,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45783</v>
+        <v>45802</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4311,13 +4311,13 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="n">
         <v>1</v>
-      </c>
-      <c r="K36" t="n">
-        <v>0</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
@@ -4351,35 +4351,35 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Lundvårlök</t>
         </is>
       </c>
       <c r="W36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 21713-2025 artfynd.xlsx", "A 21713-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 25479-2025 artfynd.xlsx", "A 25479-2025")</f>
         <v/>
       </c>
       <c r="X36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 21713-2025 karta.png", "A 21713-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 25479-2025 karta.png", "A 25479-2025")</f>
         <v/>
       </c>
       <c r="Y36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 21713-2025 georefererad karta.tif", "A 21713-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 25479-2025 georefererad karta.tif", "A 25479-2025")</f>
         <v/>
       </c>
       <c r="AA36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 21713-2025 FSC-klagomål.docx", "A 21713-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 25479-2025 FSC-klagomål.docx", "A 25479-2025")</f>
         <v/>
       </c>
       <c r="AB36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 21713-2025 FSC-klagomål mail.docx", "A 21713-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 25479-2025 FSC-klagomål mail.docx", "A 25479-2025")</f>
         <v/>
       </c>
       <c r="AC36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 21713-2025 tillsynsbegäran.docx", "A 21713-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 25479-2025 tillsynsbegäran.docx", "A 25479-2025")</f>
         <v/>
       </c>
       <c r="AD36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 21713-2025 tillsynsbegäran mail.docx", "A 21713-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 25479-2025 tillsynsbegäran mail.docx", "A 25479-2025")</f>
         <v/>
       </c>
     </row>
@@ -4403,7 +4403,7 @@
         <v>45089</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4508,7 +4508,7 @@
         <v>44999</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4613,7 +4613,7 @@
         <v>44509</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4686,7 +4686,7 @@
         <v>44663</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4759,7 +4759,7 @@
         <v>44509</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4832,7 +4832,7 @@
         <v>44697</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4905,7 +4905,7 @@
         <v>44510</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4978,7 +4978,7 @@
         <v>44834</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5051,7 +5051,7 @@
         <v>44771</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5124,7 +5124,7 @@
         <v>44466</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5197,7 +5197,7 @@
         <v>44789</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5270,7 +5270,7 @@
         <v>44733</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5326,7 +5326,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 2979-2024</t>
+          <t>A 43380-2022</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5340,10 +5340,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45315</v>
+        <v>44834</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5355,13 +5355,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I49" t="n">
-        <v>4.7</v>
+        <v>1.7</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5404,7 +5399,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 24670-2024</t>
+          <t>A 47609-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5414,14 +5409,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45460</v>
+        <v>45203</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5434,7 +5429,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.2</v>
+        <v>2.4</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5477,7 +5472,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 18609-2025</t>
+          <t>A 9974-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5491,10 +5486,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45763</v>
+        <v>45363</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5550,7 +5545,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 3471-2025</t>
+          <t>A 15970-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5564,10 +5559,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45680</v>
+        <v>45405</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5580,7 +5575,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>3.7</v>
+        <v>1.8</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5623,7 +5618,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 33359-2023</t>
+          <t>A 5163-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5637,10 +5632,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45128</v>
+        <v>45330</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5652,8 +5647,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I53" t="n">
-        <v>0.9</v>
+        <v>7.1</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5696,7 +5696,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 37757-2024</t>
+          <t>A 37724-2022</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5710,10 +5710,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45541</v>
+        <v>44810</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5726,7 +5726,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5769,7 +5769,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 31596-2023</t>
+          <t>A 37728-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5783,10 +5783,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45117</v>
+        <v>44810</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5799,7 +5799,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5842,7 +5842,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 2816-2025</t>
+          <t>A 56818-2022</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5852,14 +5852,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45677</v>
+        <v>44894</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5872,7 +5872,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5915,7 +5915,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 44613-2023</t>
+          <t>A 33359-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5929,10 +5929,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45189</v>
+        <v>45128</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5944,13 +5944,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I57" t="n">
-        <v>3.8</v>
+        <v>0.9</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5993,7 +5988,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 58360-2023</t>
+          <t>A 54894-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6007,10 +6002,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45250</v>
+        <v>45236</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6023,7 +6018,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>2.5</v>
+        <v>0.6</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -6066,7 +6061,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 28785-2023</t>
+          <t>A 36689-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6080,10 +6075,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45104</v>
+        <v>45537</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6095,8 +6090,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I59" t="n">
-        <v>2.1</v>
+        <v>9.5</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6139,7 +6139,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 16101-2025</t>
+          <t>A 28746-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6153,10 +6153,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45750</v>
+        <v>45478</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6169,7 +6169,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.5</v>
+        <v>1.9</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6212,7 +6212,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 4756-2025</t>
+          <t>A 37082-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6222,14 +6222,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45688</v>
+        <v>45155</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6242,7 +6242,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6285,7 +6285,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 48397-2022</t>
+          <t>A 2752-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6299,10 +6299,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44858</v>
+        <v>44944</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6314,8 +6314,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I62" t="n">
-        <v>1.7</v>
+        <v>0.6</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6358,7 +6363,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 6886-2024</t>
+          <t>A 38080-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6372,10 +6377,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45342</v>
+        <v>45545</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6387,13 +6392,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I63" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6436,7 +6436,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 33358-2023</t>
+          <t>A 28785-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6446,14 +6446,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45128</v>
+        <v>45104</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6466,7 +6466,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.4</v>
+        <v>2.1</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 16665-2025</t>
+          <t>A 48397-2022</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6523,10 +6523,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45754</v>
+        <v>44858</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6539,7 +6539,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>2.4</v>
+        <v>1.7</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6582,7 +6582,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 43711-2024</t>
+          <t>A 13225-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6592,14 +6592,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45569</v>
+        <v>45386</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6612,7 +6612,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>3.4</v>
+        <v>0.7</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6655,7 +6655,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 23484-2025</t>
+          <t>A 13226-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6669,10 +6669,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45792</v>
+        <v>45386</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6685,7 +6685,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>3.5</v>
+        <v>0.7</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6728,7 +6728,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 554-2026</t>
+          <t>A 15998-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6742,10 +6742,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46029</v>
+        <v>45405</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6758,7 +6758,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6801,7 +6801,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 47641-2023</t>
+          <t>A 16001-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6815,10 +6815,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45203</v>
+        <v>45405</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6831,7 +6831,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>4.8</v>
+        <v>0.2</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6874,7 +6874,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 826-2026</t>
+          <t>A 43828-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6888,10 +6888,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46030</v>
+        <v>45572</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6903,13 +6903,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I70" t="n">
-        <v>0.3</v>
+        <v>0.9</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6952,7 +6947,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 829-2026</t>
+          <t>A 8260-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6966,10 +6961,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46030</v>
+        <v>46064</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6981,13 +6976,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I71" t="n">
-        <v>6.9</v>
+        <v>3.3</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -7030,7 +7020,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 821-2026</t>
+          <t>A 8259-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7044,10 +7034,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46030</v>
+        <v>46064</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7059,13 +7049,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I72" t="n">
-        <v>4.3</v>
+        <v>3.1</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7108,7 +7093,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 3346-2024</t>
+          <t>A 29244-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7122,10 +7107,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45317</v>
+        <v>45824</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7138,7 +7123,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7181,7 +7166,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 39298-2023</t>
+          <t>A 29354-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7195,10 +7180,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45166</v>
+        <v>45824</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7211,7 +7196,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>4.6</v>
+        <v>0.8</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7254,7 +7239,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 39507-2024</t>
+          <t>A 10731-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7268,10 +7253,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45551</v>
+        <v>46078</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7285,11 +7270,11 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.3</v>
+        <v>4.8</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7332,7 +7317,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 788-2024</t>
+          <t>A 18609-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7346,10 +7331,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45300</v>
+        <v>45763</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7405,7 +7390,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 28550-2025</t>
+          <t>A 56750-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7419,10 +7404,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45818</v>
+        <v>45238</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7435,7 +7420,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>5</v>
+        <v>0.8</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7478,7 +7463,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 9612-2025</t>
+          <t>A 42715-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7492,10 +7477,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45715</v>
+        <v>45176</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7508,7 +7493,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7551,7 +7536,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 9974-2024</t>
+          <t>A 2981-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7565,10 +7550,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45363</v>
+        <v>45315</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7580,8 +7565,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I79" t="n">
-        <v>0.6</v>
+        <v>6.4</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7624,7 +7614,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 29244-2025</t>
+          <t>A 13633-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7638,10 +7628,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45824</v>
+        <v>45390</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7654,7 +7644,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7697,7 +7687,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 29354-2025</t>
+          <t>A 32459-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7711,10 +7701,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45824</v>
+        <v>45838</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7727,7 +7717,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7770,7 +7760,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 11943-2025</t>
+          <t>A 32958-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7784,10 +7774,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45728</v>
+        <v>45839</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7800,7 +7790,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.2</v>
+        <v>5</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7843,7 +7833,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 1989-2026</t>
+          <t>A 37756-2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7857,10 +7847,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46035</v>
+        <v>45541</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7873,7 +7863,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>2.5</v>
+        <v>3.2</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7916,7 +7906,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 42715-2023</t>
+          <t>A 58641-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7926,14 +7916,14 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45176</v>
+        <v>45251</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7946,7 +7936,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7989,7 +7979,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 28918-2023</t>
+          <t>A 18603-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -8003,10 +7993,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45104</v>
+        <v>45763</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8019,7 +8009,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -8062,7 +8052,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 32958-2025</t>
+          <t>A 3346-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -8076,10 +8066,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45839</v>
+        <v>45317</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8092,7 +8082,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8135,7 +8125,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 32459-2025</t>
+          <t>A 14307-2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8149,10 +8139,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45838</v>
+        <v>46099</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8165,7 +8155,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8208,7 +8198,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 2981-2024</t>
+          <t>A 3520-2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8222,10 +8212,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45315</v>
+        <v>46042</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8237,13 +8227,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I88" t="n">
-        <v>6.4</v>
+        <v>0.8</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8286,7 +8271,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 34154-2025</t>
+          <t>A 788-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8300,10 +8285,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45845</v>
+        <v>45300</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8316,7 +8301,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>5</v>
+        <v>0.6</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8359,7 +8344,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 43932-2023</t>
+          <t>A 3470-2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8373,10 +8358,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45187</v>
+        <v>46042</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8389,7 +8374,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8432,7 +8417,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 43935-2023</t>
+          <t>A 9850-2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8446,10 +8431,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45187</v>
+        <v>46072</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8462,7 +8447,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>2.9</v>
+        <v>2.2</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8505,7 +8490,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 37756-2024</t>
+          <t>A 3513-2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8519,10 +8504,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45541</v>
+        <v>46042</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8535,7 +8520,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>3.2</v>
+        <v>0.9</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8578,7 +8563,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 2747-2023</t>
+          <t>A 36355-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8592,10 +8577,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>44944</v>
+        <v>45868</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8607,13 +8592,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I93" t="n">
-        <v>4.6</v>
+        <v>3.6</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8656,7 +8636,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 48427-2022</t>
+          <t>A 25552-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8670,10 +8650,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>44858</v>
+        <v>45803</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8685,13 +8665,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I94" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8734,7 +8709,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 3013-2026</t>
+          <t>A 50715-2024</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8748,10 +8723,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>46038</v>
+        <v>45602</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8764,7 +8739,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8807,7 +8782,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 8084-2022</t>
+          <t>A 38147-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8821,10 +8796,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>44608</v>
+        <v>45882</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8837,7 +8812,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8880,7 +8855,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 43828-2024</t>
+          <t>A 7402-2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8894,10 +8869,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45572</v>
+        <v>46059</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8910,7 +8885,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>0.9</v>
+        <v>4.7</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8953,7 +8928,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 36355-2025</t>
+          <t>A 2816-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8963,14 +8938,14 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45868</v>
+        <v>45677</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8983,7 +8958,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>3.6</v>
+        <v>2</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -9026,7 +9001,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 13225-2024</t>
+          <t>A 16101-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -9040,10 +9015,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45386</v>
+        <v>45750</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9056,7 +9031,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -9099,7 +9074,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 13226-2024</t>
+          <t>A 34422-2024</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -9109,14 +9084,14 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45386</v>
+        <v>45525</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9129,7 +9104,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -9172,7 +9147,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 47552-2023</t>
+          <t>A 11943-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9186,10 +9161,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45203</v>
+        <v>45728</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9202,7 +9177,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9245,7 +9220,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 25552-2025</t>
+          <t>A 44613-2023</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9259,10 +9234,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45803</v>
+        <v>45189</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9274,8 +9249,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I102" t="n">
-        <v>2</v>
+        <v>3.8</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9318,7 +9298,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 34147-2025</t>
+          <t>A 34154-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9335,7 +9315,7 @@
         <v>45845</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9348,7 +9328,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>18.7</v>
+        <v>5</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9391,7 +9371,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 38147-2025</t>
+          <t>A 43937-2023</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9405,10 +9385,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45882</v>
+        <v>45187</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9421,7 +9401,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>1.6</v>
+        <v>2.6</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9464,7 +9444,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 51757-2025</t>
+          <t>A 43939-2023</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9474,14 +9454,14 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45951</v>
+        <v>45187</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9493,13 +9473,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I105" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9542,7 +9517,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 5374-2026</t>
+          <t>A 67426-2021</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9556,10 +9531,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>46050</v>
+        <v>44523</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9572,7 +9547,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9615,7 +9590,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 52930-2025</t>
+          <t>A 5079-2026</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9629,10 +9604,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45957</v>
+        <v>46049</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9644,13 +9619,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I107" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9693,7 +9663,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 52929-2025</t>
+          <t>A 3534-2025</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9707,10 +9677,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45957</v>
+        <v>45680</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9724,11 +9694,11 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I108" t="n">
-        <v>8.300000000000001</v>
+        <v>4.8</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9771,7 +9741,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 2752-2023</t>
+          <t>A 7831-2025</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9785,10 +9755,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>44944</v>
+        <v>45706</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9798,11 +9768,6 @@
       <c r="G109" t="inlineStr">
         <is>
           <t>HÖRBY</t>
-        </is>
-      </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I109" t="n">
@@ -9849,7 +9814,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 37082-2023</t>
+          <t>A 65073-2023</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9859,14 +9824,14 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45155</v>
+        <v>45287</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9879,7 +9844,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>0.5</v>
+        <v>1.7</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9922,7 +9887,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 54431-2023</t>
+          <t>A 18735-2023</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9936,10 +9901,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45226</v>
+        <v>45043</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9952,7 +9917,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>3.2</v>
+        <v>1</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9995,7 +9960,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 54765-2025</t>
+          <t>A 28493-2023</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -10009,10 +9974,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45966</v>
+        <v>45103</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10025,7 +9990,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>2.6</v>
+        <v>0.8</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -10068,7 +10033,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 8310-2026</t>
+          <t>A 36840-2024</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -10082,10 +10047,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>46064</v>
+        <v>45538</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10097,8 +10062,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I113" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -10141,7 +10111,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 8260-2026</t>
+          <t>A 60913-2023</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -10155,10 +10125,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>46064</v>
+        <v>45261</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10171,7 +10141,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>3.3</v>
+        <v>0.7</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -10214,7 +10184,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 55304-2025</t>
+          <t>A 8084-2022</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10224,14 +10194,14 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45970</v>
+        <v>44608</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10244,7 +10214,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>0.4</v>
+        <v>1.5</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10287,7 +10257,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 55306-2025</t>
+          <t>A 28625-2023</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10297,14 +10267,14 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45970</v>
+        <v>45103</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10317,7 +10287,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>0.3</v>
+        <v>4.8</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10360,7 +10330,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 28625-2023</t>
+          <t>A 4597-2026</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10374,10 +10344,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45103</v>
+        <v>46048</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10390,7 +10360,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>4.8</v>
+        <v>1.3</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10433,7 +10403,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 8259-2026</t>
+          <t>A 13804-2024</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10447,10 +10417,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>46064</v>
+        <v>45391</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10463,7 +10433,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>3.1</v>
+        <v>0.5</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10506,7 +10476,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 40994-2025</t>
+          <t>A 34147-2025</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10520,10 +10490,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45898</v>
+        <v>45845</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10536,7 +10506,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>5.6</v>
+        <v>18.7</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10579,7 +10549,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 57269-2025</t>
+          <t>A 6886-2024</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10593,10 +10563,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45979</v>
+        <v>45342</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10614,7 +10584,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>5.5</v>
+        <v>0.5</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10657,7 +10627,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 38080-2024</t>
+          <t>A 4590-2026</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10671,10 +10641,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45545</v>
+        <v>46048</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10687,7 +10657,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10730,7 +10700,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 13633-2024</t>
+          <t>A 6350-2026</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10744,10 +10714,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45390</v>
+        <v>46051</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10760,7 +10730,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>1.1</v>
+        <v>2.4</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10803,7 +10773,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 44816-2023</t>
+          <t>A 18369-2025</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10817,10 +10787,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45190</v>
+        <v>45762</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10833,7 +10803,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>1</v>
+        <v>2.2</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10876,7 +10846,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 28493-2023</t>
+          <t>A 1106-2023</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10890,10 +10860,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45103</v>
+        <v>44935</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10906,7 +10876,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10949,7 +10919,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 59308-2025</t>
+          <t>A 17073-2023</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10963,10 +10933,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45989</v>
+        <v>45034</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11022,7 +10992,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 10731-2026</t>
+          <t>A 2979-2024</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -11036,10 +11006,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>46078</v>
+        <v>45315</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11057,7 +11027,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -11100,7 +11070,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 43879-2023</t>
+          <t>A 3177-2026</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -11110,14 +11080,14 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45187</v>
+        <v>46041</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11129,13 +11099,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I127" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -11178,7 +11143,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 47609-2023</t>
+          <t>A 31596-2023</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -11192,10 +11157,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45203</v>
+        <v>45117</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11208,7 +11173,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>2.4</v>
+        <v>0.5</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -11251,7 +11216,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 62277-2025</t>
+          <t>A 51757-2025</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11261,14 +11226,14 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>46006</v>
+        <v>45951</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11280,8 +11245,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I129" t="n">
-        <v>2.4</v>
+        <v>1.3</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11324,7 +11294,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 43882-2023</t>
+          <t>A 52929-2025</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11338,10 +11308,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45187</v>
+        <v>45957</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11359,7 +11329,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>1.2</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11402,7 +11372,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 67426-2021</t>
+          <t>A 52930-2025</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11416,10 +11386,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>44523</v>
+        <v>45957</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11431,8 +11401,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I131" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11475,7 +11450,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 3239-2023</t>
+          <t>A 59284-2025</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11489,10 +11464,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>44946</v>
+        <v>45988</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11505,7 +11480,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>0.4</v>
+        <v>1.5</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11548,7 +11523,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 60963-2023</t>
+          <t>A 54184-2024</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11562,10 +11537,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45261</v>
+        <v>45616</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11578,7 +11553,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11621,7 +11596,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 14307-2026</t>
+          <t>A 43932-2023</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11635,10 +11610,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>46099</v>
+        <v>45187</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11651,7 +11626,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11694,7 +11669,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 43685-2022</t>
+          <t>A 43935-2023</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11704,14 +11679,14 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>44837</v>
+        <v>45187</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11724,7 +11699,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>1.3</v>
+        <v>2.9</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11767,7 +11742,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 3470-2026</t>
+          <t>A 10524-2026</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11781,10 +11756,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>46042</v>
+        <v>46076</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11797,7 +11772,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11840,7 +11815,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 55265-2023</t>
+          <t>A 10500-2026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11854,10 +11829,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45237</v>
+        <v>46076</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11870,7 +11845,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11913,7 +11888,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 3513-2026</t>
+          <t>A 20403-2024</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11927,10 +11902,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>46042</v>
+        <v>45435</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11986,7 +11961,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 3520-2026</t>
+          <t>A 54765-2025</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -12000,10 +11975,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>46042</v>
+        <v>45966</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12016,7 +11991,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>0.8</v>
+        <v>2.6</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -12059,7 +12034,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 9850-2026</t>
+          <t>A 3040-2024</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -12073,10 +12048,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>46072</v>
+        <v>45316</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12089,7 +12064,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>2.2</v>
+        <v>4</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -12132,7 +12107,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 5163-2024</t>
+          <t>A 16518-2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -12146,10 +12121,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45330</v>
+        <v>46112</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12161,13 +12136,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H141" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I141" t="n">
-        <v>7.1</v>
+        <v>0.8</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -12210,7 +12180,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 18603-2025</t>
+          <t>A 44816-2023</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -12224,10 +12194,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45763</v>
+        <v>45190</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12240,7 +12210,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -12283,7 +12253,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 7402-2026</t>
+          <t>A 47552-2023</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12297,10 +12267,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>46059</v>
+        <v>45203</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12313,7 +12283,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>4.7</v>
+        <v>1.3</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -12356,7 +12326,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 3534-2025</t>
+          <t>A 40994-2025</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12370,10 +12340,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45680</v>
+        <v>45898</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12385,13 +12355,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H144" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I144" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -12434,7 +12399,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 20595-2024</t>
+          <t>A 55304-2025</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12444,14 +12409,14 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45436</v>
+        <v>45970</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12463,13 +12428,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H145" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I145" t="n">
-        <v>3.5</v>
+        <v>0.4</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12512,7 +12472,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 43937-2023</t>
+          <t>A 55306-2025</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12522,14 +12482,14 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45187</v>
+        <v>45970</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12542,7 +12502,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>2.6</v>
+        <v>0.3</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12585,7 +12545,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 43939-2023</t>
+          <t>A 54431-2023</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12599,10 +12559,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45187</v>
+        <v>45226</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12615,7 +12575,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>0.6</v>
+        <v>3.2</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12658,7 +12618,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 28501-2023</t>
+          <t>A 19777-2023</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12672,10 +12632,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45103</v>
+        <v>45051</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12688,7 +12648,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>3.6</v>
+        <v>4.3</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12731,7 +12691,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 28527-2023</t>
+          <t>A 43879-2023</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12745,10 +12705,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45103</v>
+        <v>45187</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12760,8 +12720,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I149" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12804,7 +12769,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 54894-2023</t>
+          <t>A 29138-2026</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12814,14 +12779,14 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45236</v>
+        <v>46202</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12833,8 +12798,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I150" t="n">
-        <v>0.6</v>
+        <v>4.2</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12877,7 +12847,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 37276-2024</t>
+          <t>A 29135-2026</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12887,14 +12857,14 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45540</v>
+        <v>46202</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12906,8 +12876,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I151" t="n">
-        <v>1.6</v>
+        <v>4.7</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12950,7 +12925,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 65073-2023</t>
+          <t>A 29137-2026</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12960,14 +12935,14 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45287</v>
+        <v>46202</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12979,8 +12954,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I152" t="n">
-        <v>1.7</v>
+        <v>7.8</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -13023,7 +13003,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 36689-2024</t>
+          <t>A 57269-2025</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -13033,14 +13013,14 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45537</v>
+        <v>45979</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13058,7 +13038,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>9.5</v>
+        <v>5.5</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -13101,7 +13081,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 5079-2026</t>
+          <t>A 3471-2025</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -13115,10 +13095,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>46049</v>
+        <v>45680</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13131,7 +13111,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>1.3</v>
+        <v>3.7</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -13174,7 +13154,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 31522-2022</t>
+          <t>A 49726-2023</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -13188,10 +13168,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>44775</v>
+        <v>45208</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13204,7 +13184,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -13247,7 +13227,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 54184-2024</t>
+          <t>A 29124-2026</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -13261,10 +13241,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45616</v>
+        <v>46202</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13277,7 +13257,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>0.5</v>
+        <v>2.9</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -13320,7 +13300,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 60913-2023</t>
+          <t>A 28501-2023</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -13334,10 +13314,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45261</v>
+        <v>45103</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13350,7 +13330,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>0.7</v>
+        <v>3.6</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -13393,7 +13373,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 44073-2024</t>
+          <t>A 33873-2024</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -13407,10 +13387,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45572</v>
+        <v>45521</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13423,7 +13403,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>1</v>
+        <v>3.5</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -13466,7 +13446,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 11941-2025</t>
+          <t>A 58360-2023</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13480,10 +13460,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45728</v>
+        <v>45250</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13496,7 +13476,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>0.6</v>
+        <v>2.5</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -13539,7 +13519,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 43380-2022</t>
+          <t>A 39298-2023</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -13553,10 +13533,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>44834</v>
+        <v>45166</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13569,7 +13549,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>1.7</v>
+        <v>4.6</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13612,7 +13592,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 20403-2024</t>
+          <t>A 29219-2023</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13626,10 +13606,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45435</v>
+        <v>45105</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13642,7 +13622,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13685,7 +13665,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 1106-2023</t>
+          <t>A 3542-2025</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13699,10 +13679,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>44935</v>
+        <v>45680</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13714,8 +13694,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I162" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13758,7 +13743,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 49726-2023</t>
+          <t>A 47637-2023</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13772,10 +13757,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>45208</v>
+        <v>45203</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13788,7 +13773,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13831,7 +13816,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 36840-2024</t>
+          <t>A 59308-2025</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13845,10 +13830,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45538</v>
+        <v>45989</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13860,13 +13845,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H164" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I164" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13909,7 +13889,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 24724-2024</t>
+          <t>A 30934-2026</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13919,14 +13899,14 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45460</v>
+        <v>46213</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13939,7 +13919,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13982,7 +13962,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 4597-2026</t>
+          <t>A 34737-2026</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13996,10 +13976,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>46048</v>
+        <v>46258</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14012,7 +13992,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -14055,7 +14035,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 58641-2023</t>
+          <t>A 34740-2026</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -14065,14 +14045,14 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45251</v>
+        <v>46258</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14085,7 +14065,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>1.2</v>
+        <v>2.1</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -14128,7 +14108,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 3040-2024</t>
+          <t>A 23606-2026</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -14138,14 +14118,14 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>45316</v>
+        <v>46162</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14158,7 +14138,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>4</v>
+        <v>9.4</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -14201,7 +14181,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 15970-2024</t>
+          <t>A 31286-2026</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -14215,10 +14195,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>45405</v>
+        <v>46218</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14231,7 +14211,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -14274,7 +14254,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 18735-2023</t>
+          <t>A 24670-2024</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -14284,14 +14264,14 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45043</v>
+        <v>45460</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14304,7 +14284,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -14347,7 +14327,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 6081-2023</t>
+          <t>A 55307-2025</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -14361,10 +14341,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>44959</v>
+        <v>45970</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14377,7 +14357,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>0.4</v>
+        <v>2.5</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -14420,7 +14400,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 29219-2023</t>
+          <t>A 6081-2023</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -14434,10 +14414,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45105</v>
+        <v>44959</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14450,7 +14430,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -14493,7 +14473,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 56818-2022</t>
+          <t>A 62277-2025</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -14507,10 +14487,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>44894</v>
+        <v>46006</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14523,7 +14503,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -14566,7 +14546,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 4590-2026</t>
+          <t>A 31114-2024</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14580,10 +14560,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>46048</v>
+        <v>45502</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14596,7 +14576,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14639,7 +14619,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 6350-2026</t>
+          <t>A 11941-2025</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14653,10 +14633,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>46051</v>
+        <v>45728</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14669,7 +14649,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>2.4</v>
+        <v>0.6</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14712,7 +14692,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 18369-2025</t>
+          <t>A 57017-2025</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14726,10 +14706,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45762</v>
+        <v>45978</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14742,7 +14722,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>2.2</v>
+        <v>5.5</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14785,7 +14765,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 3177-2026</t>
+          <t>A 38684-2022</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14795,14 +14775,14 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>46041</v>
+        <v>44814</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14815,7 +14795,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14858,7 +14838,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 34422-2024</t>
+          <t>A 37757-2024</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14868,14 +14848,14 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45525</v>
+        <v>45541</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14888,7 +14868,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14931,7 +14911,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 7831-2025</t>
+          <t>A 20047-2026</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14945,10 +14925,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>45706</v>
+        <v>46136</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14961,7 +14941,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -15004,7 +14984,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 56750-2023</t>
+          <t>A 25183-2023</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -15018,10 +14998,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>45238</v>
+        <v>45079</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15034,7 +15014,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -15077,7 +15057,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 59284-2025</t>
+          <t>A 44073-2024</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -15091,10 +15071,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>45988</v>
+        <v>45572</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15107,7 +15087,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -15150,7 +15130,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 10500-2026</t>
+          <t>A 37276-2024</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -15164,10 +15144,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>46076</v>
+        <v>45540</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15180,7 +15160,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -15223,7 +15203,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 10524-2026</t>
+          <t>A 38073-2026</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -15237,10 +15217,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>46076</v>
+        <v>46280</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15253,7 +15233,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>1.6</v>
+        <v>2.3</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -15296,7 +15276,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 17073-2023</t>
+          <t>A 20595-2024</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -15310,10 +15290,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>45034</v>
+        <v>45436</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15325,8 +15305,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I184" t="n">
-        <v>1.2</v>
+        <v>3.5</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -15369,7 +15354,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 16518-2026</t>
+          <t>A 826-2026</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -15383,10 +15368,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>46112</v>
+        <v>46030</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15398,8 +15383,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I185" t="n">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -15442,7 +15432,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 19420-2022</t>
+          <t>A 829-2026</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -15456,10 +15446,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>44693</v>
+        <v>46030</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15471,8 +15461,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I186" t="n">
-        <v>0.7</v>
+        <v>6.9</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -15515,7 +15510,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 29138-2026</t>
+          <t>A 119-2023</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -15525,14 +15520,14 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>46202</v>
+        <v>44928</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15544,13 +15539,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H187" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I187" t="n">
-        <v>4.2</v>
+        <v>0.8</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -15593,7 +15583,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 29124-2026</t>
+          <t>A 821-2026</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15607,10 +15597,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>46202</v>
+        <v>46030</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15622,8 +15612,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I188" t="n">
-        <v>2.9</v>
+        <v>4.3</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15666,7 +15661,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 29135-2026</t>
+          <t>A 554-2026</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15676,14 +15671,14 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>46202</v>
+        <v>46029</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15695,13 +15690,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H189" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I189" t="n">
-        <v>4.7</v>
+        <v>0.8</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15744,7 +15734,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 29137-2026</t>
+          <t>A 43685-2022</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15754,14 +15744,14 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>46202</v>
+        <v>44837</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15773,13 +15763,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H190" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I190" t="n">
-        <v>7.8</v>
+        <v>1.3</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15822,7 +15807,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 119-2023</t>
+          <t>A 24724-2024</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15832,14 +15817,14 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>44928</v>
+        <v>45460</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15852,7 +15837,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15895,7 +15880,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 50715-2024</t>
+          <t>A 37300-2026</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15909,10 +15894,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>45602</v>
+        <v>46274</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15925,7 +15910,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15968,7 +15953,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 37724-2022</t>
+          <t>A 1989-2026</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15982,10 +15967,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>44810</v>
+        <v>46035</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15998,7 +15983,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>1.2</v>
+        <v>2.5</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -16041,7 +16026,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 37728-2022</t>
+          <t>A 6558-2025</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -16051,14 +16036,14 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>44810</v>
+        <v>45699</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16070,8 +16055,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I194" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -16114,7 +16104,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 47637-2023</t>
+          <t>A 3013-2026</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -16128,10 +16118,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>45203</v>
+        <v>46038</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16144,7 +16134,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>2</v>
+        <v>0.7</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -16187,7 +16177,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 33873-2024</t>
+          <t>A 2747-2023</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -16201,10 +16191,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>45521</v>
+        <v>44944</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16216,8 +16206,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I196" t="n">
-        <v>3.5</v>
+        <v>4.6</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -16260,7 +16255,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 3542-2025</t>
+          <t>A 31522-2022</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -16274,10 +16269,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>45680</v>
+        <v>44775</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16289,13 +16284,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H197" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I197" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -16338,7 +16328,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 13228-2024</t>
+          <t>A 55265-2023</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -16352,10 +16342,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>45386</v>
+        <v>45237</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16368,7 +16358,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -16411,7 +16401,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 15998-2024</t>
+          <t>A 5374-2026</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -16425,10 +16415,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>45405</v>
+        <v>46050</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16441,7 +16431,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -16484,7 +16474,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 16001-2024</t>
+          <t>A 28918-2023</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -16498,10 +16488,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>45405</v>
+        <v>45104</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16514,7 +16504,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -16557,7 +16547,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 31114-2024</t>
+          <t>A 3239-2023</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -16571,10 +16561,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>45502</v>
+        <v>44946</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16587,7 +16577,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -16630,7 +16620,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 13804-2024</t>
+          <t>A 13228-2024</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -16644,10 +16634,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>45391</v>
+        <v>45386</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16660,7 +16650,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16703,7 +16693,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 23606-2026</t>
+          <t>A 48427-2022</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16713,14 +16703,14 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>46162</v>
+        <v>44858</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16732,8 +16722,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I203" t="n">
-        <v>9.4</v>
+        <v>0.5</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -16776,7 +16771,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 34737-2026</t>
+          <t>A 4756-2025</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -16790,10 +16785,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>46258</v>
+        <v>45688</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16806,7 +16801,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16849,7 +16844,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 34740-2026</t>
+          <t>A 8310-2026</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16863,10 +16858,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>46258</v>
+        <v>46064</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16879,7 +16874,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16922,7 +16917,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 19777-2023</t>
+          <t>A 33358-2023</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16936,10 +16931,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>45051</v>
+        <v>45128</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16952,7 +16947,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>4.3</v>
+        <v>0.4</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16995,7 +16990,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 28746-2024</t>
+          <t>A 39507-2024</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -17009,10 +17004,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>45478</v>
+        <v>45551</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17024,8 +17019,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I207" t="n">
-        <v>1.9</v>
+        <v>0.3</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -17068,7 +17068,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 30934-2026</t>
+          <t>A 41940-2022</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -17082,10 +17082,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>46213</v>
+        <v>44833</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17098,7 +17098,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -17141,7 +17141,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 55307-2025</t>
+          <t>A 43882-2023</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -17155,10 +17155,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>45970</v>
+        <v>45187</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17170,8 +17170,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I209" t="n">
-        <v>2.5</v>
+        <v>1.2</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -17214,7 +17219,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 31286-2026</t>
+          <t>A 28527-2023</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -17228,10 +17233,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>46218</v>
+        <v>45103</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17244,7 +17249,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -17287,7 +17292,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 6558-2025</t>
+          <t>A 19420-2022</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -17297,14 +17302,14 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>45699</v>
+        <v>44693</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17316,13 +17321,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H211" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I211" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -17365,7 +17365,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 25183-2023</t>
+          <t>A 47641-2023</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -17379,10 +17379,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>45079</v>
+        <v>45203</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17395,7 +17395,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>1.5</v>
+        <v>4.8</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -17438,7 +17438,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 57017-2025</t>
+          <t>A 60963-2023</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -17452,10 +17452,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>45978</v>
+        <v>45261</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17468,7 +17468,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>5.5</v>
+        <v>1.2</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -17511,7 +17511,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 41940-2022</t>
+          <t>A 52310-2023</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -17525,10 +17525,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>44833</v>
+        <v>45224</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17541,7 +17541,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>0.7</v>
+        <v>3.5</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -17584,7 +17584,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 20047-2026</t>
+          <t>A 2170-2025</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -17598,10 +17598,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>46136</v>
+        <v>45673</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17614,7 +17614,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>1.1</v>
+        <v>3.6</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -17657,7 +17657,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 38684-2022</t>
+          <t>A 16665-2025</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -17671,10 +17671,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>44814</v>
+        <v>45754</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17687,7 +17687,7 @@
         </is>
       </c>
       <c r="I216" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -17730,7 +17730,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 38073-2026</t>
+          <t>A 43711-2024</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -17740,14 +17740,14 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>46280</v>
+        <v>45569</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17760,7 +17760,7 @@
         </is>
       </c>
       <c r="I217" t="n">
-        <v>2.3</v>
+        <v>3.4</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -17803,7 +17803,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 52310-2023</t>
+          <t>A 23484-2025</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -17817,10 +17817,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>45224</v>
+        <v>45792</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17876,7 +17876,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 2170-2025</t>
+          <t>A 28550-2025</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -17890,10 +17890,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>45673</v>
+        <v>45818</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17906,7 +17906,7 @@
         </is>
       </c>
       <c r="I219" t="n">
-        <v>3.6</v>
+        <v>5</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -17949,7 +17949,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 37300-2026</t>
+          <t>A 9612-2025</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -17963,10 +17963,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>46274</v>
+        <v>45715</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17979,7 +17979,7 @@
         </is>
       </c>
       <c r="I220" t="n">
-        <v>0.2</v>
+        <v>1.2</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -18039,7 +18039,7 @@
         <v>45230</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18112,7 +18112,7 @@
         <v>44796</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18185,7 +18185,7 @@
         <v>45722</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18258,7 +18258,7 @@
         <v>46042</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18314,7 +18314,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>S 1874-2026</t>
+          <t>S 220-2026</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -18328,10 +18328,10 @@
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>46202</v>
+        <v>46051</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18343,13 +18343,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H225" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I225" t="n">
-        <v>7.8</v>
+        <v>1.7</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -18392,7 +18387,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>S 1875-2026</t>
+          <t>S 1874-2026</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -18409,7 +18404,7 @@
         <v>46202</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18427,7 +18422,7 @@
         </is>
       </c>
       <c r="I226" t="n">
-        <v>4.2</v>
+        <v>7.8</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -18470,7 +18465,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>S 1873-2026</t>
+          <t>S 1875-2026</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -18487,7 +18482,7 @@
         <v>46202</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18505,7 +18500,7 @@
         </is>
       </c>
       <c r="I227" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -18548,7 +18543,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>S 220-2026</t>
+          <t>S 1873-2026</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -18562,10 +18557,10 @@
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>46051</v>
+        <v>46202</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18577,8 +18572,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I228" t="n">
-        <v>1.7</v>
+        <v>4.7</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>

--- a/Översikt HÖRBY.xlsx
+++ b/Översikt HÖRBY.xlsx
@@ -601,7 +601,7 @@
         <v>44964</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
         <v>44967</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         <v>44727</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -949,7 +949,7 @@
         <v>45786</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1061,7 +1061,7 @@
         <v>46160</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
         <v>45238</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 31351-2022</t>
+          <t>A 39855-2022</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1289,10 +1289,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>44774</v>
+        <v>44819</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1305,22 +1305,22 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>13.2</v>
+        <v>4.2</v>
       </c>
       <c r="J8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1329,10 +1329,10 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1341,9 +1341,231 @@
         <v>5</v>
       </c>
       <c r="U8" t="n">
+        <v>1</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Skogsknipprot
+Blåsippa
+Fläcknycklar
+Grönvit nattviol</t>
+        </is>
+      </c>
+      <c r="W8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 39855-2022 artfynd.xlsx", "A 39855-2022")</f>
+        <v/>
+      </c>
+      <c r="X8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 39855-2022 karta.png", "A 39855-2022")</f>
+        <v/>
+      </c>
+      <c r="Y8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 39855-2022 georefererad karta.tif", "A 39855-2022")</f>
+        <v/>
+      </c>
+      <c r="AA8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 39855-2022 FSC-klagomål.docx", "A 39855-2022")</f>
+        <v/>
+      </c>
+      <c r="AB8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 39855-2022 FSC-klagomål mail.docx", "A 39855-2022")</f>
+        <v/>
+      </c>
+      <c r="AC8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 39855-2022 tillsynsbegäran.docx", "A 39855-2022")</f>
+        <v/>
+      </c>
+      <c r="AD8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 39855-2022 tillsynsbegäran mail.docx", "A 39855-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 16520-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>46112</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>HÖRBY</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>2</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
         <v>3</v>
       </c>
-      <c r="V8" s="2" t="inlineStr">
+      <c r="R9" t="n">
+        <v>1</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="n">
+        <v>6</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Slåttergubbe
+Sydlig sotticka
+Älg
+Fiskgjuse
+Större brunfladdermus</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 16520-2026 artfynd.xlsx", "A 16520-2026")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 16520-2026 karta.png", "A 16520-2026")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 16520-2026 georefererad karta.tif", "A 16520-2026")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 16520-2026 FSC-klagomål.docx", "A 16520-2026")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 16520-2026 FSC-klagomål mail.docx", "A 16520-2026")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 16520-2026 tillsynsbegäran.docx", "A 16520-2026")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 16520-2026 tillsynsbegäran mail.docx", "A 16520-2026")</f>
+        <v/>
+      </c>
+      <c r="AE9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/fåglar/A 16520-2026 prioriterade fågelarter.docx", "A 16520-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 31351-2022</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>44774</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>HÖRBY</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="J10" t="n">
+        <v>5</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>3</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>3</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="n">
+        <v>5</v>
+      </c>
+      <c r="U10" t="n">
+        <v>3</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Duvhök
 Grönsångare
@@ -1352,224 +1574,111 @@
 Kungsfågel</t>
         </is>
       </c>
-      <c r="W8">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 31351-2022 artfynd.xlsx", "A 31351-2022")</f>
         <v/>
       </c>
-      <c r="X8">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 31351-2022 karta.png", "A 31351-2022")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 31351-2022 georefererad karta.tif", "A 31351-2022")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 31351-2022 FSC-klagomål.docx", "A 31351-2022")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 31351-2022 FSC-klagomål mail.docx", "A 31351-2022")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 31351-2022 tillsynsbegäran.docx", "A 31351-2022")</f>
         <v/>
       </c>
-      <c r="AD8">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 31351-2022 tillsynsbegäran mail.docx", "A 31351-2022")</f>
         <v/>
       </c>
-      <c r="AE8">
+      <c r="AE10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/fåglar/A 31351-2022 prioriterade fågelarter.docx", "A 31351-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A 16520-2026</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>46112</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>HÖRBY</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="J9" t="n">
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 20194-2024</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>45434</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>HÖRBY</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
         <v>2</v>
       </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
         <v>2</v>
       </c>
-      <c r="M9" t="n">
+      <c r="O11" t="n">
         <v>1</v>
       </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
         <v>3</v>
       </c>
-      <c r="R9" t="n">
-        <v>1</v>
-      </c>
-      <c r="S9" t="n">
+      <c r="R11" t="n">
+        <v>3</v>
+      </c>
+      <c r="S11" t="n">
         <v>5</v>
       </c>
-      <c r="T9" t="n">
-        <v>6</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>Slåttergubbe
-Sydlig sotticka
-Älg
-Fiskgjuse
-Större brunfladdermus</t>
-        </is>
-      </c>
-      <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 16520-2026 artfynd.xlsx", "A 16520-2026")</f>
-        <v/>
-      </c>
-      <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 16520-2026 karta.png", "A 16520-2026")</f>
-        <v/>
-      </c>
-      <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 16520-2026 georefererad karta.tif", "A 16520-2026")</f>
-        <v/>
-      </c>
-      <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 16520-2026 FSC-klagomål.docx", "A 16520-2026")</f>
-        <v/>
-      </c>
-      <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 16520-2026 FSC-klagomål mail.docx", "A 16520-2026")</f>
-        <v/>
-      </c>
-      <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 16520-2026 tillsynsbegäran.docx", "A 16520-2026")</f>
-        <v/>
-      </c>
-      <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 16520-2026 tillsynsbegäran mail.docx", "A 16520-2026")</f>
-        <v/>
-      </c>
-      <c r="AE9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/fåglar/A 16520-2026 prioriterade fågelarter.docx", "A 16520-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 20194-2024</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>45434</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>HÖRBY</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>2</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>2</v>
-      </c>
-      <c r="O10" t="n">
-        <v>1</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>3</v>
-      </c>
-      <c r="R10" t="n">
-        <v>3</v>
-      </c>
-      <c r="S10" t="n">
+      <c r="T11" t="n">
         <v>5</v>
       </c>
-      <c r="T10" t="n">
-        <v>5</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Naverlönn
 Ask
@@ -1578,141 +1687,32 @@
 Stor häxört</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 20194-2024 artfynd.xlsx", "A 20194-2024")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 20194-2024 karta.png", "A 20194-2024")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 20194-2024 georefererad karta.tif", "A 20194-2024")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 20194-2024 FSC-klagomål.docx", "A 20194-2024")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 20194-2024 FSC-klagomål mail.docx", "A 20194-2024")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 20194-2024 tillsynsbegäran.docx", "A 20194-2024")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 20194-2024 tillsynsbegäran mail.docx", "A 20194-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 39855-2022</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>44819</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>HÖRBY</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J11" t="n">
-        <v>4</v>
-      </c>
-      <c r="K11" t="n">
-        <v>1</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>1</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1</v>
-      </c>
-      <c r="S11" t="n">
-        <v>5</v>
-      </c>
-      <c r="T11" t="n">
-        <v>5</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Skogsknipprot
-Blåsippa
-Fläcknycklar
-Grönvit nattviol</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 39855-2022 artfynd.xlsx", "A 39855-2022")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 39855-2022 karta.png", "A 39855-2022")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 39855-2022 georefererad karta.tif", "A 39855-2022")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 39855-2022 FSC-klagomål.docx", "A 39855-2022")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 39855-2022 FSC-klagomål mail.docx", "A 39855-2022")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 39855-2022 tillsynsbegäran.docx", "A 39855-2022")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 39855-2022 tillsynsbegäran mail.docx", "A 39855-2022")</f>
         <v/>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
         <v>46150</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         <v>45545</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1952,7 +1952,7 @@
         <v>45334</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
         <v>45434</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2150,7 +2150,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 2823-2025</t>
+          <t>A 27738-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2160,14 +2160,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45677</v>
+        <v>45815</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2180,17 +2180,17 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>21.1</v>
+        <v>2.5</v>
       </c>
       <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1</v>
+      </c>
+      <c r="L16" t="n">
         <v>2</v>
       </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>1</v>
-      </c>
       <c r="M16" t="n">
         <v>0</v>
       </c>
@@ -2204,7 +2204,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -2213,372 +2213,372 @@
         <v>3</v>
       </c>
       <c r="T16" t="n">
+        <v>3</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Bokvårtlav
+Sydlig sotticka
+Västlig hakmossa</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 27738-2025 artfynd.xlsx", "A 27738-2025")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 27738-2025 karta.png", "A 27738-2025")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 27738-2025 georefererad karta.tif", "A 27738-2025")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 27738-2025 FSC-klagomål.docx", "A 27738-2025")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 27738-2025 FSC-klagomål mail.docx", "A 27738-2025")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 27738-2025 tillsynsbegäran.docx", "A 27738-2025")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 27738-2025 tillsynsbegäran mail.docx", "A 27738-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 24801-2025</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>45799</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>HÖRBY</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1</v>
+      </c>
+      <c r="N17" t="n">
+        <v>1</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2</v>
+      </c>
+      <c r="R17" t="n">
+        <v>2</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3</v>
+      </c>
+      <c r="T17" t="n">
+        <v>5</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Småvänderot
+Platt fjädermossa</t>
+        </is>
+      </c>
+      <c r="W17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 24801-2025 artfynd.xlsx", "A 24801-2025")</f>
+        <v/>
+      </c>
+      <c r="X17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 24801-2025 karta.png", "A 24801-2025")</f>
+        <v/>
+      </c>
+      <c r="Y17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 24801-2025 georefererad karta.tif", "A 24801-2025")</f>
+        <v/>
+      </c>
+      <c r="AA17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 24801-2025 FSC-klagomål.docx", "A 24801-2025")</f>
+        <v/>
+      </c>
+      <c r="AB17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 24801-2025 FSC-klagomål mail.docx", "A 24801-2025")</f>
+        <v/>
+      </c>
+      <c r="AC17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 24801-2025 tillsynsbegäran.docx", "A 24801-2025")</f>
+        <v/>
+      </c>
+      <c r="AD17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 24801-2025 tillsynsbegäran mail.docx", "A 24801-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>A 24158-2022</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>44725</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>HÖRBY</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>2</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>3</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3</v>
+      </c>
+      <c r="T18" t="n">
+        <v>5</v>
+      </c>
+      <c r="U18" t="n">
+        <v>3</v>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>Slåttergubbe
+Borsttåg
+Sotnätfjäril</t>
+        </is>
+      </c>
+      <c r="W18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 24158-2022 artfynd.xlsx", "A 24158-2022")</f>
+        <v/>
+      </c>
+      <c r="X18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 24158-2022 karta.png", "A 24158-2022")</f>
+        <v/>
+      </c>
+      <c r="Y18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 24158-2022 georefererad karta.tif", "A 24158-2022")</f>
+        <v/>
+      </c>
+      <c r="AA18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 24158-2022 FSC-klagomål.docx", "A 24158-2022")</f>
+        <v/>
+      </c>
+      <c r="AB18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 24158-2022 FSC-klagomål mail.docx", "A 24158-2022")</f>
+        <v/>
+      </c>
+      <c r="AC18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 24158-2022 tillsynsbegäran.docx", "A 24158-2022")</f>
+        <v/>
+      </c>
+      <c r="AD18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 24158-2022 tillsynsbegäran mail.docx", "A 24158-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>A 2823-2025</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>45677</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>HÖRBY</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="J19" t="n">
+        <v>2</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3</v>
+      </c>
+      <c r="T19" t="n">
         <v>4</v>
       </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>Borsttåg
 Grönvit nattviol
 Revlummer</t>
         </is>
       </c>
-      <c r="W16">
+      <c r="W19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 2823-2025 artfynd.xlsx", "A 2823-2025")</f>
         <v/>
       </c>
-      <c r="X16">
+      <c r="X19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 2823-2025 karta.png", "A 2823-2025")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Y19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 2823-2025 georefererad karta.tif", "A 2823-2025")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AA19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 2823-2025 FSC-klagomål.docx", "A 2823-2025")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AB19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 2823-2025 FSC-klagomål mail.docx", "A 2823-2025")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AC19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 2823-2025 tillsynsbegäran.docx", "A 2823-2025")</f>
         <v/>
       </c>
-      <c r="AD16">
+      <c r="AD19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 2823-2025 tillsynsbegäran mail.docx", "A 2823-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 27738-2025</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>45815</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>HÖRBY</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>1</v>
-      </c>
-      <c r="L17" t="n">
-        <v>2</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>2</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>3</v>
-      </c>
-      <c r="T17" t="n">
-        <v>3</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Bokvårtlav
-Sydlig sotticka
-Västlig hakmossa</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 27738-2025 artfynd.xlsx", "A 27738-2025")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 27738-2025 karta.png", "A 27738-2025")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 27738-2025 georefererad karta.tif", "A 27738-2025")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 27738-2025 FSC-klagomål.docx", "A 27738-2025")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 27738-2025 FSC-klagomål mail.docx", "A 27738-2025")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 27738-2025 tillsynsbegäran.docx", "A 27738-2025")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 27738-2025 tillsynsbegäran mail.docx", "A 27738-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>A 24801-2025</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>45799</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>HÖRBY</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>1</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>1</v>
-      </c>
-      <c r="N18" t="n">
-        <v>1</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>2</v>
-      </c>
-      <c r="R18" t="n">
-        <v>2</v>
-      </c>
-      <c r="S18" t="n">
-        <v>3</v>
-      </c>
-      <c r="T18" t="n">
-        <v>5</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Småvänderot
-Platt fjädermossa</t>
-        </is>
-      </c>
-      <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 24801-2025 artfynd.xlsx", "A 24801-2025")</f>
-        <v/>
-      </c>
-      <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 24801-2025 karta.png", "A 24801-2025")</f>
-        <v/>
-      </c>
-      <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 24801-2025 georefererad karta.tif", "A 24801-2025")</f>
-        <v/>
-      </c>
-      <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 24801-2025 FSC-klagomål.docx", "A 24801-2025")</f>
-        <v/>
-      </c>
-      <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 24801-2025 FSC-klagomål mail.docx", "A 24801-2025")</f>
-        <v/>
-      </c>
-      <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 24801-2025 tillsynsbegäran.docx", "A 24801-2025")</f>
-        <v/>
-      </c>
-      <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 24801-2025 tillsynsbegäran mail.docx", "A 24801-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>A 24158-2022</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="n">
-        <v>44725</v>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>HÖRBY</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>2</v>
-      </c>
-      <c r="M19" t="n">
-        <v>1</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>3</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1</v>
-      </c>
-      <c r="S19" t="n">
-        <v>3</v>
-      </c>
-      <c r="T19" t="n">
-        <v>5</v>
-      </c>
-      <c r="U19" t="n">
-        <v>3</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>Slåttergubbe
-Borsttåg
-Sotnätfjäril</t>
-        </is>
-      </c>
-      <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 24158-2022 artfynd.xlsx", "A 24158-2022")</f>
-        <v/>
-      </c>
-      <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 24158-2022 karta.png", "A 24158-2022")</f>
-        <v/>
-      </c>
-      <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 24158-2022 georefererad karta.tif", "A 24158-2022")</f>
-        <v/>
-      </c>
-      <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 24158-2022 FSC-klagomål.docx", "A 24158-2022")</f>
-        <v/>
-      </c>
-      <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 24158-2022 FSC-klagomål mail.docx", "A 24158-2022")</f>
-        <v/>
-      </c>
-      <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 24158-2022 tillsynsbegäran.docx", "A 24158-2022")</f>
-        <v/>
-      </c>
-      <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 24158-2022 tillsynsbegäran mail.docx", "A 24158-2022")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 44135-2024</t>
+          <t>A 824-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2592,10 +2592,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45572</v>
+        <v>46030</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2607,11 +2607,16 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I20" t="n">
-        <v>0.6</v>
+        <v>3.1</v>
       </c>
       <c r="J20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -2620,7 +2625,7 @@
         <v>1</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -2632,269 +2637,264 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
+        <v>2</v>
+      </c>
+      <c r="R20" t="n">
         <v>1</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>2</v>
       </c>
       <c r="T20" t="n">
+        <v>3</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>Hedblomster
+Skogslysing</t>
+        </is>
+      </c>
+      <c r="W20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 824-2026 artfynd.xlsx", "A 824-2026")</f>
+        <v/>
+      </c>
+      <c r="X20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 824-2026 karta.png", "A 824-2026")</f>
+        <v/>
+      </c>
+      <c r="Y20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 824-2026 georefererad karta.tif", "A 824-2026")</f>
+        <v/>
+      </c>
+      <c r="AA20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 824-2026 FSC-klagomål.docx", "A 824-2026")</f>
+        <v/>
+      </c>
+      <c r="AB20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 824-2026 FSC-klagomål mail.docx", "A 824-2026")</f>
+        <v/>
+      </c>
+      <c r="AC20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 824-2026 tillsynsbegäran.docx", "A 824-2026")</f>
+        <v/>
+      </c>
+      <c r="AD20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 824-2026 tillsynsbegäran mail.docx", "A 824-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>A 42724-2023</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="n">
+        <v>45176</v>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>HÖRBY</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>1</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1</v>
+      </c>
+      <c r="S21" t="n">
         <v>2</v>
       </c>
-      <c r="U20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
+      <c r="T21" t="n">
+        <v>4</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Grönvit nattviol</t>
+        </is>
+      </c>
+      <c r="W21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 42724-2023 artfynd.xlsx", "A 42724-2023")</f>
+        <v/>
+      </c>
+      <c r="X21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 42724-2023 karta.png", "A 42724-2023")</f>
+        <v/>
+      </c>
+      <c r="Y21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 42724-2023 georefererad karta.tif", "A 42724-2023")</f>
+        <v/>
+      </c>
+      <c r="AA21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 42724-2023 FSC-klagomål.docx", "A 42724-2023")</f>
+        <v/>
+      </c>
+      <c r="AB21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 42724-2023 FSC-klagomål mail.docx", "A 42724-2023")</f>
+        <v/>
+      </c>
+      <c r="AC21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 42724-2023 tillsynsbegäran.docx", "A 42724-2023")</f>
+        <v/>
+      </c>
+      <c r="AD21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 42724-2023 tillsynsbegäran mail.docx", "A 42724-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>A 44135-2024</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="n">
+        <v>45572</v>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>HÖRBY</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J22" t="n">
+        <v>2</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>Ladusvala
 Vanlig padda</t>
         </is>
       </c>
-      <c r="W20">
+      <c r="W22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 44135-2024 artfynd.xlsx", "A 44135-2024")</f>
         <v/>
       </c>
-      <c r="X20">
+      <c r="X22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 44135-2024 karta.png", "A 44135-2024")</f>
         <v/>
       </c>
-      <c r="Y20">
+      <c r="Y22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 44135-2024 georefererad karta.tif", "A 44135-2024")</f>
         <v/>
       </c>
-      <c r="AA20">
+      <c r="AA22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 44135-2024 FSC-klagomål.docx", "A 44135-2024")</f>
         <v/>
       </c>
-      <c r="AB20">
+      <c r="AB22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 44135-2024 FSC-klagomål mail.docx", "A 44135-2024")</f>
         <v/>
       </c>
-      <c r="AC20">
+      <c r="AC22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 44135-2024 tillsynsbegäran.docx", "A 44135-2024")</f>
         <v/>
       </c>
-      <c r="AD20">
+      <c r="AD22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 44135-2024 tillsynsbegäran mail.docx", "A 44135-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>A 42724-2023</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D21" s="1" t="n">
-        <v>45176</v>
-      </c>
-      <c r="E21" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>HÖRBY</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="J21" t="n">
-        <v>1</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>1</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>1</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1</v>
-      </c>
-      <c r="S21" t="n">
-        <v>2</v>
-      </c>
-      <c r="T21" t="n">
-        <v>4</v>
-      </c>
-      <c r="U21" t="n">
-        <v>0</v>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Grönvit nattviol</t>
-        </is>
-      </c>
-      <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 42724-2023 artfynd.xlsx", "A 42724-2023")</f>
-        <v/>
-      </c>
-      <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 42724-2023 karta.png", "A 42724-2023")</f>
-        <v/>
-      </c>
-      <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 42724-2023 georefererad karta.tif", "A 42724-2023")</f>
-        <v/>
-      </c>
-      <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 42724-2023 FSC-klagomål.docx", "A 42724-2023")</f>
-        <v/>
-      </c>
-      <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 42724-2023 FSC-klagomål mail.docx", "A 42724-2023")</f>
-        <v/>
-      </c>
-      <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 42724-2023 tillsynsbegäran.docx", "A 42724-2023")</f>
-        <v/>
-      </c>
-      <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 42724-2023 tillsynsbegäran mail.docx", "A 42724-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>A 824-2026</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D22" s="1" t="n">
-        <v>46030</v>
-      </c>
-      <c r="E22" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>HÖRBY</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="J22" t="n">
-        <v>1</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>1</v>
-      </c>
-      <c r="M22" t="n">
-        <v>1</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>2</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1</v>
-      </c>
-      <c r="S22" t="n">
-        <v>2</v>
-      </c>
-      <c r="T22" t="n">
-        <v>3</v>
-      </c>
-      <c r="U22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>Hedblomster
-Skogslysing</t>
-        </is>
-      </c>
-      <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 824-2026 artfynd.xlsx", "A 824-2026")</f>
-        <v/>
-      </c>
-      <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 824-2026 karta.png", "A 824-2026")</f>
-        <v/>
-      </c>
-      <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 824-2026 georefererad karta.tif", "A 824-2026")</f>
-        <v/>
-      </c>
-      <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 824-2026 FSC-klagomål.docx", "A 824-2026")</f>
-        <v/>
-      </c>
-      <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 824-2026 FSC-klagomål mail.docx", "A 824-2026")</f>
-        <v/>
-      </c>
-      <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 824-2026 tillsynsbegäran.docx", "A 824-2026")</f>
-        <v/>
-      </c>
-      <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 824-2026 tillsynsbegäran mail.docx", "A 824-2026")</f>
         <v/>
       </c>
     </row>
@@ -2918,7 +2918,7 @@
         <v>45317</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3007,7 +3007,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 47612-2023</t>
+          <t>A 31115-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45203</v>
+        <v>45502</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3037,7 +3037,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2.4</v>
+        <v>0.8</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -3046,13 +3046,13 @@
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3064,7 +3064,7 @@
         <v>1</v>
       </c>
       <c r="R24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3077,42 +3077,42 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 47612-2023 artfynd.xlsx", "A 47612-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 31115-2024 artfynd.xlsx", "A 31115-2024")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 47612-2023 karta.png", "A 47612-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 31115-2024 karta.png", "A 31115-2024")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 47612-2023 georefererad karta.tif", "A 47612-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 31115-2024 georefererad karta.tif", "A 31115-2024")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 47612-2023 FSC-klagomål.docx", "A 47612-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 31115-2024 FSC-klagomål.docx", "A 31115-2024")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 47612-2023 FSC-klagomål mail.docx", "A 47612-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 31115-2024 FSC-klagomål mail.docx", "A 31115-2024")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 47612-2023 tillsynsbegäran.docx", "A 47612-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 31115-2024 tillsynsbegäran.docx", "A 31115-2024")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 47612-2023 tillsynsbegäran mail.docx", "A 47612-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 31115-2024 tillsynsbegäran mail.docx", "A 31115-2024")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 36362-2025</t>
+          <t>A 47612-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3126,10 +3126,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45868</v>
+        <v>45203</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3142,23 +3142,23 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>3.7</v>
+        <v>2.4</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
       <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
         <v>1</v>
       </c>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" t="n">
-        <v>0</v>
-      </c>
       <c r="O25" t="n">
         <v>0</v>
       </c>
@@ -3166,10 +3166,10 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3178,46 +3178,46 @@
         <v>1</v>
       </c>
       <c r="U25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 36362-2025 artfynd.xlsx", "A 36362-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 47612-2023 artfynd.xlsx", "A 47612-2023")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 36362-2025 karta.png", "A 36362-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 47612-2023 karta.png", "A 47612-2023")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 36362-2025 georefererad karta.tif", "A 36362-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 47612-2023 georefererad karta.tif", "A 47612-2023")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 36362-2025 FSC-klagomål.docx", "A 36362-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 47612-2023 FSC-klagomål.docx", "A 47612-2023")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 36362-2025 FSC-klagomål mail.docx", "A 36362-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 47612-2023 FSC-klagomål mail.docx", "A 47612-2023")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 36362-2025 tillsynsbegäran.docx", "A 36362-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 47612-2023 tillsynsbegäran.docx", "A 47612-2023")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 36362-2025 tillsynsbegäran mail.docx", "A 36362-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 47612-2023 tillsynsbegäran mail.docx", "A 47612-2023")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 113-2023</t>
+          <t>A 40376-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3231,10 +3231,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44928</v>
+        <v>45169</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3247,19 +3247,19 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>5.1</v>
+        <v>2.7</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
         <v>0</v>
@@ -3274,7 +3274,7 @@
         <v>1</v>
       </c>
       <c r="R26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>
@@ -3287,42 +3287,46 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Slåttergubbe</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 113-2023 artfynd.xlsx", "A 113-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 40376-2023 artfynd.xlsx", "A 40376-2023")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 113-2023 karta.png", "A 113-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 40376-2023 karta.png", "A 40376-2023")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 113-2023 georefererad karta.tif", "A 113-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 40376-2023 georefererad karta.tif", "A 40376-2023")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 113-2023 FSC-klagomål.docx", "A 113-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 40376-2023 FSC-klagomål.docx", "A 40376-2023")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 113-2023 FSC-klagomål mail.docx", "A 113-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 40376-2023 FSC-klagomål mail.docx", "A 40376-2023")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 113-2023 tillsynsbegäran.docx", "A 113-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 40376-2023 tillsynsbegäran.docx", "A 40376-2023")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 113-2023 tillsynsbegäran mail.docx", "A 113-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 40376-2023 tillsynsbegäran mail.docx", "A 40376-2023")</f>
+        <v/>
+      </c>
+      <c r="AE26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/fåglar/A 40376-2023 prioriterade fågelarter.docx", "A 40376-2023")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 25833-2024</t>
+          <t>A 113-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3336,10 +3340,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45463</v>
+        <v>44928</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3352,7 +3356,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.4</v>
+        <v>5.1</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3385,7 +3389,7 @@
         <v>1</v>
       </c>
       <c r="T27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U27" t="n">
         <v>0</v>
@@ -3396,31 +3400,31 @@
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 25833-2024 artfynd.xlsx", "A 25833-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 113-2023 artfynd.xlsx", "A 113-2023")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 25833-2024 karta.png", "A 25833-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 113-2023 karta.png", "A 113-2023")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 25833-2024 georefererad karta.tif", "A 25833-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 113-2023 georefererad karta.tif", "A 113-2023")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 25833-2024 FSC-klagomål.docx", "A 25833-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 113-2023 FSC-klagomål.docx", "A 113-2023")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 25833-2024 FSC-klagomål mail.docx", "A 25833-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 113-2023 FSC-klagomål mail.docx", "A 113-2023")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 25833-2024 tillsynsbegäran.docx", "A 25833-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 113-2023 tillsynsbegäran.docx", "A 113-2023")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 25833-2024 tillsynsbegäran mail.docx", "A 25833-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 113-2023 tillsynsbegäran mail.docx", "A 113-2023")</f>
         <v/>
       </c>
     </row>
@@ -3444,7 +3448,7 @@
         <v>46174</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3537,7 +3541,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 16519-2026</t>
+          <t>A 25833-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3551,10 +3555,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46112</v>
+        <v>45463</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3567,7 +3571,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3579,10 +3583,10 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3600,49 +3604,49 @@
         <v>1</v>
       </c>
       <c r="T29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U29" t="n">
         <v>0</v>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Slåttergubbe</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 16519-2026 artfynd.xlsx", "A 16519-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 25833-2024 artfynd.xlsx", "A 25833-2024")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 16519-2026 karta.png", "A 16519-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 25833-2024 karta.png", "A 25833-2024")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 16519-2026 georefererad karta.tif", "A 16519-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 25833-2024 georefererad karta.tif", "A 25833-2024")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 16519-2026 FSC-klagomål.docx", "A 16519-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 25833-2024 FSC-klagomål.docx", "A 25833-2024")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 16519-2026 FSC-klagomål mail.docx", "A 16519-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 25833-2024 FSC-klagomål mail.docx", "A 25833-2024")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 16519-2026 tillsynsbegäran.docx", "A 16519-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 25833-2024 tillsynsbegäran.docx", "A 25833-2024")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 16519-2026 tillsynsbegäran mail.docx", "A 16519-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 25833-2024 tillsynsbegäran mail.docx", "A 25833-2024")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 40376-2023</t>
+          <t>A 16519-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3656,10 +3660,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45169</v>
+        <v>46112</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3672,22 +3676,22 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>2.7</v>
+        <v>0.8</v>
       </c>
       <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
         <v>1</v>
-      </c>
-      <c r="K30" t="n">
-        <v>0</v>
-      </c>
-      <c r="L30" t="n">
-        <v>1</v>
-      </c>
-      <c r="M30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N30" t="n">
-        <v>0</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -3699,7 +3703,7 @@
         <v>1</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S30" t="n">
         <v>1</v>
@@ -3712,46 +3716,42 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 40376-2023 artfynd.xlsx", "A 40376-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 16519-2026 artfynd.xlsx", "A 16519-2026")</f>
         <v/>
       </c>
       <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 40376-2023 karta.png", "A 40376-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 16519-2026 karta.png", "A 16519-2026")</f>
         <v/>
       </c>
       <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 40376-2023 georefererad karta.tif", "A 40376-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 16519-2026 georefererad karta.tif", "A 16519-2026")</f>
         <v/>
       </c>
       <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 40376-2023 FSC-klagomål.docx", "A 40376-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 16519-2026 FSC-klagomål.docx", "A 16519-2026")</f>
         <v/>
       </c>
       <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 40376-2023 FSC-klagomål mail.docx", "A 40376-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 16519-2026 FSC-klagomål mail.docx", "A 16519-2026")</f>
         <v/>
       </c>
       <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 40376-2023 tillsynsbegäran.docx", "A 40376-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 16519-2026 tillsynsbegäran.docx", "A 16519-2026")</f>
         <v/>
       </c>
       <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 40376-2023 tillsynsbegäran mail.docx", "A 40376-2023")</f>
-        <v/>
-      </c>
-      <c r="AE30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/fåglar/A 40376-2023 prioriterade fågelarter.docx", "A 40376-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 16519-2026 tillsynsbegäran mail.docx", "A 16519-2026")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 31115-2024</t>
+          <t>A 31284-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3765,10 +3765,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45502</v>
+        <v>46218</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3781,16 +3781,16 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.8</v>
+        <v>6.8</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
@@ -3805,7 +3805,7 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
         <v>0</v>
@@ -3821,42 +3821,42 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>Gullpudra</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="W31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 31115-2024 artfynd.xlsx", "A 31115-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 31284-2026 artfynd.xlsx", "A 31284-2026")</f>
         <v/>
       </c>
       <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 31115-2024 karta.png", "A 31115-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 31284-2026 karta.png", "A 31284-2026")</f>
         <v/>
       </c>
       <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 31115-2024 georefererad karta.tif", "A 31115-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 31284-2026 georefererad karta.tif", "A 31284-2026")</f>
         <v/>
       </c>
       <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 31115-2024 FSC-klagomål.docx", "A 31115-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 31284-2026 FSC-klagomål.docx", "A 31284-2026")</f>
         <v/>
       </c>
       <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 31115-2024 FSC-klagomål mail.docx", "A 31115-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 31284-2026 FSC-klagomål mail.docx", "A 31284-2026")</f>
         <v/>
       </c>
       <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 31115-2024 tillsynsbegäran.docx", "A 31115-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 31284-2026 tillsynsbegäran.docx", "A 31284-2026")</f>
         <v/>
       </c>
       <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 31115-2024 tillsynsbegäran mail.docx", "A 31115-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 31284-2026 tillsynsbegäran mail.docx", "A 31284-2026")</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 31284-2026</t>
+          <t>A 21713-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3870,10 +3870,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46218</v>
+        <v>45783</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3886,7 +3886,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>6.8</v>
+        <v>0.8</v>
       </c>
       <c r="J32" t="n">
         <v>1</v>
@@ -3926,35 +3926,35 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="W32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 31284-2026 artfynd.xlsx", "A 31284-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 21713-2025 artfynd.xlsx", "A 21713-2025")</f>
         <v/>
       </c>
       <c r="X32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 31284-2026 karta.png", "A 31284-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 21713-2025 karta.png", "A 21713-2025")</f>
         <v/>
       </c>
       <c r="Y32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 31284-2026 georefererad karta.tif", "A 31284-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 21713-2025 georefererad karta.tif", "A 21713-2025")</f>
         <v/>
       </c>
       <c r="AA32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 31284-2026 FSC-klagomål.docx", "A 31284-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 21713-2025 FSC-klagomål.docx", "A 21713-2025")</f>
         <v/>
       </c>
       <c r="AB32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 31284-2026 FSC-klagomål mail.docx", "A 31284-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 21713-2025 FSC-klagomål mail.docx", "A 21713-2025")</f>
         <v/>
       </c>
       <c r="AC32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 31284-2026 tillsynsbegäran.docx", "A 31284-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 21713-2025 tillsynsbegäran.docx", "A 21713-2025")</f>
         <v/>
       </c>
       <c r="AD32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 31284-2026 tillsynsbegäran mail.docx", "A 31284-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 21713-2025 tillsynsbegäran mail.docx", "A 21713-2025")</f>
         <v/>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
         <v>46206</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4083,7 +4083,7 @@
         <v>46202</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4176,7 +4176,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 21713-2025</t>
+          <t>A 25479-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4186,14 +4186,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45783</v>
+        <v>45802</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4206,13 +4206,13 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="n">
         <v>1</v>
-      </c>
-      <c r="K35" t="n">
-        <v>0</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
@@ -4246,42 +4246,42 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Lundvårlök</t>
         </is>
       </c>
       <c r="W35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 21713-2025 artfynd.xlsx", "A 21713-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 25479-2025 artfynd.xlsx", "A 25479-2025")</f>
         <v/>
       </c>
       <c r="X35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 21713-2025 karta.png", "A 21713-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 25479-2025 karta.png", "A 25479-2025")</f>
         <v/>
       </c>
       <c r="Y35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 21713-2025 georefererad karta.tif", "A 21713-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 25479-2025 georefererad karta.tif", "A 25479-2025")</f>
         <v/>
       </c>
       <c r="AA35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 21713-2025 FSC-klagomål.docx", "A 21713-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 25479-2025 FSC-klagomål.docx", "A 25479-2025")</f>
         <v/>
       </c>
       <c r="AB35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 21713-2025 FSC-klagomål mail.docx", "A 21713-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 25479-2025 FSC-klagomål mail.docx", "A 25479-2025")</f>
         <v/>
       </c>
       <c r="AC35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 21713-2025 tillsynsbegäran.docx", "A 21713-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 25479-2025 tillsynsbegäran.docx", "A 25479-2025")</f>
         <v/>
       </c>
       <c r="AD35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 21713-2025 tillsynsbegäran mail.docx", "A 21713-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 25479-2025 tillsynsbegäran mail.docx", "A 25479-2025")</f>
         <v/>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 25479-2025</t>
+          <t>A 36362-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4291,14 +4291,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45802</v>
+        <v>45868</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4311,7 +4311,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.7</v>
+        <v>3.7</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4347,39 +4347,39 @@
         <v>1</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>Lundvårlök</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="W36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 25479-2025 artfynd.xlsx", "A 25479-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 36362-2025 artfynd.xlsx", "A 36362-2025")</f>
         <v/>
       </c>
       <c r="X36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 25479-2025 karta.png", "A 25479-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 36362-2025 karta.png", "A 36362-2025")</f>
         <v/>
       </c>
       <c r="Y36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 25479-2025 georefererad karta.tif", "A 25479-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 36362-2025 georefererad karta.tif", "A 36362-2025")</f>
         <v/>
       </c>
       <c r="AA36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 25479-2025 FSC-klagomål.docx", "A 25479-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 36362-2025 FSC-klagomål.docx", "A 36362-2025")</f>
         <v/>
       </c>
       <c r="AB36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 25479-2025 FSC-klagomål mail.docx", "A 25479-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 36362-2025 FSC-klagomål mail.docx", "A 36362-2025")</f>
         <v/>
       </c>
       <c r="AC36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 25479-2025 tillsynsbegäran.docx", "A 25479-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 36362-2025 tillsynsbegäran.docx", "A 36362-2025")</f>
         <v/>
       </c>
       <c r="AD36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 25479-2025 tillsynsbegäran mail.docx", "A 25479-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 36362-2025 tillsynsbegäran mail.docx", "A 36362-2025")</f>
         <v/>
       </c>
     </row>
@@ -4403,7 +4403,7 @@
         <v>45089</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4508,7 +4508,7 @@
         <v>44999</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4613,7 +4613,7 @@
         <v>44509</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4686,7 +4686,7 @@
         <v>44663</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4759,7 +4759,7 @@
         <v>44509</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4832,7 +4832,7 @@
         <v>44697</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4905,7 +4905,7 @@
         <v>44510</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4978,7 +4978,7 @@
         <v>44834</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5051,7 +5051,7 @@
         <v>44771</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5124,7 +5124,7 @@
         <v>44466</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5197,7 +5197,7 @@
         <v>44789</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5270,7 +5270,7 @@
         <v>44733</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5326,7 +5326,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 43380-2022</t>
+          <t>A 2979-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5340,10 +5340,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44834</v>
+        <v>45315</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5355,8 +5355,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I49" t="n">
-        <v>1.7</v>
+        <v>4.7</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5399,7 +5404,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 47609-2023</t>
+          <t>A 18609-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5413,10 +5418,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45203</v>
+        <v>45763</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5429,7 +5434,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2.4</v>
+        <v>0.6</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5472,7 +5477,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 9974-2024</t>
+          <t>A 3471-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5486,10 +5491,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45363</v>
+        <v>45680</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5502,7 +5507,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.6</v>
+        <v>3.7</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5545,7 +5550,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 15970-2024</t>
+          <t>A 33359-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5559,10 +5564,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45405</v>
+        <v>45128</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5575,7 +5580,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.8</v>
+        <v>0.9</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5618,7 +5623,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 5163-2024</t>
+          <t>A 37757-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5632,10 +5637,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45330</v>
+        <v>45541</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5647,13 +5652,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I53" t="n">
-        <v>7.1</v>
+        <v>0.7</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5696,7 +5696,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 37724-2022</t>
+          <t>A 24670-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5706,14 +5706,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44810</v>
+        <v>45460</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5726,7 +5726,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.2</v>
+        <v>0.2</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5769,7 +5769,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 37728-2022</t>
+          <t>A 2816-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5779,14 +5779,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44810</v>
+        <v>45677</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5799,7 +5799,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5842,7 +5842,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 56818-2022</t>
+          <t>A 28785-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5852,14 +5852,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44894</v>
+        <v>45104</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5872,7 +5872,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5915,7 +5915,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 33359-2023</t>
+          <t>A 16101-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5929,10 +5929,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45128</v>
+        <v>45750</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5945,7 +5945,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5988,7 +5988,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 54894-2023</t>
+          <t>A 58360-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6002,10 +6002,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45236</v>
+        <v>45250</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6018,7 +6018,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.6</v>
+        <v>2.5</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -6061,7 +6061,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 36689-2024</t>
+          <t>A 31596-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6071,14 +6071,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45537</v>
+        <v>45117</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6090,13 +6090,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I59" t="n">
-        <v>9.5</v>
+        <v>0.5</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6139,7 +6134,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 28746-2024</t>
+          <t>A 4756-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6153,10 +6148,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45478</v>
+        <v>45688</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6169,7 +6164,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.9</v>
+        <v>0.9</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6212,7 +6207,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 37082-2023</t>
+          <t>A 44613-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6222,14 +6217,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45155</v>
+        <v>45189</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6241,8 +6236,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I61" t="n">
-        <v>0.5</v>
+        <v>3.8</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6285,7 +6285,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 2752-2023</t>
+          <t>A 6886-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6299,10 +6299,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44944</v>
+        <v>45342</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6320,7 +6320,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6363,7 +6363,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 38080-2024</t>
+          <t>A 48397-2022</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6377,10 +6377,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45545</v>
+        <v>44858</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6393,7 +6393,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.7</v>
+        <v>1.7</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6436,7 +6436,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 28785-2023</t>
+          <t>A 33358-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6446,14 +6446,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45104</v>
+        <v>45128</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6466,7 +6466,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>2.1</v>
+        <v>0.4</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 48397-2022</t>
+          <t>A 47641-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6523,10 +6523,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44858</v>
+        <v>45203</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6539,7 +6539,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.7</v>
+        <v>4.8</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6582,7 +6582,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 13225-2024</t>
+          <t>A 39507-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6596,10 +6596,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45386</v>
+        <v>45551</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6611,8 +6611,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I66" t="n">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6655,7 +6660,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 13226-2024</t>
+          <t>A 3346-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6669,10 +6674,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45386</v>
+        <v>45317</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6685,7 +6690,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6728,7 +6733,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 15998-2024</t>
+          <t>A 788-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6742,10 +6747,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45405</v>
+        <v>45300</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6758,7 +6763,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6801,7 +6806,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 16001-2024</t>
+          <t>A 39298-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6815,10 +6820,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45405</v>
+        <v>45166</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6831,7 +6836,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.2</v>
+        <v>4.6</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6874,7 +6879,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 43828-2024</t>
+          <t>A 9974-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6888,10 +6893,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45572</v>
+        <v>45363</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6904,7 +6909,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6947,7 +6952,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 8260-2026</t>
+          <t>A 11943-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6961,10 +6966,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46064</v>
+        <v>45728</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6977,7 +6982,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>3.3</v>
+        <v>1.2</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -7020,7 +7025,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 8259-2026</t>
+          <t>A 42715-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7034,10 +7039,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46064</v>
+        <v>45176</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7050,7 +7055,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>3.1</v>
+        <v>0.5</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7093,7 +7098,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 29244-2025</t>
+          <t>A 28918-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7107,10 +7112,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45824</v>
+        <v>45104</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7123,7 +7128,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.7</v>
+        <v>2</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7166,7 +7171,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 29354-2025</t>
+          <t>A 43932-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7180,10 +7185,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45824</v>
+        <v>45187</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7196,7 +7201,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0.8</v>
+        <v>3</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7239,7 +7244,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 10731-2026</t>
+          <t>A 43935-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7253,10 +7258,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46078</v>
+        <v>45187</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7268,13 +7273,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I75" t="n">
-        <v>4.8</v>
+        <v>2.9</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7317,7 +7317,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 18609-2025</t>
+          <t>A 2747-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7331,10 +7331,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45763</v>
+        <v>44944</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7346,8 +7346,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I76" t="n">
-        <v>0.6</v>
+        <v>4.6</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7390,7 +7395,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 56750-2023</t>
+          <t>A 48427-2022</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7404,10 +7409,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45238</v>
+        <v>44858</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7419,8 +7424,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I77" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7463,7 +7473,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 42715-2023</t>
+          <t>A 8084-2022</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7477,10 +7487,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45176</v>
+        <v>44608</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7493,7 +7503,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7536,7 +7546,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 2981-2024</t>
+          <t>A 43828-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7550,10 +7560,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45315</v>
+        <v>45572</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7565,13 +7575,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I79" t="n">
-        <v>6.4</v>
+        <v>0.9</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7614,7 +7619,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 13633-2024</t>
+          <t>A 13225-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7628,10 +7633,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45390</v>
+        <v>45386</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7644,7 +7649,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7687,7 +7692,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 32459-2025</t>
+          <t>A 13226-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7701,10 +7706,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45838</v>
+        <v>45386</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7717,7 +7722,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7760,7 +7765,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 32958-2025</t>
+          <t>A 47552-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7774,10 +7779,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45839</v>
+        <v>45203</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7790,7 +7795,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>5</v>
+        <v>1.3</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7833,7 +7838,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 37756-2024</t>
+          <t>A 2752-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7847,10 +7852,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45541</v>
+        <v>44944</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7862,8 +7867,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I83" t="n">
-        <v>3.2</v>
+        <v>0.6</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7906,7 +7916,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 58641-2023</t>
+          <t>A 54431-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7916,14 +7926,14 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45251</v>
+        <v>45226</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7936,7 +7946,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.2</v>
+        <v>3.2</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7979,7 +7989,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 18603-2025</t>
+          <t>A 37082-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7989,14 +7999,14 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45763</v>
+        <v>45155</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8052,7 +8062,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 3346-2024</t>
+          <t>A 28625-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -8066,10 +8076,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45317</v>
+        <v>45103</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8082,7 +8092,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>0.5</v>
+        <v>4.8</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8125,7 +8135,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 14307-2026</t>
+          <t>A 38080-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8139,10 +8149,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46099</v>
+        <v>45545</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8155,7 +8165,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8198,7 +8208,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 3520-2026</t>
+          <t>A 13633-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8212,10 +8222,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>46042</v>
+        <v>45390</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8228,7 +8238,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8271,7 +8281,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 788-2024</t>
+          <t>A 44816-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8285,10 +8295,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45300</v>
+        <v>45190</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8301,7 +8311,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8344,7 +8354,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 3470-2026</t>
+          <t>A 28493-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8358,10 +8368,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46042</v>
+        <v>45103</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8374,7 +8384,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8417,7 +8427,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 9850-2026</t>
+          <t>A 65073-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8431,10 +8441,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46072</v>
+        <v>45287</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8447,7 +8457,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8490,7 +8500,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 3513-2026</t>
+          <t>A 43879-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8504,10 +8514,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>46042</v>
+        <v>45187</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8519,8 +8529,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I92" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8563,7 +8578,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 36355-2025</t>
+          <t>A 47609-2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8577,10 +8592,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45868</v>
+        <v>45203</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8593,7 +8608,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>3.6</v>
+        <v>2.4</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8636,7 +8651,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 25552-2025</t>
+          <t>A 5079-2026</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8650,10 +8665,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45803</v>
+        <v>46049</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8666,7 +8681,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8709,7 +8724,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 50715-2024</t>
+          <t>A 34154-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8723,10 +8738,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45602</v>
+        <v>45845</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8739,7 +8754,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0.4</v>
+        <v>5</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8782,7 +8797,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 38147-2025</t>
+          <t>A 43882-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8796,10 +8811,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45882</v>
+        <v>45187</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8811,8 +8826,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I96" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8855,7 +8875,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 7402-2026</t>
+          <t>A 67426-2021</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8869,10 +8889,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>46059</v>
+        <v>44523</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8885,7 +8905,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>4.7</v>
+        <v>0.6</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8928,7 +8948,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 2816-2025</t>
+          <t>A 3239-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8938,14 +8958,14 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45677</v>
+        <v>44946</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8958,7 +8978,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>2</v>
+        <v>0.4</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -9001,7 +9021,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 16101-2025</t>
+          <t>A 60963-2023</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -9015,10 +9035,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45750</v>
+        <v>45261</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9031,7 +9051,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -9074,7 +9094,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 34422-2024</t>
+          <t>A 43685-2022</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -9088,10 +9108,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45525</v>
+        <v>44837</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9104,7 +9124,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -9147,7 +9167,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 11943-2025</t>
+          <t>A 55265-2023</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9161,10 +9181,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45728</v>
+        <v>45237</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9220,7 +9240,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 44613-2023</t>
+          <t>A 5163-2024</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9234,10 +9254,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45189</v>
+        <v>45330</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9251,11 +9271,11 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I102" t="n">
-        <v>3.8</v>
+        <v>7.1</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9298,7 +9318,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 34154-2025</t>
+          <t>A 34147-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9315,7 +9335,7 @@
         <v>45845</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9328,7 +9348,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>5</v>
+        <v>18.7</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9371,7 +9391,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 43937-2023</t>
+          <t>A 18603-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9385,10 +9405,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45187</v>
+        <v>45763</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9401,7 +9421,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>2.6</v>
+        <v>0.5</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9444,7 +9464,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 43939-2023</t>
+          <t>A 51757-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9454,14 +9474,14 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45187</v>
+        <v>45951</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9473,8 +9493,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I105" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9517,7 +9542,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 67426-2021</t>
+          <t>A 52930-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9531,10 +9556,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>44523</v>
+        <v>45957</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9546,8 +9571,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I106" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9590,7 +9620,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 5079-2026</t>
+          <t>A 52929-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9604,10 +9634,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>46049</v>
+        <v>45957</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9619,8 +9649,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I107" t="n">
-        <v>1.3</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9680,7 +9715,7 @@
         <v>45680</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9741,7 +9776,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 7831-2025</t>
+          <t>A 20595-2024</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9755,10 +9790,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45706</v>
+        <v>45436</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9770,8 +9805,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I109" t="n">
-        <v>0.6</v>
+        <v>3.5</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9814,7 +9854,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 65073-2023</t>
+          <t>A 43937-2023</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9828,10 +9868,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45287</v>
+        <v>45187</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9844,7 +9884,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>1.7</v>
+        <v>2.6</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9887,7 +9927,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 18735-2023</t>
+          <t>A 43939-2023</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9901,10 +9941,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45043</v>
+        <v>45187</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9917,7 +9957,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9960,7 +10000,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 28493-2023</t>
+          <t>A 28501-2023</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9977,7 +10017,7 @@
         <v>45103</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9990,7 +10030,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>0.8</v>
+        <v>3.6</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -10033,7 +10073,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 36840-2024</t>
+          <t>A 28527-2023</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -10047,10 +10087,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45538</v>
+        <v>45103</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10062,13 +10102,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I113" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -10111,7 +10146,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 60913-2023</t>
+          <t>A 54894-2023</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -10125,10 +10160,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45261</v>
+        <v>45236</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10141,7 +10176,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -10184,7 +10219,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 8084-2022</t>
+          <t>A 54765-2025</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10198,10 +10233,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>44608</v>
+        <v>45966</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10214,7 +10249,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>1.5</v>
+        <v>2.6</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10257,7 +10292,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 28625-2023</t>
+          <t>A 55304-2025</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10267,14 +10302,14 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45103</v>
+        <v>45970</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10287,7 +10322,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>4.8</v>
+        <v>0.4</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10330,7 +10365,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 4597-2026</t>
+          <t>A 55306-2025</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10340,14 +10375,14 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>46048</v>
+        <v>45970</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10360,7 +10395,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>1.3</v>
+        <v>0.3</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10403,7 +10438,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 13804-2024</t>
+          <t>A 40994-2025</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10417,10 +10452,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45391</v>
+        <v>45898</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10433,7 +10468,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>0.5</v>
+        <v>5.6</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10476,7 +10511,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 34147-2025</t>
+          <t>A 37276-2024</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10490,10 +10525,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45845</v>
+        <v>45540</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10506,7 +10541,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>18.7</v>
+        <v>1.6</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10549,7 +10584,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 6886-2024</t>
+          <t>A 57269-2025</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10563,10 +10598,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45342</v>
+        <v>45979</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10584,7 +10619,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>0.5</v>
+        <v>5.5</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10627,7 +10662,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 4590-2026</t>
+          <t>A 36689-2024</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10637,14 +10672,14 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>46048</v>
+        <v>45537</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10656,8 +10691,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I121" t="n">
-        <v>1.1</v>
+        <v>9.5</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10700,7 +10740,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 6350-2026</t>
+          <t>A 59308-2025</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10714,10 +10754,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>46051</v>
+        <v>45989</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10730,7 +10770,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>2.4</v>
+        <v>1.2</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10773,7 +10813,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 18369-2025</t>
+          <t>A 4597-2026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10787,10 +10827,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45762</v>
+        <v>46048</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10803,7 +10843,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>2.2</v>
+        <v>1.3</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10846,7 +10886,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 1106-2023</t>
+          <t>A 31522-2022</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10860,10 +10900,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>44935</v>
+        <v>44775</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10876,7 +10916,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10919,7 +10959,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 17073-2023</t>
+          <t>A 54184-2024</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10933,10 +10973,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45034</v>
+        <v>45616</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10949,7 +10989,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10992,7 +11032,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 2979-2024</t>
+          <t>A 60913-2023</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -11006,10 +11046,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45315</v>
+        <v>45261</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11021,13 +11061,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I126" t="n">
-        <v>4.7</v>
+        <v>0.7</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -11070,7 +11105,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 3177-2026</t>
+          <t>A 44073-2024</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -11080,14 +11115,14 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>46041</v>
+        <v>45572</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11100,7 +11135,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -11143,7 +11178,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 31596-2023</t>
+          <t>A 11941-2025</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -11157,10 +11192,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45117</v>
+        <v>45728</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11173,7 +11208,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -11216,7 +11251,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 51757-2025</t>
+          <t>A 43380-2022</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11226,14 +11261,14 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45951</v>
+        <v>44834</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11245,13 +11280,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I129" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11294,7 +11324,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 52929-2025</t>
+          <t>A 20403-2024</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11308,10 +11338,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45957</v>
+        <v>45435</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11323,13 +11353,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H130" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I130" t="n">
-        <v>8.300000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11372,7 +11397,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 52930-2025</t>
+          <t>A 1106-2023</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11386,10 +11411,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45957</v>
+        <v>44935</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11401,13 +11426,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H131" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I131" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11450,7 +11470,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 59284-2025</t>
+          <t>A 62277-2025</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11464,10 +11484,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45988</v>
+        <v>46006</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11480,7 +11500,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11523,7 +11543,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 54184-2024</t>
+          <t>A 554-2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11537,10 +11557,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45616</v>
+        <v>46029</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11553,7 +11573,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11596,7 +11616,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 43932-2023</t>
+          <t>A 49726-2023</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11610,10 +11630,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45187</v>
+        <v>45208</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11626,7 +11646,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>3</v>
+        <v>1.3</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11669,7 +11689,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 43935-2023</t>
+          <t>A 36840-2024</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11683,10 +11703,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45187</v>
+        <v>45538</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11698,8 +11718,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I135" t="n">
-        <v>2.9</v>
+        <v>0.9</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11742,7 +11767,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 10524-2026</t>
+          <t>A 826-2026</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11756,10 +11781,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>46076</v>
+        <v>46030</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11771,8 +11796,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I136" t="n">
-        <v>1.6</v>
+        <v>0.3</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11815,7 +11845,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 10500-2026</t>
+          <t>A 829-2026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11829,10 +11859,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>46076</v>
+        <v>46030</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11844,8 +11874,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I137" t="n">
-        <v>1.1</v>
+        <v>6.9</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11888,7 +11923,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 20403-2024</t>
+          <t>A 821-2026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11902,10 +11937,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45435</v>
+        <v>46030</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11917,8 +11952,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I138" t="n">
-        <v>0.9</v>
+        <v>4.3</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11961,7 +12001,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 54765-2025</t>
+          <t>A 24724-2024</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11971,14 +12011,14 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45966</v>
+        <v>45460</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11991,7 +12031,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>2.6</v>
+        <v>1.4</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -12034,7 +12074,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 3040-2024</t>
+          <t>A 58641-2023</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -12044,14 +12084,14 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45316</v>
+        <v>45251</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12064,7 +12104,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>4</v>
+        <v>1.2</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -12107,7 +12147,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 16518-2026</t>
+          <t>A 1989-2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -12121,10 +12161,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>46112</v>
+        <v>46035</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12137,7 +12177,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>0.8</v>
+        <v>2.5</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -12180,7 +12220,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 44816-2023</t>
+          <t>A 4590-2026</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -12194,10 +12234,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45190</v>
+        <v>46048</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12210,7 +12250,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -12253,7 +12293,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 47552-2023</t>
+          <t>A 3013-2026</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12267,10 +12307,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45203</v>
+        <v>46038</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12283,7 +12323,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -12326,7 +12366,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 40994-2025</t>
+          <t>A 3040-2024</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12340,10 +12380,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45898</v>
+        <v>45316</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12356,7 +12396,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>5.6</v>
+        <v>4</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -12399,7 +12439,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 55304-2025</t>
+          <t>A 6350-2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12409,14 +12449,14 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45970</v>
+        <v>46051</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12429,7 +12469,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>0.4</v>
+        <v>2.4</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12472,7 +12512,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 55306-2025</t>
+          <t>A 18369-2025</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12482,14 +12522,14 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45970</v>
+        <v>45762</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12502,7 +12542,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>0.3</v>
+        <v>2.2</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12545,7 +12585,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 54431-2023</t>
+          <t>A 15970-2024</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12559,10 +12599,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45226</v>
+        <v>45405</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12575,7 +12615,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>3.2</v>
+        <v>1.8</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12618,7 +12658,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 19777-2023</t>
+          <t>A 18735-2023</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12632,10 +12672,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45051</v>
+        <v>45043</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12648,7 +12688,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>4.3</v>
+        <v>1</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12691,7 +12731,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 43879-2023</t>
+          <t>A 5374-2026</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12705,10 +12745,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45187</v>
+        <v>46050</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12720,13 +12760,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H149" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I149" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12769,7 +12804,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 29138-2026</t>
+          <t>A 6081-2023</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12779,14 +12814,14 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>46202</v>
+        <v>44959</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12798,13 +12833,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H150" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I150" t="n">
-        <v>4.2</v>
+        <v>0.4</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12847,7 +12877,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 29135-2026</t>
+          <t>A 29219-2023</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12857,14 +12887,14 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>46202</v>
+        <v>45105</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12876,13 +12906,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H151" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I151" t="n">
-        <v>4.7</v>
+        <v>0.7</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12925,7 +12950,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 29137-2026</t>
+          <t>A 56818-2022</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12935,14 +12960,14 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>46202</v>
+        <v>44894</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12954,13 +12979,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H152" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I152" t="n">
-        <v>7.8</v>
+        <v>1.8</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -13003,7 +13023,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 57269-2025</t>
+          <t>A 3177-2026</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -13013,14 +13033,14 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45979</v>
+        <v>46041</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13032,13 +13052,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H153" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I153" t="n">
-        <v>5.5</v>
+        <v>0.5</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -13081,7 +13096,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 3471-2025</t>
+          <t>A 8310-2026</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -13095,10 +13110,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45680</v>
+        <v>46064</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13111,7 +13126,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>3.7</v>
+        <v>1.4</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -13154,7 +13169,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 49726-2023</t>
+          <t>A 8260-2026</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -13168,10 +13183,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45208</v>
+        <v>46064</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13184,7 +13199,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>1.3</v>
+        <v>3.3</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -13227,7 +13242,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 29124-2026</t>
+          <t>A 8259-2026</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -13241,10 +13256,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>46202</v>
+        <v>46064</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13257,7 +13272,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -13300,7 +13315,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 28501-2023</t>
+          <t>A 34422-2024</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -13310,14 +13325,14 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45103</v>
+        <v>45525</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13330,7 +13345,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>3.6</v>
+        <v>1.5</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -13373,7 +13388,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 33873-2024</t>
+          <t>A 10731-2026</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -13387,10 +13402,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45521</v>
+        <v>46078</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13402,8 +13417,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I158" t="n">
-        <v>3.5</v>
+        <v>4.8</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -13446,7 +13466,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 58360-2023</t>
+          <t>A 7831-2025</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13460,10 +13480,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45250</v>
+        <v>45706</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13476,7 +13496,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>2.5</v>
+        <v>0.6</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -13519,7 +13539,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 39298-2023</t>
+          <t>A 56750-2023</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -13533,10 +13553,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45166</v>
+        <v>45238</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13549,7 +13569,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>4.6</v>
+        <v>0.8</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13592,7 +13612,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 29219-2023</t>
+          <t>A 59284-2025</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13606,10 +13626,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45105</v>
+        <v>45988</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13622,7 +13642,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13665,7 +13685,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 3542-2025</t>
+          <t>A 10500-2026</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13679,10 +13699,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45680</v>
+        <v>46076</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13694,13 +13714,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H162" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I162" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13743,7 +13758,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 47637-2023</t>
+          <t>A 10524-2026</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13757,10 +13772,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>45203</v>
+        <v>46076</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13773,7 +13788,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13816,7 +13831,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 59308-2025</t>
+          <t>A 14307-2026</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13830,10 +13845,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45989</v>
+        <v>46099</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13846,7 +13861,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13889,7 +13904,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 30934-2026</t>
+          <t>A 16518-2026</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13903,10 +13918,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>46213</v>
+        <v>46112</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13919,7 +13934,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13962,7 +13977,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 34737-2026</t>
+          <t>A 17073-2023</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13976,10 +13991,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>46258</v>
+        <v>45034</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13992,7 +14007,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -14035,7 +14050,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 34740-2026</t>
+          <t>A 3470-2026</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -14049,10 +14064,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>46258</v>
+        <v>46042</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14065,7 +14080,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -14108,7 +14123,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 23606-2026</t>
+          <t>A 3513-2026</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -14118,14 +14133,14 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>46162</v>
+        <v>46042</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14138,7 +14153,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>9.4</v>
+        <v>0.9</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -14181,7 +14196,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 31286-2026</t>
+          <t>A 3520-2026</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -14195,10 +14210,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>46218</v>
+        <v>46042</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14211,7 +14226,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -14254,7 +14269,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 24670-2024</t>
+          <t>A 19420-2022</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -14264,14 +14279,14 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45460</v>
+        <v>44693</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14284,7 +14299,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -14327,7 +14342,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 55307-2025</t>
+          <t>A 9850-2026</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -14341,10 +14356,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45970</v>
+        <v>46072</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14357,7 +14372,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -14400,7 +14415,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 6081-2023</t>
+          <t>A 29138-2026</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -14410,14 +14425,14 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>44959</v>
+        <v>46202</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14429,8 +14444,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I172" t="n">
-        <v>0.4</v>
+        <v>4.2</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -14473,7 +14493,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 62277-2025</t>
+          <t>A 29124-2026</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -14487,10 +14507,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>46006</v>
+        <v>46202</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14503,7 +14523,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -14546,7 +14566,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 31114-2024</t>
+          <t>A 29135-2026</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14556,14 +14576,14 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45502</v>
+        <v>46202</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14575,8 +14595,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I174" t="n">
-        <v>0.6</v>
+        <v>4.7</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14619,7 +14644,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 11941-2025</t>
+          <t>A 29137-2026</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14629,14 +14654,14 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45728</v>
+        <v>46202</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14648,8 +14673,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I175" t="n">
-        <v>0.6</v>
+        <v>7.8</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14692,7 +14722,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 57017-2025</t>
+          <t>A 7402-2026</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14706,10 +14736,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45978</v>
+        <v>46059</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14722,7 +14752,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>5.5</v>
+        <v>4.7</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14765,7 +14795,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 38684-2022</t>
+          <t>A 119-2023</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14779,10 +14809,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>44814</v>
+        <v>44928</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14795,7 +14825,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>2.5</v>
+        <v>0.8</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14838,7 +14868,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 37757-2024</t>
+          <t>A 50715-2024</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14852,10 +14882,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45541</v>
+        <v>45602</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14868,7 +14898,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14911,7 +14941,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 20047-2026</t>
+          <t>A 37724-2022</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14925,10 +14955,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>46136</v>
+        <v>44810</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14941,7 +14971,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14984,7 +15014,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 25183-2023</t>
+          <t>A 37728-2022</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14998,10 +15028,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>45079</v>
+        <v>44810</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15014,7 +15044,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -15057,7 +15087,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 44073-2024</t>
+          <t>A 47637-2023</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -15071,10 +15101,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>45572</v>
+        <v>45203</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15087,7 +15117,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -15130,7 +15160,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 37276-2024</t>
+          <t>A 33873-2024</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -15144,10 +15174,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>45540</v>
+        <v>45521</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15160,7 +15190,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>1.6</v>
+        <v>3.5</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -15203,7 +15233,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 38073-2026</t>
+          <t>A 3542-2025</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -15217,10 +15247,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>46280</v>
+        <v>45680</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15232,8 +15262,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I183" t="n">
-        <v>2.3</v>
+        <v>1.4</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -15276,7 +15311,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 20595-2024</t>
+          <t>A 13228-2024</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -15290,10 +15325,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>45436</v>
+        <v>45386</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15305,13 +15340,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H184" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I184" t="n">
-        <v>3.5</v>
+        <v>0.7</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -15354,7 +15384,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 826-2026</t>
+          <t>A 15998-2024</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -15368,10 +15398,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>46030</v>
+        <v>45405</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15383,13 +15413,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H185" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I185" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -15432,7 +15457,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 829-2026</t>
+          <t>A 16001-2024</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -15446,10 +15471,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>46030</v>
+        <v>45405</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15461,13 +15486,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H186" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I186" t="n">
-        <v>6.9</v>
+        <v>0.2</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -15510,7 +15530,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 119-2023</t>
+          <t>A 31114-2024</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -15524,10 +15544,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>44928</v>
+        <v>45502</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15540,7 +15560,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -15583,7 +15603,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 821-2026</t>
+          <t>A 13804-2024</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15597,10 +15617,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>46030</v>
+        <v>45391</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15612,13 +15632,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H188" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I188" t="n">
-        <v>4.3</v>
+        <v>0.5</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15661,7 +15676,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 554-2026</t>
+          <t>A 19777-2023</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15675,10 +15690,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>46029</v>
+        <v>45051</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15691,7 +15706,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>0.8</v>
+        <v>4.3</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15734,7 +15749,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 43685-2022</t>
+          <t>A 28746-2024</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15744,14 +15759,14 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>44837</v>
+        <v>45478</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15764,7 +15779,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15807,7 +15822,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 24724-2024</t>
+          <t>A 23606-2026</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15821,10 +15836,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>45460</v>
+        <v>46162</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15837,7 +15852,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>1.4</v>
+        <v>9.4</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15880,7 +15895,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 37300-2026</t>
+          <t>A 6558-2025</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15890,14 +15905,14 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>46274</v>
+        <v>45699</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15909,8 +15924,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I192" t="n">
-        <v>0.2</v>
+        <v>0.9</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15953,7 +15973,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 1989-2026</t>
+          <t>A 25183-2023</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15967,10 +15987,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>46035</v>
+        <v>45079</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15983,7 +16003,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -16026,7 +16046,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 6558-2025</t>
+          <t>A 34737-2026</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -16036,14 +16056,14 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>45699</v>
+        <v>46258</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16055,13 +16075,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H194" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I194" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -16104,7 +16119,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 3013-2026</t>
+          <t>A 34740-2026</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -16118,10 +16133,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>46038</v>
+        <v>46258</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16134,7 +16149,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>0.7</v>
+        <v>2.1</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -16177,7 +16192,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 2747-2023</t>
+          <t>A 30934-2026</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -16191,10 +16206,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>44944</v>
+        <v>46213</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16206,13 +16221,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H196" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I196" t="n">
-        <v>4.6</v>
+        <v>1.1</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -16255,7 +16265,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 31522-2022</t>
+          <t>A 41940-2022</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -16269,10 +16279,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>44775</v>
+        <v>44833</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16285,7 +16295,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>1.8</v>
+        <v>0.7</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -16328,7 +16338,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 55265-2023</t>
+          <t>A 55307-2025</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -16342,10 +16352,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>45237</v>
+        <v>45970</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16358,7 +16368,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>1.2</v>
+        <v>2.5</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -16401,7 +16411,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 5374-2026</t>
+          <t>A 31286-2026</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -16415,10 +16425,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>46050</v>
+        <v>46218</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16431,7 +16441,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -16474,7 +16484,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 28918-2023</t>
+          <t>A 38684-2022</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -16488,10 +16498,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>45104</v>
+        <v>44814</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16504,7 +16514,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -16547,7 +16557,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 3239-2023</t>
+          <t>A 57017-2025</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -16561,10 +16571,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>44946</v>
+        <v>45978</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16577,7 +16587,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>0.4</v>
+        <v>5.5</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -16620,7 +16630,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 13228-2024</t>
+          <t>A 52310-2023</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -16634,10 +16644,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>45386</v>
+        <v>45224</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16650,7 +16660,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>0.7</v>
+        <v>3.5</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16693,7 +16703,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 48427-2022</t>
+          <t>A 20047-2026</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16707,10 +16717,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>44858</v>
+        <v>46136</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16722,13 +16732,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H203" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I203" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -16771,7 +16776,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 4756-2025</t>
+          <t>A 2170-2025</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -16785,10 +16790,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>45688</v>
+        <v>45673</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16801,7 +16806,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>0.9</v>
+        <v>3.6</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16844,7 +16849,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 8310-2026</t>
+          <t>A 38073-2026</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16858,10 +16863,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>46064</v>
+        <v>46280</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16874,7 +16879,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>1.4</v>
+        <v>2.3</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16917,7 +16922,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 33358-2023</t>
+          <t>A 16665-2025</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16931,10 +16936,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>45128</v>
+        <v>45754</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16947,7 +16952,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>0.4</v>
+        <v>2.4</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16990,7 +16995,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 39507-2024</t>
+          <t>A 43711-2024</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -17000,14 +17005,14 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>45551</v>
+        <v>45569</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17019,13 +17024,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H207" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I207" t="n">
-        <v>0.3</v>
+        <v>3.4</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -17068,7 +17068,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 41940-2022</t>
+          <t>A 37300-2026</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -17082,10 +17082,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>44833</v>
+        <v>46274</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17098,7 +17098,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -17141,7 +17141,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 43882-2023</t>
+          <t>A 23484-2025</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -17155,10 +17155,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>45187</v>
+        <v>45792</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17170,13 +17170,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H209" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I209" t="n">
-        <v>1.2</v>
+        <v>3.5</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -17219,7 +17214,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 28527-2023</t>
+          <t>A 28550-2025</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -17233,10 +17228,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>45103</v>
+        <v>45818</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17249,7 +17244,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>0.7</v>
+        <v>5</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -17292,7 +17287,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 19420-2022</t>
+          <t>A 9612-2025</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -17306,10 +17301,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>44693</v>
+        <v>45715</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17322,7 +17317,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -17365,7 +17360,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 47641-2023</t>
+          <t>A 29244-2025</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -17379,10 +17374,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>45203</v>
+        <v>45824</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17395,7 +17390,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>4.8</v>
+        <v>0.7</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -17438,7 +17433,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 60963-2023</t>
+          <t>A 29354-2025</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -17452,10 +17447,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>45261</v>
+        <v>45824</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17468,7 +17463,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -17511,7 +17506,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 52310-2023</t>
+          <t>A 32958-2025</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -17525,10 +17520,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>45224</v>
+        <v>45839</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17541,7 +17536,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -17584,7 +17579,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 2170-2025</t>
+          <t>A 32459-2025</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -17598,10 +17593,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>45673</v>
+        <v>45838</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17614,7 +17609,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>3.6</v>
+        <v>1.2</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -17657,7 +17652,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 16665-2025</t>
+          <t>A 2981-2024</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -17671,10 +17666,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>45754</v>
+        <v>45315</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17686,8 +17681,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I216" t="n">
-        <v>2.4</v>
+        <v>6.4</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -17730,7 +17730,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 43711-2024</t>
+          <t>A 37756-2024</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -17740,14 +17740,14 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>45569</v>
+        <v>45541</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17760,7 +17760,7 @@
         </is>
       </c>
       <c r="I217" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -17803,7 +17803,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 23484-2025</t>
+          <t>A 36355-2025</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -17817,10 +17817,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>45792</v>
+        <v>45868</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17833,7 +17833,7 @@
         </is>
       </c>
       <c r="I218" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -17876,7 +17876,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 28550-2025</t>
+          <t>A 25552-2025</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -17890,10 +17890,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>45818</v>
+        <v>45803</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17906,7 +17906,7 @@
         </is>
       </c>
       <c r="I219" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -17949,7 +17949,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 9612-2025</t>
+          <t>A 38147-2025</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -17963,10 +17963,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>45715</v>
+        <v>45882</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17979,7 +17979,7 @@
         </is>
       </c>
       <c r="I220" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -18039,7 +18039,7 @@
         <v>45230</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18112,7 +18112,7 @@
         <v>44796</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18185,7 +18185,7 @@
         <v>45722</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18258,7 +18258,7 @@
         <v>46042</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18314,7 +18314,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>S 220-2026</t>
+          <t>S 1874-2026</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -18328,10 +18328,10 @@
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>46051</v>
+        <v>46202</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18343,8 +18343,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I225" t="n">
-        <v>1.7</v>
+        <v>7.8</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -18387,7 +18392,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>S 1874-2026</t>
+          <t>S 1875-2026</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -18404,7 +18409,7 @@
         <v>46202</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18422,7 +18427,7 @@
         </is>
       </c>
       <c r="I226" t="n">
-        <v>7.8</v>
+        <v>4.2</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -18465,7 +18470,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>S 1875-2026</t>
+          <t>S 1873-2026</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -18482,7 +18487,7 @@
         <v>46202</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18500,7 +18505,7 @@
         </is>
       </c>
       <c r="I227" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -18543,7 +18548,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>S 1873-2026</t>
+          <t>S 220-2026</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -18557,10 +18562,10 @@
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>46202</v>
+        <v>46051</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18572,13 +18577,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H228" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I228" t="n">
-        <v>4.7</v>
+        <v>1.7</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>

--- a/Översikt HÖRBY.xlsx
+++ b/Översikt HÖRBY.xlsx
@@ -601,7 +601,7 @@
         <v>44964</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
         <v>44967</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         <v>44727</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -949,7 +949,7 @@
         <v>45786</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1061,7 +1061,7 @@
         <v>46160</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
         <v>45238</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
         <v>44819</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
         <v>46112</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1514,7 +1514,7 @@
         <v>44774</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1627,7 +1627,7 @@
         <v>45434</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1736,7 +1736,7 @@
         <v>46150</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         <v>45545</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1952,7 +1952,7 @@
         <v>45334</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
         <v>45434</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
         <v>45815</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2274,7 +2274,7 @@
         <v>45799</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2381,7 +2381,7 @@
         <v>44725</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2488,7 +2488,7 @@
         <v>45677</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2595,7 +2595,7 @@
         <v>46030</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2706,7 +2706,7 @@
         <v>45176</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         <v>45572</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2918,7 +2918,7 @@
         <v>45317</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3024,7 +3024,7 @@
         <v>45502</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3129,7 +3129,7 @@
         <v>45203</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3234,7 +3234,7 @@
         <v>45169</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3343,7 +3343,7 @@
         <v>44928</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3448,7 +3448,7 @@
         <v>46174</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3558,7 +3558,7 @@
         <v>45463</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3663,7 +3663,7 @@
         <v>46112</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3768,7 +3768,7 @@
         <v>46218</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
         <v>45783</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3978,7 +3978,7 @@
         <v>46206</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4083,7 +4083,7 @@
         <v>46202</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4193,7 +4193,7 @@
         <v>45802</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4298,7 +4298,7 @@
         <v>45868</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4403,7 +4403,7 @@
         <v>45089</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4508,7 +4508,7 @@
         <v>44999</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4613,7 +4613,7 @@
         <v>44509</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4686,7 +4686,7 @@
         <v>44663</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4759,7 +4759,7 @@
         <v>44509</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4832,7 +4832,7 @@
         <v>44697</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4905,7 +4905,7 @@
         <v>44510</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4978,7 +4978,7 @@
         <v>44834</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5051,7 +5051,7 @@
         <v>44771</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5124,7 +5124,7 @@
         <v>44466</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5197,7 +5197,7 @@
         <v>44789</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5270,7 +5270,7 @@
         <v>44733</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5343,7 +5343,7 @@
         <v>45315</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5421,7 +5421,7 @@
         <v>45763</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5494,7 +5494,7 @@
         <v>45680</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5567,7 +5567,7 @@
         <v>45128</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5640,7 +5640,7 @@
         <v>45541</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5713,7 +5713,7 @@
         <v>45460</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5786,7 +5786,7 @@
         <v>45677</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5859,7 +5859,7 @@
         <v>45104</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5932,7 +5932,7 @@
         <v>45750</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
         <v>45250</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6078,7 +6078,7 @@
         <v>45117</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6151,7 +6151,7 @@
         <v>45688</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6224,7 +6224,7 @@
         <v>45189</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6302,7 +6302,7 @@
         <v>45342</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6380,7 +6380,7 @@
         <v>44858</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6453,7 +6453,7 @@
         <v>45128</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6526,7 +6526,7 @@
         <v>45203</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6599,7 +6599,7 @@
         <v>45551</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6677,7 +6677,7 @@
         <v>45317</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6750,7 +6750,7 @@
         <v>45300</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6823,7 +6823,7 @@
         <v>45166</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6896,7 +6896,7 @@
         <v>45363</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6969,7 +6969,7 @@
         <v>45728</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7042,7 +7042,7 @@
         <v>45176</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7115,7 +7115,7 @@
         <v>45104</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7188,7 +7188,7 @@
         <v>45187</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7261,7 +7261,7 @@
         <v>45187</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7334,7 +7334,7 @@
         <v>44944</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7412,7 +7412,7 @@
         <v>44858</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7490,7 +7490,7 @@
         <v>44608</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         <v>45572</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7636,7 +7636,7 @@
         <v>45386</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7709,7 +7709,7 @@
         <v>45386</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7782,7 +7782,7 @@
         <v>45203</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7855,7 +7855,7 @@
         <v>44944</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7933,7 +7933,7 @@
         <v>45226</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8006,7 +8006,7 @@
         <v>45155</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8079,7 +8079,7 @@
         <v>45103</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8152,7 +8152,7 @@
         <v>45545</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8225,7 +8225,7 @@
         <v>45390</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8298,7 +8298,7 @@
         <v>45190</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8371,7 +8371,7 @@
         <v>45103</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8444,7 +8444,7 @@
         <v>45287</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8517,7 +8517,7 @@
         <v>45187</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8595,7 +8595,7 @@
         <v>45203</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8668,7 +8668,7 @@
         <v>46049</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8741,7 +8741,7 @@
         <v>45845</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8814,7 +8814,7 @@
         <v>45187</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8892,7 +8892,7 @@
         <v>44523</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8965,7 +8965,7 @@
         <v>44946</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9038,7 +9038,7 @@
         <v>45261</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9111,7 +9111,7 @@
         <v>44837</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9184,7 +9184,7 @@
         <v>45237</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9257,7 +9257,7 @@
         <v>45330</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9335,7 +9335,7 @@
         <v>45845</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9408,7 +9408,7 @@
         <v>45763</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9481,7 +9481,7 @@
         <v>45951</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9559,7 +9559,7 @@
         <v>45957</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9637,7 +9637,7 @@
         <v>45957</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9715,7 +9715,7 @@
         <v>45680</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9793,7 +9793,7 @@
         <v>45436</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9871,7 +9871,7 @@
         <v>45187</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9944,7 +9944,7 @@
         <v>45187</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10017,7 +10017,7 @@
         <v>45103</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10090,7 +10090,7 @@
         <v>45103</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10163,7 +10163,7 @@
         <v>45236</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10236,7 +10236,7 @@
         <v>45966</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10309,7 +10309,7 @@
         <v>45970</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10382,7 +10382,7 @@
         <v>45970</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10455,7 +10455,7 @@
         <v>45898</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10528,7 +10528,7 @@
         <v>45540</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10601,7 +10601,7 @@
         <v>45979</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10679,7 +10679,7 @@
         <v>45537</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10757,7 +10757,7 @@
         <v>45989</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10830,7 +10830,7 @@
         <v>46048</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10903,7 +10903,7 @@
         <v>44775</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10976,7 +10976,7 @@
         <v>45616</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11049,7 +11049,7 @@
         <v>45261</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11122,7 +11122,7 @@
         <v>45572</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11195,7 +11195,7 @@
         <v>45728</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11268,7 +11268,7 @@
         <v>44834</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11341,7 +11341,7 @@
         <v>45435</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11414,7 +11414,7 @@
         <v>44935</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11487,7 +11487,7 @@
         <v>46006</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11560,7 +11560,7 @@
         <v>46029</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11633,7 +11633,7 @@
         <v>45208</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11706,7 +11706,7 @@
         <v>45538</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11784,7 +11784,7 @@
         <v>46030</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11862,7 +11862,7 @@
         <v>46030</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11940,7 +11940,7 @@
         <v>46030</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12018,7 +12018,7 @@
         <v>45460</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12091,7 +12091,7 @@
         <v>45251</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12164,7 +12164,7 @@
         <v>46035</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12237,7 +12237,7 @@
         <v>46048</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12310,7 +12310,7 @@
         <v>46038</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12383,7 +12383,7 @@
         <v>45316</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12456,7 +12456,7 @@
         <v>46051</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12529,7 +12529,7 @@
         <v>45762</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12602,7 +12602,7 @@
         <v>45405</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12675,7 +12675,7 @@
         <v>45043</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12748,7 +12748,7 @@
         <v>46050</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12821,7 +12821,7 @@
         <v>44959</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12894,7 +12894,7 @@
         <v>45105</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12967,7 +12967,7 @@
         <v>44894</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13040,7 +13040,7 @@
         <v>46041</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13113,7 +13113,7 @@
         <v>46064</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13186,7 +13186,7 @@
         <v>46064</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13259,7 +13259,7 @@
         <v>46064</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13332,7 +13332,7 @@
         <v>45525</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13405,7 +13405,7 @@
         <v>46078</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13483,7 +13483,7 @@
         <v>45706</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13556,7 +13556,7 @@
         <v>45238</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13629,7 +13629,7 @@
         <v>45988</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13702,7 +13702,7 @@
         <v>46076</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13775,7 +13775,7 @@
         <v>46076</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13848,7 +13848,7 @@
         <v>46099</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13921,7 +13921,7 @@
         <v>46112</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13994,7 +13994,7 @@
         <v>45034</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14067,7 +14067,7 @@
         <v>46042</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14140,7 +14140,7 @@
         <v>46042</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14213,7 +14213,7 @@
         <v>46042</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14286,7 +14286,7 @@
         <v>44693</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14359,7 +14359,7 @@
         <v>46072</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14432,7 +14432,7 @@
         <v>46202</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14510,7 +14510,7 @@
         <v>46202</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14583,7 +14583,7 @@
         <v>46202</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14661,7 +14661,7 @@
         <v>46202</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14739,7 +14739,7 @@
         <v>46059</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14812,7 +14812,7 @@
         <v>44928</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14885,7 +14885,7 @@
         <v>45602</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14958,7 +14958,7 @@
         <v>44810</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15031,7 +15031,7 @@
         <v>44810</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15104,7 +15104,7 @@
         <v>45203</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15177,7 +15177,7 @@
         <v>45521</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15250,7 +15250,7 @@
         <v>45680</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15328,7 +15328,7 @@
         <v>45386</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15401,7 +15401,7 @@
         <v>45405</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15474,7 +15474,7 @@
         <v>45405</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15547,7 +15547,7 @@
         <v>45502</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15620,7 +15620,7 @@
         <v>45391</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15693,7 +15693,7 @@
         <v>45051</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15766,7 +15766,7 @@
         <v>45478</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15839,7 +15839,7 @@
         <v>46162</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15912,7 +15912,7 @@
         <v>45699</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15990,7 +15990,7 @@
         <v>45079</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16063,7 +16063,7 @@
         <v>46258</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16136,7 +16136,7 @@
         <v>46258</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16209,7 +16209,7 @@
         <v>46213</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16282,7 +16282,7 @@
         <v>44833</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16355,7 +16355,7 @@
         <v>45970</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16428,7 +16428,7 @@
         <v>46218</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16501,7 +16501,7 @@
         <v>44814</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16574,7 +16574,7 @@
         <v>45978</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16647,7 +16647,7 @@
         <v>45224</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16720,7 +16720,7 @@
         <v>46136</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16793,7 +16793,7 @@
         <v>45673</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16866,7 +16866,7 @@
         <v>46280</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16939,7 +16939,7 @@
         <v>45754</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17012,7 +17012,7 @@
         <v>45569</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17085,7 +17085,7 @@
         <v>46274</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17158,7 +17158,7 @@
         <v>45792</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17231,7 +17231,7 @@
         <v>45818</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17304,7 +17304,7 @@
         <v>45715</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17377,7 +17377,7 @@
         <v>45824</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17450,7 +17450,7 @@
         <v>45824</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17523,7 +17523,7 @@
         <v>45839</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17596,7 +17596,7 @@
         <v>45838</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17669,7 +17669,7 @@
         <v>45315</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17747,7 +17747,7 @@
         <v>45541</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17820,7 +17820,7 @@
         <v>45868</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17893,7 +17893,7 @@
         <v>45803</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17966,7 +17966,7 @@
         <v>45882</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18039,7 +18039,7 @@
         <v>45230</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18112,7 +18112,7 @@
         <v>44796</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18185,7 +18185,7 @@
         <v>45722</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18258,7 +18258,7 @@
         <v>46042</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18331,7 +18331,7 @@
         <v>46202</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18409,7 +18409,7 @@
         <v>46202</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18487,7 +18487,7 @@
         <v>46202</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18565,7 +18565,7 @@
         <v>46051</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>

--- a/Översikt HÖRBY.xlsx
+++ b/Översikt HÖRBY.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE228"/>
+  <dimension ref="A1:AE233"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>44964</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
         <v>44967</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         <v>44727</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -949,7 +949,7 @@
         <v>45786</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1061,7 +1061,7 @@
         <v>46160</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
         <v>45238</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 39855-2022</t>
+          <t>A 16520-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1285,14 +1285,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>44819</v>
+        <v>46112</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1305,22 +1305,22 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>4.2</v>
+        <v>2.3</v>
       </c>
       <c r="J8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>2</v>
+      </c>
+      <c r="M8" t="n">
         <v>1</v>
       </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
       <c r="N8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1329,7 +1329,7 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R8" t="n">
         <v>1</v>
@@ -1338,12 +1338,125 @@
         <v>5</v>
       </c>
       <c r="T8" t="n">
+        <v>6</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>Slåttergubbe
+Sydlig sotticka
+Älg
+Fiskgjuse
+Större brunfladdermus</t>
+        </is>
+      </c>
+      <c r="W8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 16520-2026 artfynd.xlsx", "A 16520-2026")</f>
+        <v/>
+      </c>
+      <c r="X8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 16520-2026 karta.png", "A 16520-2026")</f>
+        <v/>
+      </c>
+      <c r="Y8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 16520-2026 georefererad karta.tif", "A 16520-2026")</f>
+        <v/>
+      </c>
+      <c r="AA8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 16520-2026 FSC-klagomål.docx", "A 16520-2026")</f>
+        <v/>
+      </c>
+      <c r="AB8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 16520-2026 FSC-klagomål mail.docx", "A 16520-2026")</f>
+        <v/>
+      </c>
+      <c r="AC8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 16520-2026 tillsynsbegäran.docx", "A 16520-2026")</f>
+        <v/>
+      </c>
+      <c r="AD8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 16520-2026 tillsynsbegäran mail.docx", "A 16520-2026")</f>
+        <v/>
+      </c>
+      <c r="AE8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/fåglar/A 16520-2026 prioriterade fågelarter.docx", "A 16520-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 39855-2022</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>44819</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>HÖRBY</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J9" t="n">
+        <v>4</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1</v>
+      </c>
+      <c r="S9" t="n">
         <v>5</v>
       </c>
-      <c r="U8" t="n">
+      <c r="T9" t="n">
+        <v>5</v>
+      </c>
+      <c r="U9" t="n">
         <v>1</v>
       </c>
-      <c r="V8" s="2" t="inlineStr">
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>Ask
 Skogsknipprot
@@ -1352,145 +1465,32 @@
 Grönvit nattviol</t>
         </is>
       </c>
-      <c r="W8">
+      <c r="W9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 39855-2022 artfynd.xlsx", "A 39855-2022")</f>
         <v/>
       </c>
-      <c r="X8">
+      <c r="X9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 39855-2022 karta.png", "A 39855-2022")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="Y9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 39855-2022 georefererad karta.tif", "A 39855-2022")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AA9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 39855-2022 FSC-klagomål.docx", "A 39855-2022")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AB9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 39855-2022 FSC-klagomål mail.docx", "A 39855-2022")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AC9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 39855-2022 tillsynsbegäran.docx", "A 39855-2022")</f>
         <v/>
       </c>
-      <c r="AD8">
+      <c r="AD9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 39855-2022 tillsynsbegäran mail.docx", "A 39855-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A 16520-2026</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>46112</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>HÖRBY</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="J9" t="n">
-        <v>2</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>2</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>3</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1</v>
-      </c>
-      <c r="S9" t="n">
-        <v>5</v>
-      </c>
-      <c r="T9" t="n">
-        <v>6</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>Slåttergubbe
-Sydlig sotticka
-Älg
-Fiskgjuse
-Större brunfladdermus</t>
-        </is>
-      </c>
-      <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 16520-2026 artfynd.xlsx", "A 16520-2026")</f>
-        <v/>
-      </c>
-      <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 16520-2026 karta.png", "A 16520-2026")</f>
-        <v/>
-      </c>
-      <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 16520-2026 georefererad karta.tif", "A 16520-2026")</f>
-        <v/>
-      </c>
-      <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 16520-2026 FSC-klagomål.docx", "A 16520-2026")</f>
-        <v/>
-      </c>
-      <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 16520-2026 FSC-klagomål mail.docx", "A 16520-2026")</f>
-        <v/>
-      </c>
-      <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 16520-2026 tillsynsbegäran.docx", "A 16520-2026")</f>
-        <v/>
-      </c>
-      <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 16520-2026 tillsynsbegäran mail.docx", "A 16520-2026")</f>
-        <v/>
-      </c>
-      <c r="AE9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/fåglar/A 16520-2026 prioriterade fågelarter.docx", "A 16520-2026")</f>
         <v/>
       </c>
     </row>
@@ -1514,7 +1514,7 @@
         <v>44774</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1627,7 +1627,7 @@
         <v>45434</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1736,7 +1736,7 @@
         <v>46150</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         <v>45545</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1952,7 +1952,7 @@
         <v>45334</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
         <v>45434</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
         <v>45815</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2274,7 +2274,7 @@
         <v>45799</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2381,7 +2381,7 @@
         <v>44725</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2488,7 +2488,7 @@
         <v>45677</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 824-2026</t>
+          <t>A 42724-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2592,10 +2592,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46030</v>
+        <v>45176</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2607,13 +2607,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I20" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="J20" t="n">
         <v>1</v>
@@ -2622,22 +2617,22 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
         <v>1</v>
       </c>
-      <c r="M20" t="n">
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
         <v>1</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>2</v>
       </c>
       <c r="R20" t="n">
         <v>1</v>
@@ -2646,149 +2641,154 @@
         <v>2</v>
       </c>
       <c r="T20" t="n">
+        <v>4</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Grönvit nattviol</t>
+        </is>
+      </c>
+      <c r="W20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 42724-2023 artfynd.xlsx", "A 42724-2023")</f>
+        <v/>
+      </c>
+      <c r="X20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 42724-2023 karta.png", "A 42724-2023")</f>
+        <v/>
+      </c>
+      <c r="Y20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 42724-2023 georefererad karta.tif", "A 42724-2023")</f>
+        <v/>
+      </c>
+      <c r="AA20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 42724-2023 FSC-klagomål.docx", "A 42724-2023")</f>
+        <v/>
+      </c>
+      <c r="AB20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 42724-2023 FSC-klagomål mail.docx", "A 42724-2023")</f>
+        <v/>
+      </c>
+      <c r="AC20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 42724-2023 tillsynsbegäran.docx", "A 42724-2023")</f>
+        <v/>
+      </c>
+      <c r="AD20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 42724-2023 tillsynsbegäran mail.docx", "A 42724-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>A 824-2026</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="n">
+        <v>46030</v>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>HÖRBY</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>2</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2</v>
+      </c>
+      <c r="T21" t="n">
         <v>3</v>
       </c>
-      <c r="U20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
         <is>
           <t>Hedblomster
 Skogslysing</t>
         </is>
       </c>
-      <c r="W20">
+      <c r="W21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 824-2026 artfynd.xlsx", "A 824-2026")</f>
         <v/>
       </c>
-      <c r="X20">
+      <c r="X21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 824-2026 karta.png", "A 824-2026")</f>
         <v/>
       </c>
-      <c r="Y20">
+      <c r="Y21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 824-2026 georefererad karta.tif", "A 824-2026")</f>
         <v/>
       </c>
-      <c r="AA20">
+      <c r="AA21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 824-2026 FSC-klagomål.docx", "A 824-2026")</f>
         <v/>
       </c>
-      <c r="AB20">
+      <c r="AB21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 824-2026 FSC-klagomål mail.docx", "A 824-2026")</f>
         <v/>
       </c>
-      <c r="AC20">
+      <c r="AC21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 824-2026 tillsynsbegäran.docx", "A 824-2026")</f>
         <v/>
       </c>
-      <c r="AD20">
+      <c r="AD21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 824-2026 tillsynsbegäran mail.docx", "A 824-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>A 42724-2023</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D21" s="1" t="n">
-        <v>45176</v>
-      </c>
-      <c r="E21" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>HÖRBY</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="J21" t="n">
-        <v>1</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>1</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>1</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1</v>
-      </c>
-      <c r="S21" t="n">
-        <v>2</v>
-      </c>
-      <c r="T21" t="n">
-        <v>4</v>
-      </c>
-      <c r="U21" t="n">
-        <v>0</v>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Grönvit nattviol</t>
-        </is>
-      </c>
-      <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 42724-2023 artfynd.xlsx", "A 42724-2023")</f>
-        <v/>
-      </c>
-      <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 42724-2023 karta.png", "A 42724-2023")</f>
-        <v/>
-      </c>
-      <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 42724-2023 georefererad karta.tif", "A 42724-2023")</f>
-        <v/>
-      </c>
-      <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 42724-2023 FSC-klagomål.docx", "A 42724-2023")</f>
-        <v/>
-      </c>
-      <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 42724-2023 FSC-klagomål mail.docx", "A 42724-2023")</f>
-        <v/>
-      </c>
-      <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 42724-2023 tillsynsbegäran.docx", "A 42724-2023")</f>
-        <v/>
-      </c>
-      <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 42724-2023 tillsynsbegäran mail.docx", "A 42724-2023")</f>
         <v/>
       </c>
     </row>
@@ -2812,7 +2812,7 @@
         <v>45572</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2918,7 +2918,7 @@
         <v>45317</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3024,7 +3024,7 @@
         <v>45502</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3129,7 +3129,7 @@
         <v>45203</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3217,7 +3217,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 40376-2023</t>
+          <t>A 24823-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3231,10 +3231,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45169</v>
+        <v>46174</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3246,17 +3246,22 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I26" t="n">
-        <v>2.7</v>
+        <v>5.1</v>
       </c>
       <c r="J26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
@@ -3271,7 +3276,7 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -3283,50 +3288,46 @@
         <v>1</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tandrot</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 40376-2023 artfynd.xlsx", "A 40376-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 24823-2026 artfynd.xlsx", "A 24823-2026")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 40376-2023 karta.png", "A 40376-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 24823-2026 karta.png", "A 24823-2026")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 40376-2023 georefererad karta.tif", "A 40376-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 24823-2026 georefererad karta.tif", "A 24823-2026")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 40376-2023 FSC-klagomål.docx", "A 40376-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 24823-2026 FSC-klagomål.docx", "A 24823-2026")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 40376-2023 FSC-klagomål mail.docx", "A 40376-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 24823-2026 FSC-klagomål mail.docx", "A 24823-2026")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 40376-2023 tillsynsbegäran.docx", "A 40376-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 24823-2026 tillsynsbegäran.docx", "A 24823-2026")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 40376-2023 tillsynsbegäran mail.docx", "A 40376-2023")</f>
-        <v/>
-      </c>
-      <c r="AE26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/fåglar/A 40376-2023 prioriterade fågelarter.docx", "A 40376-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 24823-2026 tillsynsbegäran mail.docx", "A 24823-2026")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 113-2023</t>
+          <t>A 40376-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3340,10 +3341,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44928</v>
+        <v>45169</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3356,19 +3357,19 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>5.1</v>
+        <v>2.7</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
         <v>0</v>
@@ -3383,7 +3384,7 @@
         <v>1</v>
       </c>
       <c r="R27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
@@ -3396,42 +3397,46 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Slåttergubbe</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 113-2023 artfynd.xlsx", "A 113-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 40376-2023 artfynd.xlsx", "A 40376-2023")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 113-2023 karta.png", "A 113-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 40376-2023 karta.png", "A 40376-2023")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 113-2023 georefererad karta.tif", "A 113-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 40376-2023 georefererad karta.tif", "A 40376-2023")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 113-2023 FSC-klagomål.docx", "A 113-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 40376-2023 FSC-klagomål.docx", "A 40376-2023")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 113-2023 FSC-klagomål mail.docx", "A 113-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 40376-2023 FSC-klagomål mail.docx", "A 40376-2023")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 113-2023 tillsynsbegäran.docx", "A 113-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 40376-2023 tillsynsbegäran.docx", "A 40376-2023")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 113-2023 tillsynsbegäran mail.docx", "A 113-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 40376-2023 tillsynsbegäran mail.docx", "A 40376-2023")</f>
+        <v/>
+      </c>
+      <c r="AE27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/fåglar/A 40376-2023 prioriterade fågelarter.docx", "A 40376-2023")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 24823-2026</t>
+          <t>A 16519-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3445,10 +3450,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46174</v>
+        <v>46112</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3460,13 +3465,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I28" t="n">
-        <v>5.1</v>
+        <v>0.8</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3490,10 +3490,10 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
@@ -3502,46 +3502,46 @@
         <v>1</v>
       </c>
       <c r="U28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Tandrot</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 24823-2026 artfynd.xlsx", "A 24823-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 16519-2026 artfynd.xlsx", "A 16519-2026")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 24823-2026 karta.png", "A 24823-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 16519-2026 karta.png", "A 16519-2026")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 24823-2026 georefererad karta.tif", "A 24823-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 16519-2026 georefererad karta.tif", "A 16519-2026")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 24823-2026 FSC-klagomål.docx", "A 24823-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 16519-2026 FSC-klagomål.docx", "A 16519-2026")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 24823-2026 FSC-klagomål mail.docx", "A 24823-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 16519-2026 FSC-klagomål mail.docx", "A 16519-2026")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 24823-2026 tillsynsbegäran.docx", "A 24823-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 16519-2026 tillsynsbegäran.docx", "A 16519-2026")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 24823-2026 tillsynsbegäran mail.docx", "A 24823-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 16519-2026 tillsynsbegäran mail.docx", "A 16519-2026")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 25833-2024</t>
+          <t>A 113-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3555,10 +3555,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45463</v>
+        <v>44928</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3571,7 +3571,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.4</v>
+        <v>5.1</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3604,7 +3604,7 @@
         <v>1</v>
       </c>
       <c r="T29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U29" t="n">
         <v>0</v>
@@ -3615,38 +3615,38 @@
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 25833-2024 artfynd.xlsx", "A 25833-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 113-2023 artfynd.xlsx", "A 113-2023")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 25833-2024 karta.png", "A 25833-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 113-2023 karta.png", "A 113-2023")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 25833-2024 georefererad karta.tif", "A 25833-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 113-2023 georefererad karta.tif", "A 113-2023")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 25833-2024 FSC-klagomål.docx", "A 25833-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 113-2023 FSC-klagomål.docx", "A 113-2023")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 25833-2024 FSC-klagomål mail.docx", "A 25833-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 113-2023 FSC-klagomål mail.docx", "A 113-2023")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 25833-2024 tillsynsbegäran.docx", "A 25833-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 113-2023 tillsynsbegäran.docx", "A 113-2023")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 25833-2024 tillsynsbegäran mail.docx", "A 25833-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 113-2023 tillsynsbegäran mail.docx", "A 113-2023")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 16519-2026</t>
+          <t>A 25833-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3660,10 +3660,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46112</v>
+        <v>45463</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3676,7 +3676,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3688,10 +3688,10 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -3709,42 +3709,42 @@
         <v>1</v>
       </c>
       <c r="T30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U30" t="n">
         <v>0</v>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Slåttergubbe</t>
         </is>
       </c>
       <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 16519-2026 artfynd.xlsx", "A 16519-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 25833-2024 artfynd.xlsx", "A 25833-2024")</f>
         <v/>
       </c>
       <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 16519-2026 karta.png", "A 16519-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 25833-2024 karta.png", "A 25833-2024")</f>
         <v/>
       </c>
       <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 16519-2026 georefererad karta.tif", "A 16519-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 25833-2024 georefererad karta.tif", "A 25833-2024")</f>
         <v/>
       </c>
       <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 16519-2026 FSC-klagomål.docx", "A 16519-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 25833-2024 FSC-klagomål.docx", "A 25833-2024")</f>
         <v/>
       </c>
       <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 16519-2026 FSC-klagomål mail.docx", "A 16519-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 25833-2024 FSC-klagomål mail.docx", "A 25833-2024")</f>
         <v/>
       </c>
       <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 16519-2026 tillsynsbegäran.docx", "A 16519-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 25833-2024 tillsynsbegäran.docx", "A 25833-2024")</f>
         <v/>
       </c>
       <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 16519-2026 tillsynsbegäran mail.docx", "A 16519-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 25833-2024 tillsynsbegäran mail.docx", "A 25833-2024")</f>
         <v/>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
         <v>46218</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3856,7 +3856,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 21713-2025</t>
+          <t>A 30165-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3870,10 +3870,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45783</v>
+        <v>46206</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3886,23 +3886,23 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="n">
         <v>1</v>
       </c>
-      <c r="K32" t="n">
-        <v>0</v>
-      </c>
-      <c r="L32" t="n">
-        <v>0</v>
-      </c>
-      <c r="M32" t="n">
-        <v>0</v>
-      </c>
-      <c r="N32" t="n">
-        <v>0</v>
-      </c>
       <c r="O32" t="n">
         <v>0</v>
       </c>
@@ -3910,10 +3910,10 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S32" t="n">
         <v>1</v>
@@ -3926,42 +3926,42 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="W32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 21713-2025 artfynd.xlsx", "A 21713-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 30165-2026 artfynd.xlsx", "A 30165-2026")</f>
         <v/>
       </c>
       <c r="X32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 21713-2025 karta.png", "A 21713-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 30165-2026 karta.png", "A 30165-2026")</f>
         <v/>
       </c>
       <c r="Y32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 21713-2025 georefererad karta.tif", "A 21713-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 30165-2026 georefererad karta.tif", "A 30165-2026")</f>
         <v/>
       </c>
       <c r="AA32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 21713-2025 FSC-klagomål.docx", "A 21713-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 30165-2026 FSC-klagomål.docx", "A 30165-2026")</f>
         <v/>
       </c>
       <c r="AB32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 21713-2025 FSC-klagomål mail.docx", "A 21713-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 30165-2026 FSC-klagomål mail.docx", "A 30165-2026")</f>
         <v/>
       </c>
       <c r="AC32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 21713-2025 tillsynsbegäran.docx", "A 21713-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 30165-2026 tillsynsbegäran.docx", "A 30165-2026")</f>
         <v/>
       </c>
       <c r="AD32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 21713-2025 tillsynsbegäran mail.docx", "A 21713-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 30165-2026 tillsynsbegäran mail.docx", "A 30165-2026")</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 30165-2026</t>
+          <t>A 29129-2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>46206</v>
+        <v>46202</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3990,8 +3990,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I33" t="n">
-        <v>1.4</v>
+        <v>10.5</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -4000,13 +4005,13 @@
         <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M33" t="n">
         <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4018,7 +4023,7 @@
         <v>1</v>
       </c>
       <c r="R33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
         <v>1</v>
@@ -4031,42 +4036,42 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Ekticka</t>
         </is>
       </c>
       <c r="W33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 30165-2026 artfynd.xlsx", "A 30165-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 29129-2026 artfynd.xlsx", "A 29129-2026")</f>
         <v/>
       </c>
       <c r="X33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 30165-2026 karta.png", "A 30165-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 29129-2026 karta.png", "A 29129-2026")</f>
         <v/>
       </c>
       <c r="Y33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 30165-2026 georefererad karta.tif", "A 30165-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 29129-2026 georefererad karta.tif", "A 29129-2026")</f>
         <v/>
       </c>
       <c r="AA33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 30165-2026 FSC-klagomål.docx", "A 30165-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 29129-2026 FSC-klagomål.docx", "A 29129-2026")</f>
         <v/>
       </c>
       <c r="AB33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 30165-2026 FSC-klagomål mail.docx", "A 30165-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 29129-2026 FSC-klagomål mail.docx", "A 29129-2026")</f>
         <v/>
       </c>
       <c r="AC33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 30165-2026 tillsynsbegäran.docx", "A 30165-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 29129-2026 tillsynsbegäran.docx", "A 29129-2026")</f>
         <v/>
       </c>
       <c r="AD33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 30165-2026 tillsynsbegäran mail.docx", "A 30165-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 29129-2026 tillsynsbegäran mail.docx", "A 29129-2026")</f>
         <v/>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 29129-2026</t>
+          <t>A 21713-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4080,10 +4085,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>46202</v>
+        <v>45783</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4095,22 +4100,17 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I34" t="n">
-        <v>10.5</v>
+        <v>0.8</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
         <v>0</v>
@@ -4125,7 +4125,7 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
         <v>0</v>
@@ -4141,35 +4141,35 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>Ekticka</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="W34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 29129-2026 artfynd.xlsx", "A 29129-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 21713-2025 artfynd.xlsx", "A 21713-2025")</f>
         <v/>
       </c>
       <c r="X34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 29129-2026 karta.png", "A 29129-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 21713-2025 karta.png", "A 21713-2025")</f>
         <v/>
       </c>
       <c r="Y34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 29129-2026 georefererad karta.tif", "A 29129-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 21713-2025 georefererad karta.tif", "A 21713-2025")</f>
         <v/>
       </c>
       <c r="AA34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 29129-2026 FSC-klagomål.docx", "A 29129-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 21713-2025 FSC-klagomål.docx", "A 21713-2025")</f>
         <v/>
       </c>
       <c r="AB34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 29129-2026 FSC-klagomål mail.docx", "A 29129-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 21713-2025 FSC-klagomål mail.docx", "A 21713-2025")</f>
         <v/>
       </c>
       <c r="AC34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 29129-2026 tillsynsbegäran.docx", "A 29129-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 21713-2025 tillsynsbegäran.docx", "A 21713-2025")</f>
         <v/>
       </c>
       <c r="AD34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 29129-2026 tillsynsbegäran mail.docx", "A 29129-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 21713-2025 tillsynsbegäran mail.docx", "A 21713-2025")</f>
         <v/>
       </c>
     </row>
@@ -4193,7 +4193,7 @@
         <v>45802</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4298,7 +4298,7 @@
         <v>45868</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4403,7 +4403,7 @@
         <v>45089</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4508,7 +4508,7 @@
         <v>44999</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4613,7 +4613,7 @@
         <v>44509</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4686,7 +4686,7 @@
         <v>44663</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4759,7 +4759,7 @@
         <v>44509</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4832,7 +4832,7 @@
         <v>44697</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4905,7 +4905,7 @@
         <v>44510</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4978,7 +4978,7 @@
         <v>44834</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5051,7 +5051,7 @@
         <v>44771</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5124,7 +5124,7 @@
         <v>44466</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5197,7 +5197,7 @@
         <v>44789</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5270,7 +5270,7 @@
         <v>44733</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5326,7 +5326,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 2979-2024</t>
+          <t>A 24670-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5336,14 +5336,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45315</v>
+        <v>45460</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5355,13 +5355,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I49" t="n">
-        <v>4.7</v>
+        <v>0.2</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5404,7 +5399,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 18609-2025</t>
+          <t>A 2979-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5418,10 +5413,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45763</v>
+        <v>45315</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5433,8 +5428,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I50" t="n">
-        <v>0.6</v>
+        <v>4.7</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5477,7 +5477,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 3471-2025</t>
+          <t>A 18609-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5491,10 +5491,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45680</v>
+        <v>45763</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>3.7</v>
+        <v>0.6</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5550,7 +5550,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 33359-2023</t>
+          <t>A 3471-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5564,10 +5564,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45128</v>
+        <v>45680</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5580,7 +5580,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.9</v>
+        <v>3.7</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5623,7 +5623,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 37757-2024</t>
+          <t>A 33359-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5637,10 +5637,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45541</v>
+        <v>45128</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5653,7 +5653,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5696,7 +5696,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 24670-2024</t>
+          <t>A 37757-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5706,14 +5706,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45460</v>
+        <v>45541</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5726,7 +5726,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5769,7 +5769,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 2816-2025</t>
+          <t>A 31596-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5779,14 +5779,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45677</v>
+        <v>45117</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5799,7 +5799,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5842,7 +5842,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 28785-2023</t>
+          <t>A 44613-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5852,14 +5852,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45104</v>
+        <v>45189</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5871,8 +5871,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I56" t="n">
-        <v>2.1</v>
+        <v>3.8</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5915,7 +5920,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 16101-2025</t>
+          <t>A 2816-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5925,14 +5930,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45750</v>
+        <v>45677</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5945,7 +5950,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5988,7 +5993,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 58360-2023</t>
+          <t>A 28785-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5998,14 +6003,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45250</v>
+        <v>45104</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6018,7 +6023,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -6061,7 +6066,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 31596-2023</t>
+          <t>A 16101-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6075,10 +6080,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45117</v>
+        <v>45750</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6134,7 +6139,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 4756-2025</t>
+          <t>A 58360-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6148,10 +6153,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45688</v>
+        <v>45250</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6164,7 +6169,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.9</v>
+        <v>2.5</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6207,7 +6212,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 44613-2023</t>
+          <t>A 4756-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6221,10 +6226,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45189</v>
+        <v>45688</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6236,13 +6241,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I61" t="n">
-        <v>3.8</v>
+        <v>0.9</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6285,7 +6285,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 6886-2024</t>
+          <t>A 48397-2022</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6299,10 +6299,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45342</v>
+        <v>44858</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6314,13 +6314,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I62" t="n">
-        <v>0.5</v>
+        <v>1.7</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6363,7 +6358,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 48397-2022</t>
+          <t>A 6886-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6377,10 +6372,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44858</v>
+        <v>45342</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6392,8 +6387,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I63" t="n">
-        <v>1.7</v>
+        <v>0.5</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6453,7 +6453,7 @@
         <v>45128</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6509,7 +6509,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 47641-2023</t>
+          <t>A 39298-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6523,10 +6523,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45203</v>
+        <v>45166</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6539,7 +6539,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6599,7 +6599,7 @@
         <v>45551</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6677,7 +6677,7 @@
         <v>45317</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6750,7 +6750,7 @@
         <v>45300</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6806,7 +6806,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 39298-2023</t>
+          <t>A 9974-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6820,10 +6820,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45166</v>
+        <v>45363</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6836,7 +6836,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>4.6</v>
+        <v>0.6</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6879,7 +6879,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 9974-2024</t>
+          <t>A 11943-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6893,10 +6893,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45363</v>
+        <v>45728</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6909,7 +6909,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6952,7 +6952,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 11943-2025</t>
+          <t>A 42715-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6966,10 +6966,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45728</v>
+        <v>45176</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6982,7 +6982,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -7025,7 +7025,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 42715-2023</t>
+          <t>A 28918-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7039,10 +7039,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45176</v>
+        <v>45104</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7055,7 +7055,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7098,7 +7098,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 28918-2023</t>
+          <t>A 47641-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7112,10 +7112,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45104</v>
+        <v>45203</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7128,7 +7128,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>2</v>
+        <v>4.8</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7188,7 +7188,7 @@
         <v>45187</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7261,7 +7261,7 @@
         <v>45187</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7334,7 +7334,7 @@
         <v>44944</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7412,7 +7412,7 @@
         <v>44858</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7490,7 +7490,7 @@
         <v>44608</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         <v>45572</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7636,7 +7636,7 @@
         <v>45386</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7709,7 +7709,7 @@
         <v>45386</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7782,7 +7782,7 @@
         <v>45203</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7838,7 +7838,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 2752-2023</t>
+          <t>A 25552-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7852,10 +7852,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>44944</v>
+        <v>45803</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7867,13 +7867,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I83" t="n">
-        <v>0.6</v>
+        <v>2</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7916,7 +7911,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 54431-2023</t>
+          <t>A 2752-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7930,10 +7925,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45226</v>
+        <v>44944</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7945,8 +7940,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I84" t="n">
-        <v>3.2</v>
+        <v>0.6</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7989,7 +7989,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 37082-2023</t>
+          <t>A 38147-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7999,14 +7999,14 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45155</v>
+        <v>45882</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8019,7 +8019,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -8062,7 +8062,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 28625-2023</t>
+          <t>A 37082-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -8072,14 +8072,14 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45103</v>
+        <v>45155</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8092,7 +8092,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>4.8</v>
+        <v>0.5</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8135,7 +8135,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 38080-2024</t>
+          <t>A 54431-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8149,10 +8149,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45545</v>
+        <v>45226</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8165,7 +8165,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.7</v>
+        <v>3.2</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8208,7 +8208,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 13633-2024</t>
+          <t>A 28625-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8222,10 +8222,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45390</v>
+        <v>45103</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8238,7 +8238,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1.1</v>
+        <v>4.8</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8281,7 +8281,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 44816-2023</t>
+          <t>A 65073-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8295,10 +8295,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45190</v>
+        <v>45287</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8311,7 +8311,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8354,7 +8354,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 28493-2023</t>
+          <t>A 38080-2024</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8368,10 +8368,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45103</v>
+        <v>45545</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8384,7 +8384,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8427,7 +8427,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 65073-2023</t>
+          <t>A 34154-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8441,10 +8441,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45287</v>
+        <v>45845</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8457,7 +8457,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>1.7</v>
+        <v>5</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8500,7 +8500,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 43879-2023</t>
+          <t>A 5079-2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8514,10 +8514,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45187</v>
+        <v>46049</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8529,13 +8529,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I92" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8578,7 +8573,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 47609-2023</t>
+          <t>A 13633-2024</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8592,10 +8587,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45203</v>
+        <v>45390</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8608,7 +8603,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>2.4</v>
+        <v>1.1</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8651,7 +8646,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 5079-2026</t>
+          <t>A 44816-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8665,10 +8660,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>46049</v>
+        <v>45190</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8681,7 +8676,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8724,7 +8719,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 34154-2025</t>
+          <t>A 28493-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8738,10 +8733,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45845</v>
+        <v>45103</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8754,7 +8749,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>5</v>
+        <v>0.8</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8797,7 +8792,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 43882-2023</t>
+          <t>A 43879-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8814,7 +8809,7 @@
         <v>45187</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8832,7 +8827,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8875,7 +8870,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 67426-2021</t>
+          <t>A 47609-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8889,10 +8884,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>44523</v>
+        <v>45203</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8905,7 +8900,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>0.6</v>
+        <v>2.4</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8948,7 +8943,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 3239-2023</t>
+          <t>A 34147-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8962,10 +8957,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>44946</v>
+        <v>45845</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8978,7 +8973,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>0.4</v>
+        <v>18.7</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -9021,7 +9016,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 60963-2023</t>
+          <t>A 43882-2023</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -9035,10 +9030,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45261</v>
+        <v>45187</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9048,6 +9043,11 @@
       <c r="G99" t="inlineStr">
         <is>
           <t>HÖRBY</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I99" t="n">
@@ -9094,7 +9094,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 43685-2022</t>
+          <t>A 67426-2021</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -9104,14 +9104,14 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>44837</v>
+        <v>44523</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9124,7 +9124,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -9167,7 +9167,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 55265-2023</t>
+          <t>A 51757-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9177,14 +9177,14 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45237</v>
+        <v>45951</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9196,8 +9196,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I101" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9240,7 +9245,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 5163-2024</t>
+          <t>A 3239-2023</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9254,10 +9259,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45330</v>
+        <v>44946</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9269,13 +9274,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I102" t="n">
-        <v>7.1</v>
+        <v>0.4</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9318,7 +9318,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 34147-2025</t>
+          <t>A 60963-2023</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9332,10 +9332,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45845</v>
+        <v>45261</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9348,7 +9348,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>18.7</v>
+        <v>1.2</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9391,7 +9391,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 18603-2025</t>
+          <t>A 52930-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9405,10 +9405,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45763</v>
+        <v>45957</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9420,8 +9420,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I104" t="n">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9464,7 +9469,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 51757-2025</t>
+          <t>A 52929-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9474,14 +9479,14 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45951</v>
+        <v>45957</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9499,7 +9504,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1.3</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9542,7 +9547,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 52930-2025</t>
+          <t>A 43685-2022</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9552,14 +9557,14 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45957</v>
+        <v>44837</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9571,13 +9576,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I106" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9620,7 +9620,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 52929-2025</t>
+          <t>A 4597-2026</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9634,10 +9634,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45957</v>
+        <v>46048</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9649,13 +9649,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I107" t="n">
-        <v>8.300000000000001</v>
+        <v>1.3</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9698,7 +9693,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 3534-2025</t>
+          <t>A 54765-2025</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9712,10 +9707,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45680</v>
+        <v>45966</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9727,13 +9722,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I108" t="n">
-        <v>4.8</v>
+        <v>2.6</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9776,7 +9766,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 20595-2024</t>
+          <t>A 55304-2025</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9786,14 +9776,14 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45436</v>
+        <v>45970</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9805,13 +9795,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I109" t="n">
-        <v>3.5</v>
+        <v>0.4</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9854,7 +9839,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 43937-2023</t>
+          <t>A 55306-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9864,14 +9849,14 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45187</v>
+        <v>45970</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9884,7 +9869,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>2.6</v>
+        <v>0.3</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9927,7 +9912,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 43939-2023</t>
+          <t>A 55265-2023</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9941,10 +9926,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45187</v>
+        <v>45237</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9957,7 +9942,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -10000,7 +9985,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 28501-2023</t>
+          <t>A 40994-2025</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -10014,10 +9999,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45103</v>
+        <v>45898</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10030,7 +10015,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>3.6</v>
+        <v>5.6</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -10073,7 +10058,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 28527-2023</t>
+          <t>A 5163-2024</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -10087,10 +10072,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45103</v>
+        <v>45330</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10102,8 +10087,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I113" t="n">
-        <v>0.7</v>
+        <v>7.1</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -10146,7 +10136,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 54894-2023</t>
+          <t>A 57269-2025</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -10160,10 +10150,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45236</v>
+        <v>45979</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10175,8 +10165,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I114" t="n">
-        <v>0.6</v>
+        <v>5.5</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -10219,7 +10214,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 54765-2025</t>
+          <t>A 18603-2025</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10233,10 +10228,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45966</v>
+        <v>45763</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10249,7 +10244,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>2.6</v>
+        <v>0.5</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10292,7 +10287,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 55304-2025</t>
+          <t>A 59308-2025</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10302,14 +10297,14 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45970</v>
+        <v>45989</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10322,7 +10317,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10365,7 +10360,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 55306-2025</t>
+          <t>A 4590-2026</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10375,14 +10370,14 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45970</v>
+        <v>46048</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10395,7 +10390,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>0.3</v>
+        <v>1.1</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10438,7 +10433,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 40994-2025</t>
+          <t>A 3534-2025</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10452,10 +10447,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45898</v>
+        <v>45680</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10467,8 +10462,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I118" t="n">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10511,7 +10511,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 37276-2024</t>
+          <t>A 20595-2024</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10525,10 +10525,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45540</v>
+        <v>45436</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10540,8 +10540,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I119" t="n">
-        <v>1.6</v>
+        <v>3.5</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10584,7 +10589,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 57269-2025</t>
+          <t>A 6350-2026</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10598,10 +10603,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45979</v>
+        <v>46051</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10613,13 +10618,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I120" t="n">
-        <v>5.5</v>
+        <v>2.4</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10662,7 +10662,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 36689-2024</t>
+          <t>A 18369-2025</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10672,14 +10672,14 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45537</v>
+        <v>45762</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10691,13 +10691,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I121" t="n">
-        <v>9.5</v>
+        <v>2.2</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10740,7 +10735,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 59308-2025</t>
+          <t>A 43937-2023</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10754,10 +10749,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45989</v>
+        <v>45187</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10770,7 +10765,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>1.2</v>
+        <v>2.6</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10813,7 +10808,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 4597-2026</t>
+          <t>A 43939-2023</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10827,10 +10822,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>46048</v>
+        <v>45187</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10843,7 +10838,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10886,7 +10881,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 31522-2022</t>
+          <t>A 28501-2023</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10900,10 +10895,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>44775</v>
+        <v>45103</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10916,7 +10911,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>1.8</v>
+        <v>3.6</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10959,7 +10954,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 54184-2024</t>
+          <t>A 28527-2023</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10973,10 +10968,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45616</v>
+        <v>45103</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10989,7 +10984,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -11032,7 +11027,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 60913-2023</t>
+          <t>A 54894-2023</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -11046,10 +11041,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45261</v>
+        <v>45236</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11062,7 +11057,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -11105,7 +11100,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 44073-2024</t>
+          <t>A 62277-2025</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -11119,10 +11114,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45572</v>
+        <v>46006</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11135,7 +11130,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>1</v>
+        <v>2.4</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -11178,7 +11173,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 11941-2025</t>
+          <t>A 37276-2024</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -11192,10 +11187,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45728</v>
+        <v>45540</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11208,7 +11203,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -11251,7 +11246,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 43380-2022</t>
+          <t>A 3177-2026</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11261,14 +11256,14 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>44834</v>
+        <v>46041</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11281,7 +11276,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>1.7</v>
+        <v>0.5</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11324,7 +11319,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 20403-2024</t>
+          <t>A 554-2026</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11338,10 +11333,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45435</v>
+        <v>46029</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11354,7 +11349,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11397,7 +11392,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 1106-2023</t>
+          <t>A 826-2026</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11411,10 +11406,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>44935</v>
+        <v>46030</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11426,8 +11421,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I131" t="n">
-        <v>1.2</v>
+        <v>0.3</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11470,7 +11470,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 62277-2025</t>
+          <t>A 829-2026</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11484,10 +11484,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>46006</v>
+        <v>46030</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11499,8 +11499,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I132" t="n">
-        <v>2.4</v>
+        <v>6.9</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11543,7 +11548,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 554-2026</t>
+          <t>A 821-2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11557,10 +11562,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>46029</v>
+        <v>46030</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11572,8 +11577,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I133" t="n">
-        <v>0.8</v>
+        <v>4.3</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11616,7 +11626,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 49726-2023</t>
+          <t>A 1989-2026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11630,10 +11640,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45208</v>
+        <v>46035</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11646,7 +11656,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>1.3</v>
+        <v>2.5</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11689,7 +11699,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 36840-2024</t>
+          <t>A 36689-2024</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11699,14 +11709,14 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45538</v>
+        <v>45537</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11724,7 +11734,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>0.9</v>
+        <v>9.5</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11767,7 +11777,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 826-2026</t>
+          <t>A 3013-2026</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11781,10 +11791,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>46030</v>
+        <v>46038</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11796,13 +11806,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H136" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I136" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11845,7 +11850,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 829-2026</t>
+          <t>A 59284-2025</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11859,10 +11864,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>46030</v>
+        <v>45988</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11874,13 +11879,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H137" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I137" t="n">
-        <v>6.9</v>
+        <v>1.5</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11923,7 +11923,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 821-2026</t>
+          <t>A 31522-2022</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11937,10 +11937,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>46030</v>
+        <v>44775</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11952,13 +11952,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H138" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I138" t="n">
-        <v>4.3</v>
+        <v>1.8</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -12001,7 +11996,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 24724-2024</t>
+          <t>A 54184-2024</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -12011,14 +12006,14 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45460</v>
+        <v>45616</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12031,7 +12026,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -12074,7 +12069,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 58641-2023</t>
+          <t>A 10500-2026</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -12084,14 +12079,14 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45251</v>
+        <v>46076</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12104,7 +12099,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -12147,7 +12142,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 1989-2026</t>
+          <t>A 5374-2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -12161,10 +12156,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>46035</v>
+        <v>46050</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12177,7 +12172,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -12220,7 +12215,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 4590-2026</t>
+          <t>A 60913-2023</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -12234,10 +12229,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>46048</v>
+        <v>45261</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12250,7 +12245,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -12293,7 +12288,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 3013-2026</t>
+          <t>A 44073-2024</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12307,10 +12302,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>46038</v>
+        <v>45572</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12323,7 +12318,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -12366,7 +12361,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 3040-2024</t>
+          <t>A 16518-2026</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12380,10 +12375,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45316</v>
+        <v>46112</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12396,7 +12391,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>4</v>
+        <v>0.8</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -12439,7 +12434,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 6350-2026</t>
+          <t>A 11941-2025</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12453,10 +12448,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>46051</v>
+        <v>45728</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12469,7 +12464,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>2.4</v>
+        <v>0.6</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12512,7 +12507,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 18369-2025</t>
+          <t>A 43380-2022</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12526,10 +12521,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45762</v>
+        <v>44834</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12542,7 +12537,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12585,7 +12580,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 15970-2024</t>
+          <t>A 8310-2026</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12599,10 +12594,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45405</v>
+        <v>46064</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12615,7 +12610,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12658,7 +12653,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 18735-2023</t>
+          <t>A 8260-2026</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12672,10 +12667,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45043</v>
+        <v>46064</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12688,7 +12683,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>1</v>
+        <v>3.3</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12731,7 +12726,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 5374-2026</t>
+          <t>A 8259-2026</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12745,10 +12740,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>46050</v>
+        <v>46064</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12761,7 +12756,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>0.5</v>
+        <v>3.1</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12804,7 +12799,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 6081-2023</t>
+          <t>A 20403-2024</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12818,10 +12813,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>44959</v>
+        <v>45435</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12834,7 +12829,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12877,7 +12872,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 29219-2023</t>
+          <t>A 1106-2023</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12891,10 +12886,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45105</v>
+        <v>44935</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12907,7 +12902,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12950,7 +12945,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 56818-2022</t>
+          <t>A 10731-2026</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12964,10 +12959,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>44894</v>
+        <v>46078</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12979,8 +12974,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I152" t="n">
-        <v>1.8</v>
+        <v>4.8</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -13023,7 +13023,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 3177-2026</t>
+          <t>A 29138-2026</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -13033,14 +13033,14 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>46041</v>
+        <v>46202</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13052,8 +13052,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I153" t="n">
-        <v>0.5</v>
+        <v>4.2</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -13096,7 +13101,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 8310-2026</t>
+          <t>A 29124-2026</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -13110,10 +13115,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>46064</v>
+        <v>46202</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13126,7 +13131,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>1.4</v>
+        <v>2.9</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -13169,7 +13174,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 8260-2026</t>
+          <t>A 29135-2026</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -13179,14 +13184,14 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>46064</v>
+        <v>46202</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13198,8 +13203,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I155" t="n">
-        <v>3.3</v>
+        <v>4.7</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -13242,7 +13252,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 8259-2026</t>
+          <t>A 29137-2026</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -13252,14 +13262,14 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>46064</v>
+        <v>46202</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13271,8 +13281,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I156" t="n">
-        <v>3.1</v>
+        <v>7.8</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -13315,7 +13330,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 34422-2024</t>
+          <t>A 49726-2023</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -13325,14 +13340,14 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45525</v>
+        <v>45208</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13345,7 +13360,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -13388,7 +13403,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 10731-2026</t>
+          <t>A 36840-2024</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -13402,10 +13417,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>46078</v>
+        <v>45538</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13419,11 +13434,11 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I158" t="n">
-        <v>4.8</v>
+        <v>0.9</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -13466,7 +13481,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 7831-2025</t>
+          <t>A 24724-2024</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13476,14 +13491,14 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45706</v>
+        <v>45460</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13496,7 +13511,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -13539,7 +13554,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 56750-2023</t>
+          <t>A 58641-2023</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -13549,14 +13564,14 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45238</v>
+        <v>45251</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13569,7 +13584,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13612,7 +13627,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 59284-2025</t>
+          <t>A 14307-2026</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13626,10 +13641,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45988</v>
+        <v>46099</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13642,7 +13657,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13685,7 +13700,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 10500-2026</t>
+          <t>A 3040-2024</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13699,10 +13714,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>46076</v>
+        <v>45316</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13715,7 +13730,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>1.1</v>
+        <v>4</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13758,7 +13773,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 10524-2026</t>
+          <t>A 3470-2026</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13772,10 +13787,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>46076</v>
+        <v>46042</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13788,7 +13803,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13831,7 +13846,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 14307-2026</t>
+          <t>A 3513-2026</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13845,10 +13860,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>46099</v>
+        <v>46042</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13861,7 +13876,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13904,7 +13919,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 16518-2026</t>
+          <t>A 3520-2026</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13918,10 +13933,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>46112</v>
+        <v>46042</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13977,7 +13992,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 17073-2023</t>
+          <t>A 9850-2026</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13991,10 +14006,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45034</v>
+        <v>46072</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14007,7 +14022,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>1.2</v>
+        <v>2.2</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -14050,7 +14065,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 3470-2026</t>
+          <t>A 15970-2024</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -14064,10 +14079,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>46042</v>
+        <v>45405</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14080,7 +14095,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -14123,7 +14138,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 3513-2026</t>
+          <t>A 18735-2023</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -14137,10 +14152,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>46042</v>
+        <v>45043</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14153,7 +14168,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -14196,7 +14211,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 3520-2026</t>
+          <t>A 6081-2023</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -14210,10 +14225,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>46042</v>
+        <v>44959</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14226,7 +14241,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -14269,7 +14284,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 19420-2022</t>
+          <t>A 29219-2023</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -14283,10 +14298,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>44693</v>
+        <v>45105</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14342,7 +14357,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 9850-2026</t>
+          <t>A 56818-2022</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -14356,10 +14371,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>46072</v>
+        <v>44894</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14372,7 +14387,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -14415,7 +14430,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 29138-2026</t>
+          <t>A 7402-2026</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -14425,14 +14440,14 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>46202</v>
+        <v>46059</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14444,13 +14459,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H172" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I172" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -14493,7 +14503,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 29124-2026</t>
+          <t>A 34422-2024</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -14503,14 +14513,14 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>46202</v>
+        <v>45525</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14523,7 +14533,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>2.9</v>
+        <v>1.5</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -14566,7 +14576,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 29135-2026</t>
+          <t>A 7831-2025</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14576,14 +14586,14 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>46202</v>
+        <v>45706</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14595,13 +14605,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H174" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I174" t="n">
-        <v>4.7</v>
+        <v>0.6</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14644,7 +14649,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 29137-2026</t>
+          <t>A 56750-2023</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14654,14 +14659,14 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>46202</v>
+        <v>45238</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14673,13 +14678,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H175" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I175" t="n">
-        <v>7.8</v>
+        <v>0.8</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14722,7 +14722,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 7402-2026</t>
+          <t>A 23606-2026</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14732,14 +14732,14 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>46059</v>
+        <v>46162</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14752,7 +14752,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>4.7</v>
+        <v>9.4</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14795,7 +14795,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 119-2023</t>
+          <t>A 17073-2023</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14809,10 +14809,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>44928</v>
+        <v>45034</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14825,7 +14825,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14868,7 +14868,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 50715-2024</t>
+          <t>A 34737-2026</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14882,10 +14882,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45602</v>
+        <v>46258</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14898,7 +14898,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14941,7 +14941,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 37724-2022</t>
+          <t>A 34740-2026</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14955,10 +14955,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>44810</v>
+        <v>46258</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14971,7 +14971,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>1.2</v>
+        <v>2.1</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -15014,7 +15014,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 37728-2022</t>
+          <t>A 19420-2022</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -15028,10 +15028,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>44810</v>
+        <v>44693</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15044,7 +15044,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -15087,7 +15087,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 47637-2023</t>
+          <t>A 30934-2026</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -15101,10 +15101,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>45203</v>
+        <v>46213</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15117,7 +15117,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>2</v>
+        <v>1.1</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -15160,7 +15160,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 33873-2024</t>
+          <t>A 55307-2025</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -15174,10 +15174,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>45521</v>
+        <v>45970</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15190,7 +15190,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -15233,7 +15233,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 3542-2025</t>
+          <t>A 31286-2026</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -15247,10 +15247,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>45680</v>
+        <v>46218</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15262,13 +15262,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H183" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I183" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -15311,7 +15306,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 13228-2024</t>
+          <t>A 119-2023</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -15325,10 +15320,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>45386</v>
+        <v>44928</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15341,7 +15336,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -15384,7 +15379,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 15998-2024</t>
+          <t>A 50715-2024</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -15398,10 +15393,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>45405</v>
+        <v>45602</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15457,7 +15452,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 16001-2024</t>
+          <t>A 37724-2022</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -15471,10 +15466,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>45405</v>
+        <v>44810</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15487,7 +15482,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>0.2</v>
+        <v>1.2</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -15530,7 +15525,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 31114-2024</t>
+          <t>A 37728-2022</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -15544,10 +15539,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>45502</v>
+        <v>44810</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15560,7 +15555,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -15603,7 +15598,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 13804-2024</t>
+          <t>A 47637-2023</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15617,10 +15612,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>45391</v>
+        <v>45203</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15633,7 +15628,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15676,7 +15671,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 19777-2023</t>
+          <t>A 33873-2024</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15690,10 +15685,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>45051</v>
+        <v>45521</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15706,7 +15701,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>4.3</v>
+        <v>3.5</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15749,7 +15744,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 28746-2024</t>
+          <t>A 57017-2025</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15763,10 +15758,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>45478</v>
+        <v>45978</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15779,7 +15774,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>1.9</v>
+        <v>5.5</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15822,7 +15817,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 23606-2026</t>
+          <t>A 3542-2025</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15832,14 +15827,14 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>46162</v>
+        <v>45680</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15851,8 +15846,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I191" t="n">
-        <v>9.4</v>
+        <v>1.4</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15895,7 +15895,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 6558-2025</t>
+          <t>A 13228-2024</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15905,14 +15905,14 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>45699</v>
+        <v>45386</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15924,13 +15924,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H192" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I192" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15973,7 +15968,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 25183-2023</t>
+          <t>A 15998-2024</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15987,10 +15982,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>45079</v>
+        <v>45405</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16003,7 +15998,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>1.5</v>
+        <v>0.4</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -16046,7 +16041,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 34737-2026</t>
+          <t>A 16001-2024</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -16060,10 +16055,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>46258</v>
+        <v>45405</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16076,7 +16071,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -16119,7 +16114,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 34740-2026</t>
+          <t>A 31114-2024</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -16133,10 +16128,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>46258</v>
+        <v>45502</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16149,7 +16144,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>2.1</v>
+        <v>0.6</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -16192,7 +16187,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 30934-2026</t>
+          <t>A 13804-2024</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -16206,10 +16201,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>46213</v>
+        <v>45391</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16222,7 +16217,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -16265,7 +16260,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 41940-2022</t>
+          <t>A 19777-2023</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -16279,10 +16274,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>44833</v>
+        <v>45051</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16295,7 +16290,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>0.7</v>
+        <v>4.3</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -16338,7 +16333,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 55307-2025</t>
+          <t>A 28746-2024</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -16352,10 +16347,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>45970</v>
+        <v>45478</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16368,7 +16363,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -16411,7 +16406,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 31286-2026</t>
+          <t>A 38073-2026</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -16425,10 +16420,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>46218</v>
+        <v>46280</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16441,7 +16436,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>1.1</v>
+        <v>2.3</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -16484,7 +16479,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 38684-2022</t>
+          <t>A 6558-2025</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -16494,14 +16489,14 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>44814</v>
+        <v>45699</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16513,8 +16508,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I200" t="n">
-        <v>2.5</v>
+        <v>0.9</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -16557,7 +16557,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 57017-2025</t>
+          <t>A 25183-2023</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -16571,10 +16571,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>45978</v>
+        <v>45079</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16587,7 +16587,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>5.5</v>
+        <v>1.5</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -16630,7 +16630,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 52310-2023</t>
+          <t>A 37300-2026</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -16644,10 +16644,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>45224</v>
+        <v>46274</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16660,7 +16660,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>3.5</v>
+        <v>0.2</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16703,7 +16703,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 20047-2026</t>
+          <t>A 38936-2026</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16717,10 +16717,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>46136</v>
+        <v>46286</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16732,8 +16732,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I203" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -16776,7 +16781,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 2170-2025</t>
+          <t>A 38948-2026</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -16790,10 +16795,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>45673</v>
+        <v>46286</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16805,8 +16810,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I204" t="n">
-        <v>3.6</v>
+        <v>1.5</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16849,7 +16859,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 38073-2026</t>
+          <t>A 10524-2026</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16863,10 +16873,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>46280</v>
+        <v>46076</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16879,7 +16889,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>2.3</v>
+        <v>1.6</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16922,7 +16932,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 16665-2025</t>
+          <t>A 20047-2026</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16936,10 +16946,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>45754</v>
+        <v>46136</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16952,7 +16962,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>2.4</v>
+        <v>1.1</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16995,7 +17005,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 43711-2024</t>
+          <t>A 38824-2026</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -17005,14 +17015,14 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>45569</v>
+        <v>46286</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17024,8 +17034,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I207" t="n">
-        <v>3.4</v>
+        <v>11.2</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -17068,7 +17083,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 37300-2026</t>
+          <t>A 41940-2022</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -17082,10 +17097,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>46274</v>
+        <v>44833</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17098,7 +17113,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -17141,7 +17156,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 23484-2025</t>
+          <t>A 38906-2026</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -17155,10 +17170,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>45792</v>
+        <v>46286</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17170,8 +17185,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I209" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -17214,7 +17234,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 28550-2025</t>
+          <t>A 38730-2026</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -17228,10 +17248,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>45818</v>
+        <v>46285</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17244,7 +17264,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>5</v>
+        <v>0.4</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -17287,7 +17307,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 9612-2025</t>
+          <t>A 38684-2022</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -17301,10 +17321,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>45715</v>
+        <v>44814</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17317,7 +17337,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>1.2</v>
+        <v>2.5</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -17360,7 +17380,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 29244-2025</t>
+          <t>A 52310-2023</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -17374,10 +17394,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>45824</v>
+        <v>45224</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17390,7 +17410,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>0.7</v>
+        <v>3.5</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -17433,7 +17453,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 29354-2025</t>
+          <t>A 2170-2025</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -17447,10 +17467,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>45824</v>
+        <v>45673</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17463,7 +17483,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>0.8</v>
+        <v>3.6</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -17506,7 +17526,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 32958-2025</t>
+          <t>A 16665-2025</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -17520,10 +17540,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>45839</v>
+        <v>45754</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17536,7 +17556,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>5</v>
+        <v>2.4</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -17579,7 +17599,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 32459-2025</t>
+          <t>A 43711-2024</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -17589,14 +17609,14 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>45838</v>
+        <v>45569</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17609,7 +17629,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>1.2</v>
+        <v>3.4</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -17652,7 +17672,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 2981-2024</t>
+          <t>A 23484-2025</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -17666,10 +17686,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>45315</v>
+        <v>45792</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17681,13 +17701,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H216" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I216" t="n">
-        <v>6.4</v>
+        <v>3.5</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -17730,7 +17745,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 37756-2024</t>
+          <t>A 28550-2025</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -17744,10 +17759,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>45541</v>
+        <v>45818</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17760,7 +17775,7 @@
         </is>
       </c>
       <c r="I217" t="n">
-        <v>3.2</v>
+        <v>5</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -17803,7 +17818,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 36355-2025</t>
+          <t>A 9612-2025</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -17817,10 +17832,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>45868</v>
+        <v>45715</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17833,7 +17848,7 @@
         </is>
       </c>
       <c r="I218" t="n">
-        <v>3.6</v>
+        <v>1.2</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -17876,7 +17891,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 25552-2025</t>
+          <t>A 29244-2025</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -17890,10 +17905,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>45803</v>
+        <v>45824</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17906,7 +17921,7 @@
         </is>
       </c>
       <c r="I219" t="n">
-        <v>2</v>
+        <v>0.7</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -17949,7 +17964,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 38147-2025</t>
+          <t>A 29354-2025</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -17963,10 +17978,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>45882</v>
+        <v>45824</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17979,7 +17994,7 @@
         </is>
       </c>
       <c r="I220" t="n">
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -18022,24 +18037,24 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>S 3888-2023</t>
+          <t>A 32958-2025</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>samrådsanmälan</t>
+          <t>avverkningsanmälan</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Askåterföring</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>45230</v>
+        <v>45839</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18052,7 +18067,7 @@
         </is>
       </c>
       <c r="I221" t="n">
-        <v>13.9</v>
+        <v>5</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -18095,24 +18110,24 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>S 4691-2022</t>
+          <t>A 32459-2025</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>samrådsanmälan</t>
+          <t>avverkningsanmälan</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Askåterföring</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>44796</v>
+        <v>45838</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18125,7 +18140,7 @@
         </is>
       </c>
       <c r="I222" t="n">
-        <v>39</v>
+        <v>1.2</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -18168,24 +18183,24 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>S 734-2025</t>
+          <t>A 2981-2024</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>samrådsanmälan</t>
+          <t>avverkningsanmälan</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Askåterföring</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>45722</v>
+        <v>45315</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18197,8 +18212,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I223" t="n">
-        <v>27.4</v>
+        <v>6.4</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -18241,24 +18261,24 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>S 144-2026</t>
+          <t>A 37756-2024</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>samrådsanmälan</t>
+          <t>avverkningsanmälan</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Askåterföring</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>46042</v>
+        <v>45541</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18271,7 +18291,7 @@
         </is>
       </c>
       <c r="I224" t="n">
-        <v>18.3</v>
+        <v>3.2</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -18314,24 +18334,24 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>S 1874-2026</t>
+          <t>A 36355-2025</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>samrådsanmälan</t>
+          <t>avverkningsanmälan</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>46202</v>
+        <v>45868</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18343,13 +18363,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H225" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I225" t="n">
-        <v>7.8</v>
+        <v>3.6</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -18392,7 +18407,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>S 1875-2026</t>
+          <t>S 3888-2023</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -18402,14 +18417,14 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Askåterföring</t>
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>46202</v>
+        <v>45230</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18421,13 +18436,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H226" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I226" t="n">
-        <v>4.2</v>
+        <v>13.9</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -18470,153 +18480,528 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
+          <t>S 4691-2022</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>Askåterföring</t>
+        </is>
+      </c>
+      <c r="D227" s="1" t="n">
+        <v>44796</v>
+      </c>
+      <c r="E227" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>HÖRBY</t>
+        </is>
+      </c>
+      <c r="I227" t="n">
+        <v>39</v>
+      </c>
+      <c r="J227" t="n">
+        <v>0</v>
+      </c>
+      <c r="K227" t="n">
+        <v>0</v>
+      </c>
+      <c r="L227" t="n">
+        <v>0</v>
+      </c>
+      <c r="M227" t="n">
+        <v>0</v>
+      </c>
+      <c r="N227" t="n">
+        <v>0</v>
+      </c>
+      <c r="O227" t="n">
+        <v>0</v>
+      </c>
+      <c r="P227" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q227" t="n">
+        <v>0</v>
+      </c>
+      <c r="R227" t="n">
+        <v>0</v>
+      </c>
+      <c r="S227" t="n">
+        <v>0</v>
+      </c>
+      <c r="T227" t="n">
+        <v>0</v>
+      </c>
+      <c r="U227" t="n">
+        <v>0</v>
+      </c>
+      <c r="V227" s="2" t="inlineStr"/>
+    </row>
+    <row r="228" ht="15" customHeight="1">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>S 734-2025</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>Askåterföring</t>
+        </is>
+      </c>
+      <c r="D228" s="1" t="n">
+        <v>45722</v>
+      </c>
+      <c r="E228" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>HÖRBY</t>
+        </is>
+      </c>
+      <c r="I228" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="J228" t="n">
+        <v>0</v>
+      </c>
+      <c r="K228" t="n">
+        <v>0</v>
+      </c>
+      <c r="L228" t="n">
+        <v>0</v>
+      </c>
+      <c r="M228" t="n">
+        <v>0</v>
+      </c>
+      <c r="N228" t="n">
+        <v>0</v>
+      </c>
+      <c r="O228" t="n">
+        <v>0</v>
+      </c>
+      <c r="P228" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q228" t="n">
+        <v>0</v>
+      </c>
+      <c r="R228" t="n">
+        <v>0</v>
+      </c>
+      <c r="S228" t="n">
+        <v>0</v>
+      </c>
+      <c r="T228" t="n">
+        <v>0</v>
+      </c>
+      <c r="U228" t="n">
+        <v>0</v>
+      </c>
+      <c r="V228" s="2" t="inlineStr"/>
+    </row>
+    <row r="229" ht="15" customHeight="1">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>S 144-2026</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>Askåterföring</t>
+        </is>
+      </c>
+      <c r="D229" s="1" t="n">
+        <v>46042</v>
+      </c>
+      <c r="E229" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>HÖRBY</t>
+        </is>
+      </c>
+      <c r="I229" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="J229" t="n">
+        <v>0</v>
+      </c>
+      <c r="K229" t="n">
+        <v>0</v>
+      </c>
+      <c r="L229" t="n">
+        <v>0</v>
+      </c>
+      <c r="M229" t="n">
+        <v>0</v>
+      </c>
+      <c r="N229" t="n">
+        <v>0</v>
+      </c>
+      <c r="O229" t="n">
+        <v>0</v>
+      </c>
+      <c r="P229" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q229" t="n">
+        <v>0</v>
+      </c>
+      <c r="R229" t="n">
+        <v>0</v>
+      </c>
+      <c r="S229" t="n">
+        <v>0</v>
+      </c>
+      <c r="T229" t="n">
+        <v>0</v>
+      </c>
+      <c r="U229" t="n">
+        <v>0</v>
+      </c>
+      <c r="V229" s="2" t="inlineStr"/>
+    </row>
+    <row r="230" ht="15" customHeight="1">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>S 1874-2026</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Annan skogsbruksåtgärd</t>
+        </is>
+      </c>
+      <c r="D230" s="1" t="n">
+        <v>46202</v>
+      </c>
+      <c r="E230" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>HÖRBY</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I230" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="J230" t="n">
+        <v>0</v>
+      </c>
+      <c r="K230" t="n">
+        <v>0</v>
+      </c>
+      <c r="L230" t="n">
+        <v>0</v>
+      </c>
+      <c r="M230" t="n">
+        <v>0</v>
+      </c>
+      <c r="N230" t="n">
+        <v>0</v>
+      </c>
+      <c r="O230" t="n">
+        <v>0</v>
+      </c>
+      <c r="P230" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q230" t="n">
+        <v>0</v>
+      </c>
+      <c r="R230" t="n">
+        <v>0</v>
+      </c>
+      <c r="S230" t="n">
+        <v>0</v>
+      </c>
+      <c r="T230" t="n">
+        <v>0</v>
+      </c>
+      <c r="U230" t="n">
+        <v>0</v>
+      </c>
+      <c r="V230" s="2" t="inlineStr"/>
+    </row>
+    <row r="231" ht="15" customHeight="1">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>S 1875-2026</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>Annan skogsbruksåtgärd</t>
+        </is>
+      </c>
+      <c r="D231" s="1" t="n">
+        <v>46202</v>
+      </c>
+      <c r="E231" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>HÖRBY</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I231" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J231" t="n">
+        <v>0</v>
+      </c>
+      <c r="K231" t="n">
+        <v>0</v>
+      </c>
+      <c r="L231" t="n">
+        <v>0</v>
+      </c>
+      <c r="M231" t="n">
+        <v>0</v>
+      </c>
+      <c r="N231" t="n">
+        <v>0</v>
+      </c>
+      <c r="O231" t="n">
+        <v>0</v>
+      </c>
+      <c r="P231" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q231" t="n">
+        <v>0</v>
+      </c>
+      <c r="R231" t="n">
+        <v>0</v>
+      </c>
+      <c r="S231" t="n">
+        <v>0</v>
+      </c>
+      <c r="T231" t="n">
+        <v>0</v>
+      </c>
+      <c r="U231" t="n">
+        <v>0</v>
+      </c>
+      <c r="V231" s="2" t="inlineStr"/>
+    </row>
+    <row r="232" ht="15" customHeight="1">
+      <c r="A232" t="inlineStr">
+        <is>
           <t>S 1873-2026</t>
         </is>
       </c>
-      <c r="B227" t="inlineStr">
+      <c r="B232" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C227" t="inlineStr">
+      <c r="C232" t="inlineStr">
         <is>
           <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
-      <c r="D227" s="1" t="n">
+      <c r="D232" s="1" t="n">
         <v>46202</v>
       </c>
-      <c r="E227" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F227" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G227" t="inlineStr">
-        <is>
-          <t>HÖRBY</t>
-        </is>
-      </c>
-      <c r="H227" t="inlineStr">
+      <c r="E232" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>HÖRBY</t>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr">
         <is>
           <t>Sveaskog</t>
         </is>
       </c>
-      <c r="I227" t="n">
+      <c r="I232" t="n">
         <v>4.7</v>
       </c>
-      <c r="J227" t="n">
-        <v>0</v>
-      </c>
-      <c r="K227" t="n">
-        <v>0</v>
-      </c>
-      <c r="L227" t="n">
-        <v>0</v>
-      </c>
-      <c r="M227" t="n">
-        <v>0</v>
-      </c>
-      <c r="N227" t="n">
-        <v>0</v>
-      </c>
-      <c r="O227" t="n">
-        <v>0</v>
-      </c>
-      <c r="P227" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q227" t="n">
-        <v>0</v>
-      </c>
-      <c r="R227" t="n">
-        <v>0</v>
-      </c>
-      <c r="S227" t="n">
-        <v>0</v>
-      </c>
-      <c r="T227" t="n">
-        <v>0</v>
-      </c>
-      <c r="U227" t="n">
-        <v>0</v>
-      </c>
-      <c r="V227" s="2" t="inlineStr"/>
-    </row>
-    <row r="228">
-      <c r="A228" t="inlineStr">
+      <c r="J232" t="n">
+        <v>0</v>
+      </c>
+      <c r="K232" t="n">
+        <v>0</v>
+      </c>
+      <c r="L232" t="n">
+        <v>0</v>
+      </c>
+      <c r="M232" t="n">
+        <v>0</v>
+      </c>
+      <c r="N232" t="n">
+        <v>0</v>
+      </c>
+      <c r="O232" t="n">
+        <v>0</v>
+      </c>
+      <c r="P232" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q232" t="n">
+        <v>0</v>
+      </c>
+      <c r="R232" t="n">
+        <v>0</v>
+      </c>
+      <c r="S232" t="n">
+        <v>0</v>
+      </c>
+      <c r="T232" t="n">
+        <v>0</v>
+      </c>
+      <c r="U232" t="n">
+        <v>0</v>
+      </c>
+      <c r="V232" s="2" t="inlineStr"/>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
         <is>
           <t>S 220-2026</t>
         </is>
       </c>
-      <c r="B228" t="inlineStr">
+      <c r="B233" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C228" t="inlineStr">
+      <c r="C233" t="inlineStr">
         <is>
           <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
-      <c r="D228" s="1" t="n">
+      <c r="D233" s="1" t="n">
         <v>46051</v>
       </c>
-      <c r="E228" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F228" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G228" t="inlineStr">
-        <is>
-          <t>HÖRBY</t>
-        </is>
-      </c>
-      <c r="I228" t="n">
+      <c r="E233" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>HÖRBY</t>
+        </is>
+      </c>
+      <c r="I233" t="n">
         <v>1.7</v>
       </c>
-      <c r="J228" t="n">
-        <v>0</v>
-      </c>
-      <c r="K228" t="n">
-        <v>0</v>
-      </c>
-      <c r="L228" t="n">
-        <v>0</v>
-      </c>
-      <c r="M228" t="n">
-        <v>0</v>
-      </c>
-      <c r="N228" t="n">
-        <v>0</v>
-      </c>
-      <c r="O228" t="n">
-        <v>0</v>
-      </c>
-      <c r="P228" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q228" t="n">
-        <v>0</v>
-      </c>
-      <c r="R228" t="n">
-        <v>0</v>
-      </c>
-      <c r="S228" t="n">
-        <v>0</v>
-      </c>
-      <c r="T228" t="n">
-        <v>0</v>
-      </c>
-      <c r="U228" t="n">
-        <v>0</v>
-      </c>
-      <c r="V228" s="2" t="inlineStr"/>
+      <c r="J233" t="n">
+        <v>0</v>
+      </c>
+      <c r="K233" t="n">
+        <v>0</v>
+      </c>
+      <c r="L233" t="n">
+        <v>0</v>
+      </c>
+      <c r="M233" t="n">
+        <v>0</v>
+      </c>
+      <c r="N233" t="n">
+        <v>0</v>
+      </c>
+      <c r="O233" t="n">
+        <v>0</v>
+      </c>
+      <c r="P233" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q233" t="n">
+        <v>0</v>
+      </c>
+      <c r="R233" t="n">
+        <v>0</v>
+      </c>
+      <c r="S233" t="n">
+        <v>0</v>
+      </c>
+      <c r="T233" t="n">
+        <v>0</v>
+      </c>
+      <c r="U233" t="n">
+        <v>0</v>
+      </c>
+      <c r="V233" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt HÖRBY.xlsx
+++ b/Översikt HÖRBY.xlsx
@@ -601,7 +601,7 @@
         <v>44964</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
         <v>44967</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         <v>44727</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -949,7 +949,7 @@
         <v>45786</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1061,7 +1061,7 @@
         <v>46160</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
         <v>45238</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 16520-2026</t>
+          <t>A 31351-2022</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1285,14 +1285,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46112</v>
+        <v>44774</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1305,19 +1305,19 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>2.3</v>
+        <v>13.2</v>
       </c>
       <c r="J8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -1332,18 +1332,349 @@
         <v>3</v>
       </c>
       <c r="R8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
       </c>
       <c r="T8" t="n">
+        <v>5</v>
+      </c>
+      <c r="U8" t="n">
+        <v>3</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>Duvhök
+Grönsångare
+Sädesärla
+Fjällvråk
+Kungsfågel</t>
+        </is>
+      </c>
+      <c r="W8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 31351-2022 artfynd.xlsx", "A 31351-2022")</f>
+        <v/>
+      </c>
+      <c r="X8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 31351-2022 karta.png", "A 31351-2022")</f>
+        <v/>
+      </c>
+      <c r="Y8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 31351-2022 georefererad karta.tif", "A 31351-2022")</f>
+        <v/>
+      </c>
+      <c r="AA8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 31351-2022 FSC-klagomål.docx", "A 31351-2022")</f>
+        <v/>
+      </c>
+      <c r="AB8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 31351-2022 FSC-klagomål mail.docx", "A 31351-2022")</f>
+        <v/>
+      </c>
+      <c r="AC8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 31351-2022 tillsynsbegäran.docx", "A 31351-2022")</f>
+        <v/>
+      </c>
+      <c r="AD8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 31351-2022 tillsynsbegäran mail.docx", "A 31351-2022")</f>
+        <v/>
+      </c>
+      <c r="AE8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/fåglar/A 31351-2022 prioriterade fågelarter.docx", "A 31351-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 20194-2024</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>45434</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>HÖRBY</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>2</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>3</v>
+      </c>
+      <c r="R9" t="n">
+        <v>3</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="n">
+        <v>5</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Naverlönn
+Ask
+Skogsalm
+Scharlakansskål
+Stor häxört</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 20194-2024 artfynd.xlsx", "A 20194-2024")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 20194-2024 karta.png", "A 20194-2024")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 20194-2024 georefererad karta.tif", "A 20194-2024")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 20194-2024 FSC-klagomål.docx", "A 20194-2024")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 20194-2024 FSC-klagomål mail.docx", "A 20194-2024")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 20194-2024 tillsynsbegäran.docx", "A 20194-2024")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 20194-2024 tillsynsbegäran mail.docx", "A 20194-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 39855-2022</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>44819</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>HÖRBY</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J10" t="n">
+        <v>4</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="n">
+        <v>5</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Skogsknipprot
+Blåsippa
+Fläcknycklar
+Grönvit nattviol</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 39855-2022 artfynd.xlsx", "A 39855-2022")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 39855-2022 karta.png", "A 39855-2022")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 39855-2022 georefererad karta.tif", "A 39855-2022")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 39855-2022 FSC-klagomål.docx", "A 39855-2022")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 39855-2022 FSC-klagomål mail.docx", "A 39855-2022")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 39855-2022 tillsynsbegäran.docx", "A 39855-2022")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 39855-2022 tillsynsbegäran mail.docx", "A 39855-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 16520-2026</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>46112</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>HÖRBY</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="J11" t="n">
+        <v>2</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>2</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>3</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="n">
         <v>6</v>
       </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Slåttergubbe
 Sydlig sotticka
@@ -1352,374 +1683,43 @@
 Större brunfladdermus</t>
         </is>
       </c>
-      <c r="W8">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 16520-2026 artfynd.xlsx", "A 16520-2026")</f>
         <v/>
       </c>
-      <c r="X8">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 16520-2026 karta.png", "A 16520-2026")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 16520-2026 georefererad karta.tif", "A 16520-2026")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 16520-2026 FSC-klagomål.docx", "A 16520-2026")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 16520-2026 FSC-klagomål mail.docx", "A 16520-2026")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 16520-2026 tillsynsbegäran.docx", "A 16520-2026")</f>
         <v/>
       </c>
-      <c r="AD8">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 16520-2026 tillsynsbegäran mail.docx", "A 16520-2026")</f>
         <v/>
       </c>
-      <c r="AE8">
+      <c r="AE11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/fåglar/A 16520-2026 prioriterade fågelarter.docx", "A 16520-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A 39855-2022</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>44819</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>HÖRBY</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J9" t="n">
-        <v>4</v>
-      </c>
-      <c r="K9" t="n">
-        <v>1</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>1</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1</v>
-      </c>
-      <c r="S9" t="n">
-        <v>5</v>
-      </c>
-      <c r="T9" t="n">
-        <v>5</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Skogsknipprot
-Blåsippa
-Fläcknycklar
-Grönvit nattviol</t>
-        </is>
-      </c>
-      <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 39855-2022 artfynd.xlsx", "A 39855-2022")</f>
-        <v/>
-      </c>
-      <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 39855-2022 karta.png", "A 39855-2022")</f>
-        <v/>
-      </c>
-      <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 39855-2022 georefererad karta.tif", "A 39855-2022")</f>
-        <v/>
-      </c>
-      <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 39855-2022 FSC-klagomål.docx", "A 39855-2022")</f>
-        <v/>
-      </c>
-      <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 39855-2022 FSC-klagomål mail.docx", "A 39855-2022")</f>
-        <v/>
-      </c>
-      <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 39855-2022 tillsynsbegäran.docx", "A 39855-2022")</f>
-        <v/>
-      </c>
-      <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 39855-2022 tillsynsbegäran mail.docx", "A 39855-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 31351-2022</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>44774</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>HÖRBY</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="J10" t="n">
-        <v>5</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>3</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>3</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>5</v>
-      </c>
-      <c r="T10" t="n">
-        <v>5</v>
-      </c>
-      <c r="U10" t="n">
-        <v>3</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Duvhök
-Grönsångare
-Sädesärla
-Fjällvråk
-Kungsfågel</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 31351-2022 artfynd.xlsx", "A 31351-2022")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 31351-2022 karta.png", "A 31351-2022")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 31351-2022 georefererad karta.tif", "A 31351-2022")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 31351-2022 FSC-klagomål.docx", "A 31351-2022")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 31351-2022 FSC-klagomål mail.docx", "A 31351-2022")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 31351-2022 tillsynsbegäran.docx", "A 31351-2022")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 31351-2022 tillsynsbegäran mail.docx", "A 31351-2022")</f>
-        <v/>
-      </c>
-      <c r="AE10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/fåglar/A 31351-2022 prioriterade fågelarter.docx", "A 31351-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 20194-2024</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>45434</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>HÖRBY</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>2</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>2</v>
-      </c>
-      <c r="O11" t="n">
-        <v>1</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>3</v>
-      </c>
-      <c r="R11" t="n">
-        <v>3</v>
-      </c>
-      <c r="S11" t="n">
-        <v>5</v>
-      </c>
-      <c r="T11" t="n">
-        <v>5</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Naverlönn
-Ask
-Skogsalm
-Scharlakansskål
-Stor häxört</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 20194-2024 artfynd.xlsx", "A 20194-2024")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 20194-2024 karta.png", "A 20194-2024")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 20194-2024 georefererad karta.tif", "A 20194-2024")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 20194-2024 FSC-klagomål.docx", "A 20194-2024")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 20194-2024 FSC-klagomål mail.docx", "A 20194-2024")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 20194-2024 tillsynsbegäran.docx", "A 20194-2024")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 20194-2024 tillsynsbegäran mail.docx", "A 20194-2024")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 21774-2026</t>
+          <t>A 5619-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1733,10 +1733,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46150</v>
+        <v>45334</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1749,45 +1749,261 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>1.2</v>
+        <v>4.6</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>2</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
         <v>3</v>
       </c>
-      <c r="M12" t="n">
-        <v>1</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>4</v>
-      </c>
       <c r="R12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S12" t="n">
         <v>4</v>
       </c>
       <c r="T12" t="n">
+        <v>7</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Skogsalm
+Gullpudra
+Trubbfjädermossa</t>
+        </is>
+      </c>
+      <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 5619-2024 artfynd.xlsx", "A 5619-2024")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 5619-2024 karta.png", "A 5619-2024")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 5619-2024 georefererad karta.tif", "A 5619-2024")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 5619-2024 FSC-klagomål.docx", "A 5619-2024")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 5619-2024 FSC-klagomål mail.docx", "A 5619-2024")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 5619-2024 tillsynsbegäran.docx", "A 5619-2024")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 5619-2024 tillsynsbegäran mail.docx", "A 5619-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A 38084-2024</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>45545</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>HÖRBY</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>4</v>
+      </c>
+      <c r="T13" t="n">
+        <v>4</v>
+      </c>
+      <c r="U13" t="n">
+        <v>4</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>Myskmadra
+Skogsbräsma
+Tandrot
+Grönsiska</t>
+        </is>
+      </c>
+      <c r="W13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 38084-2024 artfynd.xlsx", "A 38084-2024")</f>
+        <v/>
+      </c>
+      <c r="X13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 38084-2024 karta.png", "A 38084-2024")</f>
+        <v/>
+      </c>
+      <c r="Y13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 38084-2024 georefererad karta.tif", "A 38084-2024")</f>
+        <v/>
+      </c>
+      <c r="AA13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 38084-2024 FSC-klagomål.docx", "A 38084-2024")</f>
+        <v/>
+      </c>
+      <c r="AB13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 38084-2024 FSC-klagomål mail.docx", "A 38084-2024")</f>
+        <v/>
+      </c>
+      <c r="AC13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 38084-2024 tillsynsbegäran.docx", "A 38084-2024")</f>
+        <v/>
+      </c>
+      <c r="AD13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 38084-2024 tillsynsbegäran mail.docx", "A 38084-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A 21774-2026</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>46150</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>HÖRBY</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>3</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>4</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1</v>
+      </c>
+      <c r="S14" t="n">
+        <v>4</v>
+      </c>
+      <c r="T14" t="n">
         <v>6</v>
       </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>Violettkantad guldvinge
 Granspira
@@ -1795,248 +2011,32 @@
 Svinrot</t>
         </is>
       </c>
-      <c r="W12">
+      <c r="W14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 21774-2026 artfynd.xlsx", "A 21774-2026")</f>
         <v/>
       </c>
-      <c r="X12">
+      <c r="X14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 21774-2026 karta.png", "A 21774-2026")</f>
         <v/>
       </c>
-      <c r="Y12">
+      <c r="Y14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 21774-2026 georefererad karta.tif", "A 21774-2026")</f>
         <v/>
       </c>
-      <c r="AA12">
+      <c r="AA14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 21774-2026 FSC-klagomål.docx", "A 21774-2026")</f>
         <v/>
       </c>
-      <c r="AB12">
+      <c r="AB14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 21774-2026 FSC-klagomål mail.docx", "A 21774-2026")</f>
         <v/>
       </c>
-      <c r="AC12">
+      <c r="AC14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 21774-2026 tillsynsbegäran.docx", "A 21774-2026")</f>
         <v/>
       </c>
-      <c r="AD12">
+      <c r="AD14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 21774-2026 tillsynsbegäran mail.docx", "A 21774-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A 38084-2024</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>45545</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>HÖRBY</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J13" t="n">
-        <v>1</v>
-      </c>
-      <c r="K13" t="n">
-        <v>2</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>4</v>
-      </c>
-      <c r="T13" t="n">
-        <v>4</v>
-      </c>
-      <c r="U13" t="n">
-        <v>4</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Myskmadra
-Skogsbräsma
-Tandrot
-Grönsiska</t>
-        </is>
-      </c>
-      <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 38084-2024 artfynd.xlsx", "A 38084-2024")</f>
-        <v/>
-      </c>
-      <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 38084-2024 karta.png", "A 38084-2024")</f>
-        <v/>
-      </c>
-      <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 38084-2024 georefererad karta.tif", "A 38084-2024")</f>
-        <v/>
-      </c>
-      <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 38084-2024 FSC-klagomål.docx", "A 38084-2024")</f>
-        <v/>
-      </c>
-      <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 38084-2024 FSC-klagomål mail.docx", "A 38084-2024")</f>
-        <v/>
-      </c>
-      <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 38084-2024 tillsynsbegäran.docx", "A 38084-2024")</f>
-        <v/>
-      </c>
-      <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 38084-2024 tillsynsbegäran mail.docx", "A 38084-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>A 5619-2024</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>45334</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>HÖRBY</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>1</v>
-      </c>
-      <c r="L14" t="n">
-        <v>1</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>2</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>3</v>
-      </c>
-      <c r="R14" t="n">
-        <v>2</v>
-      </c>
-      <c r="S14" t="n">
-        <v>4</v>
-      </c>
-      <c r="T14" t="n">
-        <v>7</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Skogsalm
-Gullpudra
-Trubbfjädermossa</t>
-        </is>
-      </c>
-      <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 5619-2024 artfynd.xlsx", "A 5619-2024")</f>
-        <v/>
-      </c>
-      <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 5619-2024 karta.png", "A 5619-2024")</f>
-        <v/>
-      </c>
-      <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 5619-2024 georefererad karta.tif", "A 5619-2024")</f>
-        <v/>
-      </c>
-      <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 5619-2024 FSC-klagomål.docx", "A 5619-2024")</f>
-        <v/>
-      </c>
-      <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 5619-2024 FSC-klagomål mail.docx", "A 5619-2024")</f>
-        <v/>
-      </c>
-      <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 5619-2024 tillsynsbegäran.docx", "A 5619-2024")</f>
-        <v/>
-      </c>
-      <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 5619-2024 tillsynsbegäran mail.docx", "A 5619-2024")</f>
         <v/>
       </c>
     </row>
@@ -2060,7 +2060,7 @@
         <v>45434</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
         <v>45815</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2274,7 +2274,7 @@
         <v>45799</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2381,7 +2381,7 @@
         <v>44725</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2488,7 +2488,7 @@
         <v>45677</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 42724-2023</t>
+          <t>A 44135-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2592,10 +2592,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45176</v>
+        <v>45572</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2608,22 +2608,22 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>2.8</v>
+        <v>0.6</v>
       </c>
       <c r="J20" t="n">
+        <v>2</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
         <v>1</v>
       </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
       <c r="M20" t="n">
         <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2635,266 +2635,266 @@
         <v>1</v>
       </c>
       <c r="R20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>2</v>
       </c>
       <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>Ladusvala
+Vanlig padda</t>
+        </is>
+      </c>
+      <c r="W20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 44135-2024 artfynd.xlsx", "A 44135-2024")</f>
+        <v/>
+      </c>
+      <c r="X20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 44135-2024 karta.png", "A 44135-2024")</f>
+        <v/>
+      </c>
+      <c r="Y20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 44135-2024 georefererad karta.tif", "A 44135-2024")</f>
+        <v/>
+      </c>
+      <c r="AA20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 44135-2024 FSC-klagomål.docx", "A 44135-2024")</f>
+        <v/>
+      </c>
+      <c r="AB20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 44135-2024 FSC-klagomål mail.docx", "A 44135-2024")</f>
+        <v/>
+      </c>
+      <c r="AC20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 44135-2024 tillsynsbegäran.docx", "A 44135-2024")</f>
+        <v/>
+      </c>
+      <c r="AD20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 44135-2024 tillsynsbegäran mail.docx", "A 44135-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>A 824-2026</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="n">
+        <v>46030</v>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>HÖRBY</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>2</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2</v>
+      </c>
+      <c r="T21" t="n">
+        <v>3</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>Hedblomster
+Skogslysing</t>
+        </is>
+      </c>
+      <c r="W21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 824-2026 artfynd.xlsx", "A 824-2026")</f>
+        <v/>
+      </c>
+      <c r="X21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 824-2026 karta.png", "A 824-2026")</f>
+        <v/>
+      </c>
+      <c r="Y21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 824-2026 georefererad karta.tif", "A 824-2026")</f>
+        <v/>
+      </c>
+      <c r="AA21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 824-2026 FSC-klagomål.docx", "A 824-2026")</f>
+        <v/>
+      </c>
+      <c r="AB21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 824-2026 FSC-klagomål mail.docx", "A 824-2026")</f>
+        <v/>
+      </c>
+      <c r="AC21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 824-2026 tillsynsbegäran.docx", "A 824-2026")</f>
+        <v/>
+      </c>
+      <c r="AD21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 824-2026 tillsynsbegäran mail.docx", "A 824-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>A 42724-2023</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="n">
+        <v>45176</v>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>HÖRBY</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>1</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2</v>
+      </c>
+      <c r="T22" t="n">
         <v>4</v>
       </c>
-      <c r="U20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>Ask
 Grönvit nattviol</t>
         </is>
       </c>
-      <c r="W20">
+      <c r="W22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 42724-2023 artfynd.xlsx", "A 42724-2023")</f>
         <v/>
       </c>
-      <c r="X20">
+      <c r="X22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 42724-2023 karta.png", "A 42724-2023")</f>
         <v/>
       </c>
-      <c r="Y20">
+      <c r="Y22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 42724-2023 georefererad karta.tif", "A 42724-2023")</f>
         <v/>
       </c>
-      <c r="AA20">
+      <c r="AA22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 42724-2023 FSC-klagomål.docx", "A 42724-2023")</f>
         <v/>
       </c>
-      <c r="AB20">
+      <c r="AB22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 42724-2023 FSC-klagomål mail.docx", "A 42724-2023")</f>
         <v/>
       </c>
-      <c r="AC20">
+      <c r="AC22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 42724-2023 tillsynsbegäran.docx", "A 42724-2023")</f>
         <v/>
       </c>
-      <c r="AD20">
+      <c r="AD22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 42724-2023 tillsynsbegäran mail.docx", "A 42724-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>A 824-2026</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D21" s="1" t="n">
-        <v>46030</v>
-      </c>
-      <c r="E21" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>HÖRBY</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="J21" t="n">
-        <v>1</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>1</v>
-      </c>
-      <c r="M21" t="n">
-        <v>1</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>2</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1</v>
-      </c>
-      <c r="S21" t="n">
-        <v>2</v>
-      </c>
-      <c r="T21" t="n">
-        <v>3</v>
-      </c>
-      <c r="U21" t="n">
-        <v>0</v>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>Hedblomster
-Skogslysing</t>
-        </is>
-      </c>
-      <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 824-2026 artfynd.xlsx", "A 824-2026")</f>
-        <v/>
-      </c>
-      <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 824-2026 karta.png", "A 824-2026")</f>
-        <v/>
-      </c>
-      <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 824-2026 georefererad karta.tif", "A 824-2026")</f>
-        <v/>
-      </c>
-      <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 824-2026 FSC-klagomål.docx", "A 824-2026")</f>
-        <v/>
-      </c>
-      <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 824-2026 FSC-klagomål mail.docx", "A 824-2026")</f>
-        <v/>
-      </c>
-      <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 824-2026 tillsynsbegäran.docx", "A 824-2026")</f>
-        <v/>
-      </c>
-      <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 824-2026 tillsynsbegäran mail.docx", "A 824-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>A 44135-2024</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D22" s="1" t="n">
-        <v>45572</v>
-      </c>
-      <c r="E22" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>HÖRBY</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="J22" t="n">
-        <v>2</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>1</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>1</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
-        <v>2</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2</v>
-      </c>
-      <c r="U22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>Ladusvala
-Vanlig padda</t>
-        </is>
-      </c>
-      <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 44135-2024 artfynd.xlsx", "A 44135-2024")</f>
-        <v/>
-      </c>
-      <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 44135-2024 karta.png", "A 44135-2024")</f>
-        <v/>
-      </c>
-      <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 44135-2024 georefererad karta.tif", "A 44135-2024")</f>
-        <v/>
-      </c>
-      <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 44135-2024 FSC-klagomål.docx", "A 44135-2024")</f>
-        <v/>
-      </c>
-      <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 44135-2024 FSC-klagomål mail.docx", "A 44135-2024")</f>
-        <v/>
-      </c>
-      <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 44135-2024 tillsynsbegäran.docx", "A 44135-2024")</f>
-        <v/>
-      </c>
-      <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 44135-2024 tillsynsbegäran mail.docx", "A 44135-2024")</f>
         <v/>
       </c>
     </row>
@@ -2918,7 +2918,7 @@
         <v>45317</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3007,7 +3007,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 31115-2024</t>
+          <t>A 113-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45502</v>
+        <v>44928</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3037,7 +3037,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.8</v>
+        <v>5.1</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -3046,10 +3046,10 @@
         <v>0</v>
       </c>
       <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
         <v>1</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
@@ -3064,7 +3064,7 @@
         <v>1</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3077,42 +3077,42 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Gullpudra</t>
+          <t>Slåttergubbe</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 31115-2024 artfynd.xlsx", "A 31115-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 113-2023 artfynd.xlsx", "A 113-2023")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 31115-2024 karta.png", "A 31115-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 113-2023 karta.png", "A 113-2023")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 31115-2024 georefererad karta.tif", "A 31115-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 113-2023 georefererad karta.tif", "A 113-2023")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 31115-2024 FSC-klagomål.docx", "A 31115-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 113-2023 FSC-klagomål.docx", "A 113-2023")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 31115-2024 FSC-klagomål mail.docx", "A 31115-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 113-2023 FSC-klagomål mail.docx", "A 113-2023")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 31115-2024 tillsynsbegäran.docx", "A 31115-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 113-2023 tillsynsbegäran.docx", "A 113-2023")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 31115-2024 tillsynsbegäran mail.docx", "A 31115-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 113-2023 tillsynsbegäran mail.docx", "A 113-2023")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 47612-2023</t>
+          <t>A 25833-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3126,10 +3126,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45203</v>
+        <v>45463</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3142,7 +3142,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>2.4</v>
+        <v>1.4</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -3154,10 +3154,10 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3175,49 +3175,49 @@
         <v>1</v>
       </c>
       <c r="T25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U25" t="n">
         <v>0</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Slåttergubbe</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 47612-2023 artfynd.xlsx", "A 47612-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 25833-2024 artfynd.xlsx", "A 25833-2024")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 47612-2023 karta.png", "A 47612-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 25833-2024 karta.png", "A 25833-2024")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 47612-2023 georefererad karta.tif", "A 47612-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 25833-2024 georefererad karta.tif", "A 25833-2024")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 47612-2023 FSC-klagomål.docx", "A 47612-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 25833-2024 FSC-klagomål.docx", "A 25833-2024")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 47612-2023 FSC-klagomål mail.docx", "A 47612-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 25833-2024 FSC-klagomål mail.docx", "A 25833-2024")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 47612-2023 tillsynsbegäran.docx", "A 47612-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 25833-2024 tillsynsbegäran.docx", "A 25833-2024")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 47612-2023 tillsynsbegäran mail.docx", "A 47612-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 25833-2024 tillsynsbegäran mail.docx", "A 25833-2024")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 24823-2026</t>
+          <t>A 25479-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3227,14 +3227,14 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46174</v>
+        <v>45802</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3246,19 +3246,14 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I26" t="n">
-        <v>5.1</v>
+        <v>0.7</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -3288,46 +3283,46 @@
         <v>1</v>
       </c>
       <c r="U26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Tandrot</t>
+          <t>Lundvårlök</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 24823-2026 artfynd.xlsx", "A 24823-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 25479-2025 artfynd.xlsx", "A 25479-2025")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 24823-2026 karta.png", "A 24823-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 25479-2025 karta.png", "A 25479-2025")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 24823-2026 georefererad karta.tif", "A 24823-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 25479-2025 georefererad karta.tif", "A 25479-2025")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 24823-2026 FSC-klagomål.docx", "A 24823-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 25479-2025 FSC-klagomål.docx", "A 25479-2025")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 24823-2026 FSC-klagomål mail.docx", "A 24823-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 25479-2025 FSC-klagomål mail.docx", "A 25479-2025")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 24823-2026 tillsynsbegäran.docx", "A 24823-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 25479-2025 tillsynsbegäran.docx", "A 25479-2025")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 24823-2026 tillsynsbegäran mail.docx", "A 24823-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 25479-2025 tillsynsbegäran mail.docx", "A 25479-2025")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 40376-2023</t>
+          <t>A 47612-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3341,10 +3336,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45169</v>
+        <v>45203</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3357,22 +3352,22 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
         <v>1</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" t="n">
-        <v>1</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" t="n">
-        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3384,7 +3379,7 @@
         <v>1</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
@@ -3397,46 +3392,42 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 40376-2023 artfynd.xlsx", "A 40376-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 47612-2023 artfynd.xlsx", "A 47612-2023")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 40376-2023 karta.png", "A 40376-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 47612-2023 karta.png", "A 47612-2023")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 40376-2023 georefererad karta.tif", "A 40376-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 47612-2023 georefererad karta.tif", "A 47612-2023")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 40376-2023 FSC-klagomål.docx", "A 40376-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 47612-2023 FSC-klagomål.docx", "A 47612-2023")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 40376-2023 FSC-klagomål mail.docx", "A 40376-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 47612-2023 FSC-klagomål mail.docx", "A 47612-2023")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 40376-2023 tillsynsbegäran.docx", "A 40376-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 47612-2023 tillsynsbegäran.docx", "A 47612-2023")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 40376-2023 tillsynsbegäran mail.docx", "A 40376-2023")</f>
-        <v/>
-      </c>
-      <c r="AE27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/fåglar/A 40376-2023 prioriterade fågelarter.docx", "A 40376-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 47612-2023 tillsynsbegäran mail.docx", "A 47612-2023")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 16519-2026</t>
+          <t>A 40376-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3450,10 +3441,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46112</v>
+        <v>45169</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3466,22 +3457,22 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.8</v>
+        <v>2.7</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M28" t="n">
         <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3493,7 +3484,7 @@
         <v>1</v>
       </c>
       <c r="R28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
@@ -3506,42 +3497,46 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 16519-2026 artfynd.xlsx", "A 16519-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 40376-2023 artfynd.xlsx", "A 40376-2023")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 16519-2026 karta.png", "A 16519-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 40376-2023 karta.png", "A 40376-2023")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 16519-2026 georefererad karta.tif", "A 16519-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 40376-2023 georefererad karta.tif", "A 40376-2023")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 16519-2026 FSC-klagomål.docx", "A 16519-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 40376-2023 FSC-klagomål.docx", "A 40376-2023")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 16519-2026 FSC-klagomål mail.docx", "A 16519-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 40376-2023 FSC-klagomål mail.docx", "A 40376-2023")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 16519-2026 tillsynsbegäran.docx", "A 16519-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 40376-2023 tillsynsbegäran.docx", "A 40376-2023")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 16519-2026 tillsynsbegäran mail.docx", "A 16519-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 40376-2023 tillsynsbegäran mail.docx", "A 40376-2023")</f>
+        <v/>
+      </c>
+      <c r="AE28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/fåglar/A 40376-2023 prioriterade fågelarter.docx", "A 40376-2023")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 113-2023</t>
+          <t>A 31115-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3555,10 +3550,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44928</v>
+        <v>45502</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3571,7 +3566,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>5.1</v>
+        <v>0.8</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3580,10 +3575,10 @@
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
         <v>0</v>
@@ -3598,7 +3593,7 @@
         <v>1</v>
       </c>
       <c r="R29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
@@ -3611,42 +3606,42 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Slåttergubbe</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 113-2023 artfynd.xlsx", "A 113-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 31115-2024 artfynd.xlsx", "A 31115-2024")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 113-2023 karta.png", "A 113-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 31115-2024 karta.png", "A 31115-2024")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 113-2023 georefererad karta.tif", "A 113-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 31115-2024 georefererad karta.tif", "A 31115-2024")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 113-2023 FSC-klagomål.docx", "A 113-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 31115-2024 FSC-klagomål.docx", "A 31115-2024")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 113-2023 FSC-klagomål mail.docx", "A 113-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 31115-2024 FSC-klagomål mail.docx", "A 31115-2024")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 113-2023 tillsynsbegäran.docx", "A 113-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 31115-2024 tillsynsbegäran.docx", "A 31115-2024")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 113-2023 tillsynsbegäran mail.docx", "A 113-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 31115-2024 tillsynsbegäran mail.docx", "A 31115-2024")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 25833-2024</t>
+          <t>A 29129-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3660,10 +3655,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45463</v>
+        <v>46202</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3675,8 +3670,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I30" t="n">
-        <v>1.4</v>
+        <v>10.5</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3685,10 +3685,10 @@
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
         <v>0</v>
@@ -3703,55 +3703,55 @@
         <v>1</v>
       </c>
       <c r="R30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
         <v>1</v>
       </c>
       <c r="T30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U30" t="n">
         <v>0</v>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>Slåttergubbe</t>
+          <t>Ekticka</t>
         </is>
       </c>
       <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 25833-2024 artfynd.xlsx", "A 25833-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 29129-2026 artfynd.xlsx", "A 29129-2026")</f>
         <v/>
       </c>
       <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 25833-2024 karta.png", "A 25833-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 29129-2026 karta.png", "A 29129-2026")</f>
         <v/>
       </c>
       <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 25833-2024 georefererad karta.tif", "A 25833-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 29129-2026 georefererad karta.tif", "A 29129-2026")</f>
         <v/>
       </c>
       <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 25833-2024 FSC-klagomål.docx", "A 25833-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 29129-2026 FSC-klagomål.docx", "A 29129-2026")</f>
         <v/>
       </c>
       <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 25833-2024 FSC-klagomål mail.docx", "A 25833-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 29129-2026 FSC-klagomål mail.docx", "A 29129-2026")</f>
         <v/>
       </c>
       <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 25833-2024 tillsynsbegäran.docx", "A 25833-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 29129-2026 tillsynsbegäran.docx", "A 29129-2026")</f>
         <v/>
       </c>
       <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 25833-2024 tillsynsbegäran mail.docx", "A 25833-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 29129-2026 tillsynsbegäran mail.docx", "A 29129-2026")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 31284-2026</t>
+          <t>A 36362-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3765,10 +3765,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46218</v>
+        <v>45868</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3781,13 +3781,13 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>6.8</v>
+        <v>3.7</v>
       </c>
       <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="n">
         <v>1</v>
-      </c>
-      <c r="K31" t="n">
-        <v>0</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
@@ -3817,46 +3817,46 @@
         <v>1</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="W31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 31284-2026 artfynd.xlsx", "A 31284-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 36362-2025 artfynd.xlsx", "A 36362-2025")</f>
         <v/>
       </c>
       <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 31284-2026 karta.png", "A 31284-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 36362-2025 karta.png", "A 36362-2025")</f>
         <v/>
       </c>
       <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 31284-2026 georefererad karta.tif", "A 31284-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 36362-2025 georefererad karta.tif", "A 36362-2025")</f>
         <v/>
       </c>
       <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 31284-2026 FSC-klagomål.docx", "A 31284-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 36362-2025 FSC-klagomål.docx", "A 36362-2025")</f>
         <v/>
       </c>
       <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 31284-2026 FSC-klagomål mail.docx", "A 31284-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 36362-2025 FSC-klagomål mail.docx", "A 36362-2025")</f>
         <v/>
       </c>
       <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 31284-2026 tillsynsbegäran.docx", "A 31284-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 36362-2025 tillsynsbegäran.docx", "A 36362-2025")</f>
         <v/>
       </c>
       <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 31284-2026 tillsynsbegäran mail.docx", "A 31284-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 36362-2025 tillsynsbegäran mail.docx", "A 36362-2025")</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 30165-2026</t>
+          <t>A 21713-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3870,10 +3870,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46206</v>
+        <v>45783</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3886,10 +3886,10 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
@@ -3901,7 +3901,7 @@
         <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -3910,10 +3910,10 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
         <v>1</v>
@@ -3926,42 +3926,42 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="W32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 30165-2026 artfynd.xlsx", "A 30165-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 21713-2025 artfynd.xlsx", "A 21713-2025")</f>
         <v/>
       </c>
       <c r="X32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 30165-2026 karta.png", "A 30165-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 21713-2025 karta.png", "A 21713-2025")</f>
         <v/>
       </c>
       <c r="Y32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 30165-2026 georefererad karta.tif", "A 30165-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 21713-2025 georefererad karta.tif", "A 21713-2025")</f>
         <v/>
       </c>
       <c r="AA32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 30165-2026 FSC-klagomål.docx", "A 30165-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 21713-2025 FSC-klagomål.docx", "A 21713-2025")</f>
         <v/>
       </c>
       <c r="AB32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 30165-2026 FSC-klagomål mail.docx", "A 30165-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 21713-2025 FSC-klagomål mail.docx", "A 21713-2025")</f>
         <v/>
       </c>
       <c r="AC32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 30165-2026 tillsynsbegäran.docx", "A 30165-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 21713-2025 tillsynsbegäran.docx", "A 21713-2025")</f>
         <v/>
       </c>
       <c r="AD32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 30165-2026 tillsynsbegäran mail.docx", "A 30165-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 21713-2025 tillsynsbegäran mail.docx", "A 21713-2025")</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 29129-2026</t>
+          <t>A 24823-2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>46202</v>
+        <v>46174</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3996,7 +3996,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>10.5</v>
+        <v>5.1</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -4005,7 +4005,7 @@
         <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
         <v>0</v>
@@ -4020,7 +4020,7 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
@@ -4032,46 +4032,46 @@
         <v>1</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>Ekticka</t>
+          <t>Tandrot</t>
         </is>
       </c>
       <c r="W33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 29129-2026 artfynd.xlsx", "A 29129-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 24823-2026 artfynd.xlsx", "A 24823-2026")</f>
         <v/>
       </c>
       <c r="X33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 29129-2026 karta.png", "A 29129-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 24823-2026 karta.png", "A 24823-2026")</f>
         <v/>
       </c>
       <c r="Y33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 29129-2026 georefererad karta.tif", "A 29129-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 24823-2026 georefererad karta.tif", "A 24823-2026")</f>
         <v/>
       </c>
       <c r="AA33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 29129-2026 FSC-klagomål.docx", "A 29129-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 24823-2026 FSC-klagomål.docx", "A 24823-2026")</f>
         <v/>
       </c>
       <c r="AB33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 29129-2026 FSC-klagomål mail.docx", "A 29129-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 24823-2026 FSC-klagomål mail.docx", "A 24823-2026")</f>
         <v/>
       </c>
       <c r="AC33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 29129-2026 tillsynsbegäran.docx", "A 29129-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 24823-2026 tillsynsbegäran.docx", "A 24823-2026")</f>
         <v/>
       </c>
       <c r="AD33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 29129-2026 tillsynsbegäran mail.docx", "A 29129-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 24823-2026 tillsynsbegäran mail.docx", "A 24823-2026")</f>
         <v/>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 21713-2025</t>
+          <t>A 16519-2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4085,10 +4085,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45783</v>
+        <v>46112</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4104,20 +4104,20 @@
         <v>0.8</v>
       </c>
       <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="n">
         <v>1</v>
       </c>
-      <c r="K34" t="n">
-        <v>0</v>
-      </c>
-      <c r="L34" t="n">
-        <v>0</v>
-      </c>
-      <c r="M34" t="n">
-        <v>0</v>
-      </c>
-      <c r="N34" t="n">
-        <v>0</v>
-      </c>
       <c r="O34" t="n">
         <v>0</v>
       </c>
@@ -4125,10 +4125,10 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S34" t="n">
         <v>1</v>
@@ -4141,42 +4141,42 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="W34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 21713-2025 artfynd.xlsx", "A 21713-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 16519-2026 artfynd.xlsx", "A 16519-2026")</f>
         <v/>
       </c>
       <c r="X34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 21713-2025 karta.png", "A 21713-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 16519-2026 karta.png", "A 16519-2026")</f>
         <v/>
       </c>
       <c r="Y34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 21713-2025 georefererad karta.tif", "A 21713-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 16519-2026 georefererad karta.tif", "A 16519-2026")</f>
         <v/>
       </c>
       <c r="AA34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 21713-2025 FSC-klagomål.docx", "A 21713-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 16519-2026 FSC-klagomål.docx", "A 16519-2026")</f>
         <v/>
       </c>
       <c r="AB34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 21713-2025 FSC-klagomål mail.docx", "A 21713-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 16519-2026 FSC-klagomål mail.docx", "A 16519-2026")</f>
         <v/>
       </c>
       <c r="AC34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 21713-2025 tillsynsbegäran.docx", "A 21713-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 16519-2026 tillsynsbegäran.docx", "A 16519-2026")</f>
         <v/>
       </c>
       <c r="AD34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 21713-2025 tillsynsbegäran mail.docx", "A 21713-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 16519-2026 tillsynsbegäran mail.docx", "A 16519-2026")</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 25479-2025</t>
+          <t>A 31284-2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4186,14 +4186,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45802</v>
+        <v>46218</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4206,13 +4206,13 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.7</v>
+        <v>6.8</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
@@ -4246,42 +4246,42 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>Lundvårlök</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="W35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 25479-2025 artfynd.xlsx", "A 25479-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 31284-2026 artfynd.xlsx", "A 31284-2026")</f>
         <v/>
       </c>
       <c r="X35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 25479-2025 karta.png", "A 25479-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 31284-2026 karta.png", "A 31284-2026")</f>
         <v/>
       </c>
       <c r="Y35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 25479-2025 georefererad karta.tif", "A 25479-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 31284-2026 georefererad karta.tif", "A 31284-2026")</f>
         <v/>
       </c>
       <c r="AA35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 25479-2025 FSC-klagomål.docx", "A 25479-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 31284-2026 FSC-klagomål.docx", "A 31284-2026")</f>
         <v/>
       </c>
       <c r="AB35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 25479-2025 FSC-klagomål mail.docx", "A 25479-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 31284-2026 FSC-klagomål mail.docx", "A 31284-2026")</f>
         <v/>
       </c>
       <c r="AC35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 25479-2025 tillsynsbegäran.docx", "A 25479-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 31284-2026 tillsynsbegäran.docx", "A 31284-2026")</f>
         <v/>
       </c>
       <c r="AD35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 25479-2025 tillsynsbegäran mail.docx", "A 25479-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 31284-2026 tillsynsbegäran mail.docx", "A 31284-2026")</f>
         <v/>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 36362-2025</t>
+          <t>A 30165-2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4295,10 +4295,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45868</v>
+        <v>46206</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4311,23 +4311,23 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>3.7</v>
+        <v>1.4</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
       </c>
       <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" t="n">
         <v>1</v>
       </c>
-      <c r="L36" t="n">
-        <v>0</v>
-      </c>
-      <c r="M36" t="n">
-        <v>0</v>
-      </c>
-      <c r="N36" t="n">
-        <v>0</v>
-      </c>
       <c r="O36" t="n">
         <v>0</v>
       </c>
@@ -4335,10 +4335,10 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S36" t="n">
         <v>1</v>
@@ -4347,39 +4347,39 @@
         <v>1</v>
       </c>
       <c r="U36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="W36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 36362-2025 artfynd.xlsx", "A 36362-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 30165-2026 artfynd.xlsx", "A 30165-2026")</f>
         <v/>
       </c>
       <c r="X36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 36362-2025 karta.png", "A 36362-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 30165-2026 karta.png", "A 30165-2026")</f>
         <v/>
       </c>
       <c r="Y36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 36362-2025 georefererad karta.tif", "A 36362-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 30165-2026 georefererad karta.tif", "A 30165-2026")</f>
         <v/>
       </c>
       <c r="AA36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 36362-2025 FSC-klagomål.docx", "A 36362-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 30165-2026 FSC-klagomål.docx", "A 30165-2026")</f>
         <v/>
       </c>
       <c r="AB36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 36362-2025 FSC-klagomål mail.docx", "A 36362-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 30165-2026 FSC-klagomål mail.docx", "A 30165-2026")</f>
         <v/>
       </c>
       <c r="AC36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 36362-2025 tillsynsbegäran.docx", "A 36362-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 30165-2026 tillsynsbegäran.docx", "A 30165-2026")</f>
         <v/>
       </c>
       <c r="AD36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 36362-2025 tillsynsbegäran mail.docx", "A 36362-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 30165-2026 tillsynsbegäran mail.docx", "A 30165-2026")</f>
         <v/>
       </c>
     </row>
@@ -4403,7 +4403,7 @@
         <v>45089</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4508,7 +4508,7 @@
         <v>44999</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4613,7 +4613,7 @@
         <v>44509</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4686,7 +4686,7 @@
         <v>44663</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4759,7 +4759,7 @@
         <v>44509</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4832,7 +4832,7 @@
         <v>44697</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4905,7 +4905,7 @@
         <v>44510</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4978,7 +4978,7 @@
         <v>44834</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5051,7 +5051,7 @@
         <v>44771</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5124,7 +5124,7 @@
         <v>44466</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5197,7 +5197,7 @@
         <v>44789</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5253,7 +5253,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 25850-2022</t>
+          <t>A 2816-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5263,14 +5263,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44733</v>
+        <v>45677</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5283,7 +5283,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5326,7 +5326,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 24670-2024</t>
+          <t>A 16101-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5336,14 +5336,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45460</v>
+        <v>45750</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5356,7 +5356,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5399,7 +5399,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 2979-2024</t>
+          <t>A 2170-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5413,10 +5413,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45315</v>
+        <v>45673</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5428,13 +5428,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I50" t="n">
-        <v>4.7</v>
+        <v>3.6</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5477,7 +5472,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 18609-2025</t>
+          <t>A 34422-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5487,14 +5482,14 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45763</v>
+        <v>45525</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5507,7 +5502,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5550,7 +5545,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 3471-2025</t>
+          <t>A 11943-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5564,10 +5559,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45680</v>
+        <v>45728</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5580,7 +5575,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>3.7</v>
+        <v>1.2</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5623,7 +5618,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 33359-2023</t>
+          <t>A 44613-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5637,10 +5632,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45128</v>
+        <v>45189</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5652,8 +5647,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I53" t="n">
-        <v>0.9</v>
+        <v>3.8</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5696,7 +5696,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 37757-2024</t>
+          <t>A 43937-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5710,10 +5710,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45541</v>
+        <v>45187</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5726,7 +5726,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.7</v>
+        <v>2.6</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5769,7 +5769,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 31596-2023</t>
+          <t>A 43939-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5783,10 +5783,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45117</v>
+        <v>45187</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5799,7 +5799,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5842,7 +5842,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 44613-2023</t>
+          <t>A 67426-2021</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5856,10 +5856,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45189</v>
+        <v>44523</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5871,13 +5871,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I56" t="n">
-        <v>3.8</v>
+        <v>0.6</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5920,7 +5915,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 2816-2025</t>
+          <t>A 3534-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5930,14 +5925,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45677</v>
+        <v>45680</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5949,8 +5944,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I57" t="n">
-        <v>2</v>
+        <v>4.8</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5993,7 +5993,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 28785-2023</t>
+          <t>A 25850-2022</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6003,14 +6003,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45104</v>
+        <v>44733</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6023,7 +6023,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>2.1</v>
+        <v>0.8</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -6066,7 +6066,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 16101-2025</t>
+          <t>A 43380-2022</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6080,10 +6080,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45750</v>
+        <v>44834</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6096,7 +6096,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.5</v>
+        <v>1.7</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6139,7 +6139,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 58360-2023</t>
+          <t>A 7831-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6153,10 +6153,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45250</v>
+        <v>45706</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6169,7 +6169,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>2.5</v>
+        <v>0.6</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6212,7 +6212,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 4756-2025</t>
+          <t>A 47609-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6226,10 +6226,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45688</v>
+        <v>45203</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6242,7 +6242,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.9</v>
+        <v>2.4</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6285,7 +6285,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 48397-2022</t>
+          <t>A 18735-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6299,10 +6299,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44858</v>
+        <v>45043</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6315,7 +6315,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6358,7 +6358,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 6886-2024</t>
+          <t>A 9974-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6372,10 +6372,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45342</v>
+        <v>45363</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6387,13 +6387,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I63" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6436,7 +6431,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 33358-2023</t>
+          <t>A 15970-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6450,10 +6445,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45128</v>
+        <v>45405</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6466,7 +6461,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.4</v>
+        <v>1.8</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6509,7 +6504,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 39298-2023</t>
+          <t>A 5163-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6523,10 +6518,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45166</v>
+        <v>45330</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6538,8 +6533,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I65" t="n">
-        <v>4.6</v>
+        <v>7.1</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6582,7 +6582,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 39507-2024</t>
+          <t>A 28493-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6596,10 +6596,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45551</v>
+        <v>45103</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6611,13 +6611,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I66" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6660,7 +6655,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 3346-2024</t>
+          <t>A 36840-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6674,10 +6669,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45317</v>
+        <v>45538</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6689,8 +6684,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I67" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6733,7 +6733,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 788-2024</t>
+          <t>A 60913-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6747,10 +6747,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45300</v>
+        <v>45261</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6763,7 +6763,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6806,7 +6806,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 9974-2024</t>
+          <t>A 37724-2022</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6820,10 +6820,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45363</v>
+        <v>44810</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6836,7 +6836,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6879,7 +6879,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 11943-2025</t>
+          <t>A 37728-2022</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6893,10 +6893,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45728</v>
+        <v>44810</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6909,7 +6909,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6952,7 +6952,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 42715-2023</t>
+          <t>A 8084-2022</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6966,10 +6966,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45176</v>
+        <v>44608</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6982,7 +6982,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -7025,7 +7025,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 28918-2023</t>
+          <t>A 56818-2022</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7039,10 +7039,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45104</v>
+        <v>44894</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7055,7 +7055,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7098,7 +7098,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 47641-2023</t>
+          <t>A 16665-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7112,10 +7112,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45203</v>
+        <v>45754</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7128,7 +7128,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>4.8</v>
+        <v>2.4</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7171,7 +7171,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 43932-2023</t>
+          <t>A 33359-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7185,10 +7185,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45187</v>
+        <v>45128</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7201,7 +7201,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>3</v>
+        <v>0.9</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7244,7 +7244,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 43935-2023</t>
+          <t>A 28625-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7258,10 +7258,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45187</v>
+        <v>45103</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7274,7 +7274,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>2.9</v>
+        <v>4.8</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7317,7 +7317,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 2747-2023</t>
+          <t>A 54894-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7331,10 +7331,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44944</v>
+        <v>45236</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7346,13 +7346,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I76" t="n">
-        <v>4.6</v>
+        <v>0.6</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7395,7 +7390,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 48427-2022</t>
+          <t>A 36689-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7405,14 +7400,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44858</v>
+        <v>45537</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7430,7 +7425,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.5</v>
+        <v>9.5</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7473,7 +7468,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 8084-2022</t>
+          <t>A 38080-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7487,10 +7482,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44608</v>
+        <v>45545</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7503,7 +7498,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7546,7 +7541,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 43828-2024</t>
+          <t>A 13804-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7560,10 +7555,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45572</v>
+        <v>45391</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7576,7 +7571,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7619,7 +7614,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 13225-2024</t>
+          <t>A 28746-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7633,10 +7628,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45386</v>
+        <v>45478</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7649,7 +7644,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7692,7 +7687,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 13226-2024</t>
+          <t>A 37082-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7702,14 +7697,14 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45386</v>
+        <v>45155</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7722,7 +7717,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7765,7 +7760,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 47552-2023</t>
+          <t>A 43711-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7775,14 +7770,14 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45203</v>
+        <v>45569</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7795,7 +7790,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.3</v>
+        <v>3.4</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7838,7 +7833,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 25552-2025</t>
+          <t>A 34154-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7852,10 +7847,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45803</v>
+        <v>45845</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7868,7 +7863,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7928,7 +7923,7 @@
         <v>44944</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7989,7 +7984,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 38147-2025</t>
+          <t>A 6886-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -8003,10 +7998,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45882</v>
+        <v>45342</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8018,8 +8013,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I85" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -8062,7 +8062,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 37082-2023</t>
+          <t>A 1106-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -8072,14 +8072,14 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45155</v>
+        <v>44935</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8092,7 +8092,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8135,7 +8135,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 54431-2023</t>
+          <t>A 28785-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8145,14 +8145,14 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45226</v>
+        <v>45104</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8165,7 +8165,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>3.2</v>
+        <v>2.1</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8208,7 +8208,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 28625-2023</t>
+          <t>A 23484-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8222,10 +8222,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45103</v>
+        <v>45792</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8238,7 +8238,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>4.8</v>
+        <v>3.5</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8281,7 +8281,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 65073-2023</t>
+          <t>A 13225-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8295,10 +8295,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45287</v>
+        <v>45386</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8311,7 +8311,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1.7</v>
+        <v>0.7</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8354,7 +8354,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 38080-2024</t>
+          <t>A 13226-2024</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8368,10 +8368,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45545</v>
+        <v>45386</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8427,7 +8427,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 34154-2025</t>
+          <t>A 48397-2022</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8441,10 +8441,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45845</v>
+        <v>44858</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8457,7 +8457,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>5</v>
+        <v>1.7</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8500,7 +8500,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 5079-2026</t>
+          <t>A 17073-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8514,10 +8514,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>46049</v>
+        <v>45034</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8530,7 +8530,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8573,7 +8573,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 13633-2024</t>
+          <t>A 2979-2024</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8587,10 +8587,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45390</v>
+        <v>45315</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8602,8 +8602,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I93" t="n">
-        <v>1.1</v>
+        <v>4.7</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8646,7 +8651,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 44816-2023</t>
+          <t>A 15998-2024</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8660,10 +8665,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45190</v>
+        <v>45405</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8676,7 +8681,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8719,7 +8724,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 28493-2023</t>
+          <t>A 16001-2024</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8733,10 +8738,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45103</v>
+        <v>45405</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8749,7 +8754,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0.8</v>
+        <v>0.2</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8792,7 +8797,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 43879-2023</t>
+          <t>A 31596-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8806,10 +8811,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45187</v>
+        <v>45117</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8821,13 +8826,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I96" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8870,7 +8870,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 47609-2023</t>
+          <t>A 43828-2024</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8884,10 +8884,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45203</v>
+        <v>45572</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8900,7 +8900,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>2.4</v>
+        <v>0.9</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8960,7 +8960,7 @@
         <v>45845</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9016,7 +9016,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 43882-2023</t>
+          <t>A 54184-2024</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -9030,10 +9030,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45187</v>
+        <v>45616</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9045,13 +9045,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I99" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -9094,7 +9089,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 67426-2021</t>
+          <t>A 28550-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -9108,10 +9103,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>44523</v>
+        <v>45818</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9124,7 +9119,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>0.6</v>
+        <v>5</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -9167,7 +9162,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 51757-2025</t>
+          <t>A 43932-2023</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9177,14 +9172,14 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45951</v>
+        <v>45187</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9196,13 +9191,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I101" t="n">
-        <v>1.3</v>
+        <v>3</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9245,7 +9235,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 3239-2023</t>
+          <t>A 43935-2023</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9259,10 +9249,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>44946</v>
+        <v>45187</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9275,7 +9265,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>0.4</v>
+        <v>2.9</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9318,7 +9308,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 60963-2023</t>
+          <t>A 9612-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9332,10 +9322,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45261</v>
+        <v>45715</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9391,7 +9381,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 52930-2025</t>
+          <t>A 18609-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9405,10 +9395,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45957</v>
+        <v>45763</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9420,13 +9410,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I104" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9469,7 +9454,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 52929-2025</t>
+          <t>A 20403-2024</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9483,10 +9468,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45957</v>
+        <v>45435</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9498,13 +9483,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I105" t="n">
-        <v>8.300000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9547,7 +9527,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 43685-2022</t>
+          <t>A 51757-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9557,14 +9537,14 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>44837</v>
+        <v>45951</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9574,6 +9554,11 @@
       <c r="G106" t="inlineStr">
         <is>
           <t>HÖRBY</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I106" t="n">
@@ -9620,7 +9605,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 4597-2026</t>
+          <t>A 56750-2023</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9634,10 +9619,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>46048</v>
+        <v>45238</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9650,7 +9635,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9693,7 +9678,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 54765-2025</t>
+          <t>A 3040-2024</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9707,10 +9692,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45966</v>
+        <v>45316</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9723,7 +9708,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>2.6</v>
+        <v>4</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9766,7 +9751,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 55304-2025</t>
+          <t>A 42715-2023</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9776,14 +9761,14 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45970</v>
+        <v>45176</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9796,7 +9781,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9839,7 +9824,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 55306-2025</t>
+          <t>A 44816-2023</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9849,14 +9834,14 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45970</v>
+        <v>45190</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9869,7 +9854,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9912,7 +9897,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 55265-2023</t>
+          <t>A 13633-2024</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9926,10 +9911,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45237</v>
+        <v>45390</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9942,7 +9927,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9985,7 +9970,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 40994-2025</t>
+          <t>A 47552-2023</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9999,10 +9984,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45898</v>
+        <v>45203</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10015,7 +10000,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>5.6</v>
+        <v>1.3</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -10058,7 +10043,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 5163-2024</t>
+          <t>A 52929-2025</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -10072,10 +10057,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45330</v>
+        <v>45957</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10089,11 +10074,11 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I113" t="n">
-        <v>7.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -10136,7 +10121,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 57269-2025</t>
+          <t>A 52930-2025</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -10150,10 +10135,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45979</v>
+        <v>45957</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10171,7 +10156,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>5.5</v>
+        <v>1.6</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -10214,7 +10199,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 18603-2025</t>
+          <t>A 54431-2023</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10228,10 +10213,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45763</v>
+        <v>45226</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10244,7 +10229,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>0.5</v>
+        <v>3.2</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10287,7 +10272,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 59308-2025</t>
+          <t>A 19777-2023</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10301,10 +10286,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45989</v>
+        <v>45051</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10317,7 +10302,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>1.2</v>
+        <v>4.3</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10360,7 +10345,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 4590-2026</t>
+          <t>A 58641-2023</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10370,14 +10355,14 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>46048</v>
+        <v>45251</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10390,7 +10375,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10433,7 +10418,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 3534-2025</t>
+          <t>A 54765-2025</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10447,10 +10432,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45680</v>
+        <v>45966</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10462,13 +10447,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I118" t="n">
-        <v>4.8</v>
+        <v>2.6</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10511,7 +10491,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 20595-2024</t>
+          <t>A 43879-2023</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10525,10 +10505,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45436</v>
+        <v>45187</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10546,7 +10526,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>3.5</v>
+        <v>1.1</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10589,7 +10569,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 6350-2026</t>
+          <t>A 3471-2025</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10603,10 +10583,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>46051</v>
+        <v>45680</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10619,7 +10599,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>2.4</v>
+        <v>3.7</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10662,7 +10642,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 18369-2025</t>
+          <t>A 18603-2025</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10676,10 +10656,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45762</v>
+        <v>45763</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10692,7 +10672,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>2.2</v>
+        <v>0.5</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10735,7 +10715,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 43937-2023</t>
+          <t>A 49726-2023</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10749,10 +10729,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45187</v>
+        <v>45208</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10765,7 +10745,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>2.6</v>
+        <v>1.3</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10808,7 +10788,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 43939-2023</t>
+          <t>A 3346-2024</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10822,10 +10802,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45187</v>
+        <v>45317</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10838,7 +10818,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10881,7 +10861,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 28501-2023</t>
+          <t>A 40994-2025</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10895,10 +10875,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45103</v>
+        <v>45898</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10911,7 +10891,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>3.6</v>
+        <v>5.6</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10954,7 +10934,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 28527-2023</t>
+          <t>A 28501-2023</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10971,7 +10951,7 @@
         <v>45103</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10984,7 +10964,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>0.7</v>
+        <v>3.6</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -11027,7 +11007,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 54894-2023</t>
+          <t>A 55304-2025</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -11037,14 +11017,14 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45236</v>
+        <v>45970</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11057,7 +11037,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -11100,7 +11080,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 62277-2025</t>
+          <t>A 55306-2025</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -11110,14 +11090,14 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>46006</v>
+        <v>45970</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11130,7 +11110,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>2.4</v>
+        <v>0.3</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -11173,7 +11153,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 37276-2024</t>
+          <t>A 29244-2025</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -11187,10 +11167,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45540</v>
+        <v>45824</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11203,7 +11183,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -11246,7 +11226,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 3177-2026</t>
+          <t>A 33873-2024</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11256,14 +11236,14 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>46041</v>
+        <v>45521</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11276,7 +11256,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>0.5</v>
+        <v>3.5</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11319,7 +11299,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 554-2026</t>
+          <t>A 788-2024</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11333,10 +11313,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>46029</v>
+        <v>45300</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11349,7 +11329,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11392,7 +11372,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 826-2026</t>
+          <t>A 29354-2025</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11406,10 +11386,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>46030</v>
+        <v>45824</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11421,13 +11401,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H131" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I131" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11470,7 +11445,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 829-2026</t>
+          <t>A 57269-2025</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11484,10 +11459,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>46030</v>
+        <v>45979</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11505,7 +11480,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>6.9</v>
+        <v>5.5</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11548,7 +11523,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 821-2026</t>
+          <t>A 58360-2023</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11562,10 +11537,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>46030</v>
+        <v>45250</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11577,13 +11552,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H133" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I133" t="n">
-        <v>4.3</v>
+        <v>2.5</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11626,7 +11596,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 1989-2026</t>
+          <t>A 39298-2023</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11640,10 +11610,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>46035</v>
+        <v>45166</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11656,7 +11626,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>2.5</v>
+        <v>4.6</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11699,7 +11669,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 36689-2024</t>
+          <t>A 29219-2023</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11709,14 +11679,14 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45537</v>
+        <v>45105</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11728,13 +11698,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H135" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I135" t="n">
-        <v>9.5</v>
+        <v>0.7</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11777,7 +11742,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 3013-2026</t>
+          <t>A 3542-2025</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11791,10 +11756,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>46038</v>
+        <v>45680</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11806,8 +11771,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I136" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11850,7 +11820,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 59284-2025</t>
+          <t>A 50715-2024</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11864,10 +11834,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45988</v>
+        <v>45602</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11880,7 +11850,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>1.5</v>
+        <v>0.4</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11923,7 +11893,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 31522-2022</t>
+          <t>A 59308-2025</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11937,10 +11907,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>44775</v>
+        <v>45989</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11953,7 +11923,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11996,7 +11966,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 54184-2024</t>
+          <t>A 47637-2023</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -12010,10 +11980,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45616</v>
+        <v>45203</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12026,7 +11996,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -12069,7 +12039,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 10500-2026</t>
+          <t>A 826-2026</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -12083,10 +12053,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>46076</v>
+        <v>46030</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12098,8 +12068,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I140" t="n">
-        <v>1.1</v>
+        <v>0.3</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -12142,7 +12117,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 5374-2026</t>
+          <t>A 829-2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -12156,10 +12131,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>46050</v>
+        <v>46030</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12171,8 +12146,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I141" t="n">
-        <v>0.5</v>
+        <v>6.9</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -12215,7 +12195,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 60913-2023</t>
+          <t>A 821-2026</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -12229,10 +12209,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45261</v>
+        <v>46030</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12244,8 +12224,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I142" t="n">
-        <v>0.7</v>
+        <v>4.3</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -12288,7 +12273,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 44073-2024</t>
+          <t>A 554-2026</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12302,10 +12287,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45572</v>
+        <v>46029</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12318,7 +12303,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -12361,7 +12346,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 16518-2026</t>
+          <t>A 2981-2024</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12375,10 +12360,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>46112</v>
+        <v>45315</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12390,8 +12375,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I144" t="n">
-        <v>0.8</v>
+        <v>6.4</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -12434,7 +12424,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 11941-2025</t>
+          <t>A 62277-2025</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12448,10 +12438,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45728</v>
+        <v>46006</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12464,7 +12454,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>0.6</v>
+        <v>2.4</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12507,7 +12497,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 43380-2022</t>
+          <t>A 1989-2026</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12521,10 +12511,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>44834</v>
+        <v>46035</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12537,7 +12527,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>1.7</v>
+        <v>2.5</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12580,7 +12570,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 8310-2026</t>
+          <t>A 3013-2026</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12594,10 +12584,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>46064</v>
+        <v>46038</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12610,7 +12600,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12653,7 +12643,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 8260-2026</t>
+          <t>A 32459-2025</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12667,10 +12657,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>46064</v>
+        <v>45838</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12683,7 +12673,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>3.3</v>
+        <v>1.2</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12726,7 +12716,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 8259-2026</t>
+          <t>A 24670-2024</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12736,14 +12726,14 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>46064</v>
+        <v>45460</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12756,7 +12746,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>3.1</v>
+        <v>0.2</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12799,7 +12789,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 20403-2024</t>
+          <t>A 32958-2025</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12813,10 +12803,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45435</v>
+        <v>45839</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12829,7 +12819,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>0.9</v>
+        <v>5</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12872,7 +12862,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 1106-2023</t>
+          <t>A 6081-2023</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12886,10 +12876,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>44935</v>
+        <v>44959</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12902,7 +12892,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>1.2</v>
+        <v>0.4</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12945,7 +12935,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 10731-2026</t>
+          <t>A 5374-2026</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12959,10 +12949,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>46078</v>
+        <v>46050</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12974,13 +12964,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H152" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I152" t="n">
-        <v>4.8</v>
+        <v>0.5</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -13023,7 +13008,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 29138-2026</t>
+          <t>A 31114-2024</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -13033,14 +13018,14 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>46202</v>
+        <v>45502</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13052,13 +13037,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H153" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I153" t="n">
-        <v>4.2</v>
+        <v>0.6</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -13101,7 +13081,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 29124-2026</t>
+          <t>A 11941-2025</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -13115,10 +13095,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>46202</v>
+        <v>45728</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13131,7 +13111,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>2.9</v>
+        <v>0.6</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -13174,7 +13154,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 29135-2026</t>
+          <t>A 38936-2026</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -13184,14 +13164,14 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>46202</v>
+        <v>46286</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13209,7 +13189,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>4.7</v>
+        <v>1.4</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -13252,7 +13232,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 29137-2026</t>
+          <t>A 38948-2026</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -13262,14 +13242,14 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>46202</v>
+        <v>46286</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13287,7 +13267,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>7.8</v>
+        <v>1.5</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -13330,7 +13310,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 49726-2023</t>
+          <t>A 38906-2026</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -13344,10 +13324,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45208</v>
+        <v>46286</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13359,8 +13339,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I157" t="n">
-        <v>1.3</v>
+        <v>3.1</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -13403,7 +13388,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 36840-2024</t>
+          <t>A 37300-2026</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -13417,10 +13402,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45538</v>
+        <v>46274</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13432,13 +13417,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H158" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I158" t="n">
-        <v>0.9</v>
+        <v>0.2</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -13481,7 +13461,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 24724-2024</t>
+          <t>A 20047-2026</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13491,14 +13471,14 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45460</v>
+        <v>46136</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13511,7 +13491,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -13554,7 +13534,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 58641-2023</t>
+          <t>A 8310-2026</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -13564,14 +13544,14 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45251</v>
+        <v>46064</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13584,7 +13564,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13627,7 +13607,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 14307-2026</t>
+          <t>A 8260-2026</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13641,10 +13621,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>46099</v>
+        <v>46064</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13657,7 +13637,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>1</v>
+        <v>3.3</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13700,7 +13680,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 3040-2024</t>
+          <t>A 8259-2026</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13714,10 +13694,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45316</v>
+        <v>46064</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13730,7 +13710,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>4</v>
+        <v>3.1</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13773,7 +13753,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 3470-2026</t>
+          <t>A 38684-2022</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13787,10 +13767,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>46042</v>
+        <v>44814</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13803,7 +13783,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13846,7 +13826,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 3513-2026</t>
+          <t>A 37757-2024</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13860,10 +13840,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>46042</v>
+        <v>45541</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13876,7 +13856,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13919,7 +13899,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 3520-2026</t>
+          <t>A 38824-2026</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13933,10 +13913,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>46042</v>
+        <v>46286</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13948,8 +13928,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I165" t="n">
-        <v>0.8</v>
+        <v>11.2</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13992,7 +13977,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 9850-2026</t>
+          <t>A 38730-2026</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -14006,10 +13991,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>46072</v>
+        <v>46285</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14022,7 +14007,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>2.2</v>
+        <v>0.4</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -14065,7 +14050,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 15970-2024</t>
+          <t>A 25183-2023</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -14079,10 +14064,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45405</v>
+        <v>45079</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14095,7 +14080,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -14138,7 +14123,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 18735-2023</t>
+          <t>A 10731-2026</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -14152,10 +14137,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>45043</v>
+        <v>46078</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14167,8 +14152,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I168" t="n">
-        <v>1</v>
+        <v>4.8</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -14211,7 +14201,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 6081-2023</t>
+          <t>A 44073-2024</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -14225,10 +14215,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>44959</v>
+        <v>45572</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14241,7 +14231,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -14284,7 +14274,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 29219-2023</t>
+          <t>A 37276-2024</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -14298,10 +14288,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45105</v>
+        <v>45540</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14314,7 +14304,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>0.7</v>
+        <v>1.6</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -14357,7 +14347,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 56818-2022</t>
+          <t>A 20595-2024</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -14371,10 +14361,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>44894</v>
+        <v>45436</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14386,8 +14376,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I171" t="n">
-        <v>1.8</v>
+        <v>3.5</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -14430,7 +14425,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 7402-2026</t>
+          <t>A 10524-2026</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -14444,10 +14439,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>46059</v>
+        <v>46076</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14460,7 +14455,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>4.7</v>
+        <v>1.6</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -14503,7 +14498,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 34422-2024</t>
+          <t>A 37756-2024</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -14513,14 +14508,14 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45525</v>
+        <v>45541</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14533,7 +14528,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>1.5</v>
+        <v>3.2</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -14576,7 +14571,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 7831-2025</t>
+          <t>A 119-2023</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14590,10 +14585,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45706</v>
+        <v>44928</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14606,7 +14601,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14649,7 +14644,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 56750-2023</t>
+          <t>A 43685-2022</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14659,14 +14654,14 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45238</v>
+        <v>44837</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14679,7 +14674,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14722,7 +14717,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 23606-2026</t>
+          <t>A 24724-2024</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14736,10 +14731,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>46162</v>
+        <v>45460</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14752,7 +14747,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>9.4</v>
+        <v>1.4</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14795,7 +14790,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 17073-2023</t>
+          <t>A 14307-2026</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14809,10 +14804,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45034</v>
+        <v>46099</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14825,7 +14820,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14868,7 +14863,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 34737-2026</t>
+          <t>A 3520-2026</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14882,10 +14877,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>46258</v>
+        <v>46042</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14898,7 +14893,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14941,7 +14936,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 34740-2026</t>
+          <t>A 3470-2026</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14955,10 +14950,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>46258</v>
+        <v>46042</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14971,7 +14966,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -15014,7 +15009,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 19420-2022</t>
+          <t>A 6558-2025</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -15024,14 +15019,14 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>44693</v>
+        <v>45699</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15043,8 +15038,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I180" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -15087,7 +15087,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 30934-2026</t>
+          <t>A 9850-2026</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -15101,10 +15101,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>46213</v>
+        <v>46072</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15117,7 +15117,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>1.1</v>
+        <v>2.2</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -15160,7 +15160,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 55307-2025</t>
+          <t>A 3513-2026</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -15174,10 +15174,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>45970</v>
+        <v>46042</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15190,7 +15190,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>2.5</v>
+        <v>0.9</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -15233,7 +15233,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 31286-2026</t>
+          <t>A 2747-2023</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -15247,10 +15247,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>46218</v>
+        <v>44944</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15262,8 +15262,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I183" t="n">
-        <v>1.1</v>
+        <v>4.6</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -15306,7 +15311,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 119-2023</t>
+          <t>A 31522-2022</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -15320,10 +15325,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>44928</v>
+        <v>44775</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15336,7 +15341,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>0.8</v>
+        <v>1.8</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -15379,7 +15384,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 50715-2024</t>
+          <t>A 36355-2025</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -15393,10 +15398,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>45602</v>
+        <v>45868</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15409,7 +15414,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>0.4</v>
+        <v>3.6</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -15452,7 +15457,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 37724-2022</t>
+          <t>A 55265-2023</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -15466,10 +15471,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>44810</v>
+        <v>45237</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15525,7 +15530,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 37728-2022</t>
+          <t>A 28918-2023</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -15539,10 +15544,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>44810</v>
+        <v>45104</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15555,7 +15560,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -15598,7 +15603,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 47637-2023</t>
+          <t>A 3239-2023</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15612,10 +15617,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>45203</v>
+        <v>44946</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15628,7 +15633,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>2</v>
+        <v>0.4</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15671,7 +15676,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 33873-2024</t>
+          <t>A 13228-2024</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15685,10 +15690,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>45521</v>
+        <v>45386</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15701,7 +15706,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>3.5</v>
+        <v>0.7</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15744,7 +15749,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 57017-2025</t>
+          <t>A 48427-2022</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15758,10 +15763,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>45978</v>
+        <v>44858</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15773,8 +15778,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I190" t="n">
-        <v>5.5</v>
+        <v>0.5</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15817,7 +15827,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 3542-2025</t>
+          <t>A 7402-2026</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15831,10 +15841,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>45680</v>
+        <v>46059</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15846,13 +15856,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H191" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I191" t="n">
-        <v>1.4</v>
+        <v>4.7</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15895,7 +15900,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 13228-2024</t>
+          <t>A 4756-2025</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15909,10 +15914,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>45386</v>
+        <v>45688</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15925,7 +15930,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15968,7 +15973,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 15998-2024</t>
+          <t>A 33358-2023</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15982,10 +15987,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>45405</v>
+        <v>45128</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16041,7 +16046,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 16001-2024</t>
+          <t>A 25552-2025</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -16055,10 +16060,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>45405</v>
+        <v>45803</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16071,7 +16076,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -16114,7 +16119,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 31114-2024</t>
+          <t>A 39507-2024</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -16128,10 +16133,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>45502</v>
+        <v>45551</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16143,8 +16148,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I195" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -16187,7 +16197,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 13804-2024</t>
+          <t>A 41940-2022</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -16201,10 +16211,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>45391</v>
+        <v>44833</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16217,7 +16227,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -16260,7 +16270,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 19777-2023</t>
+          <t>A 43882-2023</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -16274,10 +16284,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>45051</v>
+        <v>45187</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16289,8 +16299,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I197" t="n">
-        <v>4.3</v>
+        <v>1.2</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -16333,7 +16348,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 28746-2024</t>
+          <t>A 28527-2023</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -16347,10 +16362,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>45478</v>
+        <v>45103</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16363,7 +16378,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>1.9</v>
+        <v>0.7</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -16406,7 +16421,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 38073-2026</t>
+          <t>A 38147-2025</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -16420,10 +16435,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>46280</v>
+        <v>45882</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16436,7 +16451,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>2.3</v>
+        <v>1.6</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -16479,7 +16494,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 6558-2025</t>
+          <t>A 5079-2026</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -16489,14 +16504,14 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>45699</v>
+        <v>46049</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16508,13 +16523,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H200" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I200" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -16557,7 +16567,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 25183-2023</t>
+          <t>A 19420-2022</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -16571,10 +16581,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>45079</v>
+        <v>44693</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16587,7 +16597,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -16630,7 +16640,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 37300-2026</t>
+          <t>A 65073-2023</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -16644,10 +16654,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>46274</v>
+        <v>45287</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16660,7 +16670,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>0.2</v>
+        <v>1.7</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16703,7 +16713,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 38936-2026</t>
+          <t>A 47641-2023</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16717,10 +16727,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>46286</v>
+        <v>45203</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16732,13 +16742,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H203" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I203" t="n">
-        <v>1.4</v>
+        <v>4.8</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -16781,7 +16786,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 38948-2026</t>
+          <t>A 60963-2023</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -16795,10 +16800,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>46286</v>
+        <v>45261</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16810,13 +16815,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H204" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I204" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16859,7 +16859,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 10524-2026</t>
+          <t>A 52310-2023</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16873,10 +16873,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>46076</v>
+        <v>45224</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16889,7 +16889,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>1.6</v>
+        <v>3.5</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16932,7 +16932,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 20047-2026</t>
+          <t>A 4597-2026</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16946,10 +16946,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>46136</v>
+        <v>46048</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16962,7 +16962,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -17005,7 +17005,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 38824-2026</t>
+          <t>A 4590-2026</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -17019,10 +17019,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>46286</v>
+        <v>46048</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17034,13 +17034,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H207" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I207" t="n">
-        <v>11.2</v>
+        <v>1.1</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -17083,7 +17078,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 41940-2022</t>
+          <t>A 6350-2026</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -17097,10 +17092,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>44833</v>
+        <v>46051</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17113,7 +17108,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>0.7</v>
+        <v>2.4</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -17156,7 +17151,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 38906-2026</t>
+          <t>A 18369-2025</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -17170,10 +17165,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>46286</v>
+        <v>45762</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17185,13 +17180,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H209" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I209" t="n">
-        <v>3.1</v>
+        <v>2.2</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -17234,7 +17224,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 38730-2026</t>
+          <t>A 3177-2026</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -17244,14 +17234,14 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>46285</v>
+        <v>46041</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17264,7 +17254,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -17307,7 +17297,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 38684-2022</t>
+          <t>A 59284-2025</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -17321,10 +17311,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>44814</v>
+        <v>45988</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17337,7 +17327,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -17380,7 +17370,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 52310-2023</t>
+          <t>A 10500-2026</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -17394,10 +17384,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>45224</v>
+        <v>46076</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17410,7 +17400,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>3.5</v>
+        <v>1.1</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -17453,7 +17443,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 2170-2025</t>
+          <t>A 16518-2026</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -17467,10 +17457,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>45673</v>
+        <v>46112</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17483,7 +17473,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>3.6</v>
+        <v>0.8</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -17526,7 +17516,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 16665-2025</t>
+          <t>A 29138-2026</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -17536,14 +17526,14 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>45754</v>
+        <v>46202</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17555,8 +17545,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I214" t="n">
-        <v>2.4</v>
+        <v>4.2</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -17599,7 +17594,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 43711-2024</t>
+          <t>A 29135-2026</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -17609,14 +17604,14 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>45569</v>
+        <v>46202</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17628,8 +17623,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I215" t="n">
-        <v>3.4</v>
+        <v>4.7</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -17672,7 +17672,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 23484-2025</t>
+          <t>A 29137-2026</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -17682,14 +17682,14 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>45792</v>
+        <v>46202</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17701,8 +17701,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I216" t="n">
-        <v>3.5</v>
+        <v>7.8</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -17745,7 +17750,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 28550-2025</t>
+          <t>A 29124-2026</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -17759,10 +17764,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>45818</v>
+        <v>46202</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17775,7 +17780,7 @@
         </is>
       </c>
       <c r="I217" t="n">
-        <v>5</v>
+        <v>2.9</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -17818,7 +17823,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 9612-2025</t>
+          <t>A 30934-2026</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -17832,10 +17837,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>45715</v>
+        <v>46213</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17848,7 +17853,7 @@
         </is>
       </c>
       <c r="I218" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -17891,7 +17896,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 29244-2025</t>
+          <t>A 34737-2026</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -17905,10 +17910,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>45824</v>
+        <v>46258</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17964,7 +17969,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 29354-2025</t>
+          <t>A 34740-2026</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -17978,10 +17983,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>45824</v>
+        <v>46258</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17994,7 +17999,7 @@
         </is>
       </c>
       <c r="I220" t="n">
-        <v>0.8</v>
+        <v>2.1</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -18037,7 +18042,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 32958-2025</t>
+          <t>A 23606-2026</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -18047,14 +18052,14 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>45839</v>
+        <v>46162</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18067,7 +18072,7 @@
         </is>
       </c>
       <c r="I221" t="n">
-        <v>5</v>
+        <v>9.4</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -18110,7 +18115,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 32459-2025</t>
+          <t>A 31286-2026</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -18124,10 +18129,10 @@
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>45838</v>
+        <v>46218</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18140,7 +18145,7 @@
         </is>
       </c>
       <c r="I222" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -18183,7 +18188,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 2981-2024</t>
+          <t>A 55307-2025</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -18197,10 +18202,10 @@
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>45315</v>
+        <v>45970</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18212,13 +18217,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H223" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I223" t="n">
-        <v>6.4</v>
+        <v>2.5</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -18261,7 +18261,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 37756-2024</t>
+          <t>A 57017-2025</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -18275,10 +18275,10 @@
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>45541</v>
+        <v>45978</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18291,7 +18291,7 @@
         </is>
       </c>
       <c r="I224" t="n">
-        <v>3.2</v>
+        <v>5.5</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -18334,7 +18334,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 36355-2025</t>
+          <t>A 38073-2026</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -18348,10 +18348,10 @@
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>45868</v>
+        <v>46280</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18364,7 +18364,7 @@
         </is>
       </c>
       <c r="I225" t="n">
-        <v>3.6</v>
+        <v>2.3</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -18424,7 +18424,7 @@
         <v>45230</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18497,7 +18497,7 @@
         <v>44796</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18570,7 +18570,7 @@
         <v>45722</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18643,7 +18643,7 @@
         <v>46042</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18699,7 +18699,7 @@
     <row r="230" ht="15" customHeight="1">
       <c r="A230" t="inlineStr">
         <is>
-          <t>S 1874-2026</t>
+          <t>S 220-2026</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -18713,10 +18713,10 @@
         </is>
       </c>
       <c r="D230" s="1" t="n">
-        <v>46202</v>
+        <v>46051</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18728,13 +18728,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H230" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I230" t="n">
-        <v>7.8</v>
+        <v>1.7</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
@@ -18777,7 +18772,7 @@
     <row r="231" ht="15" customHeight="1">
       <c r="A231" t="inlineStr">
         <is>
-          <t>S 1875-2026</t>
+          <t>S 1874-2026</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -18794,7 +18789,7 @@
         <v>46202</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18812,7 +18807,7 @@
         </is>
       </c>
       <c r="I231" t="n">
-        <v>4.2</v>
+        <v>7.8</v>
       </c>
       <c r="J231" t="n">
         <v>0</v>
@@ -18855,7 +18850,7 @@
     <row r="232" ht="15" customHeight="1">
       <c r="A232" t="inlineStr">
         <is>
-          <t>S 1873-2026</t>
+          <t>S 1875-2026</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -18872,7 +18867,7 @@
         <v>46202</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18890,7 +18885,7 @@
         </is>
       </c>
       <c r="I232" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="J232" t="n">
         <v>0</v>
@@ -18933,7 +18928,7 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>S 220-2026</t>
+          <t>S 1873-2026</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -18947,10 +18942,10 @@
         </is>
       </c>
       <c r="D233" s="1" t="n">
-        <v>46051</v>
+        <v>46202</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18962,8 +18957,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I233" t="n">
-        <v>1.7</v>
+        <v>4.7</v>
       </c>
       <c r="J233" t="n">
         <v>0</v>

--- a/Översikt HÖRBY.xlsx
+++ b/Översikt HÖRBY.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE233"/>
+  <dimension ref="A1:AE234"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>44964</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
         <v>44967</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         <v>44727</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -949,7 +949,7 @@
         <v>45786</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1061,7 +1061,7 @@
         <v>46160</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
         <v>45238</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 31351-2022</t>
+          <t>A 39855-2022</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1289,10 +1289,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>44774</v>
+        <v>44819</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1305,22 +1305,22 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>13.2</v>
+        <v>4.2</v>
       </c>
       <c r="J8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1329,10 +1329,10 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1341,9 +1341,231 @@
         <v>5</v>
       </c>
       <c r="U8" t="n">
+        <v>1</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Skogsknipprot
+Blåsippa
+Fläcknycklar
+Grönvit nattviol</t>
+        </is>
+      </c>
+      <c r="W8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 39855-2022 artfynd.xlsx", "A 39855-2022")</f>
+        <v/>
+      </c>
+      <c r="X8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 39855-2022 karta.png", "A 39855-2022")</f>
+        <v/>
+      </c>
+      <c r="Y8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 39855-2022 georefererad karta.tif", "A 39855-2022")</f>
+        <v/>
+      </c>
+      <c r="AA8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 39855-2022 FSC-klagomål.docx", "A 39855-2022")</f>
+        <v/>
+      </c>
+      <c r="AB8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 39855-2022 FSC-klagomål mail.docx", "A 39855-2022")</f>
+        <v/>
+      </c>
+      <c r="AC8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 39855-2022 tillsynsbegäran.docx", "A 39855-2022")</f>
+        <v/>
+      </c>
+      <c r="AD8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 39855-2022 tillsynsbegäran mail.docx", "A 39855-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 16520-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>46112</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>HÖRBY</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>2</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
         <v>3</v>
       </c>
-      <c r="V8" s="2" t="inlineStr">
+      <c r="R9" t="n">
+        <v>1</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="n">
+        <v>6</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Slåttergubbe
+Sydlig sotticka
+Älg
+Fiskgjuse
+Större brunfladdermus</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 16520-2026 artfynd.xlsx", "A 16520-2026")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 16520-2026 karta.png", "A 16520-2026")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 16520-2026 georefererad karta.tif", "A 16520-2026")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 16520-2026 FSC-klagomål.docx", "A 16520-2026")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 16520-2026 FSC-klagomål mail.docx", "A 16520-2026")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 16520-2026 tillsynsbegäran.docx", "A 16520-2026")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 16520-2026 tillsynsbegäran mail.docx", "A 16520-2026")</f>
+        <v/>
+      </c>
+      <c r="AE9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/fåglar/A 16520-2026 prioriterade fågelarter.docx", "A 16520-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 31351-2022</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>44774</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>HÖRBY</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="J10" t="n">
+        <v>5</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>3</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>3</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="n">
+        <v>5</v>
+      </c>
+      <c r="U10" t="n">
+        <v>3</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Duvhök
 Grönsångare
@@ -1352,111 +1574,111 @@
 Kungsfågel</t>
         </is>
       </c>
-      <c r="W8">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 31351-2022 artfynd.xlsx", "A 31351-2022")</f>
         <v/>
       </c>
-      <c r="X8">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 31351-2022 karta.png", "A 31351-2022")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 31351-2022 georefererad karta.tif", "A 31351-2022")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 31351-2022 FSC-klagomål.docx", "A 31351-2022")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 31351-2022 FSC-klagomål mail.docx", "A 31351-2022")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 31351-2022 tillsynsbegäran.docx", "A 31351-2022")</f>
         <v/>
       </c>
-      <c r="AD8">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 31351-2022 tillsynsbegäran mail.docx", "A 31351-2022")</f>
         <v/>
       </c>
-      <c r="AE8">
+      <c r="AE10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/fåglar/A 31351-2022 prioriterade fågelarter.docx", "A 31351-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
         <is>
           <t>A 20194-2024</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
         <v>45434</v>
       </c>
-      <c r="E9" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>HÖRBY</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
+      <c r="E11" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>HÖRBY</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
         <v>4.4</v>
       </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
         <v>2</v>
       </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
         <v>2</v>
       </c>
-      <c r="O9" t="n">
+      <c r="O11" t="n">
         <v>1</v>
       </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
         <v>3</v>
       </c>
-      <c r="R9" t="n">
+      <c r="R11" t="n">
         <v>3</v>
       </c>
-      <c r="S9" t="n">
+      <c r="S11" t="n">
         <v>5</v>
       </c>
-      <c r="T9" t="n">
+      <c r="T11" t="n">
         <v>5</v>
       </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Naverlönn
 Ask
@@ -1465,261 +1687,39 @@
 Stor häxört</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 20194-2024 artfynd.xlsx", "A 20194-2024")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 20194-2024 karta.png", "A 20194-2024")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 20194-2024 georefererad karta.tif", "A 20194-2024")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 20194-2024 FSC-klagomål.docx", "A 20194-2024")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 20194-2024 FSC-klagomål mail.docx", "A 20194-2024")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 20194-2024 tillsynsbegäran.docx", "A 20194-2024")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 20194-2024 tillsynsbegäran mail.docx", "A 20194-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 39855-2022</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>44819</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>HÖRBY</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J10" t="n">
-        <v>4</v>
-      </c>
-      <c r="K10" t="n">
-        <v>1</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>1</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1</v>
-      </c>
-      <c r="S10" t="n">
-        <v>5</v>
-      </c>
-      <c r="T10" t="n">
-        <v>5</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Skogsknipprot
-Blåsippa
-Fläcknycklar
-Grönvit nattviol</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 39855-2022 artfynd.xlsx", "A 39855-2022")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 39855-2022 karta.png", "A 39855-2022")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 39855-2022 georefererad karta.tif", "A 39855-2022")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 39855-2022 FSC-klagomål.docx", "A 39855-2022")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 39855-2022 FSC-klagomål mail.docx", "A 39855-2022")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 39855-2022 tillsynsbegäran.docx", "A 39855-2022")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 39855-2022 tillsynsbegäran mail.docx", "A 39855-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 16520-2026</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>46112</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>HÖRBY</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="J11" t="n">
-        <v>2</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>2</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>3</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1</v>
-      </c>
-      <c r="S11" t="n">
-        <v>5</v>
-      </c>
-      <c r="T11" t="n">
-        <v>6</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Slåttergubbe
-Sydlig sotticka
-Älg
-Fiskgjuse
-Större brunfladdermus</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 16520-2026 artfynd.xlsx", "A 16520-2026")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 16520-2026 karta.png", "A 16520-2026")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 16520-2026 georefererad karta.tif", "A 16520-2026")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 16520-2026 FSC-klagomål.docx", "A 16520-2026")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 16520-2026 FSC-klagomål mail.docx", "A 16520-2026")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 16520-2026 tillsynsbegäran.docx", "A 16520-2026")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 16520-2026 tillsynsbegäran mail.docx", "A 16520-2026")</f>
-        <v/>
-      </c>
-      <c r="AE11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/fåglar/A 16520-2026 prioriterade fågelarter.docx", "A 16520-2026")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 5619-2024</t>
+          <t>A 21774-2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1733,10 +1733,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45334</v>
+        <v>46150</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1749,45 +1749,261 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>4.6</v>
+        <v>1.2</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
       </c>
       <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>3</v>
+      </c>
+      <c r="M12" t="n">
         <v>1</v>
       </c>
-      <c r="L12" t="n">
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>4</v>
+      </c>
+      <c r="R12" t="n">
         <v>1</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>2</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>3</v>
-      </c>
-      <c r="R12" t="n">
-        <v>2</v>
       </c>
       <c r="S12" t="n">
         <v>4</v>
       </c>
       <c r="T12" t="n">
+        <v>6</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>Violettkantad guldvinge
+Granspira
+Sotnätfjäril
+Svinrot</t>
+        </is>
+      </c>
+      <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 21774-2026 artfynd.xlsx", "A 21774-2026")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 21774-2026 karta.png", "A 21774-2026")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 21774-2026 georefererad karta.tif", "A 21774-2026")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 21774-2026 FSC-klagomål.docx", "A 21774-2026")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 21774-2026 FSC-klagomål mail.docx", "A 21774-2026")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 21774-2026 tillsynsbegäran.docx", "A 21774-2026")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 21774-2026 tillsynsbegäran mail.docx", "A 21774-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A 38084-2024</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>45545</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>HÖRBY</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>4</v>
+      </c>
+      <c r="T13" t="n">
+        <v>4</v>
+      </c>
+      <c r="U13" t="n">
+        <v>4</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>Myskmadra
+Skogsbräsma
+Tandrot
+Grönsiska</t>
+        </is>
+      </c>
+      <c r="W13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 38084-2024 artfynd.xlsx", "A 38084-2024")</f>
+        <v/>
+      </c>
+      <c r="X13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 38084-2024 karta.png", "A 38084-2024")</f>
+        <v/>
+      </c>
+      <c r="Y13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 38084-2024 georefererad karta.tif", "A 38084-2024")</f>
+        <v/>
+      </c>
+      <c r="AA13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 38084-2024 FSC-klagomål.docx", "A 38084-2024")</f>
+        <v/>
+      </c>
+      <c r="AB13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 38084-2024 FSC-klagomål mail.docx", "A 38084-2024")</f>
+        <v/>
+      </c>
+      <c r="AC13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 38084-2024 tillsynsbegäran.docx", "A 38084-2024")</f>
+        <v/>
+      </c>
+      <c r="AD13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 38084-2024 tillsynsbegäran mail.docx", "A 38084-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A 5619-2024</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>45334</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>HÖRBY</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>2</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>3</v>
+      </c>
+      <c r="R14" t="n">
+        <v>2</v>
+      </c>
+      <c r="S14" t="n">
+        <v>4</v>
+      </c>
+      <c r="T14" t="n">
         <v>7</v>
       </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>Ask
 Skogsalm
@@ -1795,248 +2011,32 @@
 Trubbfjädermossa</t>
         </is>
       </c>
-      <c r="W12">
+      <c r="W14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 5619-2024 artfynd.xlsx", "A 5619-2024")</f>
         <v/>
       </c>
-      <c r="X12">
+      <c r="X14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 5619-2024 karta.png", "A 5619-2024")</f>
         <v/>
       </c>
-      <c r="Y12">
+      <c r="Y14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 5619-2024 georefererad karta.tif", "A 5619-2024")</f>
         <v/>
       </c>
-      <c r="AA12">
+      <c r="AA14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 5619-2024 FSC-klagomål.docx", "A 5619-2024")</f>
         <v/>
       </c>
-      <c r="AB12">
+      <c r="AB14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 5619-2024 FSC-klagomål mail.docx", "A 5619-2024")</f>
         <v/>
       </c>
-      <c r="AC12">
+      <c r="AC14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 5619-2024 tillsynsbegäran.docx", "A 5619-2024")</f>
         <v/>
       </c>
-      <c r="AD12">
+      <c r="AD14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 5619-2024 tillsynsbegäran mail.docx", "A 5619-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A 38084-2024</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>45545</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>HÖRBY</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J13" t="n">
-        <v>1</v>
-      </c>
-      <c r="K13" t="n">
-        <v>2</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>4</v>
-      </c>
-      <c r="T13" t="n">
-        <v>4</v>
-      </c>
-      <c r="U13" t="n">
-        <v>4</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Myskmadra
-Skogsbräsma
-Tandrot
-Grönsiska</t>
-        </is>
-      </c>
-      <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 38084-2024 artfynd.xlsx", "A 38084-2024")</f>
-        <v/>
-      </c>
-      <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 38084-2024 karta.png", "A 38084-2024")</f>
-        <v/>
-      </c>
-      <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 38084-2024 georefererad karta.tif", "A 38084-2024")</f>
-        <v/>
-      </c>
-      <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 38084-2024 FSC-klagomål.docx", "A 38084-2024")</f>
-        <v/>
-      </c>
-      <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 38084-2024 FSC-klagomål mail.docx", "A 38084-2024")</f>
-        <v/>
-      </c>
-      <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 38084-2024 tillsynsbegäran.docx", "A 38084-2024")</f>
-        <v/>
-      </c>
-      <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 38084-2024 tillsynsbegäran mail.docx", "A 38084-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>A 21774-2026</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>46150</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>HÖRBY</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>3</v>
-      </c>
-      <c r="M14" t="n">
-        <v>1</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>4</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1</v>
-      </c>
-      <c r="S14" t="n">
-        <v>4</v>
-      </c>
-      <c r="T14" t="n">
-        <v>6</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>Violettkantad guldvinge
-Granspira
-Sotnätfjäril
-Svinrot</t>
-        </is>
-      </c>
-      <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 21774-2026 artfynd.xlsx", "A 21774-2026")</f>
-        <v/>
-      </c>
-      <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 21774-2026 karta.png", "A 21774-2026")</f>
-        <v/>
-      </c>
-      <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 21774-2026 georefererad karta.tif", "A 21774-2026")</f>
-        <v/>
-      </c>
-      <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 21774-2026 FSC-klagomål.docx", "A 21774-2026")</f>
-        <v/>
-      </c>
-      <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 21774-2026 FSC-klagomål mail.docx", "A 21774-2026")</f>
-        <v/>
-      </c>
-      <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 21774-2026 tillsynsbegäran.docx", "A 21774-2026")</f>
-        <v/>
-      </c>
-      <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 21774-2026 tillsynsbegäran mail.docx", "A 21774-2026")</f>
         <v/>
       </c>
     </row>
@@ -2060,7 +2060,7 @@
         <v>45434</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
         <v>45815</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2274,7 +2274,7 @@
         <v>45799</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2381,7 +2381,7 @@
         <v>44725</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2488,7 +2488,7 @@
         <v>45677</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 44135-2024</t>
+          <t>A 824-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2592,10 +2592,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45572</v>
+        <v>46030</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2607,11 +2607,16 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I20" t="n">
-        <v>0.6</v>
+        <v>3.1</v>
       </c>
       <c r="J20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -2620,7 +2625,7 @@
         <v>1</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -2632,269 +2637,264 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
+        <v>2</v>
+      </c>
+      <c r="R20" t="n">
         <v>1</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>2</v>
       </c>
       <c r="T20" t="n">
+        <v>3</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>Hedblomster
+Skogslysing</t>
+        </is>
+      </c>
+      <c r="W20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 824-2026 artfynd.xlsx", "A 824-2026")</f>
+        <v/>
+      </c>
+      <c r="X20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 824-2026 karta.png", "A 824-2026")</f>
+        <v/>
+      </c>
+      <c r="Y20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 824-2026 georefererad karta.tif", "A 824-2026")</f>
+        <v/>
+      </c>
+      <c r="AA20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 824-2026 FSC-klagomål.docx", "A 824-2026")</f>
+        <v/>
+      </c>
+      <c r="AB20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 824-2026 FSC-klagomål mail.docx", "A 824-2026")</f>
+        <v/>
+      </c>
+      <c r="AC20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 824-2026 tillsynsbegäran.docx", "A 824-2026")</f>
+        <v/>
+      </c>
+      <c r="AD20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 824-2026 tillsynsbegäran mail.docx", "A 824-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>A 42724-2023</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="n">
+        <v>45176</v>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>HÖRBY</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>1</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1</v>
+      </c>
+      <c r="S21" t="n">
         <v>2</v>
       </c>
-      <c r="U20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
+      <c r="T21" t="n">
+        <v>4</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Grönvit nattviol</t>
+        </is>
+      </c>
+      <c r="W21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 42724-2023 artfynd.xlsx", "A 42724-2023")</f>
+        <v/>
+      </c>
+      <c r="X21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 42724-2023 karta.png", "A 42724-2023")</f>
+        <v/>
+      </c>
+      <c r="Y21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 42724-2023 georefererad karta.tif", "A 42724-2023")</f>
+        <v/>
+      </c>
+      <c r="AA21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 42724-2023 FSC-klagomål.docx", "A 42724-2023")</f>
+        <v/>
+      </c>
+      <c r="AB21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 42724-2023 FSC-klagomål mail.docx", "A 42724-2023")</f>
+        <v/>
+      </c>
+      <c r="AC21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 42724-2023 tillsynsbegäran.docx", "A 42724-2023")</f>
+        <v/>
+      </c>
+      <c r="AD21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 42724-2023 tillsynsbegäran mail.docx", "A 42724-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>A 44135-2024</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="n">
+        <v>45572</v>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>HÖRBY</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J22" t="n">
+        <v>2</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>Ladusvala
 Vanlig padda</t>
         </is>
       </c>
-      <c r="W20">
+      <c r="W22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 44135-2024 artfynd.xlsx", "A 44135-2024")</f>
         <v/>
       </c>
-      <c r="X20">
+      <c r="X22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 44135-2024 karta.png", "A 44135-2024")</f>
         <v/>
       </c>
-      <c r="Y20">
+      <c r="Y22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 44135-2024 georefererad karta.tif", "A 44135-2024")</f>
         <v/>
       </c>
-      <c r="AA20">
+      <c r="AA22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 44135-2024 FSC-klagomål.docx", "A 44135-2024")</f>
         <v/>
       </c>
-      <c r="AB20">
+      <c r="AB22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 44135-2024 FSC-klagomål mail.docx", "A 44135-2024")</f>
         <v/>
       </c>
-      <c r="AC20">
+      <c r="AC22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 44135-2024 tillsynsbegäran.docx", "A 44135-2024")</f>
         <v/>
       </c>
-      <c r="AD20">
+      <c r="AD22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 44135-2024 tillsynsbegäran mail.docx", "A 44135-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>A 824-2026</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D21" s="1" t="n">
-        <v>46030</v>
-      </c>
-      <c r="E21" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>HÖRBY</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="J21" t="n">
-        <v>1</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>1</v>
-      </c>
-      <c r="M21" t="n">
-        <v>1</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>2</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1</v>
-      </c>
-      <c r="S21" t="n">
-        <v>2</v>
-      </c>
-      <c r="T21" t="n">
-        <v>3</v>
-      </c>
-      <c r="U21" t="n">
-        <v>0</v>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>Hedblomster
-Skogslysing</t>
-        </is>
-      </c>
-      <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 824-2026 artfynd.xlsx", "A 824-2026")</f>
-        <v/>
-      </c>
-      <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 824-2026 karta.png", "A 824-2026")</f>
-        <v/>
-      </c>
-      <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 824-2026 georefererad karta.tif", "A 824-2026")</f>
-        <v/>
-      </c>
-      <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 824-2026 FSC-klagomål.docx", "A 824-2026")</f>
-        <v/>
-      </c>
-      <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 824-2026 FSC-klagomål mail.docx", "A 824-2026")</f>
-        <v/>
-      </c>
-      <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 824-2026 tillsynsbegäran.docx", "A 824-2026")</f>
-        <v/>
-      </c>
-      <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 824-2026 tillsynsbegäran mail.docx", "A 824-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>A 42724-2023</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D22" s="1" t="n">
-        <v>45176</v>
-      </c>
-      <c r="E22" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>HÖRBY</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="J22" t="n">
-        <v>1</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>1</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>1</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1</v>
-      </c>
-      <c r="S22" t="n">
-        <v>2</v>
-      </c>
-      <c r="T22" t="n">
-        <v>4</v>
-      </c>
-      <c r="U22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Grönvit nattviol</t>
-        </is>
-      </c>
-      <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 42724-2023 artfynd.xlsx", "A 42724-2023")</f>
-        <v/>
-      </c>
-      <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 42724-2023 karta.png", "A 42724-2023")</f>
-        <v/>
-      </c>
-      <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 42724-2023 georefererad karta.tif", "A 42724-2023")</f>
-        <v/>
-      </c>
-      <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 42724-2023 FSC-klagomål.docx", "A 42724-2023")</f>
-        <v/>
-      </c>
-      <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 42724-2023 FSC-klagomål mail.docx", "A 42724-2023")</f>
-        <v/>
-      </c>
-      <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 42724-2023 tillsynsbegäran.docx", "A 42724-2023")</f>
-        <v/>
-      </c>
-      <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 42724-2023 tillsynsbegäran mail.docx", "A 42724-2023")</f>
         <v/>
       </c>
     </row>
@@ -2918,7 +2918,7 @@
         <v>45317</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3007,7 +3007,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 113-2023</t>
+          <t>A 31115-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44928</v>
+        <v>45502</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3037,7 +3037,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>5.1</v>
+        <v>0.8</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -3046,10 +3046,10 @@
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
@@ -3064,7 +3064,7 @@
         <v>1</v>
       </c>
       <c r="R24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3077,42 +3077,42 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Slåttergubbe</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 113-2023 artfynd.xlsx", "A 113-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 31115-2024 artfynd.xlsx", "A 31115-2024")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 113-2023 karta.png", "A 113-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 31115-2024 karta.png", "A 31115-2024")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 113-2023 georefererad karta.tif", "A 113-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 31115-2024 georefererad karta.tif", "A 31115-2024")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 113-2023 FSC-klagomål.docx", "A 113-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 31115-2024 FSC-klagomål.docx", "A 31115-2024")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 113-2023 FSC-klagomål mail.docx", "A 113-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 31115-2024 FSC-klagomål mail.docx", "A 31115-2024")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 113-2023 tillsynsbegäran.docx", "A 113-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 31115-2024 tillsynsbegäran.docx", "A 31115-2024")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 113-2023 tillsynsbegäran mail.docx", "A 113-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 31115-2024 tillsynsbegäran mail.docx", "A 31115-2024")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 25833-2024</t>
+          <t>A 36362-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3126,10 +3126,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45463</v>
+        <v>45868</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3142,19 +3142,19 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.4</v>
+        <v>3.7</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
         <v>0</v>
@@ -3166,58 +3166,58 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
       </c>
       <c r="T25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Slåttergubbe</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 25833-2024 artfynd.xlsx", "A 25833-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 36362-2025 artfynd.xlsx", "A 36362-2025")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 25833-2024 karta.png", "A 25833-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 36362-2025 karta.png", "A 36362-2025")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 25833-2024 georefererad karta.tif", "A 25833-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 36362-2025 georefererad karta.tif", "A 36362-2025")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 25833-2024 FSC-klagomål.docx", "A 25833-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 36362-2025 FSC-klagomål.docx", "A 36362-2025")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 25833-2024 FSC-klagomål mail.docx", "A 25833-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 36362-2025 FSC-klagomål mail.docx", "A 36362-2025")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 25833-2024 tillsynsbegäran.docx", "A 25833-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 36362-2025 tillsynsbegäran.docx", "A 36362-2025")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 25833-2024 tillsynsbegäran mail.docx", "A 25833-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 36362-2025 tillsynsbegäran mail.docx", "A 36362-2025")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 25479-2025</t>
+          <t>A 47612-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3227,14 +3227,14 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45802</v>
+        <v>45203</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3247,23 +3247,23 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.7</v>
+        <v>2.4</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
         <v>1</v>
       </c>
-      <c r="L26" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" t="n">
-        <v>0</v>
-      </c>
       <c r="O26" t="n">
         <v>0</v>
       </c>
@@ -3271,10 +3271,10 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>
@@ -3287,42 +3287,42 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Lundvårlök</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 25479-2025 artfynd.xlsx", "A 25479-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 47612-2023 artfynd.xlsx", "A 47612-2023")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 25479-2025 karta.png", "A 25479-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 47612-2023 karta.png", "A 47612-2023")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 25479-2025 georefererad karta.tif", "A 25479-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 47612-2023 georefererad karta.tif", "A 47612-2023")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 25479-2025 FSC-klagomål.docx", "A 25479-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 47612-2023 FSC-klagomål.docx", "A 47612-2023")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 25479-2025 FSC-klagomål mail.docx", "A 25479-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 47612-2023 FSC-klagomål mail.docx", "A 47612-2023")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 25479-2025 tillsynsbegäran.docx", "A 25479-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 47612-2023 tillsynsbegäran.docx", "A 47612-2023")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 25479-2025 tillsynsbegäran mail.docx", "A 25479-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 47612-2023 tillsynsbegäran mail.docx", "A 47612-2023")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 47612-2023</t>
+          <t>A 40376-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3336,10 +3336,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45203</v>
+        <v>45169</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3352,22 +3352,22 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M27" t="n">
         <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3379,7 +3379,7 @@
         <v>1</v>
       </c>
       <c r="R27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
@@ -3392,42 +3392,46 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 47612-2023 artfynd.xlsx", "A 47612-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 40376-2023 artfynd.xlsx", "A 40376-2023")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 47612-2023 karta.png", "A 47612-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 40376-2023 karta.png", "A 40376-2023")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 47612-2023 georefererad karta.tif", "A 47612-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 40376-2023 georefererad karta.tif", "A 40376-2023")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 47612-2023 FSC-klagomål.docx", "A 47612-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 40376-2023 FSC-klagomål.docx", "A 40376-2023")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 47612-2023 FSC-klagomål mail.docx", "A 47612-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 40376-2023 FSC-klagomål mail.docx", "A 40376-2023")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 47612-2023 tillsynsbegäran.docx", "A 47612-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 40376-2023 tillsynsbegäran.docx", "A 40376-2023")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 47612-2023 tillsynsbegäran mail.docx", "A 47612-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 40376-2023 tillsynsbegäran mail.docx", "A 40376-2023")</f>
+        <v/>
+      </c>
+      <c r="AE27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/fåglar/A 40376-2023 prioriterade fågelarter.docx", "A 40376-2023")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 40376-2023</t>
+          <t>A 113-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3441,10 +3445,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45169</v>
+        <v>44928</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3457,19 +3461,19 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2.7</v>
+        <v>5.1</v>
       </c>
       <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
         <v>1</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" t="n">
-        <v>1</v>
-      </c>
-      <c r="M28" t="n">
-        <v>0</v>
       </c>
       <c r="N28" t="n">
         <v>0</v>
@@ -3484,7 +3488,7 @@
         <v>1</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
@@ -3497,46 +3501,42 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Slåttergubbe</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 40376-2023 artfynd.xlsx", "A 40376-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 113-2023 artfynd.xlsx", "A 113-2023")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 40376-2023 karta.png", "A 40376-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 113-2023 karta.png", "A 113-2023")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 40376-2023 georefererad karta.tif", "A 40376-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 113-2023 georefererad karta.tif", "A 113-2023")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 40376-2023 FSC-klagomål.docx", "A 40376-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 113-2023 FSC-klagomål.docx", "A 113-2023")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 40376-2023 FSC-klagomål mail.docx", "A 40376-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 113-2023 FSC-klagomål mail.docx", "A 113-2023")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 40376-2023 tillsynsbegäran.docx", "A 40376-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 113-2023 tillsynsbegäran.docx", "A 113-2023")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 40376-2023 tillsynsbegäran mail.docx", "A 40376-2023")</f>
-        <v/>
-      </c>
-      <c r="AE28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/fåglar/A 40376-2023 prioriterade fågelarter.docx", "A 40376-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 113-2023 tillsynsbegäran mail.docx", "A 113-2023")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 31115-2024</t>
+          <t>A 24823-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3550,10 +3550,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45502</v>
+        <v>46174</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3565,8 +3565,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I29" t="n">
-        <v>0.8</v>
+        <v>5.1</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3575,7 +3580,7 @@
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
         <v>0</v>
@@ -3590,7 +3595,7 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -3602,46 +3607,46 @@
         <v>1</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Gullpudra</t>
+          <t>Tandrot</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 31115-2024 artfynd.xlsx", "A 31115-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 24823-2026 artfynd.xlsx", "A 24823-2026")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 31115-2024 karta.png", "A 31115-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 24823-2026 karta.png", "A 24823-2026")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 31115-2024 georefererad karta.tif", "A 31115-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 24823-2026 georefererad karta.tif", "A 24823-2026")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 31115-2024 FSC-klagomål.docx", "A 31115-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 24823-2026 FSC-klagomål.docx", "A 24823-2026")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 31115-2024 FSC-klagomål mail.docx", "A 31115-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 24823-2026 FSC-klagomål mail.docx", "A 24823-2026")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 31115-2024 tillsynsbegäran.docx", "A 31115-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 24823-2026 tillsynsbegäran.docx", "A 24823-2026")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 31115-2024 tillsynsbegäran mail.docx", "A 31115-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 24823-2026 tillsynsbegäran mail.docx", "A 24823-2026")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 29129-2026</t>
+          <t>A 16519-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3655,10 +3660,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46202</v>
+        <v>46112</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3670,13 +3675,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I30" t="n">
-        <v>10.5</v>
+        <v>0.8</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3685,13 +3685,13 @@
         <v>0</v>
       </c>
       <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
         <v>1</v>
-      </c>
-      <c r="M30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N30" t="n">
-        <v>0</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -3703,7 +3703,7 @@
         <v>1</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S30" t="n">
         <v>1</v>
@@ -3716,42 +3716,42 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>Ekticka</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 29129-2026 artfynd.xlsx", "A 29129-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 16519-2026 artfynd.xlsx", "A 16519-2026")</f>
         <v/>
       </c>
       <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 29129-2026 karta.png", "A 29129-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 16519-2026 karta.png", "A 16519-2026")</f>
         <v/>
       </c>
       <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 29129-2026 georefererad karta.tif", "A 29129-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 16519-2026 georefererad karta.tif", "A 16519-2026")</f>
         <v/>
       </c>
       <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 29129-2026 FSC-klagomål.docx", "A 29129-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 16519-2026 FSC-klagomål.docx", "A 16519-2026")</f>
         <v/>
       </c>
       <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 29129-2026 FSC-klagomål mail.docx", "A 29129-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 16519-2026 FSC-klagomål mail.docx", "A 16519-2026")</f>
         <v/>
       </c>
       <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 29129-2026 tillsynsbegäran.docx", "A 29129-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 16519-2026 tillsynsbegäran.docx", "A 16519-2026")</f>
         <v/>
       </c>
       <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 29129-2026 tillsynsbegäran mail.docx", "A 29129-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 16519-2026 tillsynsbegäran mail.docx", "A 16519-2026")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 36362-2025</t>
+          <t>A 25833-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3765,10 +3765,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45868</v>
+        <v>45463</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3781,20 +3781,20 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>3.7</v>
+        <v>1.4</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
       </c>
       <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
         <v>1</v>
       </c>
-      <c r="L31" t="n">
-        <v>0</v>
-      </c>
-      <c r="M31" t="n">
-        <v>0</v>
-      </c>
       <c r="N31" t="n">
         <v>0</v>
       </c>
@@ -3805,58 +3805,58 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S31" t="n">
         <v>1</v>
       </c>
       <c r="T31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Slåttergubbe</t>
         </is>
       </c>
       <c r="W31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 36362-2025 artfynd.xlsx", "A 36362-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 25833-2024 artfynd.xlsx", "A 25833-2024")</f>
         <v/>
       </c>
       <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 36362-2025 karta.png", "A 36362-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 25833-2024 karta.png", "A 25833-2024")</f>
         <v/>
       </c>
       <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 36362-2025 georefererad karta.tif", "A 36362-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 25833-2024 georefererad karta.tif", "A 25833-2024")</f>
         <v/>
       </c>
       <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 36362-2025 FSC-klagomål.docx", "A 36362-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 25833-2024 FSC-klagomål.docx", "A 25833-2024")</f>
         <v/>
       </c>
       <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 36362-2025 FSC-klagomål mail.docx", "A 36362-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 25833-2024 FSC-klagomål mail.docx", "A 25833-2024")</f>
         <v/>
       </c>
       <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 36362-2025 tillsynsbegäran.docx", "A 36362-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 25833-2024 tillsynsbegäran.docx", "A 25833-2024")</f>
         <v/>
       </c>
       <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 36362-2025 tillsynsbegäran mail.docx", "A 36362-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 25833-2024 tillsynsbegäran mail.docx", "A 25833-2024")</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 21713-2025</t>
+          <t>A 31284-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3870,10 +3870,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45783</v>
+        <v>46218</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3886,7 +3886,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.8</v>
+        <v>6.8</v>
       </c>
       <c r="J32" t="n">
         <v>1</v>
@@ -3926,42 +3926,42 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="W32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 21713-2025 artfynd.xlsx", "A 21713-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 31284-2026 artfynd.xlsx", "A 31284-2026")</f>
         <v/>
       </c>
       <c r="X32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 21713-2025 karta.png", "A 21713-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 31284-2026 karta.png", "A 31284-2026")</f>
         <v/>
       </c>
       <c r="Y32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 21713-2025 georefererad karta.tif", "A 21713-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 31284-2026 georefererad karta.tif", "A 31284-2026")</f>
         <v/>
       </c>
       <c r="AA32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 21713-2025 FSC-klagomål.docx", "A 21713-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 31284-2026 FSC-klagomål.docx", "A 31284-2026")</f>
         <v/>
       </c>
       <c r="AB32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 21713-2025 FSC-klagomål mail.docx", "A 21713-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 31284-2026 FSC-klagomål mail.docx", "A 31284-2026")</f>
         <v/>
       </c>
       <c r="AC32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 21713-2025 tillsynsbegäran.docx", "A 21713-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 31284-2026 tillsynsbegäran.docx", "A 31284-2026")</f>
         <v/>
       </c>
       <c r="AD32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 21713-2025 tillsynsbegäran mail.docx", "A 21713-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 31284-2026 tillsynsbegäran mail.docx", "A 31284-2026")</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 24823-2026</t>
+          <t>A 30165-2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>46174</v>
+        <v>46206</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3990,13 +3990,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I33" t="n">
-        <v>5.1</v>
+        <v>1.4</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -4011,7 +4006,7 @@
         <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4020,10 +4015,10 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S33" t="n">
         <v>1</v>
@@ -4032,46 +4027,46 @@
         <v>1</v>
       </c>
       <c r="U33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>Tandrot</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="W33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 24823-2026 artfynd.xlsx", "A 24823-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 30165-2026 artfynd.xlsx", "A 30165-2026")</f>
         <v/>
       </c>
       <c r="X33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 24823-2026 karta.png", "A 24823-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 30165-2026 karta.png", "A 30165-2026")</f>
         <v/>
       </c>
       <c r="Y33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 24823-2026 georefererad karta.tif", "A 24823-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 30165-2026 georefererad karta.tif", "A 30165-2026")</f>
         <v/>
       </c>
       <c r="AA33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 24823-2026 FSC-klagomål.docx", "A 24823-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 30165-2026 FSC-klagomål.docx", "A 30165-2026")</f>
         <v/>
       </c>
       <c r="AB33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 24823-2026 FSC-klagomål mail.docx", "A 24823-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 30165-2026 FSC-klagomål mail.docx", "A 30165-2026")</f>
         <v/>
       </c>
       <c r="AC33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 24823-2026 tillsynsbegäran.docx", "A 24823-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 30165-2026 tillsynsbegäran.docx", "A 30165-2026")</f>
         <v/>
       </c>
       <c r="AD33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 24823-2026 tillsynsbegäran mail.docx", "A 24823-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 30165-2026 tillsynsbegäran mail.docx", "A 30165-2026")</f>
         <v/>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 16519-2026</t>
+          <t>A 29129-2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4085,10 +4080,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>46112</v>
+        <v>46202</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4100,8 +4095,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I34" t="n">
-        <v>0.8</v>
+        <v>10.5</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -4110,13 +4110,13 @@
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M34" t="n">
         <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4128,7 +4128,7 @@
         <v>1</v>
       </c>
       <c r="R34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
         <v>1</v>
@@ -4141,42 +4141,42 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Ekticka</t>
         </is>
       </c>
       <c r="W34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 16519-2026 artfynd.xlsx", "A 16519-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 29129-2026 artfynd.xlsx", "A 29129-2026")</f>
         <v/>
       </c>
       <c r="X34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 16519-2026 karta.png", "A 16519-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 29129-2026 karta.png", "A 29129-2026")</f>
         <v/>
       </c>
       <c r="Y34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 16519-2026 georefererad karta.tif", "A 16519-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 29129-2026 georefererad karta.tif", "A 29129-2026")</f>
         <v/>
       </c>
       <c r="AA34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 16519-2026 FSC-klagomål.docx", "A 16519-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 29129-2026 FSC-klagomål.docx", "A 29129-2026")</f>
         <v/>
       </c>
       <c r="AB34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 16519-2026 FSC-klagomål mail.docx", "A 16519-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 29129-2026 FSC-klagomål mail.docx", "A 29129-2026")</f>
         <v/>
       </c>
       <c r="AC34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 16519-2026 tillsynsbegäran.docx", "A 16519-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 29129-2026 tillsynsbegäran.docx", "A 29129-2026")</f>
         <v/>
       </c>
       <c r="AD34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 16519-2026 tillsynsbegäran mail.docx", "A 16519-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 29129-2026 tillsynsbegäran mail.docx", "A 29129-2026")</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 31284-2026</t>
+          <t>A 21713-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4190,10 +4190,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>46218</v>
+        <v>45783</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4206,7 +4206,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>6.8</v>
+        <v>0.8</v>
       </c>
       <c r="J35" t="n">
         <v>1</v>
@@ -4246,42 +4246,42 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="W35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 31284-2026 artfynd.xlsx", "A 31284-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 21713-2025 artfynd.xlsx", "A 21713-2025")</f>
         <v/>
       </c>
       <c r="X35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 31284-2026 karta.png", "A 31284-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 21713-2025 karta.png", "A 21713-2025")</f>
         <v/>
       </c>
       <c r="Y35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 31284-2026 georefererad karta.tif", "A 31284-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 21713-2025 georefererad karta.tif", "A 21713-2025")</f>
         <v/>
       </c>
       <c r="AA35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 31284-2026 FSC-klagomål.docx", "A 31284-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 21713-2025 FSC-klagomål.docx", "A 21713-2025")</f>
         <v/>
       </c>
       <c r="AB35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 31284-2026 FSC-klagomål mail.docx", "A 31284-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 21713-2025 FSC-klagomål mail.docx", "A 21713-2025")</f>
         <v/>
       </c>
       <c r="AC35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 31284-2026 tillsynsbegäran.docx", "A 31284-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 21713-2025 tillsynsbegäran.docx", "A 21713-2025")</f>
         <v/>
       </c>
       <c r="AD35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 31284-2026 tillsynsbegäran mail.docx", "A 31284-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 21713-2025 tillsynsbegäran mail.docx", "A 21713-2025")</f>
         <v/>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 30165-2026</t>
+          <t>A 25479-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4291,14 +4291,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>46206</v>
+        <v>45802</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4311,13 +4311,13 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
@@ -4326,7 +4326,7 @@
         <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4335,10 +4335,10 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
         <v>1</v>
@@ -4351,35 +4351,35 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Lundvårlök</t>
         </is>
       </c>
       <c r="W36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 30165-2026 artfynd.xlsx", "A 30165-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 25479-2025 artfynd.xlsx", "A 25479-2025")</f>
         <v/>
       </c>
       <c r="X36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 30165-2026 karta.png", "A 30165-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 25479-2025 karta.png", "A 25479-2025")</f>
         <v/>
       </c>
       <c r="Y36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 30165-2026 georefererad karta.tif", "A 30165-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 25479-2025 georefererad karta.tif", "A 25479-2025")</f>
         <v/>
       </c>
       <c r="AA36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 30165-2026 FSC-klagomål.docx", "A 30165-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 25479-2025 FSC-klagomål.docx", "A 25479-2025")</f>
         <v/>
       </c>
       <c r="AB36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 30165-2026 FSC-klagomål mail.docx", "A 30165-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 25479-2025 FSC-klagomål mail.docx", "A 25479-2025")</f>
         <v/>
       </c>
       <c r="AC36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 30165-2026 tillsynsbegäran.docx", "A 30165-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 25479-2025 tillsynsbegäran.docx", "A 25479-2025")</f>
         <v/>
       </c>
       <c r="AD36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 30165-2026 tillsynsbegäran mail.docx", "A 30165-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 25479-2025 tillsynsbegäran mail.docx", "A 25479-2025")</f>
         <v/>
       </c>
     </row>
@@ -4403,7 +4403,7 @@
         <v>45089</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4508,7 +4508,7 @@
         <v>44999</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4613,7 +4613,7 @@
         <v>44509</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4686,7 +4686,7 @@
         <v>44663</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4759,7 +4759,7 @@
         <v>44509</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4832,7 +4832,7 @@
         <v>44697</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4905,7 +4905,7 @@
         <v>44510</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4978,7 +4978,7 @@
         <v>44834</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5051,7 +5051,7 @@
         <v>44771</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5124,7 +5124,7 @@
         <v>44466</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5197,7 +5197,7 @@
         <v>44789</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5253,7 +5253,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 2816-2025</t>
+          <t>A 25850-2022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5263,14 +5263,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45677</v>
+        <v>44733</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5283,7 +5283,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5326,7 +5326,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 16101-2025</t>
+          <t>A 2979-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5340,10 +5340,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45750</v>
+        <v>45315</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5355,8 +5355,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I49" t="n">
-        <v>0.5</v>
+        <v>4.7</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5399,7 +5404,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 2170-2025</t>
+          <t>A 24670-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5409,14 +5414,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45673</v>
+        <v>45460</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5429,7 +5434,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>3.6</v>
+        <v>0.2</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5472,7 +5477,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 34422-2024</t>
+          <t>A 18609-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5482,14 +5487,14 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45525</v>
+        <v>45763</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5502,7 +5507,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5545,7 +5550,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 11943-2025</t>
+          <t>A 3471-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5559,10 +5564,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45728</v>
+        <v>45680</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5575,7 +5580,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.2</v>
+        <v>3.7</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5618,7 +5623,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 44613-2023</t>
+          <t>A 33359-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5632,10 +5637,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45189</v>
+        <v>45128</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5647,13 +5652,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I53" t="n">
-        <v>3.8</v>
+        <v>0.9</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5696,7 +5696,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 43937-2023</t>
+          <t>A 37757-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5710,10 +5710,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45187</v>
+        <v>45541</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5726,7 +5726,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>2.6</v>
+        <v>0.7</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5769,7 +5769,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 43939-2023</t>
+          <t>A 31596-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5783,10 +5783,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45187</v>
+        <v>45117</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5799,7 +5799,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5842,7 +5842,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 67426-2021</t>
+          <t>A 44613-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5856,10 +5856,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44523</v>
+        <v>45189</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5871,8 +5871,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I56" t="n">
-        <v>0.6</v>
+        <v>3.8</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5915,7 +5920,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 3534-2025</t>
+          <t>A 2816-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5925,14 +5930,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45680</v>
+        <v>45677</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5944,13 +5949,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I57" t="n">
-        <v>4.8</v>
+        <v>2</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5993,7 +5993,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 25850-2022</t>
+          <t>A 28785-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6003,14 +6003,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44733</v>
+        <v>45104</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6023,7 +6023,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.8</v>
+        <v>2.1</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -6066,7 +6066,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 43380-2022</t>
+          <t>A 16101-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6080,10 +6080,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44834</v>
+        <v>45750</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6096,7 +6096,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.7</v>
+        <v>0.5</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6139,7 +6139,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 7831-2025</t>
+          <t>A 58360-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6153,10 +6153,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45706</v>
+        <v>45250</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6169,7 +6169,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.6</v>
+        <v>2.5</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6212,7 +6212,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 47609-2023</t>
+          <t>A 4756-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6226,10 +6226,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45203</v>
+        <v>45688</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6242,7 +6242,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>2.4</v>
+        <v>0.9</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6285,7 +6285,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 18735-2023</t>
+          <t>A 48397-2022</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6299,10 +6299,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45043</v>
+        <v>44858</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6315,7 +6315,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6358,7 +6358,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 9974-2024</t>
+          <t>A 6886-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6372,10 +6372,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45363</v>
+        <v>45342</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6387,8 +6387,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I63" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6431,7 +6436,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 15970-2024</t>
+          <t>A 33358-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6445,10 +6450,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45405</v>
+        <v>45128</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6461,7 +6466,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.8</v>
+        <v>0.4</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6504,7 +6509,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 5163-2024</t>
+          <t>A 47641-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6518,10 +6523,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45330</v>
+        <v>45203</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6533,13 +6538,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I65" t="n">
-        <v>7.1</v>
+        <v>4.8</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6582,7 +6582,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 28493-2023</t>
+          <t>A 39298-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6596,10 +6596,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45103</v>
+        <v>45166</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6612,7 +6612,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.8</v>
+        <v>4.6</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6655,7 +6655,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 36840-2024</t>
+          <t>A 39507-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6669,10 +6669,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45538</v>
+        <v>45551</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6690,7 +6690,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.9</v>
+        <v>0.3</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6733,7 +6733,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 60913-2023</t>
+          <t>A 3346-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6747,10 +6747,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45261</v>
+        <v>45317</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6763,7 +6763,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6806,7 +6806,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 37724-2022</t>
+          <t>A 788-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6820,10 +6820,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44810</v>
+        <v>45300</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6836,7 +6836,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6879,7 +6879,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 37728-2022</t>
+          <t>A 9974-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6893,10 +6893,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44810</v>
+        <v>45363</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6909,7 +6909,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6952,7 +6952,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 8084-2022</t>
+          <t>A 11943-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6966,10 +6966,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44608</v>
+        <v>45728</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6982,7 +6982,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -7025,7 +7025,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 56818-2022</t>
+          <t>A 42715-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7039,10 +7039,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44894</v>
+        <v>45176</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7055,7 +7055,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7098,7 +7098,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 16665-2025</t>
+          <t>A 28918-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7112,10 +7112,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45754</v>
+        <v>45104</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7128,7 +7128,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7171,7 +7171,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 33359-2023</t>
+          <t>A 2747-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7185,10 +7185,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45128</v>
+        <v>44944</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7200,8 +7200,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I74" t="n">
-        <v>0.9</v>
+        <v>4.6</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7244,7 +7249,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 28625-2023</t>
+          <t>A 43932-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7258,10 +7263,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45103</v>
+        <v>45187</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7274,7 +7279,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>4.8</v>
+        <v>3</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7317,7 +7322,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 54894-2023</t>
+          <t>A 43935-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7331,10 +7336,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45236</v>
+        <v>45187</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7347,7 +7352,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0.6</v>
+        <v>2.9</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7390,7 +7395,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 36689-2024</t>
+          <t>A 48427-2022</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7400,14 +7405,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45537</v>
+        <v>44858</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7425,7 +7430,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>9.5</v>
+        <v>0.5</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7468,7 +7473,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 38080-2024</t>
+          <t>A 8084-2022</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7482,10 +7487,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45545</v>
+        <v>44608</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7498,7 +7503,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7541,7 +7546,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 13804-2024</t>
+          <t>A 43828-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7555,10 +7560,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45391</v>
+        <v>45572</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7571,7 +7576,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7614,7 +7619,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 28746-2024</t>
+          <t>A 13225-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7628,10 +7633,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45478</v>
+        <v>45386</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7644,7 +7649,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.9</v>
+        <v>0.7</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7687,7 +7692,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 37082-2023</t>
+          <t>A 13226-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7697,14 +7702,14 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45155</v>
+        <v>45386</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7717,7 +7722,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7760,7 +7765,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 43711-2024</t>
+          <t>A 47552-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7770,14 +7775,14 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45569</v>
+        <v>45203</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7790,7 +7795,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>3.4</v>
+        <v>1.3</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7833,7 +7838,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 34154-2025</t>
+          <t>A 36355-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7847,10 +7852,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45845</v>
+        <v>45868</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7863,7 +7868,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>5</v>
+        <v>3.6</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7906,7 +7911,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 2752-2023</t>
+          <t>A 25552-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7920,10 +7925,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>44944</v>
+        <v>45803</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7935,13 +7940,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I84" t="n">
-        <v>0.6</v>
+        <v>2</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7984,7 +7984,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 6886-2024</t>
+          <t>A 2752-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7998,10 +7998,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45342</v>
+        <v>44944</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8019,7 +8019,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -8062,7 +8062,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 1106-2023</t>
+          <t>A 38147-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -8076,10 +8076,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44935</v>
+        <v>45882</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8092,7 +8092,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8135,7 +8135,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 28785-2023</t>
+          <t>A 37082-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8149,10 +8149,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45104</v>
+        <v>45155</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8165,7 +8165,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>2.1</v>
+        <v>0.5</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8208,7 +8208,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 23484-2025</t>
+          <t>A 54431-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8222,10 +8222,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45792</v>
+        <v>45226</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8238,7 +8238,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8281,7 +8281,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 13225-2024</t>
+          <t>A 28625-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8295,10 +8295,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45386</v>
+        <v>45103</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8311,7 +8311,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>0.7</v>
+        <v>4.8</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8354,7 +8354,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 13226-2024</t>
+          <t>A 38080-2024</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8368,10 +8368,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45386</v>
+        <v>45545</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8427,7 +8427,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 48397-2022</t>
+          <t>A 34154-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8441,10 +8441,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>44858</v>
+        <v>45845</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8457,7 +8457,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>1.7</v>
+        <v>5</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8500,7 +8500,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 17073-2023</t>
+          <t>A 13633-2024</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8514,10 +8514,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45034</v>
+        <v>45390</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8530,7 +8530,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8573,7 +8573,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 2979-2024</t>
+          <t>A 44816-2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8587,10 +8587,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45315</v>
+        <v>45190</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8602,13 +8602,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I93" t="n">
-        <v>4.7</v>
+        <v>1</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8651,7 +8646,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 15998-2024</t>
+          <t>A 28493-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8665,10 +8660,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45405</v>
+        <v>45103</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8681,7 +8676,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8724,7 +8719,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 16001-2024</t>
+          <t>A 43879-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8738,10 +8733,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45405</v>
+        <v>45187</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8753,8 +8748,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I95" t="n">
-        <v>0.2</v>
+        <v>1.1</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8797,7 +8797,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 31596-2023</t>
+          <t>A 47609-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8811,10 +8811,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45117</v>
+        <v>45203</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8827,7 +8827,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>0.5</v>
+        <v>2.4</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8870,7 +8870,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 43828-2024</t>
+          <t>A 65073-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8884,10 +8884,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45572</v>
+        <v>45287</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8900,7 +8900,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>0.9</v>
+        <v>1.7</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8960,7 +8960,7 @@
         <v>45845</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9016,7 +9016,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 54184-2024</t>
+          <t>A 43882-2023</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -9030,10 +9030,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45616</v>
+        <v>45187</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9045,8 +9045,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I99" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -9089,7 +9094,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 28550-2025</t>
+          <t>A 67426-2021</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -9103,10 +9108,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45818</v>
+        <v>44523</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9119,7 +9124,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>5</v>
+        <v>0.6</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -9162,7 +9167,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 43932-2023</t>
+          <t>A 3239-2023</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9176,10 +9181,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45187</v>
+        <v>44946</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9192,7 +9197,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>3</v>
+        <v>0.4</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9235,7 +9240,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 43935-2023</t>
+          <t>A 51757-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9245,14 +9250,14 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45187</v>
+        <v>45951</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9264,8 +9269,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I102" t="n">
-        <v>2.9</v>
+        <v>1.3</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9308,7 +9318,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 9612-2025</t>
+          <t>A 60963-2023</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9322,10 +9332,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45715</v>
+        <v>45261</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9381,7 +9391,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 18609-2025</t>
+          <t>A 5079-2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9395,10 +9405,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45763</v>
+        <v>46049</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9411,7 +9421,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9454,7 +9464,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 20403-2024</t>
+          <t>A 43685-2022</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9464,14 +9474,14 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45435</v>
+        <v>44837</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9484,7 +9494,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9527,7 +9537,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 51757-2025</t>
+          <t>A 52930-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9537,14 +9547,14 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45951</v>
+        <v>45957</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9562,7 +9572,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9605,7 +9615,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 56750-2023</t>
+          <t>A 52929-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9619,10 +9629,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45238</v>
+        <v>45957</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9634,8 +9644,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I107" t="n">
-        <v>0.8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9678,7 +9693,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 3040-2024</t>
+          <t>A 55265-2023</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9692,10 +9707,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45316</v>
+        <v>45237</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9708,7 +9723,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>4</v>
+        <v>1.2</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9751,7 +9766,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 42715-2023</t>
+          <t>A 5163-2024</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9765,10 +9780,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45176</v>
+        <v>45330</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9780,8 +9795,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I109" t="n">
-        <v>0.5</v>
+        <v>7.1</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9824,7 +9844,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 44816-2023</t>
+          <t>A 54765-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9838,10 +9858,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45190</v>
+        <v>45966</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9854,7 +9874,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>1</v>
+        <v>2.6</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9897,7 +9917,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 13633-2024</t>
+          <t>A 55304-2025</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9907,14 +9927,14 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45390</v>
+        <v>45970</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9927,7 +9947,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>1.1</v>
+        <v>0.4</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9970,7 +9990,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 47552-2023</t>
+          <t>A 55306-2025</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9980,14 +10000,14 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45203</v>
+        <v>45970</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10000,7 +10020,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>1.3</v>
+        <v>0.3</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -10043,7 +10063,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 52929-2025</t>
+          <t>A 40994-2025</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -10057,10 +10077,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45957</v>
+        <v>45898</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10072,13 +10092,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I113" t="n">
-        <v>8.300000000000001</v>
+        <v>5.6</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -10121,7 +10136,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 52930-2025</t>
+          <t>A 18603-2025</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -10135,10 +10150,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45957</v>
+        <v>45763</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10150,13 +10165,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H114" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I114" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -10199,7 +10209,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 54431-2023</t>
+          <t>A 57269-2025</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10213,10 +10223,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45226</v>
+        <v>45979</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10228,8 +10238,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I115" t="n">
-        <v>3.2</v>
+        <v>5.5</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10272,7 +10287,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 19777-2023</t>
+          <t>A 3534-2025</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10286,10 +10301,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45051</v>
+        <v>45680</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10301,8 +10316,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I116" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10345,7 +10365,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 58641-2023</t>
+          <t>A 20595-2024</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10355,14 +10375,14 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45251</v>
+        <v>45436</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10374,8 +10394,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I117" t="n">
-        <v>1.2</v>
+        <v>3.5</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10418,7 +10443,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 54765-2025</t>
+          <t>A 59308-2025</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10432,10 +10457,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45966</v>
+        <v>45989</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10448,7 +10473,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>2.6</v>
+        <v>1.2</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10491,7 +10516,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 43879-2023</t>
+          <t>A 43937-2023</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10508,7 +10533,7 @@
         <v>45187</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10520,13 +10545,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I119" t="n">
-        <v>1.1</v>
+        <v>2.6</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10569,7 +10589,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 3471-2025</t>
+          <t>A 43939-2023</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10583,10 +10603,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45680</v>
+        <v>45187</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10599,7 +10619,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>3.7</v>
+        <v>0.6</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10642,7 +10662,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 18603-2025</t>
+          <t>A 28501-2023</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10656,10 +10676,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45763</v>
+        <v>45103</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10672,7 +10692,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>0.5</v>
+        <v>3.6</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10715,7 +10735,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 49726-2023</t>
+          <t>A 28527-2023</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10729,10 +10749,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45208</v>
+        <v>45103</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10745,7 +10765,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10788,7 +10808,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 3346-2024</t>
+          <t>A 54894-2023</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10802,10 +10822,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45317</v>
+        <v>45236</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10818,7 +10838,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10861,7 +10881,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 40994-2025</t>
+          <t>A 37276-2024</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10875,10 +10895,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45898</v>
+        <v>45540</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10891,7 +10911,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>5.6</v>
+        <v>1.6</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10934,7 +10954,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 28501-2023</t>
+          <t>A 62277-2025</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10948,10 +10968,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45103</v>
+        <v>46006</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10964,7 +10984,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>3.6</v>
+        <v>2.4</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -11007,7 +11027,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 55304-2025</t>
+          <t>A 4597-2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -11017,14 +11037,14 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45970</v>
+        <v>46048</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11037,7 +11057,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>0.4</v>
+        <v>1.3</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -11080,7 +11100,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 55306-2025</t>
+          <t>A 36689-2024</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -11094,10 +11114,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45970</v>
+        <v>45537</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11109,8 +11129,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I127" t="n">
-        <v>0.3</v>
+        <v>9.5</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -11153,7 +11178,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 29244-2025</t>
+          <t>A 554-2026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -11167,10 +11192,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45824</v>
+        <v>46029</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11183,7 +11208,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -11226,7 +11251,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 33873-2024</t>
+          <t>A 826-2026</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11240,10 +11265,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45521</v>
+        <v>46030</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11255,8 +11280,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I129" t="n">
-        <v>3.5</v>
+        <v>0.3</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11299,7 +11329,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 788-2024</t>
+          <t>A 829-2026</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11313,10 +11343,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45300</v>
+        <v>46030</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11328,8 +11358,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I130" t="n">
-        <v>0.6</v>
+        <v>6.9</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11372,7 +11407,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 29354-2025</t>
+          <t>A 821-2026</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11386,10 +11421,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45824</v>
+        <v>46030</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11401,8 +11436,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I131" t="n">
-        <v>0.8</v>
+        <v>4.3</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11445,7 +11485,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 57269-2025</t>
+          <t>A 1989-2026</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11459,10 +11499,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45979</v>
+        <v>46035</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11474,13 +11514,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I132" t="n">
-        <v>5.5</v>
+        <v>2.5</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11523,7 +11558,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 58360-2023</t>
+          <t>A 31522-2022</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11537,10 +11572,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45250</v>
+        <v>44775</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11553,7 +11588,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11596,7 +11631,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 39298-2023</t>
+          <t>A 54184-2024</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11610,10 +11645,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45166</v>
+        <v>45616</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11626,7 +11661,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>4.6</v>
+        <v>0.5</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11669,7 +11704,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 29219-2023</t>
+          <t>A 3013-2026</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11683,10 +11718,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45105</v>
+        <v>46038</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11742,7 +11777,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 3542-2025</t>
+          <t>A 60913-2023</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11756,10 +11791,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45680</v>
+        <v>45261</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11771,13 +11806,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H136" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I136" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11820,7 +11850,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 50715-2024</t>
+          <t>A 44073-2024</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11834,10 +11864,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45602</v>
+        <v>45572</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11850,7 +11880,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11893,7 +11923,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 59308-2025</t>
+          <t>A 11941-2025</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11907,10 +11937,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45989</v>
+        <v>45728</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11923,7 +11953,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11966,7 +11996,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 47637-2023</t>
+          <t>A 43380-2022</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11980,10 +12010,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45203</v>
+        <v>44834</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11996,7 +12026,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -12039,7 +12069,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 826-2026</t>
+          <t>A 5374-2026</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -12053,10 +12083,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>46030</v>
+        <v>46050</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12068,13 +12098,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H140" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I140" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -12117,7 +12142,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 829-2026</t>
+          <t>A 20403-2024</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -12131,10 +12156,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>46030</v>
+        <v>45435</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12146,13 +12171,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H141" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I141" t="n">
-        <v>6.9</v>
+        <v>0.9</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -12195,7 +12215,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 821-2026</t>
+          <t>A 1106-2023</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -12209,10 +12229,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>46030</v>
+        <v>44935</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12224,13 +12244,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H142" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I142" t="n">
-        <v>4.3</v>
+        <v>1.2</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -12273,7 +12288,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 554-2026</t>
+          <t>A 8310-2026</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12287,10 +12302,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>46029</v>
+        <v>46064</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12303,7 +12318,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -12346,7 +12361,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 2981-2024</t>
+          <t>A 8260-2026</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12360,10 +12375,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45315</v>
+        <v>46064</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12375,13 +12390,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H144" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I144" t="n">
-        <v>6.4</v>
+        <v>3.3</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -12424,7 +12434,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 62277-2025</t>
+          <t>A 8259-2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12438,10 +12448,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>46006</v>
+        <v>46064</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12454,7 +12464,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12497,7 +12507,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 1989-2026</t>
+          <t>A 49726-2023</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12511,10 +12521,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>46035</v>
+        <v>45208</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12527,7 +12537,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>2.5</v>
+        <v>1.3</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12570,7 +12580,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 3013-2026</t>
+          <t>A 36840-2024</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12584,10 +12594,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>46038</v>
+        <v>45538</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12599,8 +12609,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I147" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12643,7 +12658,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 32459-2025</t>
+          <t>A 4590-2026</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12657,10 +12672,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45838</v>
+        <v>46048</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12673,7 +12688,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12716,7 +12731,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 24670-2024</t>
+          <t>A 24724-2024</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12733,7 +12748,7 @@
         <v>45460</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12746,7 +12761,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>0.2</v>
+        <v>1.4</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12789,7 +12804,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 32958-2025</t>
+          <t>A 10731-2026</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12803,10 +12818,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45839</v>
+        <v>46078</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12818,8 +12833,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I150" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12862,7 +12882,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 6081-2023</t>
+          <t>A 58641-2023</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12872,14 +12892,14 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>44959</v>
+        <v>45251</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12892,7 +12912,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12935,7 +12955,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 5374-2026</t>
+          <t>A 6350-2026</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12949,10 +12969,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12965,7 +12985,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>0.5</v>
+        <v>2.4</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -13008,7 +13028,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 31114-2024</t>
+          <t>A 18369-2025</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -13022,10 +13042,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45502</v>
+        <v>45762</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13038,7 +13058,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>0.6</v>
+        <v>2.2</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -13081,7 +13101,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 11941-2025</t>
+          <t>A 3040-2024</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -13095,10 +13115,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45728</v>
+        <v>45316</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13111,7 +13131,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>0.6</v>
+        <v>4</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -13154,7 +13174,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 38936-2026</t>
+          <t>A 14307-2026</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -13168,10 +13188,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>46286</v>
+        <v>46099</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13183,13 +13203,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H155" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I155" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -13232,7 +13247,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 38948-2026</t>
+          <t>A 3177-2026</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -13242,14 +13257,14 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>46286</v>
+        <v>46041</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13261,13 +13276,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H156" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I156" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -13310,7 +13320,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 38906-2026</t>
+          <t>A 15970-2024</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -13324,10 +13334,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>46286</v>
+        <v>45405</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13339,13 +13349,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H157" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I157" t="n">
-        <v>3.1</v>
+        <v>1.8</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -13388,7 +13393,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 37300-2026</t>
+          <t>A 18735-2023</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -13402,10 +13407,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>46274</v>
+        <v>45043</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13418,7 +13423,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -13461,7 +13466,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 20047-2026</t>
+          <t>A 3470-2026</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13475,10 +13480,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>46136</v>
+        <v>46042</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13491,7 +13496,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -13534,7 +13539,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 8310-2026</t>
+          <t>A 3513-2026</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -13548,10 +13553,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>46064</v>
+        <v>46042</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13564,7 +13569,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13607,7 +13612,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 8260-2026</t>
+          <t>A 3520-2026</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13621,10 +13626,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>46064</v>
+        <v>46042</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13637,7 +13642,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>3.3</v>
+        <v>0.8</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13680,7 +13685,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 8259-2026</t>
+          <t>A 6081-2023</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13694,10 +13699,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>46064</v>
+        <v>44959</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13710,7 +13715,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>3.1</v>
+        <v>0.4</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13753,7 +13758,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 38684-2022</t>
+          <t>A 29219-2023</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13767,10 +13772,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>44814</v>
+        <v>45105</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13783,7 +13788,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>2.5</v>
+        <v>0.7</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13826,7 +13831,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 37757-2024</t>
+          <t>A 59284-2025</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13840,10 +13845,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45541</v>
+        <v>45988</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13856,7 +13861,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13899,7 +13904,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 38824-2026</t>
+          <t>A 9850-2026</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13913,10 +13918,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>46286</v>
+        <v>46072</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13928,13 +13933,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H165" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I165" t="n">
-        <v>11.2</v>
+        <v>2.2</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13977,7 +13977,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 38730-2026</t>
+          <t>A 56818-2022</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13991,10 +13991,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>46285</v>
+        <v>44894</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14007,7 +14007,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>0.4</v>
+        <v>1.8</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -14050,7 +14050,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 25183-2023</t>
+          <t>A 10500-2026</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -14064,10 +14064,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45079</v>
+        <v>46076</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14080,7 +14080,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -14123,7 +14123,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 10731-2026</t>
+          <t>A 7402-2026</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -14137,10 +14137,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>46078</v>
+        <v>46059</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14152,13 +14152,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H168" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I168" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -14201,7 +14196,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 44073-2024</t>
+          <t>A 34422-2024</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -14211,14 +14206,14 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>45572</v>
+        <v>45525</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14231,7 +14226,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -14274,7 +14269,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 37276-2024</t>
+          <t>A 16518-2026</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -14288,10 +14283,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45540</v>
+        <v>46112</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14304,7 +14299,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -14347,7 +14342,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 20595-2024</t>
+          <t>A 7831-2025</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -14361,10 +14356,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45436</v>
+        <v>45706</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14376,13 +14371,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H171" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I171" t="n">
-        <v>3.5</v>
+        <v>0.6</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -14425,7 +14415,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 10524-2026</t>
+          <t>A 56750-2023</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -14439,10 +14429,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>46076</v>
+        <v>45238</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14455,7 +14445,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -14498,7 +14488,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 37756-2024</t>
+          <t>A 29138-2026</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -14508,14 +14498,14 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45541</v>
+        <v>46202</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14527,8 +14517,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I173" t="n">
-        <v>3.2</v>
+        <v>4.2</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -14571,7 +14566,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 119-2023</t>
+          <t>A 29124-2026</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14585,10 +14580,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>44928</v>
+        <v>46202</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14601,7 +14596,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>0.8</v>
+        <v>2.9</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14644,7 +14639,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 43685-2022</t>
+          <t>A 29135-2026</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14654,14 +14649,14 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>44837</v>
+        <v>46202</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14673,8 +14668,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I175" t="n">
-        <v>1.3</v>
+        <v>4.7</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14717,7 +14717,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 24724-2024</t>
+          <t>A 29137-2026</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14727,14 +14727,14 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45460</v>
+        <v>46202</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14746,8 +14746,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I176" t="n">
-        <v>1.4</v>
+        <v>7.8</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14790,7 +14795,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 14307-2026</t>
+          <t>A 17073-2023</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14804,10 +14809,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>46099</v>
+        <v>45034</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14820,7 +14825,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14863,7 +14868,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 3520-2026</t>
+          <t>A 19420-2022</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14877,10 +14882,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>46042</v>
+        <v>44693</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14893,7 +14898,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14936,7 +14941,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 3470-2026</t>
+          <t>A 119-2023</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14950,10 +14955,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>46042</v>
+        <v>44928</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14966,7 +14971,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -15009,7 +15014,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 6558-2025</t>
+          <t>A 50715-2024</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -15019,14 +15024,14 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>45699</v>
+        <v>45602</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15038,13 +15043,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H180" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I180" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -15087,7 +15087,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 9850-2026</t>
+          <t>A 37724-2022</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -15101,10 +15101,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>46072</v>
+        <v>44810</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15117,7 +15117,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>2.2</v>
+        <v>1.2</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -15160,7 +15160,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 3513-2026</t>
+          <t>A 37728-2022</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -15174,10 +15174,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>46042</v>
+        <v>44810</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15190,7 +15190,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -15233,7 +15233,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 2747-2023</t>
+          <t>A 47637-2023</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -15247,10 +15247,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>44944</v>
+        <v>45203</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15262,13 +15262,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H183" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I183" t="n">
-        <v>4.6</v>
+        <v>2</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -15311,7 +15306,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 31522-2022</t>
+          <t>A 33873-2024</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -15325,10 +15320,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>44775</v>
+        <v>45521</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15341,7 +15336,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>1.8</v>
+        <v>3.5</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -15384,7 +15379,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 36355-2025</t>
+          <t>A 23606-2026</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -15394,14 +15389,14 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>45868</v>
+        <v>46162</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15414,7 +15409,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>3.6</v>
+        <v>9.4</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -15457,7 +15452,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 55265-2023</t>
+          <t>A 34737-2026</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -15471,10 +15466,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>45237</v>
+        <v>46258</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15487,7 +15482,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -15530,7 +15525,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 28918-2023</t>
+          <t>A 34740-2026</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -15544,10 +15539,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>45104</v>
+        <v>46258</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15560,7 +15555,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -15603,7 +15598,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 3239-2023</t>
+          <t>A 3542-2025</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15617,10 +15612,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>44946</v>
+        <v>45680</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15632,8 +15627,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I188" t="n">
-        <v>0.4</v>
+        <v>1.4</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15693,7 +15693,7 @@
         <v>45386</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15749,7 +15749,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 48427-2022</t>
+          <t>A 15998-2024</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15763,10 +15763,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>44858</v>
+        <v>45405</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15778,13 +15778,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H190" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I190" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15827,7 +15822,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 7402-2026</t>
+          <t>A 16001-2024</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15841,10 +15836,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>46059</v>
+        <v>45405</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15857,7 +15852,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>4.7</v>
+        <v>0.2</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15900,7 +15895,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 4756-2025</t>
+          <t>A 31114-2024</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15914,10 +15909,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>45688</v>
+        <v>45502</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15930,7 +15925,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15973,7 +15968,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 33358-2023</t>
+          <t>A 13804-2024</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15987,10 +15982,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>45128</v>
+        <v>45391</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16003,7 +15998,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -16046,7 +16041,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 25552-2025</t>
+          <t>A 30934-2026</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -16060,10 +16055,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>45803</v>
+        <v>46213</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16076,7 +16071,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>2</v>
+        <v>1.1</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -16119,7 +16114,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 39507-2024</t>
+          <t>A 55307-2025</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -16133,10 +16128,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>45551</v>
+        <v>45970</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16148,13 +16143,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H195" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I195" t="n">
-        <v>0.3</v>
+        <v>2.5</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -16197,7 +16187,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 41940-2022</t>
+          <t>A 31286-2026</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -16211,10 +16201,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>44833</v>
+        <v>46218</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16227,7 +16217,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -16270,7 +16260,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 43882-2023</t>
+          <t>A 19777-2023</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -16284,10 +16274,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>45187</v>
+        <v>45051</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16299,13 +16289,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H197" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I197" t="n">
-        <v>1.2</v>
+        <v>4.3</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -16348,7 +16333,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 28527-2023</t>
+          <t>A 28746-2024</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -16362,10 +16347,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>45103</v>
+        <v>45478</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16378,7 +16363,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -16421,7 +16406,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 38147-2025</t>
+          <t>A 57017-2025</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -16435,10 +16420,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>45882</v>
+        <v>45978</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16451,7 +16436,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>1.6</v>
+        <v>5.5</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -16494,7 +16479,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 5079-2026</t>
+          <t>A 6558-2025</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -16504,14 +16489,14 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>46049</v>
+        <v>45699</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16523,8 +16508,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I200" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -16567,7 +16557,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 19420-2022</t>
+          <t>A 25183-2023</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -16581,10 +16571,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>44693</v>
+        <v>45079</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16597,7 +16587,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -16640,7 +16630,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 65073-2023</t>
+          <t>A 41940-2022</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -16654,10 +16644,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>45287</v>
+        <v>44833</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16670,7 +16660,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>1.7</v>
+        <v>0.7</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16713,7 +16703,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 47641-2023</t>
+          <t>A 38073-2026</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16727,10 +16717,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>45203</v>
+        <v>46280</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16743,7 +16733,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>4.8</v>
+        <v>2.3</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -16786,7 +16776,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 60963-2023</t>
+          <t>A 38684-2022</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -16800,10 +16790,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>45261</v>
+        <v>44814</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16816,7 +16806,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>1.2</v>
+        <v>2.5</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16859,7 +16849,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 52310-2023</t>
+          <t>A 37300-2026</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16873,10 +16863,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>45224</v>
+        <v>46274</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16889,7 +16879,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>3.5</v>
+        <v>0.2</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16932,7 +16922,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 4597-2026</t>
+          <t>A 52310-2023</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16946,10 +16936,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>46048</v>
+        <v>45224</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16962,7 +16952,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>1.3</v>
+        <v>3.5</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -17005,7 +16995,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 4590-2026</t>
+          <t>A 38936-2026</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -17019,10 +17009,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>46048</v>
+        <v>46286</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17034,8 +17024,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I207" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -17078,7 +17073,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 6350-2026</t>
+          <t>A 38948-2026</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -17092,10 +17087,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>46051</v>
+        <v>46286</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17107,8 +17102,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I208" t="n">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -17151,7 +17151,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 18369-2025</t>
+          <t>A 10524-2026</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -17165,10 +17165,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>45762</v>
+        <v>46076</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17181,7 +17181,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>2.2</v>
+        <v>1.6</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -17224,7 +17224,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 3177-2026</t>
+          <t>A 20047-2026</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -17234,14 +17234,14 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>46041</v>
+        <v>46136</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17254,7 +17254,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -17297,7 +17297,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 59284-2025</t>
+          <t>A 38824-2026</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -17311,10 +17311,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>45988</v>
+        <v>46286</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17326,8 +17326,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I211" t="n">
-        <v>1.5</v>
+        <v>11.2</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -17370,7 +17375,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 10500-2026</t>
+          <t>A 2170-2025</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -17384,10 +17389,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>46076</v>
+        <v>45673</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17400,7 +17405,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>1.1</v>
+        <v>3.6</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -17443,7 +17448,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 16518-2026</t>
+          <t>A 38906-2026</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -17457,10 +17462,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>46112</v>
+        <v>46286</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17472,8 +17477,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I213" t="n">
-        <v>0.8</v>
+        <v>3.1</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -17516,7 +17526,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 29138-2026</t>
+          <t>A 38730-2026</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -17526,14 +17536,14 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>46202</v>
+        <v>46285</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17545,13 +17555,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H214" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I214" t="n">
-        <v>4.2</v>
+        <v>0.4</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -17594,7 +17599,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 29135-2026</t>
+          <t>A 16665-2025</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -17604,14 +17609,14 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>46202</v>
+        <v>45754</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17623,13 +17628,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H215" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I215" t="n">
-        <v>4.7</v>
+        <v>2.4</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -17672,7 +17672,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 29137-2026</t>
+          <t>A 39481-2026</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -17682,14 +17682,14 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>46202</v>
+        <v>46289</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17701,13 +17701,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H216" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I216" t="n">
-        <v>7.8</v>
+        <v>2.3</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -17750,7 +17745,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 29124-2026</t>
+          <t>A 43711-2024</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -17760,14 +17755,14 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>46202</v>
+        <v>45569</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17780,7 +17775,7 @@
         </is>
       </c>
       <c r="I217" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -17823,7 +17818,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 30934-2026</t>
+          <t>A 23484-2025</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -17837,10 +17832,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>46213</v>
+        <v>45792</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17853,7 +17848,7 @@
         </is>
       </c>
       <c r="I218" t="n">
-        <v>1.1</v>
+        <v>3.5</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -17896,7 +17891,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 34737-2026</t>
+          <t>A 28550-2025</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -17910,10 +17905,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>46258</v>
+        <v>45818</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17926,7 +17921,7 @@
         </is>
       </c>
       <c r="I219" t="n">
-        <v>0.7</v>
+        <v>5</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -17969,7 +17964,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 34740-2026</t>
+          <t>A 9612-2025</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -17983,10 +17978,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>46258</v>
+        <v>45715</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17999,7 +17994,7 @@
         </is>
       </c>
       <c r="I220" t="n">
-        <v>2.1</v>
+        <v>1.2</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -18042,7 +18037,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 23606-2026</t>
+          <t>A 29244-2025</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -18052,14 +18047,14 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>46162</v>
+        <v>45824</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18072,7 +18067,7 @@
         </is>
       </c>
       <c r="I221" t="n">
-        <v>9.4</v>
+        <v>0.7</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -18115,7 +18110,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 31286-2026</t>
+          <t>A 29354-2025</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -18129,10 +18124,10 @@
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>46218</v>
+        <v>45824</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18145,7 +18140,7 @@
         </is>
       </c>
       <c r="I222" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -18188,7 +18183,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 55307-2025</t>
+          <t>A 32958-2025</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -18202,10 +18197,10 @@
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>45970</v>
+        <v>45839</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18218,7 +18213,7 @@
         </is>
       </c>
       <c r="I223" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -18261,7 +18256,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 57017-2025</t>
+          <t>A 32459-2025</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -18275,10 +18270,10 @@
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>45978</v>
+        <v>45838</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18291,7 +18286,7 @@
         </is>
       </c>
       <c r="I224" t="n">
-        <v>5.5</v>
+        <v>1.2</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -18334,7 +18329,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 38073-2026</t>
+          <t>A 2981-2024</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -18348,10 +18343,10 @@
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>46280</v>
+        <v>45315</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18363,8 +18358,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I225" t="n">
-        <v>2.3</v>
+        <v>6.4</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -18407,24 +18407,24 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>S 3888-2023</t>
+          <t>A 37756-2024</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>samrådsanmälan</t>
+          <t>avverkningsanmälan</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Askåterföring</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>45230</v>
+        <v>45541</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18437,7 +18437,7 @@
         </is>
       </c>
       <c r="I226" t="n">
-        <v>13.9</v>
+        <v>3.2</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -18480,7 +18480,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>S 4691-2022</t>
+          <t>S 3888-2023</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -18494,10 +18494,10 @@
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>44796</v>
+        <v>45230</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18510,7 +18510,7 @@
         </is>
       </c>
       <c r="I227" t="n">
-        <v>39</v>
+        <v>13.9</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -18553,7 +18553,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>S 734-2025</t>
+          <t>S 4691-2022</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -18567,10 +18567,10 @@
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>45722</v>
+        <v>44796</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18583,7 +18583,7 @@
         </is>
       </c>
       <c r="I228" t="n">
-        <v>27.4</v>
+        <v>39</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -18626,7 +18626,7 @@
     <row r="229" ht="15" customHeight="1">
       <c r="A229" t="inlineStr">
         <is>
-          <t>S 144-2026</t>
+          <t>S 734-2025</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -18640,10 +18640,10 @@
         </is>
       </c>
       <c r="D229" s="1" t="n">
-        <v>46042</v>
+        <v>45722</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18656,7 +18656,7 @@
         </is>
       </c>
       <c r="I229" t="n">
-        <v>18.3</v>
+        <v>27.4</v>
       </c>
       <c r="J229" t="n">
         <v>0</v>
@@ -18699,7 +18699,7 @@
     <row r="230" ht="15" customHeight="1">
       <c r="A230" t="inlineStr">
         <is>
-          <t>S 220-2026</t>
+          <t>S 144-2026</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -18709,14 +18709,14 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Askåterföring</t>
         </is>
       </c>
       <c r="D230" s="1" t="n">
-        <v>46051</v>
+        <v>46042</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18729,7 +18729,7 @@
         </is>
       </c>
       <c r="I230" t="n">
-        <v>1.7</v>
+        <v>18.3</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
@@ -18789,7 +18789,7 @@
         <v>46202</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18867,7 +18867,7 @@
         <v>46202</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18925,7 +18925,7 @@
       </c>
       <c r="V232" s="2" t="inlineStr"/>
     </row>
-    <row r="233">
+    <row r="233" ht="15" customHeight="1">
       <c r="A233" t="inlineStr">
         <is>
           <t>S 1873-2026</t>
@@ -18945,7 +18945,7 @@
         <v>46202</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19002,6 +19002,79 @@
         <v>0</v>
       </c>
       <c r="V233" s="2" t="inlineStr"/>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>S 220-2026</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>Annan skogsbruksåtgärd</t>
+        </is>
+      </c>
+      <c r="D234" s="1" t="n">
+        <v>46051</v>
+      </c>
+      <c r="E234" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>HÖRBY</t>
+        </is>
+      </c>
+      <c r="I234" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J234" t="n">
+        <v>0</v>
+      </c>
+      <c r="K234" t="n">
+        <v>0</v>
+      </c>
+      <c r="L234" t="n">
+        <v>0</v>
+      </c>
+      <c r="M234" t="n">
+        <v>0</v>
+      </c>
+      <c r="N234" t="n">
+        <v>0</v>
+      </c>
+      <c r="O234" t="n">
+        <v>0</v>
+      </c>
+      <c r="P234" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q234" t="n">
+        <v>0</v>
+      </c>
+      <c r="R234" t="n">
+        <v>0</v>
+      </c>
+      <c r="S234" t="n">
+        <v>0</v>
+      </c>
+      <c r="T234" t="n">
+        <v>0</v>
+      </c>
+      <c r="U234" t="n">
+        <v>0</v>
+      </c>
+      <c r="V234" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt HÖRBY.xlsx
+++ b/Översikt HÖRBY.xlsx
@@ -601,7 +601,7 @@
         <v>44964</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
         <v>44967</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         <v>44727</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -949,7 +949,7 @@
         <v>45786</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1061,7 +1061,7 @@
         <v>46160</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
         <v>45238</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 39855-2022</t>
+          <t>A 31351-2022</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1289,10 +1289,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>44819</v>
+        <v>44774</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1305,22 +1305,22 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>4.2</v>
+        <v>13.2</v>
       </c>
       <c r="J8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1329,10 +1329,10 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1341,9 +1341,344 @@
         <v>5</v>
       </c>
       <c r="U8" t="n">
+        <v>3</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>Duvhök
+Grönsångare
+Sädesärla
+Fjällvråk
+Kungsfågel</t>
+        </is>
+      </c>
+      <c r="W8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 31351-2022 artfynd.xlsx", "A 31351-2022")</f>
+        <v/>
+      </c>
+      <c r="X8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 31351-2022 karta.png", "A 31351-2022")</f>
+        <v/>
+      </c>
+      <c r="Y8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 31351-2022 georefererad karta.tif", "A 31351-2022")</f>
+        <v/>
+      </c>
+      <c r="AA8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 31351-2022 FSC-klagomål.docx", "A 31351-2022")</f>
+        <v/>
+      </c>
+      <c r="AB8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 31351-2022 FSC-klagomål mail.docx", "A 31351-2022")</f>
+        <v/>
+      </c>
+      <c r="AC8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 31351-2022 tillsynsbegäran.docx", "A 31351-2022")</f>
+        <v/>
+      </c>
+      <c r="AD8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 31351-2022 tillsynsbegäran mail.docx", "A 31351-2022")</f>
+        <v/>
+      </c>
+      <c r="AE8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/fåglar/A 31351-2022 prioriterade fågelarter.docx", "A 31351-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 16520-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>46112</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>HÖRBY</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>2</v>
+      </c>
+      <c r="M9" t="n">
         <v>1</v>
       </c>
-      <c r="V8" s="2" t="inlineStr">
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>3</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="n">
+        <v>6</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Slåttergubbe
+Sydlig sotticka
+Älg
+Fiskgjuse
+Större brunfladdermus</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 16520-2026 artfynd.xlsx", "A 16520-2026")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 16520-2026 karta.png", "A 16520-2026")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 16520-2026 georefererad karta.tif", "A 16520-2026")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 16520-2026 FSC-klagomål.docx", "A 16520-2026")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 16520-2026 FSC-klagomål mail.docx", "A 16520-2026")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 16520-2026 tillsynsbegäran.docx", "A 16520-2026")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 16520-2026 tillsynsbegäran mail.docx", "A 16520-2026")</f>
+        <v/>
+      </c>
+      <c r="AE9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/fåglar/A 16520-2026 prioriterade fågelarter.docx", "A 16520-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 20194-2024</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>45434</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>HÖRBY</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>3</v>
+      </c>
+      <c r="R10" t="n">
+        <v>3</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="n">
+        <v>5</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Naverlönn
+Ask
+Skogsalm
+Scharlakansskål
+Stor häxört</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 20194-2024 artfynd.xlsx", "A 20194-2024")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 20194-2024 karta.png", "A 20194-2024")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 20194-2024 georefererad karta.tif", "A 20194-2024")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 20194-2024 FSC-klagomål.docx", "A 20194-2024")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 20194-2024 FSC-klagomål mail.docx", "A 20194-2024")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 20194-2024 tillsynsbegäran.docx", "A 20194-2024")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 20194-2024 tillsynsbegäran mail.docx", "A 20194-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 39855-2022</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>44819</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>HÖRBY</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J11" t="n">
+        <v>4</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>1</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="n">
+        <v>5</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Ask
 Skogsknipprot
@@ -1352,367 +1687,32 @@
 Grönvit nattviol</t>
         </is>
       </c>
-      <c r="W8">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 39855-2022 artfynd.xlsx", "A 39855-2022")</f>
         <v/>
       </c>
-      <c r="X8">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 39855-2022 karta.png", "A 39855-2022")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 39855-2022 georefererad karta.tif", "A 39855-2022")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 39855-2022 FSC-klagomål.docx", "A 39855-2022")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 39855-2022 FSC-klagomål mail.docx", "A 39855-2022")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 39855-2022 tillsynsbegäran.docx", "A 39855-2022")</f>
         <v/>
       </c>
-      <c r="AD8">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 39855-2022 tillsynsbegäran mail.docx", "A 39855-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A 16520-2026</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>46112</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>HÖRBY</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="J9" t="n">
-        <v>2</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>2</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>3</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1</v>
-      </c>
-      <c r="S9" t="n">
-        <v>5</v>
-      </c>
-      <c r="T9" t="n">
-        <v>6</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>Slåttergubbe
-Sydlig sotticka
-Älg
-Fiskgjuse
-Större brunfladdermus</t>
-        </is>
-      </c>
-      <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 16520-2026 artfynd.xlsx", "A 16520-2026")</f>
-        <v/>
-      </c>
-      <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 16520-2026 karta.png", "A 16520-2026")</f>
-        <v/>
-      </c>
-      <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 16520-2026 georefererad karta.tif", "A 16520-2026")</f>
-        <v/>
-      </c>
-      <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 16520-2026 FSC-klagomål.docx", "A 16520-2026")</f>
-        <v/>
-      </c>
-      <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 16520-2026 FSC-klagomål mail.docx", "A 16520-2026")</f>
-        <v/>
-      </c>
-      <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 16520-2026 tillsynsbegäran.docx", "A 16520-2026")</f>
-        <v/>
-      </c>
-      <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 16520-2026 tillsynsbegäran mail.docx", "A 16520-2026")</f>
-        <v/>
-      </c>
-      <c r="AE9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/fåglar/A 16520-2026 prioriterade fågelarter.docx", "A 16520-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 31351-2022</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>44774</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>HÖRBY</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="J10" t="n">
-        <v>5</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>3</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>3</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>5</v>
-      </c>
-      <c r="T10" t="n">
-        <v>5</v>
-      </c>
-      <c r="U10" t="n">
-        <v>3</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Duvhök
-Grönsångare
-Sädesärla
-Fjällvråk
-Kungsfågel</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 31351-2022 artfynd.xlsx", "A 31351-2022")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 31351-2022 karta.png", "A 31351-2022")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 31351-2022 georefererad karta.tif", "A 31351-2022")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 31351-2022 FSC-klagomål.docx", "A 31351-2022")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 31351-2022 FSC-klagomål mail.docx", "A 31351-2022")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 31351-2022 tillsynsbegäran.docx", "A 31351-2022")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 31351-2022 tillsynsbegäran mail.docx", "A 31351-2022")</f>
-        <v/>
-      </c>
-      <c r="AE10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/fåglar/A 31351-2022 prioriterade fågelarter.docx", "A 31351-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 20194-2024</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>45434</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>HÖRBY</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>2</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>2</v>
-      </c>
-      <c r="O11" t="n">
-        <v>1</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>3</v>
-      </c>
-      <c r="R11" t="n">
-        <v>3</v>
-      </c>
-      <c r="S11" t="n">
-        <v>5</v>
-      </c>
-      <c r="T11" t="n">
-        <v>5</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Naverlönn
-Ask
-Skogsalm
-Scharlakansskål
-Stor häxört</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 20194-2024 artfynd.xlsx", "A 20194-2024")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 20194-2024 karta.png", "A 20194-2024")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 20194-2024 georefererad karta.tif", "A 20194-2024")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 20194-2024 FSC-klagomål.docx", "A 20194-2024")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 20194-2024 FSC-klagomål mail.docx", "A 20194-2024")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 20194-2024 tillsynsbegäran.docx", "A 20194-2024")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 20194-2024 tillsynsbegäran mail.docx", "A 20194-2024")</f>
         <v/>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
         <v>46150</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         <v>45545</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1952,7 +1952,7 @@
         <v>45334</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
         <v>45434</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
         <v>45815</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2274,7 +2274,7 @@
         <v>45799</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 24158-2022</t>
+          <t>A 2823-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2374,14 +2374,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44725</v>
+        <v>45677</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2394,184 +2394,184 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>3.1</v>
+        <v>21.1</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
         <v>1</v>
       </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>3</v>
-      </c>
       <c r="R18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>3</v>
       </c>
       <c r="T18" t="n">
+        <v>4</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>Borsttåg
+Grönvit nattviol
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 2823-2025 artfynd.xlsx", "A 2823-2025")</f>
+        <v/>
+      </c>
+      <c r="X18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 2823-2025 karta.png", "A 2823-2025")</f>
+        <v/>
+      </c>
+      <c r="Y18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 2823-2025 georefererad karta.tif", "A 2823-2025")</f>
+        <v/>
+      </c>
+      <c r="AA18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 2823-2025 FSC-klagomål.docx", "A 2823-2025")</f>
+        <v/>
+      </c>
+      <c r="AB18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 2823-2025 FSC-klagomål mail.docx", "A 2823-2025")</f>
+        <v/>
+      </c>
+      <c r="AC18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 2823-2025 tillsynsbegäran.docx", "A 2823-2025")</f>
+        <v/>
+      </c>
+      <c r="AD18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 2823-2025 tillsynsbegäran mail.docx", "A 2823-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>A 24158-2022</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>44725</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>HÖRBY</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>2</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>3</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3</v>
+      </c>
+      <c r="T19" t="n">
         <v>5</v>
       </c>
-      <c r="U18" t="n">
+      <c r="U19" t="n">
         <v>3</v>
       </c>
-      <c r="V18" s="2" t="inlineStr">
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>Slåttergubbe
 Borsttåg
 Sotnätfjäril</t>
         </is>
       </c>
-      <c r="W18">
+      <c r="W19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 24158-2022 artfynd.xlsx", "A 24158-2022")</f>
         <v/>
       </c>
-      <c r="X18">
+      <c r="X19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 24158-2022 karta.png", "A 24158-2022")</f>
         <v/>
       </c>
-      <c r="Y18">
+      <c r="Y19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 24158-2022 georefererad karta.tif", "A 24158-2022")</f>
         <v/>
       </c>
-      <c r="AA18">
+      <c r="AA19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 24158-2022 FSC-klagomål.docx", "A 24158-2022")</f>
         <v/>
       </c>
-      <c r="AB18">
+      <c r="AB19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 24158-2022 FSC-klagomål mail.docx", "A 24158-2022")</f>
         <v/>
       </c>
-      <c r="AC18">
+      <c r="AC19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 24158-2022 tillsynsbegäran.docx", "A 24158-2022")</f>
         <v/>
       </c>
-      <c r="AD18">
+      <c r="AD19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 24158-2022 tillsynsbegäran mail.docx", "A 24158-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>A 2823-2025</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="n">
-        <v>45677</v>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>HÖRBY</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>21.1</v>
-      </c>
-      <c r="J19" t="n">
-        <v>2</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>1</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>1</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>3</v>
-      </c>
-      <c r="T19" t="n">
-        <v>4</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>Borsttåg
-Grönvit nattviol
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 2823-2025 artfynd.xlsx", "A 2823-2025")</f>
-        <v/>
-      </c>
-      <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 2823-2025 karta.png", "A 2823-2025")</f>
-        <v/>
-      </c>
-      <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 2823-2025 georefererad karta.tif", "A 2823-2025")</f>
-        <v/>
-      </c>
-      <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 2823-2025 FSC-klagomål.docx", "A 2823-2025")</f>
-        <v/>
-      </c>
-      <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 2823-2025 FSC-klagomål mail.docx", "A 2823-2025")</f>
-        <v/>
-      </c>
-      <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 2823-2025 tillsynsbegäran.docx", "A 2823-2025")</f>
-        <v/>
-      </c>
-      <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 2823-2025 tillsynsbegäran mail.docx", "A 2823-2025")</f>
         <v/>
       </c>
     </row>
@@ -2595,7 +2595,7 @@
         <v>46030</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2689,7 +2689,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 42724-2023</t>
+          <t>A 44135-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45176</v>
+        <v>45572</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2719,22 +2719,22 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>2.8</v>
+        <v>0.6</v>
       </c>
       <c r="J21" t="n">
+        <v>2</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
         <v>1</v>
       </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
       <c r="M21" t="n">
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2746,155 +2746,155 @@
         <v>1</v>
       </c>
       <c r="R21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>2</v>
       </c>
       <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>Ladusvala
+Vanlig padda</t>
+        </is>
+      </c>
+      <c r="W21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 44135-2024 artfynd.xlsx", "A 44135-2024")</f>
+        <v/>
+      </c>
+      <c r="X21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 44135-2024 karta.png", "A 44135-2024")</f>
+        <v/>
+      </c>
+      <c r="Y21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 44135-2024 georefererad karta.tif", "A 44135-2024")</f>
+        <v/>
+      </c>
+      <c r="AA21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 44135-2024 FSC-klagomål.docx", "A 44135-2024")</f>
+        <v/>
+      </c>
+      <c r="AB21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 44135-2024 FSC-klagomål mail.docx", "A 44135-2024")</f>
+        <v/>
+      </c>
+      <c r="AC21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 44135-2024 tillsynsbegäran.docx", "A 44135-2024")</f>
+        <v/>
+      </c>
+      <c r="AD21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 44135-2024 tillsynsbegäran mail.docx", "A 44135-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>A 42724-2023</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="n">
+        <v>45176</v>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>HÖRBY</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>1</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2</v>
+      </c>
+      <c r="T22" t="n">
         <v>4</v>
       </c>
-      <c r="U21" t="n">
-        <v>0</v>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>Ask
 Grönvit nattviol</t>
         </is>
       </c>
-      <c r="W21">
+      <c r="W22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 42724-2023 artfynd.xlsx", "A 42724-2023")</f>
         <v/>
       </c>
-      <c r="X21">
+      <c r="X22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 42724-2023 karta.png", "A 42724-2023")</f>
         <v/>
       </c>
-      <c r="Y21">
+      <c r="Y22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 42724-2023 georefererad karta.tif", "A 42724-2023")</f>
         <v/>
       </c>
-      <c r="AA21">
+      <c r="AA22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 42724-2023 FSC-klagomål.docx", "A 42724-2023")</f>
         <v/>
       </c>
-      <c r="AB21">
+      <c r="AB22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 42724-2023 FSC-klagomål mail.docx", "A 42724-2023")</f>
         <v/>
       </c>
-      <c r="AC21">
+      <c r="AC22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 42724-2023 tillsynsbegäran.docx", "A 42724-2023")</f>
         <v/>
       </c>
-      <c r="AD21">
+      <c r="AD22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 42724-2023 tillsynsbegäran mail.docx", "A 42724-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>A 44135-2024</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D22" s="1" t="n">
-        <v>45572</v>
-      </c>
-      <c r="E22" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>HÖRBY</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="J22" t="n">
-        <v>2</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>1</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>1</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
-        <v>2</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2</v>
-      </c>
-      <c r="U22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>Ladusvala
-Vanlig padda</t>
-        </is>
-      </c>
-      <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 44135-2024 artfynd.xlsx", "A 44135-2024")</f>
-        <v/>
-      </c>
-      <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 44135-2024 karta.png", "A 44135-2024")</f>
-        <v/>
-      </c>
-      <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 44135-2024 georefererad karta.tif", "A 44135-2024")</f>
-        <v/>
-      </c>
-      <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 44135-2024 FSC-klagomål.docx", "A 44135-2024")</f>
-        <v/>
-      </c>
-      <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 44135-2024 FSC-klagomål mail.docx", "A 44135-2024")</f>
-        <v/>
-      </c>
-      <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 44135-2024 tillsynsbegäran.docx", "A 44135-2024")</f>
-        <v/>
-      </c>
-      <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 44135-2024 tillsynsbegäran mail.docx", "A 44135-2024")</f>
         <v/>
       </c>
     </row>
@@ -2918,7 +2918,7 @@
         <v>45317</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3007,7 +3007,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 31115-2024</t>
+          <t>A 47612-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45502</v>
+        <v>45203</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3037,7 +3037,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.8</v>
+        <v>2.4</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -3046,13 +3046,13 @@
         <v>0</v>
       </c>
       <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
         <v>1</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3064,7 +3064,7 @@
         <v>1</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3077,42 +3077,42 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Gullpudra</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 31115-2024 artfynd.xlsx", "A 31115-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 47612-2023 artfynd.xlsx", "A 47612-2023")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 31115-2024 karta.png", "A 31115-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 47612-2023 karta.png", "A 47612-2023")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 31115-2024 georefererad karta.tif", "A 31115-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 47612-2023 georefererad karta.tif", "A 47612-2023")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 31115-2024 FSC-klagomål.docx", "A 31115-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 47612-2023 FSC-klagomål.docx", "A 47612-2023")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 31115-2024 FSC-klagomål mail.docx", "A 31115-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 47612-2023 FSC-klagomål mail.docx", "A 47612-2023")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 31115-2024 tillsynsbegäran.docx", "A 31115-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 47612-2023 tillsynsbegäran.docx", "A 47612-2023")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 31115-2024 tillsynsbegäran mail.docx", "A 31115-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 47612-2023 tillsynsbegäran mail.docx", "A 47612-2023")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 36362-2025</t>
+          <t>A 25479-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3122,14 +3122,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45868</v>
+        <v>45802</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3142,7 +3142,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>3.7</v>
+        <v>0.7</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -3178,46 +3178,46 @@
         <v>1</v>
       </c>
       <c r="U25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Lundvårlök</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 36362-2025 artfynd.xlsx", "A 36362-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 25479-2025 artfynd.xlsx", "A 25479-2025")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 36362-2025 karta.png", "A 36362-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 25479-2025 karta.png", "A 25479-2025")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 36362-2025 georefererad karta.tif", "A 36362-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 25479-2025 georefererad karta.tif", "A 25479-2025")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 36362-2025 FSC-klagomål.docx", "A 36362-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 25479-2025 FSC-klagomål.docx", "A 25479-2025")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 36362-2025 FSC-klagomål mail.docx", "A 36362-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 25479-2025 FSC-klagomål mail.docx", "A 25479-2025")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 36362-2025 tillsynsbegäran.docx", "A 36362-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 25479-2025 tillsynsbegäran.docx", "A 25479-2025")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 36362-2025 tillsynsbegäran mail.docx", "A 36362-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 25479-2025 tillsynsbegäran mail.docx", "A 25479-2025")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 47612-2023</t>
+          <t>A 113-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3231,10 +3231,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45203</v>
+        <v>44928</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3247,7 +3247,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2.4</v>
+        <v>5.1</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3259,10 +3259,10 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3287,42 +3287,42 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Slåttergubbe</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 47612-2023 artfynd.xlsx", "A 47612-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 113-2023 artfynd.xlsx", "A 113-2023")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 47612-2023 karta.png", "A 47612-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 113-2023 karta.png", "A 113-2023")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 47612-2023 georefererad karta.tif", "A 47612-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 113-2023 georefererad karta.tif", "A 113-2023")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 47612-2023 FSC-klagomål.docx", "A 47612-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 113-2023 FSC-klagomål.docx", "A 113-2023")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 47612-2023 FSC-klagomål mail.docx", "A 47612-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 113-2023 FSC-klagomål mail.docx", "A 113-2023")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 47612-2023 tillsynsbegäran.docx", "A 47612-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 113-2023 tillsynsbegäran.docx", "A 113-2023")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 47612-2023 tillsynsbegäran mail.docx", "A 47612-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 113-2023 tillsynsbegäran mail.docx", "A 113-2023")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 40376-2023</t>
+          <t>A 25833-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3336,10 +3336,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45169</v>
+        <v>45463</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3352,19 +3352,19 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2.7</v>
+        <v>1.4</v>
       </c>
       <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
         <v>1</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" t="n">
-        <v>1</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0</v>
       </c>
       <c r="N27" t="n">
         <v>0</v>
@@ -3379,59 +3379,55 @@
         <v>1</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
       </c>
       <c r="T27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U27" t="n">
         <v>0</v>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Slåttergubbe</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 40376-2023 artfynd.xlsx", "A 40376-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 25833-2024 artfynd.xlsx", "A 25833-2024")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 40376-2023 karta.png", "A 40376-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 25833-2024 karta.png", "A 25833-2024")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 40376-2023 georefererad karta.tif", "A 40376-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 25833-2024 georefererad karta.tif", "A 25833-2024")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 40376-2023 FSC-klagomål.docx", "A 40376-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 25833-2024 FSC-klagomål.docx", "A 25833-2024")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 40376-2023 FSC-klagomål mail.docx", "A 40376-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 25833-2024 FSC-klagomål mail.docx", "A 25833-2024")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 40376-2023 tillsynsbegäran.docx", "A 40376-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 25833-2024 tillsynsbegäran.docx", "A 25833-2024")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 40376-2023 tillsynsbegäran mail.docx", "A 40376-2023")</f>
-        <v/>
-      </c>
-      <c r="AE27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/fåglar/A 40376-2023 prioriterade fågelarter.docx", "A 40376-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 25833-2024 tillsynsbegäran mail.docx", "A 25833-2024")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 113-2023</t>
+          <t>A 24823-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3445,10 +3441,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44928</v>
+        <v>46174</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3458,6 +3454,11 @@
       <c r="G28" t="inlineStr">
         <is>
           <t>HÖRBY</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I28" t="n">
@@ -3473,7 +3474,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
         <v>0</v>
@@ -3485,10 +3486,10 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
@@ -3497,46 +3498,46 @@
         <v>1</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Slåttergubbe</t>
+          <t>Tandrot</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 113-2023 artfynd.xlsx", "A 113-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 24823-2026 artfynd.xlsx", "A 24823-2026")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 113-2023 karta.png", "A 113-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 24823-2026 karta.png", "A 24823-2026")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 113-2023 georefererad karta.tif", "A 113-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 24823-2026 georefererad karta.tif", "A 24823-2026")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 113-2023 FSC-klagomål.docx", "A 113-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 24823-2026 FSC-klagomål.docx", "A 24823-2026")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 113-2023 FSC-klagomål mail.docx", "A 113-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 24823-2026 FSC-klagomål mail.docx", "A 24823-2026")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 113-2023 tillsynsbegäran.docx", "A 113-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 24823-2026 tillsynsbegäran.docx", "A 24823-2026")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 113-2023 tillsynsbegäran mail.docx", "A 113-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 24823-2026 tillsynsbegäran mail.docx", "A 24823-2026")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 24823-2026</t>
+          <t>A 36362-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3550,10 +3551,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46174</v>
+        <v>45868</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3565,19 +3566,14 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I29" t="n">
-        <v>5.1</v>
+        <v>3.7</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -3611,35 +3607,35 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Tandrot</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 24823-2026 artfynd.xlsx", "A 24823-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 36362-2025 artfynd.xlsx", "A 36362-2025")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 24823-2026 karta.png", "A 24823-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 36362-2025 karta.png", "A 36362-2025")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 24823-2026 georefererad karta.tif", "A 24823-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 36362-2025 georefererad karta.tif", "A 36362-2025")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 24823-2026 FSC-klagomål.docx", "A 24823-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 36362-2025 FSC-klagomål.docx", "A 36362-2025")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 24823-2026 FSC-klagomål mail.docx", "A 24823-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 36362-2025 FSC-klagomål mail.docx", "A 36362-2025")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 24823-2026 tillsynsbegäran.docx", "A 24823-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 36362-2025 tillsynsbegäran.docx", "A 36362-2025")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 24823-2026 tillsynsbegäran mail.docx", "A 24823-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 36362-2025 tillsynsbegäran mail.docx", "A 36362-2025")</f>
         <v/>
       </c>
     </row>
@@ -3663,7 +3659,7 @@
         <v>46112</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3751,7 +3747,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 25833-2024</t>
+          <t>A 40376-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3765,10 +3761,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45463</v>
+        <v>45169</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3781,19 +3777,19 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.4</v>
+        <v>2.7</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
         <v>0</v>
@@ -3808,55 +3804,59 @@
         <v>1</v>
       </c>
       <c r="R31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
         <v>1</v>
       </c>
       <c r="T31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U31" t="n">
         <v>0</v>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>Slåttergubbe</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="W31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 25833-2024 artfynd.xlsx", "A 25833-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 40376-2023 artfynd.xlsx", "A 40376-2023")</f>
         <v/>
       </c>
       <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 25833-2024 karta.png", "A 25833-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 40376-2023 karta.png", "A 40376-2023")</f>
         <v/>
       </c>
       <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 25833-2024 georefererad karta.tif", "A 25833-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 40376-2023 georefererad karta.tif", "A 40376-2023")</f>
         <v/>
       </c>
       <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 25833-2024 FSC-klagomål.docx", "A 25833-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 40376-2023 FSC-klagomål.docx", "A 40376-2023")</f>
         <v/>
       </c>
       <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 25833-2024 FSC-klagomål mail.docx", "A 25833-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 40376-2023 FSC-klagomål mail.docx", "A 40376-2023")</f>
         <v/>
       </c>
       <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 25833-2024 tillsynsbegäran.docx", "A 25833-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 40376-2023 tillsynsbegäran.docx", "A 40376-2023")</f>
         <v/>
       </c>
       <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 25833-2024 tillsynsbegäran mail.docx", "A 25833-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 40376-2023 tillsynsbegäran mail.docx", "A 40376-2023")</f>
+        <v/>
+      </c>
+      <c r="AE31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/fåglar/A 40376-2023 prioriterade fågelarter.docx", "A 40376-2023")</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 31284-2026</t>
+          <t>A 31115-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3870,10 +3870,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46218</v>
+        <v>45502</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3886,17 +3886,17 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>6.8</v>
+        <v>0.8</v>
       </c>
       <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" t="n">
         <v>1</v>
       </c>
-      <c r="K32" t="n">
-        <v>0</v>
-      </c>
-      <c r="L32" t="n">
-        <v>0</v>
-      </c>
       <c r="M32" t="n">
         <v>0</v>
       </c>
@@ -3910,7 +3910,7 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -3926,42 +3926,42 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="W32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 31284-2026 artfynd.xlsx", "A 31284-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 31115-2024 artfynd.xlsx", "A 31115-2024")</f>
         <v/>
       </c>
       <c r="X32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 31284-2026 karta.png", "A 31284-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 31115-2024 karta.png", "A 31115-2024")</f>
         <v/>
       </c>
       <c r="Y32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 31284-2026 georefererad karta.tif", "A 31284-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 31115-2024 georefererad karta.tif", "A 31115-2024")</f>
         <v/>
       </c>
       <c r="AA32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 31284-2026 FSC-klagomål.docx", "A 31284-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 31115-2024 FSC-klagomål.docx", "A 31115-2024")</f>
         <v/>
       </c>
       <c r="AB32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 31284-2026 FSC-klagomål mail.docx", "A 31284-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 31115-2024 FSC-klagomål mail.docx", "A 31115-2024")</f>
         <v/>
       </c>
       <c r="AC32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 31284-2026 tillsynsbegäran.docx", "A 31284-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 31115-2024 tillsynsbegäran.docx", "A 31115-2024")</f>
         <v/>
       </c>
       <c r="AD32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 31284-2026 tillsynsbegäran mail.docx", "A 31284-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 31115-2024 tillsynsbegäran mail.docx", "A 31115-2024")</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 30165-2026</t>
+          <t>A 31284-2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>46206</v>
+        <v>46218</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3991,10 +3991,10 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.4</v>
+        <v>6.8</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
@@ -4006,7 +4006,7 @@
         <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4015,10 +4015,10 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
         <v>1</v>
@@ -4031,42 +4031,42 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="W33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 30165-2026 artfynd.xlsx", "A 30165-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 31284-2026 artfynd.xlsx", "A 31284-2026")</f>
         <v/>
       </c>
       <c r="X33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 30165-2026 karta.png", "A 30165-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 31284-2026 karta.png", "A 31284-2026")</f>
         <v/>
       </c>
       <c r="Y33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 30165-2026 georefererad karta.tif", "A 30165-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 31284-2026 georefererad karta.tif", "A 31284-2026")</f>
         <v/>
       </c>
       <c r="AA33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 30165-2026 FSC-klagomål.docx", "A 30165-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 31284-2026 FSC-klagomål.docx", "A 31284-2026")</f>
         <v/>
       </c>
       <c r="AB33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 30165-2026 FSC-klagomål mail.docx", "A 30165-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 31284-2026 FSC-klagomål mail.docx", "A 31284-2026")</f>
         <v/>
       </c>
       <c r="AC33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 30165-2026 tillsynsbegäran.docx", "A 30165-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 31284-2026 tillsynsbegäran.docx", "A 31284-2026")</f>
         <v/>
       </c>
       <c r="AD33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 30165-2026 tillsynsbegäran mail.docx", "A 30165-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 31284-2026 tillsynsbegäran mail.docx", "A 31284-2026")</f>
         <v/>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 29129-2026</t>
+          <t>A 30165-2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4080,10 +4080,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>46202</v>
+        <v>46206</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4095,13 +4095,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I34" t="n">
-        <v>10.5</v>
+        <v>1.4</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -4110,13 +4105,13 @@
         <v>0</v>
       </c>
       <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="n">
         <v>1</v>
-      </c>
-      <c r="M34" t="n">
-        <v>0</v>
-      </c>
-      <c r="N34" t="n">
-        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4128,7 +4123,7 @@
         <v>1</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S34" t="n">
         <v>1</v>
@@ -4141,42 +4136,42 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>Ekticka</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="W34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 29129-2026 artfynd.xlsx", "A 29129-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 30165-2026 artfynd.xlsx", "A 30165-2026")</f>
         <v/>
       </c>
       <c r="X34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 29129-2026 karta.png", "A 29129-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 30165-2026 karta.png", "A 30165-2026")</f>
         <v/>
       </c>
       <c r="Y34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 29129-2026 georefererad karta.tif", "A 29129-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 30165-2026 georefererad karta.tif", "A 30165-2026")</f>
         <v/>
       </c>
       <c r="AA34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 29129-2026 FSC-klagomål.docx", "A 29129-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 30165-2026 FSC-klagomål.docx", "A 30165-2026")</f>
         <v/>
       </c>
       <c r="AB34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 29129-2026 FSC-klagomål mail.docx", "A 29129-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 30165-2026 FSC-klagomål mail.docx", "A 30165-2026")</f>
         <v/>
       </c>
       <c r="AC34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 29129-2026 tillsynsbegäran.docx", "A 29129-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 30165-2026 tillsynsbegäran.docx", "A 30165-2026")</f>
         <v/>
       </c>
       <c r="AD34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 29129-2026 tillsynsbegäran mail.docx", "A 29129-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 30165-2026 tillsynsbegäran mail.docx", "A 30165-2026")</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 21713-2025</t>
+          <t>A 29129-2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4190,10 +4185,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45783</v>
+        <v>46202</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4205,18 +4200,23 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I35" t="n">
-        <v>0.8</v>
+        <v>10.5</v>
       </c>
       <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="n">
         <v>1</v>
       </c>
-      <c r="K35" t="n">
-        <v>0</v>
-      </c>
-      <c r="L35" t="n">
-        <v>0</v>
-      </c>
       <c r="M35" t="n">
         <v>0</v>
       </c>
@@ -4230,7 +4230,7 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -4246,42 +4246,42 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Ekticka</t>
         </is>
       </c>
       <c r="W35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 21713-2025 artfynd.xlsx", "A 21713-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 29129-2026 artfynd.xlsx", "A 29129-2026")</f>
         <v/>
       </c>
       <c r="X35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 21713-2025 karta.png", "A 21713-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 29129-2026 karta.png", "A 29129-2026")</f>
         <v/>
       </c>
       <c r="Y35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 21713-2025 georefererad karta.tif", "A 21713-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 29129-2026 georefererad karta.tif", "A 29129-2026")</f>
         <v/>
       </c>
       <c r="AA35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 21713-2025 FSC-klagomål.docx", "A 21713-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 29129-2026 FSC-klagomål.docx", "A 29129-2026")</f>
         <v/>
       </c>
       <c r="AB35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 21713-2025 FSC-klagomål mail.docx", "A 21713-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 29129-2026 FSC-klagomål mail.docx", "A 29129-2026")</f>
         <v/>
       </c>
       <c r="AC35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 21713-2025 tillsynsbegäran.docx", "A 21713-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 29129-2026 tillsynsbegäran.docx", "A 29129-2026")</f>
         <v/>
       </c>
       <c r="AD35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 21713-2025 tillsynsbegäran mail.docx", "A 21713-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 29129-2026 tillsynsbegäran mail.docx", "A 29129-2026")</f>
         <v/>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 25479-2025</t>
+          <t>A 21713-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4291,14 +4291,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45802</v>
+        <v>45783</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4311,13 +4311,13 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
@@ -4351,35 +4351,35 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>Lundvårlök</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="W36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 25479-2025 artfynd.xlsx", "A 25479-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 21713-2025 artfynd.xlsx", "A 21713-2025")</f>
         <v/>
       </c>
       <c r="X36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 25479-2025 karta.png", "A 25479-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 21713-2025 karta.png", "A 21713-2025")</f>
         <v/>
       </c>
       <c r="Y36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 25479-2025 georefererad karta.tif", "A 25479-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 21713-2025 georefererad karta.tif", "A 21713-2025")</f>
         <v/>
       </c>
       <c r="AA36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 25479-2025 FSC-klagomål.docx", "A 25479-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 21713-2025 FSC-klagomål.docx", "A 21713-2025")</f>
         <v/>
       </c>
       <c r="AB36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 25479-2025 FSC-klagomål mail.docx", "A 25479-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 21713-2025 FSC-klagomål mail.docx", "A 21713-2025")</f>
         <v/>
       </c>
       <c r="AC36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 25479-2025 tillsynsbegäran.docx", "A 25479-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 21713-2025 tillsynsbegäran.docx", "A 21713-2025")</f>
         <v/>
       </c>
       <c r="AD36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 25479-2025 tillsynsbegäran mail.docx", "A 25479-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 21713-2025 tillsynsbegäran mail.docx", "A 21713-2025")</f>
         <v/>
       </c>
     </row>
@@ -4403,7 +4403,7 @@
         <v>45089</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4508,7 +4508,7 @@
         <v>44999</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4613,7 +4613,7 @@
         <v>44509</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4686,7 +4686,7 @@
         <v>44663</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4759,7 +4759,7 @@
         <v>44509</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4832,7 +4832,7 @@
         <v>44697</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4905,7 +4905,7 @@
         <v>44510</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4978,7 +4978,7 @@
         <v>44834</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5051,7 +5051,7 @@
         <v>44771</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5124,7 +5124,7 @@
         <v>44466</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5197,7 +5197,7 @@
         <v>44789</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5270,7 +5270,7 @@
         <v>44733</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5326,7 +5326,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 2979-2024</t>
+          <t>A 43380-2022</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5340,10 +5340,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45315</v>
+        <v>44834</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5355,13 +5355,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I49" t="n">
-        <v>4.7</v>
+        <v>1.7</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5404,7 +5399,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 24670-2024</t>
+          <t>A 47609-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5414,14 +5409,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45460</v>
+        <v>45203</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5434,7 +5429,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.2</v>
+        <v>2.4</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5477,7 +5472,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 18609-2025</t>
+          <t>A 9974-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5491,10 +5486,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45763</v>
+        <v>45363</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5550,7 +5545,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 3471-2025</t>
+          <t>A 15970-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5564,10 +5559,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45680</v>
+        <v>45405</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5580,7 +5575,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>3.7</v>
+        <v>1.8</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5623,7 +5618,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 33359-2023</t>
+          <t>A 5163-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5637,10 +5632,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45128</v>
+        <v>45330</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5652,8 +5647,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I53" t="n">
-        <v>0.9</v>
+        <v>7.1</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5696,7 +5696,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 37757-2024</t>
+          <t>A 37724-2022</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5710,10 +5710,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45541</v>
+        <v>44810</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5726,7 +5726,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5769,7 +5769,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 31596-2023</t>
+          <t>A 37728-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5783,10 +5783,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45117</v>
+        <v>44810</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5799,7 +5799,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5842,7 +5842,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 44613-2023</t>
+          <t>A 56818-2022</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5856,10 +5856,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45189</v>
+        <v>44894</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5871,13 +5871,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I56" t="n">
-        <v>3.8</v>
+        <v>1.8</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5920,7 +5915,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 2816-2025</t>
+          <t>A 33359-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5930,14 +5925,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45677</v>
+        <v>45128</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5950,7 +5945,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2</v>
+        <v>0.9</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5993,7 +5988,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 28785-2023</t>
+          <t>A 54894-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6003,14 +5998,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45104</v>
+        <v>45236</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6023,7 +6018,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>2.1</v>
+        <v>0.6</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -6066,7 +6061,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 16101-2025</t>
+          <t>A 36689-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6076,14 +6071,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45750</v>
+        <v>45537</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6095,8 +6090,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I59" t="n">
-        <v>0.5</v>
+        <v>9.5</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6139,7 +6139,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 58360-2023</t>
+          <t>A 38080-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6153,10 +6153,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45250</v>
+        <v>45545</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6169,7 +6169,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>2.5</v>
+        <v>0.7</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6212,7 +6212,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 4756-2025</t>
+          <t>A 826-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6226,10 +6226,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45688</v>
+        <v>46030</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6241,8 +6241,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I61" t="n">
-        <v>0.9</v>
+        <v>0.3</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6285,7 +6290,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 48397-2022</t>
+          <t>A 829-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6299,10 +6304,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44858</v>
+        <v>46030</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6314,8 +6319,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I62" t="n">
-        <v>1.7</v>
+        <v>6.9</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6358,7 +6368,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 6886-2024</t>
+          <t>A 16665-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6372,10 +6382,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45342</v>
+        <v>45754</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6387,13 +6397,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I63" t="n">
-        <v>0.5</v>
+        <v>2.4</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6436,7 +6441,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 33358-2023</t>
+          <t>A 28746-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6450,10 +6455,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45128</v>
+        <v>45478</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6466,7 +6471,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.4</v>
+        <v>1.9</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6509,7 +6514,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 47641-2023</t>
+          <t>A 821-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6523,10 +6528,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45203</v>
+        <v>46030</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6538,8 +6543,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I65" t="n">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6582,7 +6592,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 39298-2023</t>
+          <t>A 554-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6596,10 +6606,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45166</v>
+        <v>46029</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6612,7 +6622,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>4.6</v>
+        <v>0.8</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6655,7 +6665,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 39507-2024</t>
+          <t>A 37082-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6665,14 +6675,14 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45551</v>
+        <v>45155</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6684,13 +6694,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I67" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6733,7 +6738,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 3346-2024</t>
+          <t>A 1989-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6747,10 +6752,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45317</v>
+        <v>46035</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6763,7 +6768,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6806,7 +6811,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 788-2024</t>
+          <t>A 2752-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6820,10 +6825,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45300</v>
+        <v>44944</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6833,6 +6838,11 @@
       <c r="G69" t="inlineStr">
         <is>
           <t>HÖRBY</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I69" t="n">
@@ -6879,7 +6889,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 9974-2024</t>
+          <t>A 3013-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6893,10 +6903,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45363</v>
+        <v>46038</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6909,7 +6919,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6952,7 +6962,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 11943-2025</t>
+          <t>A 28785-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6962,14 +6972,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45728</v>
+        <v>45104</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6982,7 +6992,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.2</v>
+        <v>2.1</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -7025,7 +7035,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 42715-2023</t>
+          <t>A 5374-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7039,10 +7049,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45176</v>
+        <v>46050</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7098,7 +7108,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 28918-2023</t>
+          <t>A 13225-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7112,10 +7122,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45104</v>
+        <v>45386</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7128,7 +7138,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>2</v>
+        <v>0.7</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7171,7 +7181,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 2747-2023</t>
+          <t>A 13226-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7185,10 +7195,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44944</v>
+        <v>45386</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7200,13 +7210,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I74" t="n">
-        <v>4.6</v>
+        <v>0.7</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7249,7 +7254,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 43932-2023</t>
+          <t>A 48397-2022</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7263,10 +7268,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45187</v>
+        <v>44858</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7279,7 +7284,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>3</v>
+        <v>1.7</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7322,7 +7327,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 43935-2023</t>
+          <t>A 43711-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7332,14 +7337,14 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45187</v>
+        <v>45569</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7352,7 +7357,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7395,7 +7400,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 48427-2022</t>
+          <t>A 15998-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7409,10 +7414,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44858</v>
+        <v>45405</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7424,13 +7429,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I77" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7473,7 +7473,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 8084-2022</t>
+          <t>A 16001-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7487,10 +7487,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44608</v>
+        <v>45405</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7503,7 +7503,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.5</v>
+        <v>0.2</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7546,7 +7546,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 43828-2024</t>
+          <t>A 34154-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7560,10 +7560,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45572</v>
+        <v>45845</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7576,7 +7576,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.9</v>
+        <v>5</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7619,7 +7619,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 13225-2024</t>
+          <t>A 8310-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7633,10 +7633,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45386</v>
+        <v>46064</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7649,7 +7649,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7692,7 +7692,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 13226-2024</t>
+          <t>A 8260-2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7706,10 +7706,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45386</v>
+        <v>46064</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7722,7 +7722,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>0.7</v>
+        <v>3.3</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7765,7 +7765,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 47552-2023</t>
+          <t>A 8259-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7779,10 +7779,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45203</v>
+        <v>46064</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7795,7 +7795,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.3</v>
+        <v>3.1</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7838,7 +7838,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 36355-2025</t>
+          <t>A 23484-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7852,10 +7852,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45868</v>
+        <v>45792</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7868,7 +7868,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7911,7 +7911,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 25552-2025</t>
+          <t>A 43828-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7925,10 +7925,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45803</v>
+        <v>45572</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7941,7 +7941,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>2</v>
+        <v>0.9</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7984,7 +7984,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 2752-2023</t>
+          <t>A 10731-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7998,10 +7998,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>44944</v>
+        <v>46078</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8015,11 +8015,11 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I85" t="n">
-        <v>0.6</v>
+        <v>4.8</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -8062,7 +8062,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 38147-2025</t>
+          <t>A 18609-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -8076,10 +8076,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45882</v>
+        <v>45763</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8092,7 +8092,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8135,7 +8135,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 37082-2023</t>
+          <t>A 56750-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8145,14 +8145,14 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45155</v>
+        <v>45238</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8165,7 +8165,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8208,7 +8208,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 54431-2023</t>
+          <t>A 42715-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8222,10 +8222,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45226</v>
+        <v>45176</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8238,7 +8238,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>3.2</v>
+        <v>0.5</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8281,7 +8281,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 28625-2023</t>
+          <t>A 13633-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8295,10 +8295,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45103</v>
+        <v>45390</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8311,7 +8311,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>4.8</v>
+        <v>1.1</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8354,7 +8354,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 38080-2024</t>
+          <t>A 34147-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8368,10 +8368,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45545</v>
+        <v>45845</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8384,7 +8384,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>0.7</v>
+        <v>18.7</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8427,7 +8427,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 34154-2025</t>
+          <t>A 14307-2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8441,10 +8441,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45845</v>
+        <v>46099</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8457,7 +8457,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8500,7 +8500,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 13633-2024</t>
+          <t>A 3520-2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8514,10 +8514,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45390</v>
+        <v>46042</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8530,7 +8530,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8573,7 +8573,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 44816-2023</t>
+          <t>A 3470-2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8587,10 +8587,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45190</v>
+        <v>46042</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8603,7 +8603,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8646,7 +8646,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 28493-2023</t>
+          <t>A 58641-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8656,14 +8656,14 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45103</v>
+        <v>45251</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8676,7 +8676,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8719,7 +8719,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 43879-2023</t>
+          <t>A 51757-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8729,14 +8729,14 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45187</v>
+        <v>45951</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8754,7 +8754,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8797,7 +8797,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 47609-2023</t>
+          <t>A 9850-2026</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8811,10 +8811,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45203</v>
+        <v>46072</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8827,7 +8827,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8870,7 +8870,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 65073-2023</t>
+          <t>A 3513-2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8884,10 +8884,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45287</v>
+        <v>46042</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8900,7 +8900,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1.7</v>
+        <v>0.9</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8943,7 +8943,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 34147-2025</t>
+          <t>A 18603-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8957,10 +8957,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45845</v>
+        <v>45763</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8973,7 +8973,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>18.7</v>
+        <v>0.5</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -9016,7 +9016,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 43882-2023</t>
+          <t>A 3346-2024</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -9030,10 +9030,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45187</v>
+        <v>45317</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9045,13 +9045,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I99" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -9094,7 +9089,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 67426-2021</t>
+          <t>A 52929-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -9108,10 +9103,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>44523</v>
+        <v>45957</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9123,8 +9118,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I100" t="n">
-        <v>0.6</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -9167,7 +9167,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 3239-2023</t>
+          <t>A 52930-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>44946</v>
+        <v>45957</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9196,8 +9196,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I101" t="n">
-        <v>0.4</v>
+        <v>1.6</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9240,7 +9245,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 51757-2025</t>
+          <t>A 788-2024</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9250,14 +9255,14 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45951</v>
+        <v>45300</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9269,13 +9274,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I102" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9318,7 +9318,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 60963-2023</t>
+          <t>A 54765-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9332,10 +9332,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45261</v>
+        <v>45966</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9348,7 +9348,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>1.2</v>
+        <v>2.6</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9391,7 +9391,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 5079-2026</t>
+          <t>A 40994-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9405,10 +9405,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>46049</v>
+        <v>45898</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9421,7 +9421,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>1.3</v>
+        <v>5.6</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9464,7 +9464,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 43685-2022</t>
+          <t>A 55304-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9478,10 +9478,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>44837</v>
+        <v>45970</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9494,7 +9494,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1.3</v>
+        <v>0.4</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9537,7 +9537,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 52930-2025</t>
+          <t>A 55306-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9547,14 +9547,14 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45957</v>
+        <v>45970</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9566,13 +9566,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I106" t="n">
-        <v>1.6</v>
+        <v>0.3</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9615,7 +9610,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 52929-2025</t>
+          <t>A 28550-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9629,10 +9624,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45957</v>
+        <v>45818</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9644,13 +9639,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I107" t="n">
-        <v>8.300000000000001</v>
+        <v>5</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9693,7 +9683,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 55265-2023</t>
+          <t>A 7402-2026</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9707,10 +9697,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45237</v>
+        <v>46059</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9723,7 +9713,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>1.2</v>
+        <v>4.7</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9766,7 +9756,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 5163-2024</t>
+          <t>A 9612-2025</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9780,10 +9770,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45330</v>
+        <v>45715</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9795,13 +9785,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I109" t="n">
-        <v>7.1</v>
+        <v>1.2</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9844,7 +9829,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 54765-2025</t>
+          <t>A 57269-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9858,10 +9843,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45966</v>
+        <v>45979</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9873,8 +9858,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I110" t="n">
-        <v>2.6</v>
+        <v>5.5</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9917,7 +9907,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 55304-2025</t>
+          <t>A 50715-2024</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9927,14 +9917,14 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45970</v>
+        <v>45602</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9990,7 +9980,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 55306-2025</t>
+          <t>A 2816-2025</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -10004,10 +9994,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45970</v>
+        <v>45677</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10020,7 +10010,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>0.3</v>
+        <v>2</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -10063,7 +10053,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 40994-2025</t>
+          <t>A 16101-2025</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -10077,10 +10067,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45898</v>
+        <v>45750</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10093,7 +10083,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>5.6</v>
+        <v>0.5</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -10136,7 +10126,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 18603-2025</t>
+          <t>A 59308-2025</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -10150,10 +10140,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45763</v>
+        <v>45989</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10166,7 +10156,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -10209,7 +10199,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 57269-2025</t>
+          <t>A 34422-2024</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10219,14 +10209,14 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45979</v>
+        <v>45525</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10238,13 +10228,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I115" t="n">
-        <v>5.5</v>
+        <v>1.5</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10287,7 +10272,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 3534-2025</t>
+          <t>A 11943-2025</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10301,10 +10286,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45680</v>
+        <v>45728</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10316,13 +10301,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I116" t="n">
-        <v>4.8</v>
+        <v>1.2</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10365,7 +10345,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 20595-2024</t>
+          <t>A 5079-2026</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10379,10 +10359,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45436</v>
+        <v>46049</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10394,13 +10374,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H117" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I117" t="n">
-        <v>3.5</v>
+        <v>1.3</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10443,7 +10418,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 59308-2025</t>
+          <t>A 44613-2023</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10457,10 +10432,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45989</v>
+        <v>45189</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10472,8 +10447,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I118" t="n">
-        <v>1.2</v>
+        <v>3.8</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10533,7 +10513,7 @@
         <v>45187</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10606,7 +10586,7 @@
         <v>45187</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10662,7 +10642,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 28501-2023</t>
+          <t>A 67426-2021</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10676,10 +10656,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45103</v>
+        <v>44523</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10692,7 +10672,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>3.6</v>
+        <v>0.6</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10735,7 +10715,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 28527-2023</t>
+          <t>A 65073-2023</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10749,10 +10729,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45103</v>
+        <v>45287</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10765,7 +10745,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>0.7</v>
+        <v>1.7</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10808,7 +10788,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 54894-2023</t>
+          <t>A 62277-2025</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10822,10 +10802,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45236</v>
+        <v>46006</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10838,7 +10818,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>0.6</v>
+        <v>2.4</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10881,7 +10861,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 37276-2024</t>
+          <t>A 3534-2025</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10895,10 +10875,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45540</v>
+        <v>45680</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10910,8 +10890,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I124" t="n">
-        <v>1.6</v>
+        <v>4.8</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10954,7 +10939,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 62277-2025</t>
+          <t>A 7831-2025</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10968,10 +10953,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>46006</v>
+        <v>45706</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10984,7 +10969,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>2.4</v>
+        <v>0.6</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -11027,7 +11012,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 4597-2026</t>
+          <t>A 29244-2025</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -11041,10 +11026,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>46048</v>
+        <v>45824</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11057,7 +11042,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -11100,7 +11085,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 36689-2024</t>
+          <t>A 29354-2025</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -11110,14 +11095,14 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45537</v>
+        <v>45824</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11129,13 +11114,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I127" t="n">
-        <v>9.5</v>
+        <v>0.8</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -11178,7 +11158,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 554-2026</t>
+          <t>A 18735-2023</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -11192,10 +11172,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>46029</v>
+        <v>45043</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11208,7 +11188,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -11251,7 +11231,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 826-2026</t>
+          <t>A 28493-2023</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11265,10 +11245,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>46030</v>
+        <v>45103</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11280,13 +11260,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I129" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11329,7 +11304,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 829-2026</t>
+          <t>A 36840-2024</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11343,10 +11318,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>46030</v>
+        <v>45538</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11364,7 +11339,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>6.9</v>
+        <v>0.9</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11407,7 +11382,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 821-2026</t>
+          <t>A 60913-2023</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11421,10 +11396,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>46030</v>
+        <v>45261</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11436,13 +11411,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H131" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I131" t="n">
-        <v>4.3</v>
+        <v>0.7</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11485,7 +11455,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 1989-2026</t>
+          <t>A 8084-2022</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11499,10 +11469,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>46035</v>
+        <v>44608</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11515,7 +11485,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11558,7 +11528,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 31522-2022</t>
+          <t>A 2981-2024</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11572,10 +11542,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>44775</v>
+        <v>45315</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11587,8 +11557,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I133" t="n">
-        <v>1.8</v>
+        <v>6.4</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11631,7 +11606,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 54184-2024</t>
+          <t>A 28625-2023</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11645,10 +11620,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45616</v>
+        <v>45103</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11661,7 +11636,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>0.5</v>
+        <v>4.8</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11704,7 +11679,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 3013-2026</t>
+          <t>A 4597-2026</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11718,10 +11693,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>46038</v>
+        <v>46048</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11734,7 +11709,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11777,7 +11752,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 60913-2023</t>
+          <t>A 32459-2025</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11791,10 +11766,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45261</v>
+        <v>45838</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11807,7 +11782,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11850,7 +11825,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 44073-2024</t>
+          <t>A 32958-2025</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11864,10 +11839,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45572</v>
+        <v>45839</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11880,7 +11855,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11923,7 +11898,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 11941-2025</t>
+          <t>A 37756-2024</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11937,10 +11912,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45728</v>
+        <v>45541</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11953,7 +11928,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>0.6</v>
+        <v>3.2</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11996,7 +11971,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 43380-2022</t>
+          <t>A 4590-2026</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -12010,10 +11985,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>44834</v>
+        <v>46048</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12026,7 +12001,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -12069,7 +12044,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 5374-2026</t>
+          <t>A 6350-2026</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -12083,10 +12058,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12099,7 +12074,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>0.5</v>
+        <v>2.4</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -12142,7 +12117,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 20403-2024</t>
+          <t>A 13804-2024</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -12156,10 +12131,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45435</v>
+        <v>45391</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12172,7 +12147,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -12215,7 +12190,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 1106-2023</t>
+          <t>A 18369-2025</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -12229,10 +12204,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>44935</v>
+        <v>45762</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12245,7 +12220,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>1.2</v>
+        <v>2.2</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -12288,7 +12263,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 8310-2026</t>
+          <t>A 36355-2025</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12302,10 +12277,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>46064</v>
+        <v>45868</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12318,7 +12293,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>1.4</v>
+        <v>3.6</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -12361,7 +12336,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 8260-2026</t>
+          <t>A 6886-2024</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12375,10 +12350,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>46064</v>
+        <v>45342</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12390,8 +12365,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I144" t="n">
-        <v>3.3</v>
+        <v>0.5</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -12434,7 +12414,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 8259-2026</t>
+          <t>A 3177-2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12444,14 +12424,14 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>46064</v>
+        <v>46041</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12464,7 +12444,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>3.1</v>
+        <v>0.5</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12507,7 +12487,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 49726-2023</t>
+          <t>A 1106-2023</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12521,10 +12501,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45208</v>
+        <v>44935</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12537,7 +12517,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12580,7 +12560,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 36840-2024</t>
+          <t>A 17073-2023</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12594,10 +12574,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45538</v>
+        <v>45034</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12609,13 +12589,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H147" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I147" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12658,7 +12633,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 4590-2026</t>
+          <t>A 2979-2024</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12672,10 +12647,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>46048</v>
+        <v>45315</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12687,8 +12662,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I148" t="n">
-        <v>1.1</v>
+        <v>4.7</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12731,7 +12711,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 24724-2024</t>
+          <t>A 31596-2023</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12741,14 +12721,14 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45460</v>
+        <v>45117</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12761,7 +12741,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12804,7 +12784,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 10731-2026</t>
+          <t>A 59284-2025</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12818,10 +12798,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>46078</v>
+        <v>45988</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12833,13 +12813,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H150" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I150" t="n">
-        <v>4.8</v>
+        <v>1.5</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12882,7 +12857,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 58641-2023</t>
+          <t>A 25552-2025</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12892,14 +12867,14 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45251</v>
+        <v>45803</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12912,7 +12887,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12955,7 +12930,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 6350-2026</t>
+          <t>A 10500-2026</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12969,10 +12944,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>46051</v>
+        <v>46076</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12985,7 +12960,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>2.4</v>
+        <v>1.1</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -13028,7 +13003,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 18369-2025</t>
+          <t>A 54184-2024</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -13042,10 +13017,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45762</v>
+        <v>45616</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13058,7 +13033,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>2.2</v>
+        <v>0.5</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -13101,7 +13076,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 3040-2024</t>
+          <t>A 16518-2026</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -13115,10 +13090,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45316</v>
+        <v>46112</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13131,7 +13106,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>4</v>
+        <v>0.8</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -13174,7 +13149,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 14307-2026</t>
+          <t>A 43932-2023</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -13188,10 +13163,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>46099</v>
+        <v>45187</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13204,7 +13179,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -13247,7 +13222,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 3177-2026</t>
+          <t>A 43935-2023</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -13257,14 +13232,14 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>46041</v>
+        <v>45187</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13277,7 +13252,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>0.5</v>
+        <v>2.9</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -13320,7 +13295,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 15970-2024</t>
+          <t>A 29138-2026</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -13330,14 +13305,14 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45405</v>
+        <v>46202</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13349,8 +13324,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I157" t="n">
-        <v>1.8</v>
+        <v>4.2</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -13393,7 +13373,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 18735-2023</t>
+          <t>A 29135-2026</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -13403,14 +13383,14 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45043</v>
+        <v>46202</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13422,8 +13402,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I158" t="n">
-        <v>1</v>
+        <v>4.7</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -13466,7 +13451,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 3470-2026</t>
+          <t>A 29137-2026</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13476,14 +13461,14 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>46042</v>
+        <v>46202</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13495,8 +13480,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I159" t="n">
-        <v>1.5</v>
+        <v>7.8</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -13539,7 +13529,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 3513-2026</t>
+          <t>A 20403-2024</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -13553,10 +13543,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>46042</v>
+        <v>45435</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13612,7 +13602,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 3520-2026</t>
+          <t>A 38147-2025</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13626,10 +13616,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>46042</v>
+        <v>45882</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13642,7 +13632,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13685,7 +13675,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 6081-2023</t>
+          <t>A 29124-2026</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13699,10 +13689,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>44959</v>
+        <v>46202</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13715,7 +13705,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>0.4</v>
+        <v>2.9</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13758,7 +13748,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 29219-2023</t>
+          <t>A 3040-2024</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13772,10 +13762,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>45105</v>
+        <v>45316</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13788,7 +13778,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>0.7</v>
+        <v>4</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13831,7 +13821,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 59284-2025</t>
+          <t>A 44816-2023</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13845,10 +13835,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45988</v>
+        <v>45190</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13861,7 +13851,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13904,7 +13894,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 9850-2026</t>
+          <t>A 47552-2023</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13918,10 +13908,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>46072</v>
+        <v>45203</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13934,7 +13924,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>2.2</v>
+        <v>1.3</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13977,7 +13967,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 56818-2022</t>
+          <t>A 54431-2023</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13991,10 +13981,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>44894</v>
+        <v>45226</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14007,7 +13997,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>1.8</v>
+        <v>3.2</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -14050,7 +14040,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 10500-2026</t>
+          <t>A 19777-2023</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -14064,10 +14054,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>46076</v>
+        <v>45051</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14080,7 +14070,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>1.1</v>
+        <v>4.3</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -14123,7 +14113,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 7402-2026</t>
+          <t>A 43879-2023</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -14137,10 +14127,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>46059</v>
+        <v>45187</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14152,8 +14142,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I168" t="n">
-        <v>4.7</v>
+        <v>1.1</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -14196,7 +14191,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 34422-2024</t>
+          <t>A 3471-2025</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -14206,14 +14201,14 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>45525</v>
+        <v>45680</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14226,7 +14221,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>1.5</v>
+        <v>3.7</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -14269,7 +14264,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 16518-2026</t>
+          <t>A 49726-2023</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -14283,10 +14278,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>46112</v>
+        <v>45208</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14299,7 +14294,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -14342,7 +14337,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 7831-2025</t>
+          <t>A 28501-2023</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -14356,10 +14351,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45706</v>
+        <v>45103</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14372,7 +14367,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>0.6</v>
+        <v>3.6</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -14415,7 +14410,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 56750-2023</t>
+          <t>A 30934-2026</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -14429,10 +14424,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45238</v>
+        <v>46213</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14445,7 +14440,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -14488,7 +14483,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 29138-2026</t>
+          <t>A 34737-2026</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -14498,14 +14493,14 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>46202</v>
+        <v>46258</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14517,13 +14512,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H173" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I173" t="n">
-        <v>4.2</v>
+        <v>0.7</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -14566,7 +14556,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 29124-2026</t>
+          <t>A 34740-2026</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14580,10 +14570,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>46202</v>
+        <v>46258</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14596,7 +14586,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>2.9</v>
+        <v>2.1</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14639,7 +14629,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 29135-2026</t>
+          <t>A 33873-2024</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14649,14 +14639,14 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>46202</v>
+        <v>45521</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14668,13 +14658,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H175" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I175" t="n">
-        <v>4.7</v>
+        <v>3.5</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14717,7 +14702,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 29137-2026</t>
+          <t>A 23606-2026</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14727,14 +14712,14 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>46202</v>
+        <v>46162</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14746,13 +14731,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H176" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I176" t="n">
-        <v>7.8</v>
+        <v>9.4</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14795,7 +14775,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 17073-2023</t>
+          <t>A 58360-2023</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14809,10 +14789,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45034</v>
+        <v>45250</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14825,7 +14805,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>1.2</v>
+        <v>2.5</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14868,7 +14848,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 19420-2022</t>
+          <t>A 39298-2023</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14882,10 +14862,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>44693</v>
+        <v>45166</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14898,7 +14878,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>0.7</v>
+        <v>4.6</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14941,7 +14921,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 119-2023</t>
+          <t>A 29219-2023</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14955,10 +14935,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>44928</v>
+        <v>45105</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14971,7 +14951,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -15014,7 +14994,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 50715-2024</t>
+          <t>A 3542-2025</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -15028,10 +15008,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>45602</v>
+        <v>45680</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15043,8 +15023,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I180" t="n">
-        <v>0.4</v>
+        <v>1.4</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -15087,7 +15072,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 37724-2022</t>
+          <t>A 31286-2026</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -15101,10 +15086,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>44810</v>
+        <v>46218</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15117,7 +15102,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -15160,7 +15145,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 37728-2022</t>
+          <t>A 55307-2025</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -15174,10 +15159,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>44810</v>
+        <v>45970</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15190,7 +15175,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -15250,7 +15235,7 @@
         <v>45203</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15306,7 +15291,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 33873-2024</t>
+          <t>A 24670-2024</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -15316,14 +15301,14 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>45521</v>
+        <v>45460</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15336,7 +15321,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>3.5</v>
+        <v>0.2</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -15379,7 +15364,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 23606-2026</t>
+          <t>A 57017-2025</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -15389,14 +15374,14 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>46162</v>
+        <v>45978</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15409,7 +15394,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>9.4</v>
+        <v>5.5</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -15452,7 +15437,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 34737-2026</t>
+          <t>A 6081-2023</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -15466,10 +15451,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>46258</v>
+        <v>44959</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15482,7 +15467,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -15525,7 +15510,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 34740-2026</t>
+          <t>A 31114-2024</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -15539,10 +15524,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>46258</v>
+        <v>45502</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15555,7 +15540,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>2.1</v>
+        <v>0.6</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -15598,7 +15583,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 3542-2025</t>
+          <t>A 11941-2025</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15612,10 +15597,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>45680</v>
+        <v>45728</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15627,13 +15612,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H188" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I188" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15676,7 +15656,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 13228-2024</t>
+          <t>A 38073-2026</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15690,10 +15670,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>45386</v>
+        <v>46280</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15706,7 +15686,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>0.7</v>
+        <v>2.3</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15749,7 +15729,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 15998-2024</t>
+          <t>A 38684-2022</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15763,10 +15743,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>45405</v>
+        <v>44814</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15779,7 +15759,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>0.4</v>
+        <v>2.5</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15822,7 +15802,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 16001-2024</t>
+          <t>A 37757-2024</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15836,10 +15816,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>45405</v>
+        <v>45541</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15852,7 +15832,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15895,7 +15875,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 31114-2024</t>
+          <t>A 38936-2026</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15909,10 +15889,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>45502</v>
+        <v>46286</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15924,8 +15904,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I192" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15968,7 +15953,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 13804-2024</t>
+          <t>A 25183-2023</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15982,10 +15967,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>45391</v>
+        <v>45079</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15998,7 +15983,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -16041,7 +16026,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 30934-2026</t>
+          <t>A 38948-2026</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -16055,10 +16040,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>46213</v>
+        <v>46286</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16070,8 +16055,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I194" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -16114,7 +16104,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 55307-2025</t>
+          <t>A 38906-2026</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -16128,10 +16118,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>45970</v>
+        <v>46286</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16143,8 +16133,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I195" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -16187,7 +16182,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 31286-2026</t>
+          <t>A 37300-2026</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -16201,10 +16196,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>46218</v>
+        <v>46274</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16217,7 +16212,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>1.1</v>
+        <v>0.2</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -16260,7 +16255,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 19777-2023</t>
+          <t>A 20047-2026</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -16274,10 +16269,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>45051</v>
+        <v>46136</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16290,7 +16285,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>4.3</v>
+        <v>1.1</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -16333,7 +16328,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 28746-2024</t>
+          <t>A 38824-2026</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -16347,10 +16342,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>45478</v>
+        <v>46286</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16362,8 +16357,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I198" t="n">
-        <v>1.9</v>
+        <v>11.2</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -16406,7 +16406,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 57017-2025</t>
+          <t>A 44073-2024</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -16420,10 +16420,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>45978</v>
+        <v>45572</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16436,7 +16436,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>5.5</v>
+        <v>1</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -16479,7 +16479,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 6558-2025</t>
+          <t>A 37276-2024</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -16489,14 +16489,14 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>45699</v>
+        <v>45540</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16508,13 +16508,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H200" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I200" t="n">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -16557,7 +16552,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 25183-2023</t>
+          <t>A 20595-2024</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -16571,10 +16566,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>45079</v>
+        <v>45436</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16586,8 +16581,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I201" t="n">
-        <v>1.5</v>
+        <v>3.5</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -16630,7 +16630,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 41940-2022</t>
+          <t>A 10524-2026</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -16644,10 +16644,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>44833</v>
+        <v>46076</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16660,7 +16660,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>0.7</v>
+        <v>1.6</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16703,7 +16703,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 38073-2026</t>
+          <t>A 119-2023</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16717,10 +16717,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>46280</v>
+        <v>44928</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16733,7 +16733,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>2.3</v>
+        <v>0.8</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -16776,7 +16776,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 38684-2022</t>
+          <t>A 43685-2022</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -16786,14 +16786,14 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>44814</v>
+        <v>44837</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16806,7 +16806,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>2.5</v>
+        <v>1.3</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16849,7 +16849,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 37300-2026</t>
+          <t>A 39481-2026</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16863,10 +16863,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>46274</v>
+        <v>46289</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16879,7 +16879,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>0.2</v>
+        <v>2.3</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16922,7 +16922,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 52310-2023</t>
+          <t>A 38730-2026</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16936,10 +16936,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>45224</v>
+        <v>46285</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16952,7 +16952,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>3.5</v>
+        <v>0.4</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16995,7 +16995,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 38936-2026</t>
+          <t>A 24724-2024</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -17005,14 +17005,14 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>46286</v>
+        <v>45460</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17022,11 +17022,6 @@
       <c r="G207" t="inlineStr">
         <is>
           <t>HÖRBY</t>
-        </is>
-      </c>
-      <c r="H207" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I207" t="n">
@@ -17073,7 +17068,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 38948-2026</t>
+          <t>A 6558-2025</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -17083,14 +17078,14 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>46286</v>
+        <v>45699</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17104,11 +17099,11 @@
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I208" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -17151,7 +17146,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 10524-2026</t>
+          <t>A 2747-2023</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -17165,10 +17160,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>46076</v>
+        <v>44944</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17180,8 +17175,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I209" t="n">
-        <v>1.6</v>
+        <v>4.6</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -17224,7 +17224,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 20047-2026</t>
+          <t>A 31522-2022</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -17238,10 +17238,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>46136</v>
+        <v>44775</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17254,7 +17254,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -17297,7 +17297,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 38824-2026</t>
+          <t>A 55265-2023</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -17311,10 +17311,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>46286</v>
+        <v>45237</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17326,13 +17326,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H211" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I211" t="n">
-        <v>11.2</v>
+        <v>1.2</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -17375,7 +17370,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 2170-2025</t>
+          <t>A 28918-2023</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -17389,10 +17384,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>45673</v>
+        <v>45104</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17405,7 +17400,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>3.6</v>
+        <v>2</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -17448,7 +17443,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 38906-2026</t>
+          <t>A 3239-2023</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -17462,10 +17457,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>46286</v>
+        <v>44946</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17477,13 +17472,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H213" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I213" t="n">
-        <v>3.1</v>
+        <v>0.4</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -17526,7 +17516,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 38730-2026</t>
+          <t>A 13228-2024</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -17540,10 +17530,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>46285</v>
+        <v>45386</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17556,7 +17546,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -17599,7 +17589,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 16665-2025</t>
+          <t>A 48427-2022</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -17613,10 +17603,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>45754</v>
+        <v>44858</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17628,8 +17618,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I215" t="n">
-        <v>2.4</v>
+        <v>0.5</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -17672,7 +17667,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 39481-2026</t>
+          <t>A 4756-2025</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -17686,10 +17681,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>46289</v>
+        <v>45688</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17702,7 +17697,7 @@
         </is>
       </c>
       <c r="I216" t="n">
-        <v>2.3</v>
+        <v>0.9</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -17745,7 +17740,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 43711-2024</t>
+          <t>A 33358-2023</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -17755,14 +17750,14 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>45569</v>
+        <v>45128</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17775,7 +17770,7 @@
         </is>
       </c>
       <c r="I217" t="n">
-        <v>3.4</v>
+        <v>0.4</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -17818,7 +17813,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 23484-2025</t>
+          <t>A 39507-2024</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -17832,10 +17827,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>45792</v>
+        <v>45551</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17847,8 +17842,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I218" t="n">
-        <v>3.5</v>
+        <v>0.3</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -17891,7 +17891,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 28550-2025</t>
+          <t>A 41940-2022</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -17905,10 +17905,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>45818</v>
+        <v>44833</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17921,7 +17921,7 @@
         </is>
       </c>
       <c r="I219" t="n">
-        <v>5</v>
+        <v>0.7</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -17964,7 +17964,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 9612-2025</t>
+          <t>A 43882-2023</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -17978,10 +17978,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>45715</v>
+        <v>45187</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17991,6 +17991,11 @@
       <c r="G220" t="inlineStr">
         <is>
           <t>HÖRBY</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I220" t="n">
@@ -18037,7 +18042,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 29244-2025</t>
+          <t>A 28527-2023</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -18051,10 +18056,10 @@
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>45824</v>
+        <v>45103</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18110,7 +18115,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 29354-2025</t>
+          <t>A 19420-2022</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -18124,10 +18129,10 @@
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>45824</v>
+        <v>44693</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18140,7 +18145,7 @@
         </is>
       </c>
       <c r="I222" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -18183,7 +18188,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 32958-2025</t>
+          <t>A 47641-2023</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -18197,10 +18202,10 @@
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>45839</v>
+        <v>45203</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18213,7 +18218,7 @@
         </is>
       </c>
       <c r="I223" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -18256,7 +18261,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 32459-2025</t>
+          <t>A 60963-2023</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -18270,10 +18275,10 @@
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>45838</v>
+        <v>45261</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18329,7 +18334,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 2981-2024</t>
+          <t>A 52310-2023</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -18343,10 +18348,10 @@
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>45315</v>
+        <v>45224</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18358,13 +18363,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H225" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I225" t="n">
-        <v>6.4</v>
+        <v>3.5</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -18407,7 +18407,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 37756-2024</t>
+          <t>A 2170-2025</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -18421,10 +18421,10 @@
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>45541</v>
+        <v>45673</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18437,7 +18437,7 @@
         </is>
       </c>
       <c r="I226" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -18497,7 +18497,7 @@
         <v>45230</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18570,7 +18570,7 @@
         <v>44796</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18643,7 +18643,7 @@
         <v>45722</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18716,7 +18716,7 @@
         <v>46042</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18772,7 +18772,7 @@
     <row r="231" ht="15" customHeight="1">
       <c r="A231" t="inlineStr">
         <is>
-          <t>S 1874-2026</t>
+          <t>S 220-2026</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -18786,10 +18786,10 @@
         </is>
       </c>
       <c r="D231" s="1" t="n">
-        <v>46202</v>
+        <v>46051</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18801,13 +18801,8 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H231" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I231" t="n">
-        <v>7.8</v>
+        <v>1.7</v>
       </c>
       <c r="J231" t="n">
         <v>0</v>
@@ -18850,7 +18845,7 @@
     <row r="232" ht="15" customHeight="1">
       <c r="A232" t="inlineStr">
         <is>
-          <t>S 1875-2026</t>
+          <t>S 1874-2026</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -18867,7 +18862,7 @@
         <v>46202</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18885,7 +18880,7 @@
         </is>
       </c>
       <c r="I232" t="n">
-        <v>4.2</v>
+        <v>7.8</v>
       </c>
       <c r="J232" t="n">
         <v>0</v>
@@ -18928,7 +18923,7 @@
     <row r="233" ht="15" customHeight="1">
       <c r="A233" t="inlineStr">
         <is>
-          <t>S 1873-2026</t>
+          <t>S 1875-2026</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -18945,7 +18940,7 @@
         <v>46202</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18963,7 +18958,7 @@
         </is>
       </c>
       <c r="I233" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="J233" t="n">
         <v>0</v>
@@ -19006,7 +19001,7 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>S 220-2026</t>
+          <t>S 1873-2026</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -19020,10 +19015,10 @@
         </is>
       </c>
       <c r="D234" s="1" t="n">
-        <v>46051</v>
+        <v>46202</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19035,8 +19030,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I234" t="n">
-        <v>1.7</v>
+        <v>4.7</v>
       </c>
       <c r="J234" t="n">
         <v>0</v>

--- a/Översikt HÖRBY.xlsx
+++ b/Översikt HÖRBY.xlsx
@@ -601,7 +601,7 @@
         <v>44964</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
         <v>44967</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         <v>44727</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -949,7 +949,7 @@
         <v>45786</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1061,7 +1061,7 @@
         <v>46160</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
         <v>45238</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
         <v>44774</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>46112</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
         <v>45434</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1627,7 +1627,7 @@
         <v>44819</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1736,7 +1736,7 @@
         <v>46150</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         <v>45545</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1952,7 +1952,7 @@
         <v>45334</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
         <v>45434</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
         <v>45815</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2274,7 +2274,7 @@
         <v>45799</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2381,7 +2381,7 @@
         <v>45677</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2488,7 +2488,7 @@
         <v>44725</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2595,7 +2595,7 @@
         <v>46030</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2706,7 +2706,7 @@
         <v>45572</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         <v>45176</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2918,7 +2918,7 @@
         <v>45317</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3024,7 +3024,7 @@
         <v>45203</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3129,7 +3129,7 @@
         <v>45802</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3234,7 +3234,7 @@
         <v>44928</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3339,7 +3339,7 @@
         <v>45463</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3444,7 +3444,7 @@
         <v>46174</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3554,7 +3554,7 @@
         <v>45868</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3659,7 +3659,7 @@
         <v>46112</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3764,7 +3764,7 @@
         <v>45169</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
         <v>45502</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3978,7 +3978,7 @@
         <v>46218</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4083,7 +4083,7 @@
         <v>46206</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4188,7 +4188,7 @@
         <v>46202</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4298,7 +4298,7 @@
         <v>45783</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4403,7 +4403,7 @@
         <v>45089</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4508,7 +4508,7 @@
         <v>44999</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4613,7 +4613,7 @@
         <v>44509</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4686,7 +4686,7 @@
         <v>44663</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4759,7 +4759,7 @@
         <v>44509</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4832,7 +4832,7 @@
         <v>44697</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4905,7 +4905,7 @@
         <v>44510</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4978,7 +4978,7 @@
         <v>44834</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5051,7 +5051,7 @@
         <v>44771</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5124,7 +5124,7 @@
         <v>44466</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5197,7 +5197,7 @@
         <v>44789</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5270,7 +5270,7 @@
         <v>44733</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5343,7 +5343,7 @@
         <v>44834</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5416,7 +5416,7 @@
         <v>45203</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5489,7 +5489,7 @@
         <v>45363</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5562,7 +5562,7 @@
         <v>45405</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5635,7 +5635,7 @@
         <v>45330</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5713,7 +5713,7 @@
         <v>44810</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5786,7 +5786,7 @@
         <v>44810</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5859,7 +5859,7 @@
         <v>44894</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5932,7 +5932,7 @@
         <v>45128</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
         <v>45236</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6078,7 +6078,7 @@
         <v>45537</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6156,7 +6156,7 @@
         <v>45545</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6229,7 +6229,7 @@
         <v>46030</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6307,7 +6307,7 @@
         <v>46030</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6385,7 +6385,7 @@
         <v>45754</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6458,7 +6458,7 @@
         <v>45478</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6531,7 +6531,7 @@
         <v>46030</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6609,7 +6609,7 @@
         <v>46029</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6682,7 +6682,7 @@
         <v>45155</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6755,7 +6755,7 @@
         <v>46035</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6828,7 +6828,7 @@
         <v>44944</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6906,7 +6906,7 @@
         <v>46038</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6979,7 +6979,7 @@
         <v>45104</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7052,7 +7052,7 @@
         <v>46050</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7125,7 +7125,7 @@
         <v>45386</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7198,7 +7198,7 @@
         <v>45386</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7271,7 +7271,7 @@
         <v>44858</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7344,7 +7344,7 @@
         <v>45569</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7417,7 +7417,7 @@
         <v>45405</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7490,7 +7490,7 @@
         <v>45405</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         <v>45845</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7636,7 +7636,7 @@
         <v>46064</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7709,7 +7709,7 @@
         <v>46064</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7782,7 +7782,7 @@
         <v>46064</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7855,7 +7855,7 @@
         <v>45792</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7928,7 +7928,7 @@
         <v>45572</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8001,7 +8001,7 @@
         <v>46078</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8079,7 +8079,7 @@
         <v>45763</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8152,7 +8152,7 @@
         <v>45238</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8225,7 +8225,7 @@
         <v>45176</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8298,7 +8298,7 @@
         <v>45390</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8371,7 +8371,7 @@
         <v>45845</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8444,7 +8444,7 @@
         <v>46099</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8517,7 +8517,7 @@
         <v>46042</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8590,7 +8590,7 @@
         <v>46042</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8663,7 +8663,7 @@
         <v>45251</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8736,7 +8736,7 @@
         <v>45951</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8814,7 +8814,7 @@
         <v>46072</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8887,7 +8887,7 @@
         <v>46042</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8960,7 +8960,7 @@
         <v>45763</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         <v>45317</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9106,7 +9106,7 @@
         <v>45957</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9184,7 +9184,7 @@
         <v>45957</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9262,7 +9262,7 @@
         <v>45300</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9335,7 +9335,7 @@
         <v>45966</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9408,7 +9408,7 @@
         <v>45898</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9481,7 +9481,7 @@
         <v>45970</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9554,7 +9554,7 @@
         <v>45970</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9627,7 +9627,7 @@
         <v>45818</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9700,7 +9700,7 @@
         <v>46059</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9773,7 +9773,7 @@
         <v>45715</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9846,7 +9846,7 @@
         <v>45979</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9924,7 +9924,7 @@
         <v>45602</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9997,7 +9997,7 @@
         <v>45677</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10070,7 +10070,7 @@
         <v>45750</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10143,7 +10143,7 @@
         <v>45989</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10216,7 +10216,7 @@
         <v>45525</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10289,7 +10289,7 @@
         <v>45728</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10362,7 +10362,7 @@
         <v>46049</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10435,7 +10435,7 @@
         <v>45189</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10513,7 +10513,7 @@
         <v>45187</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10586,7 +10586,7 @@
         <v>45187</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10659,7 +10659,7 @@
         <v>44523</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10732,7 +10732,7 @@
         <v>45287</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10805,7 +10805,7 @@
         <v>46006</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10878,7 +10878,7 @@
         <v>45680</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10956,7 +10956,7 @@
         <v>45706</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11029,7 +11029,7 @@
         <v>45824</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11102,7 +11102,7 @@
         <v>45824</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11175,7 +11175,7 @@
         <v>45043</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11248,7 +11248,7 @@
         <v>45103</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11321,7 +11321,7 @@
         <v>45538</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11399,7 +11399,7 @@
         <v>45261</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11472,7 +11472,7 @@
         <v>44608</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11545,7 +11545,7 @@
         <v>45315</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11623,7 +11623,7 @@
         <v>45103</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11696,7 +11696,7 @@
         <v>46048</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11769,7 +11769,7 @@
         <v>45838</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11842,7 +11842,7 @@
         <v>45839</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11915,7 +11915,7 @@
         <v>45541</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11988,7 +11988,7 @@
         <v>46048</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12061,7 +12061,7 @@
         <v>46051</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12134,7 +12134,7 @@
         <v>45391</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12207,7 +12207,7 @@
         <v>45762</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12280,7 +12280,7 @@
         <v>45868</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12353,7 +12353,7 @@
         <v>45342</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12431,7 +12431,7 @@
         <v>46041</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12504,7 +12504,7 @@
         <v>44935</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12577,7 +12577,7 @@
         <v>45034</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12650,7 +12650,7 @@
         <v>45315</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12728,7 +12728,7 @@
         <v>45117</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12801,7 +12801,7 @@
         <v>45988</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12874,7 +12874,7 @@
         <v>45803</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12947,7 +12947,7 @@
         <v>46076</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13020,7 +13020,7 @@
         <v>45616</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13093,7 +13093,7 @@
         <v>46112</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13166,7 +13166,7 @@
         <v>45187</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13239,7 +13239,7 @@
         <v>45187</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13312,7 +13312,7 @@
         <v>46202</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13390,7 +13390,7 @@
         <v>46202</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13468,7 +13468,7 @@
         <v>46202</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13546,7 +13546,7 @@
         <v>45435</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13619,7 +13619,7 @@
         <v>45882</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13692,7 +13692,7 @@
         <v>46202</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13765,7 +13765,7 @@
         <v>45316</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13838,7 +13838,7 @@
         <v>45190</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13911,7 +13911,7 @@
         <v>45203</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13984,7 +13984,7 @@
         <v>45226</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14057,7 +14057,7 @@
         <v>45051</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14130,7 +14130,7 @@
         <v>45187</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14208,7 +14208,7 @@
         <v>45680</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14281,7 +14281,7 @@
         <v>45208</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14354,7 +14354,7 @@
         <v>45103</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14427,7 +14427,7 @@
         <v>46213</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14500,7 +14500,7 @@
         <v>46258</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14573,7 +14573,7 @@
         <v>46258</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14646,7 +14646,7 @@
         <v>45521</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14719,7 +14719,7 @@
         <v>46162</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14792,7 +14792,7 @@
         <v>45250</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14865,7 +14865,7 @@
         <v>45166</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14938,7 +14938,7 @@
         <v>45105</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15011,7 +15011,7 @@
         <v>45680</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15089,7 +15089,7 @@
         <v>46218</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15162,7 +15162,7 @@
         <v>45970</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15235,7 +15235,7 @@
         <v>45203</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15308,7 +15308,7 @@
         <v>45460</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15381,7 +15381,7 @@
         <v>45978</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15454,7 +15454,7 @@
         <v>44959</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15527,7 +15527,7 @@
         <v>45502</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15600,7 +15600,7 @@
         <v>45728</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15673,7 +15673,7 @@
         <v>46280</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15746,7 +15746,7 @@
         <v>44814</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15819,7 +15819,7 @@
         <v>45541</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15892,7 +15892,7 @@
         <v>46286</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15970,7 +15970,7 @@
         <v>45079</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16043,7 +16043,7 @@
         <v>46286</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16121,7 +16121,7 @@
         <v>46286</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16199,7 +16199,7 @@
         <v>46274</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16272,7 +16272,7 @@
         <v>46136</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16345,7 +16345,7 @@
         <v>46286</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16423,7 +16423,7 @@
         <v>45572</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16496,7 +16496,7 @@
         <v>45540</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16569,7 +16569,7 @@
         <v>45436</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16647,7 +16647,7 @@
         <v>46076</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16720,7 +16720,7 @@
         <v>44928</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16793,7 +16793,7 @@
         <v>44837</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16866,7 +16866,7 @@
         <v>46289</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16939,7 +16939,7 @@
         <v>46285</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17012,7 +17012,7 @@
         <v>45460</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17085,7 +17085,7 @@
         <v>45699</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17163,7 +17163,7 @@
         <v>44944</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17241,7 +17241,7 @@
         <v>44775</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17314,7 +17314,7 @@
         <v>45237</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17387,7 +17387,7 @@
         <v>45104</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17460,7 +17460,7 @@
         <v>44946</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17533,7 +17533,7 @@
         <v>45386</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17606,7 +17606,7 @@
         <v>44858</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17684,7 +17684,7 @@
         <v>45688</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17757,7 +17757,7 @@
         <v>45128</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17830,7 +17830,7 @@
         <v>45551</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17908,7 +17908,7 @@
         <v>44833</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17981,7 +17981,7 @@
         <v>45187</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18059,7 +18059,7 @@
         <v>45103</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18132,7 +18132,7 @@
         <v>44693</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18205,7 +18205,7 @@
         <v>45203</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18278,7 +18278,7 @@
         <v>45261</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18351,7 +18351,7 @@
         <v>45224</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18424,7 +18424,7 @@
         <v>45673</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18497,7 +18497,7 @@
         <v>45230</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18570,7 +18570,7 @@
         <v>44796</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18643,7 +18643,7 @@
         <v>45722</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18716,7 +18716,7 @@
         <v>46042</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18789,7 +18789,7 @@
         <v>46051</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18862,7 +18862,7 @@
         <v>46202</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18940,7 +18940,7 @@
         <v>46202</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19018,7 +19018,7 @@
         <v>46202</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>

--- a/Översikt HÖRBY.xlsx
+++ b/Översikt HÖRBY.xlsx
@@ -601,7 +601,7 @@
         <v>44964</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
         <v>44967</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         <v>44727</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -949,7 +949,7 @@
         <v>45786</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1061,7 +1061,7 @@
         <v>46160</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
         <v>45238</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
         <v>44774</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>46112</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
         <v>45434</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1627,7 +1627,7 @@
         <v>44819</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1736,7 +1736,7 @@
         <v>46150</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         <v>45545</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1952,7 +1952,7 @@
         <v>45334</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
         <v>45434</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
         <v>45815</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2274,7 +2274,7 @@
         <v>45799</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2381,7 +2381,7 @@
         <v>45677</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2488,7 +2488,7 @@
         <v>44725</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2595,7 +2595,7 @@
         <v>46030</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2706,7 +2706,7 @@
         <v>45572</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         <v>45176</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2918,7 +2918,7 @@
         <v>45317</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3024,7 +3024,7 @@
         <v>45203</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3129,7 +3129,7 @@
         <v>45802</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3234,7 +3234,7 @@
         <v>44928</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3339,7 +3339,7 @@
         <v>45463</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3444,7 +3444,7 @@
         <v>46174</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3554,7 +3554,7 @@
         <v>45868</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3659,7 +3659,7 @@
         <v>46112</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3764,7 +3764,7 @@
         <v>45169</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
         <v>45502</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3978,7 +3978,7 @@
         <v>46218</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4083,7 +4083,7 @@
         <v>46206</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4188,7 +4188,7 @@
         <v>46202</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4298,7 +4298,7 @@
         <v>45783</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4403,7 +4403,7 @@
         <v>45089</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4508,7 +4508,7 @@
         <v>44999</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4613,7 +4613,7 @@
         <v>44509</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4686,7 +4686,7 @@
         <v>44663</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4759,7 +4759,7 @@
         <v>44509</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4832,7 +4832,7 @@
         <v>44697</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4905,7 +4905,7 @@
         <v>44510</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4978,7 +4978,7 @@
         <v>44834</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5051,7 +5051,7 @@
         <v>44771</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5124,7 +5124,7 @@
         <v>44466</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5197,7 +5197,7 @@
         <v>44789</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5270,7 +5270,7 @@
         <v>44733</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5343,7 +5343,7 @@
         <v>44834</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5416,7 +5416,7 @@
         <v>45203</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5489,7 +5489,7 @@
         <v>45363</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5562,7 +5562,7 @@
         <v>45405</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5635,7 +5635,7 @@
         <v>45330</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5713,7 +5713,7 @@
         <v>44810</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5786,7 +5786,7 @@
         <v>44810</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5859,7 +5859,7 @@
         <v>44894</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5932,7 +5932,7 @@
         <v>45128</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
         <v>45236</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6078,7 +6078,7 @@
         <v>45537</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6156,7 +6156,7 @@
         <v>45545</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6229,7 +6229,7 @@
         <v>46030</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6307,7 +6307,7 @@
         <v>46030</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6385,7 +6385,7 @@
         <v>45754</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6458,7 +6458,7 @@
         <v>45478</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6531,7 +6531,7 @@
         <v>46030</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6609,7 +6609,7 @@
         <v>46029</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6682,7 +6682,7 @@
         <v>45155</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6755,7 +6755,7 @@
         <v>46035</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6828,7 +6828,7 @@
         <v>44944</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6906,7 +6906,7 @@
         <v>46038</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6979,7 +6979,7 @@
         <v>45104</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7052,7 +7052,7 @@
         <v>46050</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7125,7 +7125,7 @@
         <v>45386</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7198,7 +7198,7 @@
         <v>45386</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7271,7 +7271,7 @@
         <v>44858</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7344,7 +7344,7 @@
         <v>45569</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7417,7 +7417,7 @@
         <v>45405</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7490,7 +7490,7 @@
         <v>45405</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         <v>45845</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7636,7 +7636,7 @@
         <v>46064</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7709,7 +7709,7 @@
         <v>46064</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7782,7 +7782,7 @@
         <v>46064</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7855,7 +7855,7 @@
         <v>45792</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7928,7 +7928,7 @@
         <v>45572</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8001,7 +8001,7 @@
         <v>46078</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8079,7 +8079,7 @@
         <v>45763</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8152,7 +8152,7 @@
         <v>45238</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8225,7 +8225,7 @@
         <v>45176</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8298,7 +8298,7 @@
         <v>45390</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8371,7 +8371,7 @@
         <v>45845</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8444,7 +8444,7 @@
         <v>46099</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8517,7 +8517,7 @@
         <v>46042</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8590,7 +8590,7 @@
         <v>46042</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8663,7 +8663,7 @@
         <v>45251</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8736,7 +8736,7 @@
         <v>45951</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8814,7 +8814,7 @@
         <v>46072</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8887,7 +8887,7 @@
         <v>46042</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8960,7 +8960,7 @@
         <v>45763</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         <v>45317</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9106,7 +9106,7 @@
         <v>45957</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9184,7 +9184,7 @@
         <v>45957</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9262,7 +9262,7 @@
         <v>45300</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9335,7 +9335,7 @@
         <v>45966</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9408,7 +9408,7 @@
         <v>45898</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9481,7 +9481,7 @@
         <v>45970</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9554,7 +9554,7 @@
         <v>45970</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9627,7 +9627,7 @@
         <v>45818</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9700,7 +9700,7 @@
         <v>46059</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9773,7 +9773,7 @@
         <v>45715</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9846,7 +9846,7 @@
         <v>45979</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9924,7 +9924,7 @@
         <v>45602</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9997,7 +9997,7 @@
         <v>45677</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10070,7 +10070,7 @@
         <v>45750</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10143,7 +10143,7 @@
         <v>45989</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10216,7 +10216,7 @@
         <v>45525</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10289,7 +10289,7 @@
         <v>45728</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10362,7 +10362,7 @@
         <v>46049</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10435,7 +10435,7 @@
         <v>45189</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10513,7 +10513,7 @@
         <v>45187</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10586,7 +10586,7 @@
         <v>45187</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10659,7 +10659,7 @@
         <v>44523</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10732,7 +10732,7 @@
         <v>45287</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10805,7 +10805,7 @@
         <v>46006</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10878,7 +10878,7 @@
         <v>45680</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10956,7 +10956,7 @@
         <v>45706</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11029,7 +11029,7 @@
         <v>45824</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11102,7 +11102,7 @@
         <v>45824</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11175,7 +11175,7 @@
         <v>45043</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11248,7 +11248,7 @@
         <v>45103</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11321,7 +11321,7 @@
         <v>45538</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11399,7 +11399,7 @@
         <v>45261</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11472,7 +11472,7 @@
         <v>44608</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11545,7 +11545,7 @@
         <v>45315</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11623,7 +11623,7 @@
         <v>45103</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11696,7 +11696,7 @@
         <v>46048</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11769,7 +11769,7 @@
         <v>45838</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11842,7 +11842,7 @@
         <v>45839</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11915,7 +11915,7 @@
         <v>45541</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11988,7 +11988,7 @@
         <v>46048</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12061,7 +12061,7 @@
         <v>46051</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12134,7 +12134,7 @@
         <v>45391</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12207,7 +12207,7 @@
         <v>45762</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12280,7 +12280,7 @@
         <v>45868</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12353,7 +12353,7 @@
         <v>45342</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12431,7 +12431,7 @@
         <v>46041</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12504,7 +12504,7 @@
         <v>44935</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12577,7 +12577,7 @@
         <v>45034</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12650,7 +12650,7 @@
         <v>45315</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12728,7 +12728,7 @@
         <v>45117</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12801,7 +12801,7 @@
         <v>45988</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12874,7 +12874,7 @@
         <v>45803</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12947,7 +12947,7 @@
         <v>46076</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13020,7 +13020,7 @@
         <v>45616</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13093,7 +13093,7 @@
         <v>46112</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13166,7 +13166,7 @@
         <v>45187</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13239,7 +13239,7 @@
         <v>45187</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13312,7 +13312,7 @@
         <v>46202</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13390,7 +13390,7 @@
         <v>46202</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13468,7 +13468,7 @@
         <v>46202</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13546,7 +13546,7 @@
         <v>45435</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13619,7 +13619,7 @@
         <v>45882</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13692,7 +13692,7 @@
         <v>46202</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13765,7 +13765,7 @@
         <v>45316</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13838,7 +13838,7 @@
         <v>45190</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13911,7 +13911,7 @@
         <v>45203</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13984,7 +13984,7 @@
         <v>45226</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14057,7 +14057,7 @@
         <v>45051</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14130,7 +14130,7 @@
         <v>45187</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14208,7 +14208,7 @@
         <v>45680</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14281,7 +14281,7 @@
         <v>45208</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14354,7 +14354,7 @@
         <v>45103</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14427,7 +14427,7 @@
         <v>46213</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14500,7 +14500,7 @@
         <v>46258</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14573,7 +14573,7 @@
         <v>46258</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14646,7 +14646,7 @@
         <v>45521</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14719,7 +14719,7 @@
         <v>46162</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14792,7 +14792,7 @@
         <v>45250</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14865,7 +14865,7 @@
         <v>45166</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14938,7 +14938,7 @@
         <v>45105</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15011,7 +15011,7 @@
         <v>45680</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15089,7 +15089,7 @@
         <v>46218</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15162,7 +15162,7 @@
         <v>45970</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15235,7 +15235,7 @@
         <v>45203</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15308,7 +15308,7 @@
         <v>45460</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15381,7 +15381,7 @@
         <v>45978</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15454,7 +15454,7 @@
         <v>44959</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15527,7 +15527,7 @@
         <v>45502</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15600,7 +15600,7 @@
         <v>45728</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15673,7 +15673,7 @@
         <v>46280</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15746,7 +15746,7 @@
         <v>44814</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15819,7 +15819,7 @@
         <v>45541</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15892,7 +15892,7 @@
         <v>46286</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15970,7 +15970,7 @@
         <v>45079</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16043,7 +16043,7 @@
         <v>46286</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16121,7 +16121,7 @@
         <v>46286</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16199,7 +16199,7 @@
         <v>46274</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16272,7 +16272,7 @@
         <v>46136</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16345,7 +16345,7 @@
         <v>46286</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16423,7 +16423,7 @@
         <v>45572</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16496,7 +16496,7 @@
         <v>45540</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16569,7 +16569,7 @@
         <v>45436</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16647,7 +16647,7 @@
         <v>46076</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16720,7 +16720,7 @@
         <v>44928</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16793,7 +16793,7 @@
         <v>44837</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16866,7 +16866,7 @@
         <v>46289</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16939,7 +16939,7 @@
         <v>46285</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17012,7 +17012,7 @@
         <v>45460</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17085,7 +17085,7 @@
         <v>45699</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17163,7 +17163,7 @@
         <v>44944</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17241,7 +17241,7 @@
         <v>44775</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17314,7 +17314,7 @@
         <v>45237</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17387,7 +17387,7 @@
         <v>45104</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17460,7 +17460,7 @@
         <v>44946</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17533,7 +17533,7 @@
         <v>45386</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17606,7 +17606,7 @@
         <v>44858</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17684,7 +17684,7 @@
         <v>45688</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17757,7 +17757,7 @@
         <v>45128</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17830,7 +17830,7 @@
         <v>45551</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17908,7 +17908,7 @@
         <v>44833</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17981,7 +17981,7 @@
         <v>45187</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18059,7 +18059,7 @@
         <v>45103</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18132,7 +18132,7 @@
         <v>44693</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18205,7 +18205,7 @@
         <v>45203</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18278,7 +18278,7 @@
         <v>45261</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18351,7 +18351,7 @@
         <v>45224</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18424,7 +18424,7 @@
         <v>45673</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18497,7 +18497,7 @@
         <v>45230</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18570,7 +18570,7 @@
         <v>44796</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18643,7 +18643,7 @@
         <v>45722</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18716,7 +18716,7 @@
         <v>46042</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18789,7 +18789,7 @@
         <v>46051</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18862,7 +18862,7 @@
         <v>46202</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18940,7 +18940,7 @@
         <v>46202</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19018,7 +19018,7 @@
         <v>46202</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>

--- a/Översikt HÖRBY.xlsx
+++ b/Översikt HÖRBY.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE234"/>
+  <dimension ref="A1:AE233"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>44964</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
         <v>44967</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         <v>44727</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -949,7 +949,7 @@
         <v>45786</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1061,7 +1061,7 @@
         <v>46160</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
         <v>45238</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 31351-2022</t>
+          <t>A 39855-2022</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1289,10 +1289,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>44774</v>
+        <v>44819</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1305,22 +1305,22 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>13.2</v>
+        <v>4.2</v>
       </c>
       <c r="J8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1329,10 +1329,10 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1341,9 +1341,231 @@
         <v>5</v>
       </c>
       <c r="U8" t="n">
+        <v>1</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Skogsknipprot
+Blåsippa
+Fläcknycklar
+Grönvit nattviol</t>
+        </is>
+      </c>
+      <c r="W8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 39855-2022 artfynd.xlsx", "A 39855-2022")</f>
+        <v/>
+      </c>
+      <c r="X8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 39855-2022 karta.png", "A 39855-2022")</f>
+        <v/>
+      </c>
+      <c r="Y8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 39855-2022 georefererad karta.tif", "A 39855-2022")</f>
+        <v/>
+      </c>
+      <c r="AA8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 39855-2022 FSC-klagomål.docx", "A 39855-2022")</f>
+        <v/>
+      </c>
+      <c r="AB8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 39855-2022 FSC-klagomål mail.docx", "A 39855-2022")</f>
+        <v/>
+      </c>
+      <c r="AC8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 39855-2022 tillsynsbegäran.docx", "A 39855-2022")</f>
+        <v/>
+      </c>
+      <c r="AD8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 39855-2022 tillsynsbegäran mail.docx", "A 39855-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 16520-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>46112</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>HÖRBY</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>2</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
         <v>3</v>
       </c>
-      <c r="V8" s="2" t="inlineStr">
+      <c r="R9" t="n">
+        <v>1</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="n">
+        <v>6</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Slåttergubbe
+Sydlig sotticka
+Älg
+Fiskgjuse
+Större brunfladdermus</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 16520-2026 artfynd.xlsx", "A 16520-2026")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 16520-2026 karta.png", "A 16520-2026")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 16520-2026 georefererad karta.tif", "A 16520-2026")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 16520-2026 FSC-klagomål.docx", "A 16520-2026")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 16520-2026 FSC-klagomål mail.docx", "A 16520-2026")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 16520-2026 tillsynsbegäran.docx", "A 16520-2026")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 16520-2026 tillsynsbegäran mail.docx", "A 16520-2026")</f>
+        <v/>
+      </c>
+      <c r="AE9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/fåglar/A 16520-2026 prioriterade fågelarter.docx", "A 16520-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 31351-2022</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>44774</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>HÖRBY</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="J10" t="n">
+        <v>5</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>3</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>3</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="n">
+        <v>5</v>
+      </c>
+      <c r="U10" t="n">
+        <v>3</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Duvhök
 Grönsångare
@@ -1352,224 +1574,111 @@
 Kungsfågel</t>
         </is>
       </c>
-      <c r="W8">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 31351-2022 artfynd.xlsx", "A 31351-2022")</f>
         <v/>
       </c>
-      <c r="X8">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 31351-2022 karta.png", "A 31351-2022")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 31351-2022 georefererad karta.tif", "A 31351-2022")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 31351-2022 FSC-klagomål.docx", "A 31351-2022")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 31351-2022 FSC-klagomål mail.docx", "A 31351-2022")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 31351-2022 tillsynsbegäran.docx", "A 31351-2022")</f>
         <v/>
       </c>
-      <c r="AD8">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 31351-2022 tillsynsbegäran mail.docx", "A 31351-2022")</f>
         <v/>
       </c>
-      <c r="AE8">
+      <c r="AE10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/fåglar/A 31351-2022 prioriterade fågelarter.docx", "A 31351-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A 16520-2026</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>46112</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>HÖRBY</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="J9" t="n">
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 20194-2024</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>45434</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>HÖRBY</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
         <v>2</v>
       </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
         <v>2</v>
       </c>
-      <c r="M9" t="n">
+      <c r="O11" t="n">
         <v>1</v>
       </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
         <v>3</v>
       </c>
-      <c r="R9" t="n">
-        <v>1</v>
-      </c>
-      <c r="S9" t="n">
+      <c r="R11" t="n">
+        <v>3</v>
+      </c>
+      <c r="S11" t="n">
         <v>5</v>
       </c>
-      <c r="T9" t="n">
-        <v>6</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>Slåttergubbe
-Sydlig sotticka
-Älg
-Fiskgjuse
-Större brunfladdermus</t>
-        </is>
-      </c>
-      <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 16520-2026 artfynd.xlsx", "A 16520-2026")</f>
-        <v/>
-      </c>
-      <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 16520-2026 karta.png", "A 16520-2026")</f>
-        <v/>
-      </c>
-      <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 16520-2026 georefererad karta.tif", "A 16520-2026")</f>
-        <v/>
-      </c>
-      <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 16520-2026 FSC-klagomål.docx", "A 16520-2026")</f>
-        <v/>
-      </c>
-      <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 16520-2026 FSC-klagomål mail.docx", "A 16520-2026")</f>
-        <v/>
-      </c>
-      <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 16520-2026 tillsynsbegäran.docx", "A 16520-2026")</f>
-        <v/>
-      </c>
-      <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 16520-2026 tillsynsbegäran mail.docx", "A 16520-2026")</f>
-        <v/>
-      </c>
-      <c r="AE9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/fåglar/A 16520-2026 prioriterade fågelarter.docx", "A 16520-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 20194-2024</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>45434</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>HÖRBY</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>2</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>2</v>
-      </c>
-      <c r="O10" t="n">
-        <v>1</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>3</v>
-      </c>
-      <c r="R10" t="n">
-        <v>3</v>
-      </c>
-      <c r="S10" t="n">
+      <c r="T11" t="n">
         <v>5</v>
       </c>
-      <c r="T10" t="n">
-        <v>5</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Naverlönn
 Ask
@@ -1578,148 +1687,39 @@
 Stor häxört</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 20194-2024 artfynd.xlsx", "A 20194-2024")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 20194-2024 karta.png", "A 20194-2024")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 20194-2024 georefererad karta.tif", "A 20194-2024")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 20194-2024 FSC-klagomål.docx", "A 20194-2024")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 20194-2024 FSC-klagomål mail.docx", "A 20194-2024")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 20194-2024 tillsynsbegäran.docx", "A 20194-2024")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 20194-2024 tillsynsbegäran mail.docx", "A 20194-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 39855-2022</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>44819</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>HÖRBY</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J11" t="n">
-        <v>4</v>
-      </c>
-      <c r="K11" t="n">
-        <v>1</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>1</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1</v>
-      </c>
-      <c r="S11" t="n">
-        <v>5</v>
-      </c>
-      <c r="T11" t="n">
-        <v>5</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Skogsknipprot
-Blåsippa
-Fläcknycklar
-Grönvit nattviol</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 39855-2022 artfynd.xlsx", "A 39855-2022")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 39855-2022 karta.png", "A 39855-2022")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 39855-2022 georefererad karta.tif", "A 39855-2022")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 39855-2022 FSC-klagomål.docx", "A 39855-2022")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 39855-2022 FSC-klagomål mail.docx", "A 39855-2022")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 39855-2022 tillsynsbegäran.docx", "A 39855-2022")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 39855-2022 tillsynsbegäran mail.docx", "A 39855-2022")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 21774-2026</t>
+          <t>A 5619-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1733,10 +1733,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46150</v>
+        <v>45334</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1749,45 +1749,153 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>1.2</v>
+        <v>4.6</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>2</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
         <v>3</v>
       </c>
-      <c r="M12" t="n">
-        <v>1</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>4</v>
-      </c>
       <c r="R12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S12" t="n">
         <v>4</v>
       </c>
       <c r="T12" t="n">
+        <v>7</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Skogsalm
+Gullpudra
+Trubbfjädermossa</t>
+        </is>
+      </c>
+      <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 5619-2024 artfynd.xlsx", "A 5619-2024")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 5619-2024 karta.png", "A 5619-2024")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 5619-2024 georefererad karta.tif", "A 5619-2024")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 5619-2024 FSC-klagomål.docx", "A 5619-2024")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 5619-2024 FSC-klagomål mail.docx", "A 5619-2024")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 5619-2024 tillsynsbegäran.docx", "A 5619-2024")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 5619-2024 tillsynsbegäran mail.docx", "A 5619-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A 21774-2026</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>46150</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>HÖRBY</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>3</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>4</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1</v>
+      </c>
+      <c r="S13" t="n">
+        <v>4</v>
+      </c>
+      <c r="T13" t="n">
         <v>6</v>
       </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>Violettkantad guldvinge
 Granspira
@@ -1795,107 +1903,107 @@
 Svinrot</t>
         </is>
       </c>
-      <c r="W12">
+      <c r="W13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 21774-2026 artfynd.xlsx", "A 21774-2026")</f>
         <v/>
       </c>
-      <c r="X12">
+      <c r="X13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 21774-2026 karta.png", "A 21774-2026")</f>
         <v/>
       </c>
-      <c r="Y12">
+      <c r="Y13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 21774-2026 georefererad karta.tif", "A 21774-2026")</f>
         <v/>
       </c>
-      <c r="AA12">
+      <c r="AA13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 21774-2026 FSC-klagomål.docx", "A 21774-2026")</f>
         <v/>
       </c>
-      <c r="AB12">
+      <c r="AB13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 21774-2026 FSC-klagomål mail.docx", "A 21774-2026")</f>
         <v/>
       </c>
-      <c r="AC12">
+      <c r="AC13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 21774-2026 tillsynsbegäran.docx", "A 21774-2026")</f>
         <v/>
       </c>
-      <c r="AD12">
+      <c r="AD13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 21774-2026 tillsynsbegäran mail.docx", "A 21774-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
         <is>
           <t>A 38084-2024</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D13" s="1" t="n">
+      <c r="D14" s="1" t="n">
         <v>45545</v>
       </c>
-      <c r="E13" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>HÖRBY</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
+      <c r="E14" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>HÖRBY</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
         <v>0.5</v>
       </c>
-      <c r="J13" t="n">
+      <c r="J14" t="n">
         <v>1</v>
       </c>
-      <c r="K13" t="n">
+      <c r="K14" t="n">
         <v>2</v>
       </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
         <v>4</v>
       </c>
-      <c r="T13" t="n">
+      <c r="T14" t="n">
         <v>4</v>
       </c>
-      <c r="U13" t="n">
+      <c r="U14" t="n">
         <v>4</v>
       </c>
-      <c r="V13" s="2" t="inlineStr">
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>Myskmadra
 Skogsbräsma
@@ -1903,147 +2011,39 @@
 Grönsiska</t>
         </is>
       </c>
-      <c r="W13">
+      <c r="W14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 38084-2024 artfynd.xlsx", "A 38084-2024")</f>
         <v/>
       </c>
-      <c r="X13">
+      <c r="X14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 38084-2024 karta.png", "A 38084-2024")</f>
         <v/>
       </c>
-      <c r="Y13">
+      <c r="Y14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 38084-2024 georefererad karta.tif", "A 38084-2024")</f>
         <v/>
       </c>
-      <c r="AA13">
+      <c r="AA14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 38084-2024 FSC-klagomål.docx", "A 38084-2024")</f>
         <v/>
       </c>
-      <c r="AB13">
+      <c r="AB14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 38084-2024 FSC-klagomål mail.docx", "A 38084-2024")</f>
         <v/>
       </c>
-      <c r="AC13">
+      <c r="AC14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 38084-2024 tillsynsbegäran.docx", "A 38084-2024")</f>
         <v/>
       </c>
-      <c r="AD13">
+      <c r="AD14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 38084-2024 tillsynsbegäran mail.docx", "A 38084-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>A 5619-2024</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>45334</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>HÖRBY</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>1</v>
-      </c>
-      <c r="L14" t="n">
-        <v>1</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>2</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>3</v>
-      </c>
-      <c r="R14" t="n">
-        <v>2</v>
-      </c>
-      <c r="S14" t="n">
-        <v>4</v>
-      </c>
-      <c r="T14" t="n">
-        <v>7</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Skogsalm
-Gullpudra
-Trubbfjädermossa</t>
-        </is>
-      </c>
-      <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 5619-2024 artfynd.xlsx", "A 5619-2024")</f>
-        <v/>
-      </c>
-      <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 5619-2024 karta.png", "A 5619-2024")</f>
-        <v/>
-      </c>
-      <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 5619-2024 georefererad karta.tif", "A 5619-2024")</f>
-        <v/>
-      </c>
-      <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 5619-2024 FSC-klagomål.docx", "A 5619-2024")</f>
-        <v/>
-      </c>
-      <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 5619-2024 FSC-klagomål mail.docx", "A 5619-2024")</f>
-        <v/>
-      </c>
-      <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 5619-2024 tillsynsbegäran.docx", "A 5619-2024")</f>
-        <v/>
-      </c>
-      <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 5619-2024 tillsynsbegäran mail.docx", "A 5619-2024")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 20193-2024</t>
+          <t>A 2823-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2053,14 +2053,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45434</v>
+        <v>45677</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2073,13 +2073,13 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>11.2</v>
+        <v>21.1</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>1</v>
@@ -2106,365 +2106,365 @@
         <v>3</v>
       </c>
       <c r="T15" t="n">
+        <v>4</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>Borsttåg
+Grönvit nattviol
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 2823-2025 artfynd.xlsx", "A 2823-2025")</f>
+        <v/>
+      </c>
+      <c r="X15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 2823-2025 karta.png", "A 2823-2025")</f>
+        <v/>
+      </c>
+      <c r="Y15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 2823-2025 georefererad karta.tif", "A 2823-2025")</f>
+        <v/>
+      </c>
+      <c r="AA15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 2823-2025 FSC-klagomål.docx", "A 2823-2025")</f>
+        <v/>
+      </c>
+      <c r="AB15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 2823-2025 FSC-klagomål mail.docx", "A 2823-2025")</f>
+        <v/>
+      </c>
+      <c r="AC15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 2823-2025 tillsynsbegäran.docx", "A 2823-2025")</f>
+        <v/>
+      </c>
+      <c r="AD15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 2823-2025 tillsynsbegäran mail.docx", "A 2823-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 27738-2025</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>45815</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>HÖRBY</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1</v>
+      </c>
+      <c r="L16" t="n">
+        <v>2</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>2</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
         <v>3</v>
       </c>
-      <c r="U15" t="n">
+      <c r="T16" t="n">
+        <v>3</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Bokvårtlav
+Sydlig sotticka
+Västlig hakmossa</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 27738-2025 artfynd.xlsx", "A 27738-2025")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 27738-2025 karta.png", "A 27738-2025")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 27738-2025 georefererad karta.tif", "A 27738-2025")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 27738-2025 FSC-klagomål.docx", "A 27738-2025")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 27738-2025 FSC-klagomål mail.docx", "A 27738-2025")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 27738-2025 tillsynsbegäran.docx", "A 27738-2025")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 27738-2025 tillsynsbegäran mail.docx", "A 27738-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 24801-2025</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>45799</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>HÖRBY</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
         <v>1</v>
       </c>
-      <c r="V15" s="2" t="inlineStr">
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1</v>
+      </c>
+      <c r="N17" t="n">
+        <v>1</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2</v>
+      </c>
+      <c r="R17" t="n">
+        <v>2</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3</v>
+      </c>
+      <c r="T17" t="n">
+        <v>5</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Småvänderot
+Platt fjädermossa</t>
+        </is>
+      </c>
+      <c r="W17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 24801-2025 artfynd.xlsx", "A 24801-2025")</f>
+        <v/>
+      </c>
+      <c r="X17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 24801-2025 karta.png", "A 24801-2025")</f>
+        <v/>
+      </c>
+      <c r="Y17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 24801-2025 georefererad karta.tif", "A 24801-2025")</f>
+        <v/>
+      </c>
+      <c r="AA17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 24801-2025 FSC-klagomål.docx", "A 24801-2025")</f>
+        <v/>
+      </c>
+      <c r="AB17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 24801-2025 FSC-klagomål mail.docx", "A 24801-2025")</f>
+        <v/>
+      </c>
+      <c r="AC17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 24801-2025 tillsynsbegäran.docx", "A 24801-2025")</f>
+        <v/>
+      </c>
+      <c r="AD17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 24801-2025 tillsynsbegäran mail.docx", "A 24801-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>A 20193-2024</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>45434</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>HÖRBY</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>2</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
         <is>
           <t>Vårärt
 Strutbräken
 Vätteros</t>
         </is>
       </c>
-      <c r="W15">
+      <c r="W18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 20193-2024 artfynd.xlsx", "A 20193-2024")</f>
         <v/>
       </c>
-      <c r="X15">
+      <c r="X18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 20193-2024 karta.png", "A 20193-2024")</f>
         <v/>
       </c>
-      <c r="Y15">
+      <c r="Y18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 20193-2024 georefererad karta.tif", "A 20193-2024")</f>
         <v/>
       </c>
-      <c r="AA15">
+      <c r="AA18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 20193-2024 FSC-klagomål.docx", "A 20193-2024")</f>
         <v/>
       </c>
-      <c r="AB15">
+      <c r="AB18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 20193-2024 FSC-klagomål mail.docx", "A 20193-2024")</f>
         <v/>
       </c>
-      <c r="AC15">
+      <c r="AC18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 20193-2024 tillsynsbegäran.docx", "A 20193-2024")</f>
         <v/>
       </c>
-      <c r="AD15">
+      <c r="AD18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 20193-2024 tillsynsbegäran mail.docx", "A 20193-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>A 27738-2025</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>45815</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>HÖRBY</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>1</v>
-      </c>
-      <c r="L16" t="n">
-        <v>2</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>2</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>3</v>
-      </c>
-      <c r="T16" t="n">
-        <v>3</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>Bokvårtlav
-Sydlig sotticka
-Västlig hakmossa</t>
-        </is>
-      </c>
-      <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 27738-2025 artfynd.xlsx", "A 27738-2025")</f>
-        <v/>
-      </c>
-      <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 27738-2025 karta.png", "A 27738-2025")</f>
-        <v/>
-      </c>
-      <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 27738-2025 georefererad karta.tif", "A 27738-2025")</f>
-        <v/>
-      </c>
-      <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 27738-2025 FSC-klagomål.docx", "A 27738-2025")</f>
-        <v/>
-      </c>
-      <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 27738-2025 FSC-klagomål mail.docx", "A 27738-2025")</f>
-        <v/>
-      </c>
-      <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 27738-2025 tillsynsbegäran.docx", "A 27738-2025")</f>
-        <v/>
-      </c>
-      <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 27738-2025 tillsynsbegäran mail.docx", "A 27738-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 24801-2025</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>45799</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>HÖRBY</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>1</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>1</v>
-      </c>
-      <c r="N17" t="n">
-        <v>1</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>2</v>
-      </c>
-      <c r="R17" t="n">
-        <v>2</v>
-      </c>
-      <c r="S17" t="n">
-        <v>3</v>
-      </c>
-      <c r="T17" t="n">
-        <v>5</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Småvänderot
-Platt fjädermossa</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 24801-2025 artfynd.xlsx", "A 24801-2025")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 24801-2025 karta.png", "A 24801-2025")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 24801-2025 georefererad karta.tif", "A 24801-2025")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 24801-2025 FSC-klagomål.docx", "A 24801-2025")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 24801-2025 FSC-klagomål mail.docx", "A 24801-2025")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 24801-2025 tillsynsbegäran.docx", "A 24801-2025")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 24801-2025 tillsynsbegäran mail.docx", "A 24801-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>A 2823-2025</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>45677</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>HÖRBY</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>21.1</v>
-      </c>
-      <c r="J18" t="n">
-        <v>2</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>1</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>1</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>3</v>
-      </c>
-      <c r="T18" t="n">
-        <v>4</v>
-      </c>
-      <c r="U18" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>Borsttåg
-Grönvit nattviol
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 2823-2025 artfynd.xlsx", "A 2823-2025")</f>
-        <v/>
-      </c>
-      <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 2823-2025 karta.png", "A 2823-2025")</f>
-        <v/>
-      </c>
-      <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 2823-2025 georefererad karta.tif", "A 2823-2025")</f>
-        <v/>
-      </c>
-      <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 2823-2025 FSC-klagomål.docx", "A 2823-2025")</f>
-        <v/>
-      </c>
-      <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 2823-2025 FSC-klagomål mail.docx", "A 2823-2025")</f>
-        <v/>
-      </c>
-      <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 2823-2025 tillsynsbegäran.docx", "A 2823-2025")</f>
-        <v/>
-      </c>
-      <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 2823-2025 tillsynsbegäran mail.docx", "A 2823-2025")</f>
         <v/>
       </c>
     </row>
@@ -2488,7 +2488,7 @@
         <v>44725</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2595,7 +2595,7 @@
         <v>46030</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2689,7 +2689,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 44135-2024</t>
+          <t>A 42724-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45572</v>
+        <v>45176</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2719,22 +2719,22 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.6</v>
+        <v>2.8</v>
       </c>
       <c r="J21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
       </c>
       <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
         <v>1</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2746,155 +2746,155 @@
         <v>1</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S21" t="n">
         <v>2</v>
       </c>
       <c r="T21" t="n">
+        <v>4</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Grönvit nattviol</t>
+        </is>
+      </c>
+      <c r="W21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 42724-2023 artfynd.xlsx", "A 42724-2023")</f>
+        <v/>
+      </c>
+      <c r="X21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 42724-2023 karta.png", "A 42724-2023")</f>
+        <v/>
+      </c>
+      <c r="Y21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 42724-2023 georefererad karta.tif", "A 42724-2023")</f>
+        <v/>
+      </c>
+      <c r="AA21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 42724-2023 FSC-klagomål.docx", "A 42724-2023")</f>
+        <v/>
+      </c>
+      <c r="AB21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 42724-2023 FSC-klagomål mail.docx", "A 42724-2023")</f>
+        <v/>
+      </c>
+      <c r="AC21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 42724-2023 tillsynsbegäran.docx", "A 42724-2023")</f>
+        <v/>
+      </c>
+      <c r="AD21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 42724-2023 tillsynsbegäran mail.docx", "A 42724-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>A 44135-2024</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="n">
+        <v>45572</v>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>HÖRBY</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J22" t="n">
         <v>2</v>
       </c>
-      <c r="U21" t="n">
-        <v>0</v>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>Ladusvala
 Vanlig padda</t>
         </is>
       </c>
-      <c r="W21">
+      <c r="W22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 44135-2024 artfynd.xlsx", "A 44135-2024")</f>
         <v/>
       </c>
-      <c r="X21">
+      <c r="X22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 44135-2024 karta.png", "A 44135-2024")</f>
         <v/>
       </c>
-      <c r="Y21">
+      <c r="Y22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 44135-2024 georefererad karta.tif", "A 44135-2024")</f>
         <v/>
       </c>
-      <c r="AA21">
+      <c r="AA22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 44135-2024 FSC-klagomål.docx", "A 44135-2024")</f>
         <v/>
       </c>
-      <c r="AB21">
+      <c r="AB22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 44135-2024 FSC-klagomål mail.docx", "A 44135-2024")</f>
         <v/>
       </c>
-      <c r="AC21">
+      <c r="AC22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 44135-2024 tillsynsbegäran.docx", "A 44135-2024")</f>
         <v/>
       </c>
-      <c r="AD21">
+      <c r="AD22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 44135-2024 tillsynsbegäran mail.docx", "A 44135-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>A 42724-2023</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D22" s="1" t="n">
-        <v>45176</v>
-      </c>
-      <c r="E22" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>HÖRBY</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="J22" t="n">
-        <v>1</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>1</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>1</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1</v>
-      </c>
-      <c r="S22" t="n">
-        <v>2</v>
-      </c>
-      <c r="T22" t="n">
-        <v>4</v>
-      </c>
-      <c r="U22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Grönvit nattviol</t>
-        </is>
-      </c>
-      <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 42724-2023 artfynd.xlsx", "A 42724-2023")</f>
-        <v/>
-      </c>
-      <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 42724-2023 karta.png", "A 42724-2023")</f>
-        <v/>
-      </c>
-      <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 42724-2023 georefererad karta.tif", "A 42724-2023")</f>
-        <v/>
-      </c>
-      <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 42724-2023 FSC-klagomål.docx", "A 42724-2023")</f>
-        <v/>
-      </c>
-      <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 42724-2023 FSC-klagomål mail.docx", "A 42724-2023")</f>
-        <v/>
-      </c>
-      <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 42724-2023 tillsynsbegäran.docx", "A 42724-2023")</f>
-        <v/>
-      </c>
-      <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 42724-2023 tillsynsbegäran mail.docx", "A 42724-2023")</f>
         <v/>
       </c>
     </row>
@@ -2918,7 +2918,7 @@
         <v>45317</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3007,7 +3007,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 47612-2023</t>
+          <t>A 31115-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45203</v>
+        <v>45502</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3037,7 +3037,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2.4</v>
+        <v>0.8</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -3046,13 +3046,13 @@
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3064,7 +3064,7 @@
         <v>1</v>
       </c>
       <c r="R24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3077,35 +3077,35 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 47612-2023 artfynd.xlsx", "A 47612-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 31115-2024 artfynd.xlsx", "A 31115-2024")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 47612-2023 karta.png", "A 47612-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 31115-2024 karta.png", "A 31115-2024")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 47612-2023 georefererad karta.tif", "A 47612-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 31115-2024 georefererad karta.tif", "A 31115-2024")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 47612-2023 FSC-klagomål.docx", "A 47612-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 31115-2024 FSC-klagomål.docx", "A 31115-2024")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 47612-2023 FSC-klagomål mail.docx", "A 47612-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 31115-2024 FSC-klagomål mail.docx", "A 31115-2024")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 47612-2023 tillsynsbegäran.docx", "A 47612-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 31115-2024 tillsynsbegäran.docx", "A 31115-2024")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 47612-2023 tillsynsbegäran mail.docx", "A 47612-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 31115-2024 tillsynsbegäran mail.docx", "A 31115-2024")</f>
         <v/>
       </c>
     </row>
@@ -3129,7 +3129,7 @@
         <v>45802</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3217,7 +3217,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 113-2023</t>
+          <t>A 36362-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3231,10 +3231,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44928</v>
+        <v>45868</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3247,19 +3247,19 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>5.1</v>
+        <v>3.7</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
         <v>0</v>
@@ -3271,10 +3271,10 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>
@@ -3283,46 +3283,46 @@
         <v>1</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Slåttergubbe</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 113-2023 artfynd.xlsx", "A 113-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 36362-2025 artfynd.xlsx", "A 36362-2025")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 113-2023 karta.png", "A 113-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 36362-2025 karta.png", "A 36362-2025")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 113-2023 georefererad karta.tif", "A 113-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 36362-2025 georefererad karta.tif", "A 36362-2025")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 113-2023 FSC-klagomål.docx", "A 113-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 36362-2025 FSC-klagomål.docx", "A 36362-2025")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 113-2023 FSC-klagomål mail.docx", "A 113-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 36362-2025 FSC-klagomål mail.docx", "A 36362-2025")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 113-2023 tillsynsbegäran.docx", "A 113-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 36362-2025 tillsynsbegäran.docx", "A 36362-2025")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 113-2023 tillsynsbegäran mail.docx", "A 113-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 36362-2025 tillsynsbegäran mail.docx", "A 36362-2025")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 25833-2024</t>
+          <t>A 47612-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3336,10 +3336,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45463</v>
+        <v>45203</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3352,7 +3352,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.4</v>
+        <v>2.4</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3364,10 +3364,10 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
         <v>1</v>
-      </c>
-      <c r="N27" t="n">
-        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3385,49 +3385,49 @@
         <v>1</v>
       </c>
       <c r="T27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U27" t="n">
         <v>0</v>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Slåttergubbe</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 25833-2024 artfynd.xlsx", "A 25833-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 47612-2023 artfynd.xlsx", "A 47612-2023")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 25833-2024 karta.png", "A 25833-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 47612-2023 karta.png", "A 47612-2023")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 25833-2024 georefererad karta.tif", "A 25833-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 47612-2023 georefererad karta.tif", "A 47612-2023")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 25833-2024 FSC-klagomål.docx", "A 25833-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 47612-2023 FSC-klagomål.docx", "A 47612-2023")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 25833-2024 FSC-klagomål mail.docx", "A 25833-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 47612-2023 FSC-klagomål mail.docx", "A 47612-2023")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 25833-2024 tillsynsbegäran.docx", "A 25833-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 47612-2023 tillsynsbegäran.docx", "A 47612-2023")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 25833-2024 tillsynsbegäran mail.docx", "A 25833-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 47612-2023 tillsynsbegäran mail.docx", "A 47612-2023")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 24823-2026</t>
+          <t>A 40376-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3441,10 +3441,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46174</v>
+        <v>45169</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3456,22 +3456,17 @@
           <t>HÖRBY</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I28" t="n">
-        <v>5.1</v>
+        <v>2.7</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M28" t="n">
         <v>0</v>
@@ -3486,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
@@ -3498,46 +3493,50 @@
         <v>1</v>
       </c>
       <c r="U28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Tandrot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 24823-2026 artfynd.xlsx", "A 24823-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 40376-2023 artfynd.xlsx", "A 40376-2023")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 24823-2026 karta.png", "A 24823-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 40376-2023 karta.png", "A 40376-2023")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 24823-2026 georefererad karta.tif", "A 24823-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 40376-2023 georefererad karta.tif", "A 40376-2023")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 24823-2026 FSC-klagomål.docx", "A 24823-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 40376-2023 FSC-klagomål.docx", "A 40376-2023")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 24823-2026 FSC-klagomål mail.docx", "A 24823-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 40376-2023 FSC-klagomål mail.docx", "A 40376-2023")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 24823-2026 tillsynsbegäran.docx", "A 24823-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 40376-2023 tillsynsbegäran.docx", "A 40376-2023")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 24823-2026 tillsynsbegäran mail.docx", "A 24823-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 40376-2023 tillsynsbegäran mail.docx", "A 40376-2023")</f>
+        <v/>
+      </c>
+      <c r="AE28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/fåglar/A 40376-2023 prioriterade fågelarter.docx", "A 40376-2023")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 36362-2025</t>
+          <t>A 113-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3551,10 +3550,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45868</v>
+        <v>44928</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3567,20 +3566,20 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>3.7</v>
+        <v>5.1</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
       </c>
       <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
         <v>1</v>
       </c>
-      <c r="L29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" t="n">
-        <v>0</v>
-      </c>
       <c r="N29" t="n">
         <v>0</v>
       </c>
@@ -3591,10 +3590,10 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
@@ -3603,46 +3602,46 @@
         <v>1</v>
       </c>
       <c r="U29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Slåttergubbe</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 36362-2025 artfynd.xlsx", "A 36362-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 113-2023 artfynd.xlsx", "A 113-2023")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 36362-2025 karta.png", "A 36362-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 113-2023 karta.png", "A 113-2023")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 36362-2025 georefererad karta.tif", "A 36362-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 113-2023 georefererad karta.tif", "A 113-2023")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 36362-2025 FSC-klagomål.docx", "A 36362-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 113-2023 FSC-klagomål.docx", "A 113-2023")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 36362-2025 FSC-klagomål mail.docx", "A 36362-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 113-2023 FSC-klagomål mail.docx", "A 113-2023")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 36362-2025 tillsynsbegäran.docx", "A 36362-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 113-2023 tillsynsbegäran.docx", "A 113-2023")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 36362-2025 tillsynsbegäran mail.docx", "A 36362-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 113-2023 tillsynsbegäran mail.docx", "A 113-2023")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 16519-2026</t>
+          <t>A 24823-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3656,10 +3655,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46112</v>
+        <v>46174</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3671,8 +3670,13 @@
           <t>HÖRBY</t>
         </is>
       </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I30" t="n">
-        <v>0.8</v>
+        <v>5.1</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3687,7 +3691,7 @@
         <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -3696,10 +3700,10 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
         <v>1</v>
@@ -3708,46 +3712,46 @@
         <v>1</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Tandrot</t>
         </is>
       </c>
       <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 16519-2026 artfynd.xlsx", "A 16519-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 24823-2026 artfynd.xlsx", "A 24823-2026")</f>
         <v/>
       </c>
       <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 16519-2026 karta.png", "A 16519-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 24823-2026 karta.png", "A 24823-2026")</f>
         <v/>
       </c>
       <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 16519-2026 georefererad karta.tif", "A 16519-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 24823-2026 georefererad karta.tif", "A 24823-2026")</f>
         <v/>
       </c>
       <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 16519-2026 FSC-klagomål.docx", "A 16519-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 24823-2026 FSC-klagomål.docx", "A 24823-2026")</f>
         <v/>
       </c>
       <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 16519-2026 FSC-klagomål mail.docx", "A 16519-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 24823-2026 FSC-klagomål mail.docx", "A 24823-2026")</f>
         <v/>
       </c>
       <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 16519-2026 tillsynsbegäran.docx", "A 16519-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 24823-2026 tillsynsbegäran.docx", "A 24823-2026")</f>
         <v/>
       </c>
       <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 16519-2026 tillsynsbegäran mail.docx", "A 16519-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 24823-2026 tillsynsbegäran mail.docx", "A 24823-2026")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 40376-2023</t>
+          <t>A 25833-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3761,10 +3765,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45169</v>
+        <v>45463</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3777,19 +3781,19 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2.7</v>
+        <v>1.4</v>
       </c>
       <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
         <v>1</v>
-      </c>
-      <c r="K31" t="n">
-        <v>0</v>
-      </c>
-      <c r="L31" t="n">
-        <v>1</v>
-      </c>
-      <c r="M31" t="n">
-        <v>0</v>
       </c>
       <c r="N31" t="n">
         <v>0</v>
@@ -3804,59 +3808,55 @@
         <v>1</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S31" t="n">
         <v>1</v>
       </c>
       <c r="T31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U31" t="n">
         <v>0</v>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Slåttergubbe</t>
         </is>
       </c>
       <c r="W31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 40376-2023 artfynd.xlsx", "A 40376-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 25833-2024 artfynd.xlsx", "A 25833-2024")</f>
         <v/>
       </c>
       <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 40376-2023 karta.png", "A 40376-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 25833-2024 karta.png", "A 25833-2024")</f>
         <v/>
       </c>
       <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 40376-2023 georefererad karta.tif", "A 40376-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 25833-2024 georefererad karta.tif", "A 25833-2024")</f>
         <v/>
       </c>
       <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 40376-2023 FSC-klagomål.docx", "A 40376-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomål/A 25833-2024 FSC-klagomål.docx", "A 25833-2024")</f>
         <v/>
       </c>
       <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 40376-2023 FSC-klagomål mail.docx", "A 40376-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/klagomålsmail/A 25833-2024 FSC-klagomål mail.docx", "A 25833-2024")</f>
         <v/>
       </c>
       <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 40376-2023 tillsynsbegäran.docx", "A 40376-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsyn/A 25833-2024 tillsynsbegäran.docx", "A 25833-2024")</f>
         <v/>
       </c>
       <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 40376-2023 tillsynsbegäran mail.docx", "A 40376-2023")</f>
-        <v/>
-      </c>
-      <c r="AE31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/fåglar/A 40376-2023 prioriterade fågelarter.docx", "A 40376-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/tillsynsmail/A 25833-2024 tillsynsbegäran mail.docx", "A 25833-2024")</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 31115-2024</t>
+          <t>A 16519-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3870,10 +3870,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45502</v>
+        <v>46112</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3895,13 +3895,13 @@
         <v>0</v>
       </c>
       <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="n">
         <v>1</v>
-      </c>
-      <c r="M32" t="n">
-        <v>0</v>
-      </c>
-      <c r="N32" t="n">
-        <v>0</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -3913,7 +3913,7 @@
         <v>1</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S32" t="n">
         <v>1</v>
@@ -3926,35 +3926,35 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>Gullpudra</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="W32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 31115-2024 artfynd.xlsx", "A 31115-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/artfynd/A 16519-2026 artfynd.xlsx", "A 16519-2026")</f>
         <v/>
       </c>
       <c r="X32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 31115-2024 karta.png", "A 31115-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor/A 16519-2026 karta.png", "A 16519-2026")</f>
         <v/>
       </c>
       <c r="Y32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1266/kartor_geotiff/A 31115-2024 georefere